--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 22 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 23 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1831,7 +1831,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2713,16 +2712,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="207" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="207"/>
+      <c r="B1" s="206" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="206"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="208"/>
+      <c r="C3" s="207"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2773,10 +2772,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="209" t="s">
+      <c r="B11" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="209"/>
+      <c r="C11" s="208"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -3429,11 +3428,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>163</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3557,10 +3556,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3589,40 +3588,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3630,13 +3629,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3655,7 +3654,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3665,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4458,10 +4457,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4469,8 +4468,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -4664,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -5486,11 +5485,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>165</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5614,10 +5613,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5646,40 +5645,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5687,13 +5686,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5712,7 +5711,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5722,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6515,10 +6514,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6526,8 +6525,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -6721,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -7543,11 +7542,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>167</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7671,10 +7670,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7703,40 +7702,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7744,13 +7743,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7769,7 +7768,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7779,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8572,10 +8571,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8583,8 +8582,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -8778,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -9600,11 +9599,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9728,10 +9727,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9760,40 +9759,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9801,13 +9800,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9826,7 +9825,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9836,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10629,10 +10628,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10640,8 +10639,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -10835,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11657,11 +11656,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11784,10 +11783,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11816,40 +11815,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11857,13 +11856,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11882,7 +11881,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11892,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12671,10 +12670,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12682,8 +12681,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -12877,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13173,10 +13172,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="207" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="208"/>
+      <c r="C3" s="207"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14649,13 +14648,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="210" t="s">
+      <c r="B29" s="209" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="210"/>
-      <c r="D29" s="210"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="210"/>
+      <c r="C29" s="209"/>
+      <c r="D29" s="209"/>
+      <c r="E29" s="209"/>
+      <c r="F29" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15187,10 +15186,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="212" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="213"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15230,23 +15229,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="214" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="214" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="215" t="s">
+      <c r="D47" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="216"/>
-      <c r="F47" s="217"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="216"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="214" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15254,13 +15253,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="211" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="214"/>
-      <c r="C48" s="214"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15279,7 +15278,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="214"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15289,7 +15288,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="211"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16722,10 +16721,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="212" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="213"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16765,23 +16764,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="214" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="214" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="215" t="s">
+      <c r="D47" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="216"/>
-      <c r="F47" s="217"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="216"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="214" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16789,13 +16788,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="211" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="214"/>
-      <c r="C48" s="214"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16814,7 +16813,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="214"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16824,7 +16823,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="211"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -18409,10 +18408,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="222" t="s">
+      <c r="B44" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="223"/>
+      <c r="C44" s="222"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18477,23 +18476,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="224" t="s">
+      <c r="B47" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="224" t="s">
+      <c r="C47" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="219" t="s">
+      <c r="D47" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="220"/>
-      <c r="F47" s="221"/>
+      <c r="E47" s="219"/>
+      <c r="F47" s="220"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="224" t="s">
+      <c r="J47" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18501,13 +18500,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="218" t="s">
+      <c r="N47" s="217" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="224"/>
-      <c r="C48" s="224"/>
+      <c r="B48" s="223"/>
+      <c r="C48" s="223"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18526,7 +18525,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="224"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18536,7 +18535,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="218"/>
+      <c r="N48" s="217"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -20158,11 +20157,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20280,10 +20279,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20306,40 +20305,40 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="236"/>
-      <c r="L48" s="237"/>
-      <c r="M48" s="237"/>
-      <c r="N48" s="238"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="235"/>
+      <c r="L48" s="236"/>
+      <c r="M48" s="236"/>
+      <c r="N48" s="237"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="235" t="s">
+      <c r="B49" s="234" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="235" t="s">
+      <c r="C49" s="234" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="232" t="s">
+      <c r="D49" s="231" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="233"/>
-      <c r="F49" s="234"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="233"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="235" t="s">
+      <c r="J49" s="234" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20347,13 +20346,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="228" t="s">
+      <c r="N49" s="227" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="235"/>
-      <c r="C50" s="235"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="234"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20372,7 +20371,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="235"/>
+      <c r="J50" s="234"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20382,7 +20381,7 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="228"/>
+      <c r="N50" s="227"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="183" t="s">
@@ -21173,10 +21172,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21187,8 +21186,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -21374,13 +21373,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="229" t="s">
+      <c r="B87" s="228" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="230"/>
-      <c r="D87" s="230"/>
-      <c r="E87" s="230"/>
-      <c r="F87" s="231"/>
+      <c r="C87" s="229"/>
+      <c r="D87" s="229"/>
+      <c r="E87" s="229"/>
+      <c r="F87" s="230"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21662,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21744,11 +21743,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>202235652.46766701</v>
+        <v>210592780.769941</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>34856515.683463</v>
+        <v>35498876.043462999</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21766,11 +21765,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>384274554.09952402</v>
+        <v>393634110.92949599</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>63360880.475106001</v>
+        <v>67706440.835084006</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21778,27 +21777,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>197087957.03479201</v>
+        <v>222771518.32418001</v>
       </c>
       <c r="D10" s="205">
-        <v>23481356.599342</v>
+        <v>26001356.599342</v>
       </c>
       <c r="E10" s="205">
-        <v>122166897.53999899</v>
+        <v>127412843.419999</v>
       </c>
       <c r="F10" s="205">
-        <v>342736211.174133</v>
+        <v>376185718.343521</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>457257253.31532502</v>
+        <v>499203572.48032397</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>19803582.641127001</v>
+        <v>22605776.241119001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21806,16 +21805,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>260345948.959604</v>
+        <v>272099721.26956201</v>
       </c>
       <c r="D11" s="205">
-        <v>69632766.564611003</v>
+        <v>74129190.024606004</v>
       </c>
       <c r="E11" s="205">
         <v>38843243.600000001</v>
       </c>
       <c r="F11" s="205">
-        <v>368821959.12421501</v>
+        <v>385072154.89416802</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -21834,27 +21833,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>212151571.32393</v>
+        <v>216227344.32392699</v>
       </c>
       <c r="D12" s="205">
-        <v>35646817.945271999</v>
+        <v>39495081.025250003</v>
       </c>
       <c r="E12" s="205">
         <v>37216125.280000001</v>
       </c>
       <c r="F12" s="205">
-        <v>285014514.54920202</v>
+        <v>292938550.62917697</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>312017996.62181097</v>
+        <v>331329120.05181003</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>54764702.979327999</v>
+        <v>54962901.179328002</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21862,27 +21861,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>172122982.775594</v>
+        <v>177406766.60556901</v>
       </c>
       <c r="D13" s="205">
-        <v>27714062.529833999</v>
+        <v>28211359.809834</v>
       </c>
       <c r="E13" s="205">
-        <v>28474774.460000001</v>
+        <v>30636936.579999998</v>
       </c>
       <c r="F13" s="205">
-        <v>228311819.76542801</v>
+        <v>236255062.99540299</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>655120799.07094097</v>
+        <v>662262465.71592605</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>54200073.849916004</v>
+        <v>58078936.769892</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21890,27 +21889,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>457257253.31532502</v>
+        <v>499203572.48032397</v>
       </c>
       <c r="D14" s="205">
-        <v>19803582.641127001</v>
+        <v>22605776.241119001</v>
       </c>
       <c r="E14" s="205">
-        <v>141476575.41999999</v>
+        <v>143479278.12</v>
       </c>
       <c r="F14" s="205">
-        <v>618537411.37645197</v>
+        <v>665288626.84144294</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>289308902.14195198</v>
+        <v>316848251.04794902</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>46519240.629844002</v>
+        <v>49956938.829843998</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21926,11 +21925,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>260345948.959604</v>
+        <v>272099721.26956201</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>69632766.564611003</v>
+        <v>74129190.024606004</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21938,27 +21937,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>312017996.62181097</v>
+        <v>331329120.05181003</v>
       </c>
       <c r="D16" s="205">
-        <v>54764702.979327999</v>
+        <v>54962901.179328002</v>
       </c>
       <c r="E16" s="205">
         <v>10797297.199999999</v>
       </c>
       <c r="F16" s="205">
-        <v>377579996.801139</v>
+        <v>397089318.43113798</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>310046126.64529699</v>
+        <v>341675971.12479597</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>38581635.119948</v>
+        <v>39328537.829948001</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21982,11 +21981,11 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>197087957.03479201</v>
+        <v>222771518.32418001</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>23481356.599342</v>
+        <v>26001356.599342</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21994,7 +21993,7 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>846794107.54483998</v>
+        <v>867577535.90481806</v>
       </c>
       <c r="D18" s="205">
         <v>7746528.7219770001</v>
@@ -22003,18 +22002,18 @@
         <v>8274324.2400000002</v>
       </c>
       <c r="F18" s="205">
-        <v>862814960.50681698</v>
+        <v>883598388.86679494</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>519284585.898112</v>
+        <v>556862062.78800702</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>153492051.177313</v>
+        <v>164355132.21170899</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22022,27 +22021,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>655120799.07094097</v>
+        <v>662262465.71592605</v>
       </c>
       <c r="D19" s="205">
-        <v>54200073.849916004</v>
+        <v>58078936.769892</v>
       </c>
       <c r="E19" s="205">
-        <v>520024093.269943</v>
+        <v>560156524.46994305</v>
       </c>
       <c r="F19" s="205">
-        <v>1229344966.1908</v>
+        <v>1280497926.955761</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>165488307.35126799</v>
+        <v>181773274.10117799</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>99973594.522735998</v>
+        <v>103294334.440724</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22050,16 +22049,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>127331283.35126799</v>
+        <v>142498950.10117799</v>
       </c>
       <c r="D20" s="205">
-        <v>25598439.609776001</v>
+        <v>28052299.959775999</v>
       </c>
       <c r="E20" s="205">
         <v>2972973.04</v>
       </c>
       <c r="F20" s="205">
-        <v>155902696.00104401</v>
+        <v>173524223.100954</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22077,23 +22076,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>38157024</v>
+        <v>39274324</v>
       </c>
       <c r="D21" s="205">
-        <v>74375154.912959993</v>
+        <v>75242034.480948001</v>
       </c>
       <c r="E21" s="205">
-        <v>36767568.280000001</v>
+        <v>41848649.479999997</v>
       </c>
       <c r="F21" s="205">
-        <v>149299747.19295999</v>
+        <v>156365007.96094799</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>492267520.80561304</v>
+        <v>496893466.725613</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22124,7 +22123,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="205">
-        <v>157901166.34997499</v>
+        <v>188067175.44997501</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>169</v>
@@ -22133,7 +22132,7 @@
         <v>10180179.9</v>
       </c>
       <c r="F23" s="205">
-        <v>168081346.249975</v>
+        <v>198247355.34997499</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22144,16 +22143,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>202235652.46766701</v>
+        <v>210592780.769941</v>
       </c>
       <c r="D24" s="205">
-        <v>34856515.683463</v>
+        <v>35498876.043462999</v>
       </c>
       <c r="E24" s="205">
-        <v>93090953.700000003</v>
+        <v>93180953.700000003</v>
       </c>
       <c r="F24" s="205">
-        <v>330183121.85113001</v>
+        <v>339272610.51340401</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22164,16 +22163,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>289308902.14195198</v>
+        <v>316848251.04794902</v>
       </c>
       <c r="D25" s="205">
-        <v>46519240.629844002</v>
+        <v>49956938.829843998</v>
       </c>
       <c r="E25" s="205">
-        <v>132794773.61998001</v>
+        <v>154821801.23991001</v>
       </c>
       <c r="F25" s="205">
-        <v>468622916.39177603</v>
+        <v>521626991.11770302</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22184,16 +22183,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>310046126.64529699</v>
+        <v>341675971.12479597</v>
       </c>
       <c r="D26" s="205">
-        <v>38581635.119948</v>
+        <v>39328537.829948001</v>
       </c>
       <c r="E26" s="205">
-        <v>275553150.85995102</v>
+        <v>296580177.76995099</v>
       </c>
       <c r="F26" s="205">
-        <v>624180912.62519598</v>
+        <v>677584686.72469497</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22204,16 +22203,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>519284585.898112</v>
+        <v>556862062.78800702</v>
       </c>
       <c r="D27" s="205">
-        <v>153492051.177313</v>
+        <v>164355132.21170899</v>
       </c>
       <c r="E27" s="205">
-        <v>14408108.25</v>
+        <v>18025946.155999999</v>
       </c>
       <c r="F27" s="205">
-        <v>687184745.32542503</v>
+        <v>739243141.15571594</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22260,7 +22259,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>211238820.024753</v>
+        <v>213399540.74474099</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22270,8 +22269,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="206">
-        <v>287304226.360744</v>
+      <c r="C33" s="205">
+        <v>313888308.08042198</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22282,7 +22281,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>224357987.988646</v>
+        <v>228983933.90864599</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22335,17 +22334,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="239" t="s">
+      <c r="B41" s="238" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="240"/>
-      <c r="D41" s="241"/>
+      <c r="C41" s="239"/>
+      <c r="D41" s="240"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.70967741935483875</v>
+        <v>0.74193548387096775</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22388,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>4286148397.9562654</v>
+        <v>4552899172.0531425</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.62669591193651009</v>
+        <v>0.66569867248304726</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>2553130934.0437346</v>
+        <v>2286380159.9468575</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>319141366.75546682</v>
+        <v>326625737.13526535</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22417,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>692216951.4227339</v>
+        <v>729468972.18505895</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.46921538428773435</v>
+        <v>0.49446645795988792</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>783047872.79762781</v>
+        <v>745795852.03530276</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>97880984.099703476</v>
+        <v>106542264.57647182</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22446,46 +22445,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>990810567.19111001</v>
+        <v>1024181315.550776</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.5557052107157775</v>
+        <v>0.57442150156189087</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>792168156.21314585</v>
+        <v>758797407.85347986</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>99021019.526643232</v>
+        <v>108399629.69335426</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>5969175916.5701094</v>
+        <v>6306549459.7889767</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.59115250222557725</v>
+        <v>0.62456401782606574</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>4128346963.0545082</v>
+        <v>3790973419.83564</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>516043370.38181353</v>
+        <v>541567631.4050914</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22495,40 +22494,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22536,13 +22535,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22561,7 +22560,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22571,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22594,35 +22593,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>202235652.46766701</v>
+        <v>210592780.769941</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>34856515.683463</v>
+        <v>35498876.043462999</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>237092168.15113002</v>
+        <v>246091656.81340399</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.4888963225372055</v>
+        <v>0.50745373396927118</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>214447825.53233299</v>
+        <v>206090697.230059</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>33413885.537191309</v>
+        <v>32771525.17719131</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>247861711.06952429</v>
+        <v>238862222.40725031</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>30982713.883690536</v>
+        <v>34123174.629607186</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22646,35 +22645,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>384274554.09952402</v>
+        <v>393634110.92949599</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>63360880.475106001</v>
+        <v>67706440.835084006</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>447635434.57463002</v>
+        <v>461340551.76458001</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.59946157395532529</v>
+        <v>0.61781510561828812</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>170907816.90047598</v>
+        <v>161548260.07050401</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>128185903.524894</v>
+        <v>123840343.16491599</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>299093720.42536998</v>
+        <v>285388603.23541999</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>37386715.053171247</v>
+        <v>40769800.462202854</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22726,7 +22725,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>15126097.775</v>
+        <v>17286968.885714285</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22750,35 +22749,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>457257253.31532502</v>
+        <v>499203572.48032397</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>19803582.641127001</v>
+        <v>22605776.241119001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>477060835.95645201</v>
+        <v>521809348.721443</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.72546376514278288</v>
+        <v>0.79351258011193626</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>153455218.68467498</v>
+        <v>111508899.51967603</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>27078244.176207889</v>
+        <v>24276050.576215889</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>180533462.86088288</v>
+        <v>135784950.09589189</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>22566682.85761036</v>
+        <v>19397850.013698842</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22830,7 +22829,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>24883423.226440772</v>
+        <v>28438197.97307517</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22854,35 +22853,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>312017996.62181097</v>
+        <v>331329120.05181003</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>54764702.979327999</v>
+        <v>54962901.179328002</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>366782699.60113895</v>
+        <v>386292021.23113805</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.6606813739622116</v>
+        <v>0.69582328614507971</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>161900835.37818903</v>
+        <v>142589711.94818997</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>26474691.143325604</v>
+        <v>26276492.943325602</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>188375526.52151465</v>
+        <v>168866204.89151555</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>23546940.815189332</v>
+        <v>24123743.555930793</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22906,35 +22905,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>655120799.07094097</v>
+        <v>662262465.71592605</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>54200073.849916004</v>
+        <v>58078936.769892</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>709320872.92085695</v>
+        <v>720341402.48581803</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.67317991573755487</v>
+        <v>0.68363893287231714</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>306637545.92905903</v>
+        <v>299495879.28407395</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>37728502.489240386</v>
+        <v>33849639.56926439</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>344366048.41829944</v>
+        <v>333345518.85333836</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>43045756.05228743</v>
+        <v>47620788.407619767</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22958,35 +22957,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>289308902.14195198</v>
+        <v>316848251.04794902</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>46519240.629844002</v>
+        <v>49956938.829843998</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>335828142.77179599</v>
+        <v>366805189.87779301</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.59013662609483952</v>
+        <v>0.64457128399644426</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>215978156.85804802</v>
+        <v>188438807.95205098</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>17262163.370155998</v>
+        <v>13824465.170156002</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>233240320.22820401</v>
+        <v>202263273.12220699</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>29155040.028525501</v>
+        <v>28894753.303172428</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23010,7 +23009,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>157901166.34997499</v>
+        <v>188067175.44997501</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23018,15 +23017,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>157901166.34997499</v>
+        <v>188067175.44997501</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.39071520245830099</v>
+        <v>0.46535884585446219</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>246232497.65002501</v>
+        <v>216066488.55002499</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23034,11 +23033,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>246232497.65002501</v>
+        <v>216066488.55002499</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>30779062.206253126</v>
+        <v>30866641.221432142</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23062,35 +23061,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>260345948.959604</v>
+        <v>272099721.26956201</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>69632766.564611003</v>
+        <v>74129190.024606004</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>329978715.52421498</v>
+        <v>346228911.294168</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.60827621650627073</v>
+        <v>0.6382315049397389</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>143671360.040396</v>
+        <v>131917587.73043799</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>68831623.653384402</v>
+        <v>64335200.193389401</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>212502983.69378042</v>
+        <v>196252787.92382741</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>26562872.961722553</v>
+        <v>28036112.560546774</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23114,35 +23113,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>310046126.64529699</v>
+        <v>341675971.12479597</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>38581635.119948</v>
+        <v>39328537.829948001</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>348627761.76524496</v>
+        <v>381004508.95474398</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.50498596041786159</v>
+        <v>0.55188355311647441</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>321583469.35470301</v>
+        <v>289953624.87520403</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>20159965.490677267</v>
+        <v>19413062.780677266</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>341743434.84538031</v>
+        <v>309366687.65588129</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>42717929.355672538</v>
+        <v>44195241.093697324</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23166,35 +23165,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>197087957.03479201</v>
+        <v>222771518.32418001</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>23481356.599342</v>
+        <v>26001356.599342</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>220569313.63413399</v>
+        <v>248772874.923522</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.48981967090071377</v>
+        <v>0.55245149797304616</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>189455065.96520799</v>
+        <v>163771504.67581999</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>40282798.200471804</v>
+        <v>37762798.200471804</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>229737864.16567981</v>
+        <v>201534302.87629181</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>28717233.020709977</v>
+        <v>28790614.696613114</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23218,35 +23217,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>519284585.898112</v>
+        <v>556862062.78800702</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>153492051.177313</v>
+        <v>164355132.21170899</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>672776637.07542503</v>
+        <v>721217194.99971604</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.73675828316071978</v>
+        <v>0.78980558047292859</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>64066356.101888001</v>
+        <v>26488879.211992979</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>176314893.81540439</v>
+        <v>165451812.78100839</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>240381249.91729236</v>
+        <v>191940691.99300134</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>30047656.239661545</v>
+        <v>27420098.85614305</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23270,35 +23269,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>165488307.35126799</v>
+        <v>181773274.10117799</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>99973594.522735998</v>
+        <v>103294334.440724</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>265461901.87400401</v>
+        <v>285067608.54190201</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.51297410036218616</v>
+        <v>0.55085983714374265</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>94037381.648732007</v>
+        <v>77752414.89882201</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>157996437.38515037</v>
+        <v>154675697.46716237</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>252033819.03388238</v>
+        <v>232428112.36598438</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>31504227.379235297</v>
+        <v>33204016.052283484</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23320,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>4286148397.9562654</v>
+        <v>4552899172.0531425</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>692216951.4227339</v>
+        <v>729468972.18505895</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>4978365349.3790007</v>
+        <v>5282368144.2382002</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.59875385298838479</v>
+        <v>0.6353166265027651</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>2553130934.0437346</v>
+        <v>2286380159.9468575</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>783047872.79762745</v>
+        <v>745795852.03530264</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>3336178806.841362</v>
+        <v>3032176011.9821606</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>417022350.85517025</v>
+        <v>433168001.71173722</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23364,10 +23363,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23375,8 +23374,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -23390,7 +23389,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>93090953.700000003</v>
+        <v>93180953.700000003</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23402,7 +23401,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>65690899.740000002</v>
+        <v>67853061.859999999</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23426,7 +23425,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>141476575.41999999</v>
+        <v>143479278.12</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23462,7 +23461,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>520024093.269943</v>
+        <v>560156524.46994305</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23474,7 +23473,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>132794773.61998001</v>
+        <v>154821801.23991001</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23510,7 +23509,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>275553150.85995102</v>
+        <v>296580177.76995099</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23522,7 +23521,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>122166897.53999899</v>
+        <v>127412843.419999</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23534,7 +23533,7 @@
       </c>
       <c r="D82" s="192">
         <f>IF(E27="",0,E27)</f>
-        <v>14408108.25</v>
+        <v>18025946.155999999</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23546,7 +23545,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>39740541.32</v>
+        <v>44821622.519999996</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23556,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1475181128.5398729</v>
+        <v>1576567344.075803</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23570,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23618,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>211238820.024753</v>
+        <v>213399540.74474099</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.7596752928037851</v>
+        <v>0.76744586331460185</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>66825797.87945655</v>
+        <v>64665077.159468561</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>8353224.7349320687</v>
+        <v>9237868.1656383667</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23647,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>287304226.360744</v>
+        <v>313888308.08042198</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.68795848309072827</v>
+        <v>0.75161485447757292</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>130314326.82577759</v>
+        <v>103730245.10609961</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16289290.853222199</v>
+        <v>14818606.443728516</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23676,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>492267520.80561304</v>
+        <v>496893466.725613</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.45274490432539388</v>
+        <v>0.45699944754518079</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>595028031.50791168</v>
+        <v>590402085.58791173</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>74378503.93848896</v>
+        <v>84343155.083987385</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23761,19 +23760,19 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>990810567.19111001</v>
+        <v>1024181315.550776</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.5557052107157775</v>
+        <v>0.57442150156189087</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>792168156.21314585</v>
+        <v>758797407.85347986</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>99021019.526643232</v>
+        <v>108399629.69335426</v>
       </c>
       <c r="I94" s="116"/>
     </row>
@@ -24392,11 +24391,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>160</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -24520,10 +24519,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -24552,40 +24551,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24593,13 +24592,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24618,7 +24617,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24628,7 +24627,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25421,10 +25420,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25432,8 +25431,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -25627,13 +25626,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -26449,11 +26448,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26577,10 +26576,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26609,40 +26608,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26650,13 +26649,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26675,7 +26674,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26685,7 +26684,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27478,10 +27477,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27489,8 +27488,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -27684,13 +27683,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 23 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 25 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1927,15 +1927,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1957,6 +1948,16 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3599,10 +3600,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -3629,7 +3630,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3664,7 +3665,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4663,13 +4664,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4872,6 +4873,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4879,11 +4885,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5656,10 +5657,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -5686,7 +5687,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5721,7 +5722,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6720,13 +6721,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6929,6 +6930,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6936,11 +6942,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7713,10 +7714,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -7743,7 +7744,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7778,7 +7779,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8777,13 +8778,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8986,6 +8987,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8993,11 +8999,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9770,10 +9771,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -9800,7 +9801,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9835,7 +9836,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10834,13 +10835,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11043,6 +11044,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11050,11 +11056,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11826,10 +11827,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -11856,7 +11857,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11891,7 +11892,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12876,13 +12877,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13085,6 +13086,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13092,11 +13098,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21661,7 +21662,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,11 +21744,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>210592780.769941</v>
+        <v>223117130.28994101</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>35498876.043462999</v>
+        <v>37340749.923455</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21765,11 +21766,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>393634110.92949599</v>
+        <v>434607754.903373</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>67706440.835084006</v>
+        <v>81416791.795083001</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21777,27 +21778,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>222771518.32418001</v>
+        <v>228377311.09677401</v>
       </c>
       <c r="D10" s="205">
-        <v>26001356.599342</v>
+        <v>26505356.599342</v>
       </c>
       <c r="E10" s="205">
-        <v>127412843.419999</v>
+        <v>127302032.61999901</v>
       </c>
       <c r="F10" s="205">
-        <v>376185718.343521</v>
+        <v>382184700.31611502</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>499203572.48032397</v>
+        <v>504189113.04032397</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>22605776.241119001</v>
+        <v>23213884.341109</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21805,23 +21806,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>272099721.26956201</v>
+        <v>309241696.54955202</v>
       </c>
       <c r="D11" s="205">
-        <v>74129190.024606004</v>
+        <v>76766000.904586002</v>
       </c>
       <c r="E11" s="205">
         <v>38843243.600000001</v>
       </c>
       <c r="F11" s="205">
-        <v>385072154.89416802</v>
+        <v>424850941.054138</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>255314662.19999799</v>
+        <v>284526373.39999801</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -21833,27 +21834,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>216227344.32392699</v>
+        <v>233124411.38787901</v>
       </c>
       <c r="D12" s="205">
-        <v>39495081.025250003</v>
+        <v>52827652.705250002</v>
       </c>
       <c r="E12" s="205">
-        <v>37216125.280000001</v>
+        <v>37261125.280000001</v>
       </c>
       <c r="F12" s="205">
-        <v>292938550.62917697</v>
+        <v>323213189.37312901</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>331329120.05181003</v>
+        <v>354899621.00415897</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>54962901.179328002</v>
+        <v>55668901.179328002</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21861,27 +21862,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>177406766.60556901</v>
+        <v>201483343.51549399</v>
       </c>
       <c r="D13" s="205">
-        <v>28211359.809834</v>
+        <v>28589139.089832999</v>
       </c>
       <c r="E13" s="205">
         <v>30636936.579999998</v>
       </c>
       <c r="F13" s="205">
-        <v>236255062.99540299</v>
+        <v>260709419.18532699</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>662262465.71592605</v>
+        <v>718450266.48923695</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>58078936.769892</v>
+        <v>62114836.769892</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21889,27 +21890,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>499203572.48032397</v>
+        <v>504189113.04032397</v>
       </c>
       <c r="D14" s="205">
-        <v>22605776.241119001</v>
+        <v>23213884.341109</v>
       </c>
       <c r="E14" s="205">
-        <v>143479278.12</v>
+        <v>151076034.90000001</v>
       </c>
       <c r="F14" s="205">
-        <v>665288626.84144294</v>
+        <v>678479032.28143299</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>316848251.04794902</v>
+        <v>321858844.71594501</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>49956938.829843998</v>
+        <v>56383965.909757003</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21925,11 +21926,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>272099721.26956201</v>
+        <v>309241696.54955202</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>74129190.024606004</v>
+        <v>76766000.904586002</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21937,27 +21938,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>331329120.05181003</v>
+        <v>354899621.00415897</v>
       </c>
       <c r="D16" s="205">
-        <v>54962901.179328002</v>
+        <v>55668901.179328002</v>
       </c>
       <c r="E16" s="205">
         <v>10797297.199999999</v>
       </c>
       <c r="F16" s="205">
-        <v>397089318.43113798</v>
+        <v>421365819.38348699</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>341675971.12479597</v>
+        <v>361445781.86299402</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>39328537.829948001</v>
+        <v>44903213.509947002</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21965,7 +21966,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>255314662.19999799</v>
+        <v>284526373.39999801</v>
       </c>
       <c r="D17" s="205">
         <v>33550551.18</v>
@@ -21974,18 +21975,18 @@
         <v>169</v>
       </c>
       <c r="F17" s="205">
-        <v>288865213.37999803</v>
+        <v>318076924.57999802</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>222771518.32418001</v>
+        <v>228377311.09677401</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>26001356.599342</v>
+        <v>26505356.599342</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21993,27 +21994,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>867577535.90481806</v>
+        <v>874695319.674793</v>
       </c>
       <c r="D18" s="205">
-        <v>7746528.7219770001</v>
+        <v>8457528.7219769992</v>
       </c>
       <c r="E18" s="205">
         <v>8274324.2400000002</v>
       </c>
       <c r="F18" s="205">
-        <v>883598388.86679494</v>
+        <v>891427172.63677001</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>556862062.78800702</v>
+        <v>567121972.41786301</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>164355132.21170899</v>
+        <v>168980267.45270899</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22021,27 +22022,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>662262465.71592605</v>
+        <v>718450266.48923695</v>
       </c>
       <c r="D19" s="205">
-        <v>58078936.769892</v>
+        <v>62114836.769892</v>
       </c>
       <c r="E19" s="205">
-        <v>560156524.46994305</v>
+        <v>563406974.72994304</v>
       </c>
       <c r="F19" s="205">
-        <v>1280497926.955761</v>
+        <v>1343972077.9890721</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>181773274.10117799</v>
+        <v>194159528.81466299</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>103294334.440724</v>
+        <v>105780820.960712</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22049,16 +22050,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>142498950.10117799</v>
+        <v>153810634.81466299</v>
       </c>
       <c r="D20" s="205">
         <v>28052299.959775999</v>
       </c>
       <c r="E20" s="205">
-        <v>2972973.04</v>
+        <v>3816216.3</v>
       </c>
       <c r="F20" s="205">
-        <v>173524223.100954</v>
+        <v>185679151.07443899</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22076,23 +22077,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>39274324</v>
+        <v>40348894</v>
       </c>
       <c r="D21" s="205">
-        <v>75242034.480948001</v>
+        <v>77728521.000936002</v>
       </c>
       <c r="E21" s="205">
         <v>41848649.479999997</v>
       </c>
       <c r="F21" s="205">
-        <v>156365007.96094799</v>
+        <v>159926064.48093599</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>496893466.725613</v>
+        <v>526145889.32693201</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22103,16 +22104,16 @@
         <v>173</v>
       </c>
       <c r="C22" s="205">
-        <v>120464485.8</v>
+        <v>149370505.80000001</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>169</v>
       </c>
       <c r="E22" s="205">
-        <v>10414414.119999999</v>
+        <v>10814414.119999999</v>
       </c>
       <c r="F22" s="205">
-        <v>130878899.92</v>
+        <v>160184919.91999999</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -22123,16 +22124,16 @@
         <v>174</v>
       </c>
       <c r="C23" s="205">
-        <v>188067175.44997501</v>
+        <v>203110125.249975</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>169</v>
       </c>
       <c r="E23" s="205">
-        <v>10180179.9</v>
+        <v>10300179.9</v>
       </c>
       <c r="F23" s="205">
-        <v>198247355.34997499</v>
+        <v>213410305.149975</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22143,16 +22144,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>210592780.769941</v>
+        <v>223117130.28994101</v>
       </c>
       <c r="D24" s="205">
-        <v>35498876.043462999</v>
+        <v>37340749.923455</v>
       </c>
       <c r="E24" s="205">
-        <v>93180953.700000003</v>
+        <v>98131404.040000007</v>
       </c>
       <c r="F24" s="205">
-        <v>339272610.51340401</v>
+        <v>358589284.25339597</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22163,16 +22164,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>316848251.04794902</v>
+        <v>321858844.71594501</v>
       </c>
       <c r="D25" s="205">
-        <v>49956938.829843998</v>
+        <v>56383965.909757003</v>
       </c>
       <c r="E25" s="205">
-        <v>154821801.23991001</v>
+        <v>195682161.77985999</v>
       </c>
       <c r="F25" s="205">
-        <v>521626991.11770302</v>
+        <v>573924972.40556204</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22183,16 +22184,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>341675971.12479597</v>
+        <v>361445781.86299402</v>
       </c>
       <c r="D26" s="205">
-        <v>39328537.829948001</v>
+        <v>44903213.509947002</v>
       </c>
       <c r="E26" s="205">
-        <v>296580177.76995099</v>
+        <v>320141438.62991101</v>
       </c>
       <c r="F26" s="205">
-        <v>677584686.72469497</v>
+        <v>726490434.00285196</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22203,16 +22204,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>556862062.78800702</v>
+        <v>567121972.41786301</v>
       </c>
       <c r="D27" s="205">
-        <v>164355132.21170899</v>
+        <v>168980267.45270899</v>
       </c>
       <c r="E27" s="205">
         <v>18025946.155999999</v>
       </c>
       <c r="F27" s="205">
-        <v>739243141.15571594</v>
+        <v>754128186.02657199</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22259,7 +22260,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>213399540.74474099</v>
+        <v>223714856.18468201</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22270,7 +22271,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>313888308.08042198</v>
+        <v>319503064.902022</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22281,7 +22282,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>228983933.90864599</v>
+        <v>248720069.58996499</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22291,8 +22292,8 @@
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="205">
-        <v>267909532.81696701</v>
+      <c r="C35" s="248">
+        <v>277425819.73696703</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22302,7 +22303,7 @@
       <c r="B36" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="205">
         <v>0</v>
       </c>
       <c r="G36" s="116"/>
@@ -22334,17 +22335,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="238" t="s">
+      <c r="B41" s="245" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="239"/>
-      <c r="D41" s="240"/>
+      <c r="C41" s="246"/>
+      <c r="D41" s="247"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.74193548387096775</v>
+        <v>0.80645161290322576</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22388,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>4552899172.0531425</v>
+        <v>4854476025.634798</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.66569867248304726</v>
+        <v>0.70979350162251831</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>2286380159.9468575</v>
+        <v>1984803306.365202</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>326625737.13526535</v>
+        <v>330800551.06086701</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22417,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>729468972.18505895</v>
+        <v>772625340.52591991</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.49446645795988792</v>
+        <v>0.52371976057534753</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>745795852.03530276</v>
+        <v>702639483.6944418</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>106542264.57647182</v>
+        <v>117106580.6157403</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,19 +22446,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1024181315.550776</v>
+        <v>1069363810.413636</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.57442150156189087</v>
+        <v>0.59976251896707489</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>758797407.85347986</v>
+        <v>713614912.9906199</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>108399629.69335426</v>
+        <v>118935818.83176999</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22472,19 +22473,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>6306549459.7889767</v>
+        <v>6696465176.5743542</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.62456401782606574</v>
+        <v>0.6631790050297266</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>3790973419.83564</v>
+        <v>3401057703.0502634</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>541567631.4050914</v>
+        <v>566842950.50837719</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22505,10 +22506,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -22535,7 +22536,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22570,7 +22571,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22593,35 +22594,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>210592780.769941</v>
+        <v>223117130.28994101</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>35498876.043462999</v>
+        <v>37340749.923455</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>246091656.81340399</v>
+        <v>260457880.21339601</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.50745373396927118</v>
+        <v>0.53707763021086696</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>206090697.230059</v>
+        <v>193566347.71005899</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>32771525.17719131</v>
+        <v>30929651.297199309</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>238862222.40725031</v>
+        <v>224495999.0072583</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>34123174.629607186</v>
+        <v>37415999.834543049</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22646,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>393634110.92949599</v>
+        <v>434607754.903373</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>67706440.835084006</v>
+        <v>81416791.795083001</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>461340551.76458001</v>
+        <v>516024546.69845599</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.61781510561828812</v>
+        <v>0.69104647012002096</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>161548260.07050401</v>
+        <v>120574616.096627</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>123840343.16491599</v>
+        <v>110129992.204917</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>285388603.23541999</v>
+        <v>230704608.30154401</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>40769800.462202854</v>
+        <v>38450768.050257333</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22697,7 +22698,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>120464485.8</v>
+        <v>149370505.80000001</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22705,15 +22706,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>120464485.8</v>
+        <v>149370505.80000001</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.49887296758662331</v>
+        <v>0.6185798827222565</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>121008782.2</v>
+        <v>92102762.199999988</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22721,11 +22722,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>121008782.2</v>
+        <v>92102762.199999988</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>17286968.885714285</v>
+        <v>15350460.366666665</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,35 +22750,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>499203572.48032397</v>
+        <v>504189113.04032397</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>22605776.241119001</v>
+        <v>23213884.341109</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>521809348.721443</v>
+        <v>527402997.38143295</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.79351258011193626</v>
+        <v>0.80201881057964253</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>111508899.51967603</v>
+        <v>106523358.95967603</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>24276050.576215889</v>
+        <v>23667942.47622589</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>135784950.09589189</v>
+        <v>130191301.43590194</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>19397850.013698842</v>
+        <v>21698550.239316989</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22801,7 +22802,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>255314662.19999799</v>
+        <v>284526373.39999801</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -22809,15 +22810,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>288865213.37999797</v>
+        <v>318076924.57999802</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.59201868015916703</v>
+        <v>0.6518870128928318</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>149748621.80000201</v>
+        <v>120536910.60000199</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -22825,11 +22826,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>199067385.81152618</v>
+        <v>169855674.61152613</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>28438197.97307517</v>
+        <v>28309279.101921022</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22854,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>331329120.05181003</v>
+        <v>354899621.00415897</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>54962901.179328002</v>
+        <v>55668901.179328002</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>386292021.23113805</v>
+        <v>410568522.183487</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.69582328614507971</v>
+        <v>0.7395522625161971</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>142589711.94818997</v>
+        <v>119019210.99584103</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>26276492.943325602</v>
+        <v>25570492.943325602</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>168866204.89151555</v>
+        <v>144589703.93916661</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>24123743.555930793</v>
+        <v>24098283.989861101</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,35 +22906,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>662262465.71592605</v>
+        <v>718450266.48923695</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>58078936.769892</v>
+        <v>62114836.769892</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>720341402.48581803</v>
+        <v>780565103.25912893</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.68363893287231714</v>
+        <v>0.74079414620339945</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>299495879.28407395</v>
+        <v>243308078.51076305</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>33849639.56926439</v>
+        <v>29813739.56926439</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>333345518.85333836</v>
+        <v>273121818.08002746</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>47620788.407619767</v>
+        <v>45520303.01333791</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,35 +22958,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>316848251.04794902</v>
+        <v>321858844.71594501</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>49956938.829843998</v>
+        <v>56383965.909757003</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>366805189.87779301</v>
+        <v>378242810.62570202</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.64457128399644426</v>
+        <v>0.66467013236279449</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>188438807.95205098</v>
+        <v>183428214.28405499</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>13824465.170156002</v>
+        <v>7397438.0902429968</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>202263273.12220699</v>
+        <v>190825652.37429798</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>28894753.303172428</v>
+        <v>31804275.395716328</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23009,7 +23010,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>188067175.44997501</v>
+        <v>203110125.249975</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23017,15 +23018,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>188067175.44997501</v>
+        <v>203110125.249975</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.46535884585446219</v>
+        <v>0.50258155492331125</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>216066488.55002499</v>
+        <v>201023538.750025</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23033,11 +23034,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>216066488.55002499</v>
+        <v>201023538.750025</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>30866641.221432142</v>
+        <v>33503923.125004169</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,35 +23062,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>272099721.26956201</v>
+        <v>309241696.54955202</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>74129190.024606004</v>
+        <v>76766000.904586002</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>346228911.294168</v>
+        <v>386007697.45413804</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.6382315049397389</v>
+        <v>0.71155893002580617</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>131917587.73043799</v>
+        <v>94775612.450447977</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>64335200.193389401</v>
+        <v>61698389.313409403</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>196252787.92382741</v>
+        <v>156474001.76385736</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>28036112.560546774</v>
+        <v>26079000.293976229</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23114,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>341675971.12479597</v>
+        <v>361445781.86299402</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>39328537.829948001</v>
+        <v>44903213.509947002</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>381004508.95474398</v>
+        <v>406348995.37294102</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.55188355311647441</v>
+        <v>0.58859494336946538</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>289953624.87520403</v>
+        <v>270183814.13700598</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>19413062.780677266</v>
+        <v>13838387.100678265</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>309366687.65588129</v>
+        <v>284022201.23768425</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>44195241.093697324</v>
+        <v>47337033.539614044</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23166,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>222771518.32418001</v>
+        <v>228377311.09677401</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>26001356.599342</v>
+        <v>26505356.599342</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>248772874.923522</v>
+        <v>254882667.696116</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.55245149797304616</v>
+        <v>0.56601955345563093</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>163771504.67581999</v>
+        <v>158165711.90322599</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>37762798.200471804</v>
+        <v>37258798.200471804</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>201534302.87629181</v>
+        <v>195424510.10369781</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>28790614.696613114</v>
+        <v>32570751.683949634</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23218,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>556862062.78800702</v>
+        <v>567121972.41786301</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>164355132.21170899</v>
+        <v>168980267.45270899</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>721217194.99971604</v>
+        <v>736102239.87057197</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.78980558047292859</v>
+        <v>0.80610620611815675</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>26488879.211992979</v>
+        <v>16228969.582136989</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>165451812.78100839</v>
+        <v>160826677.5400084</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>191940691.99300134</v>
+        <v>177055647.12214541</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>27420098.85614305</v>
+        <v>29509274.520357568</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23270,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>181773274.10117799</v>
+        <v>194159528.81466299</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>103294334.440724</v>
+        <v>105780820.960712</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>285067608.54190201</v>
+        <v>299940349.77537501</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.55085983714374265</v>
+        <v>0.57959967137344515</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>77752414.89882201</v>
+        <v>65366160.185337007</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>154675697.46716237</v>
+        <v>152189210.94717437</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>232428112.36598438</v>
+        <v>217555371.13251138</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>33204016.052283484</v>
+        <v>36259228.522085227</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23320,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>4552899172.0531425</v>
+        <v>4854476025.634798</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>729468972.18505895</v>
+        <v>772625340.52591991</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>5282368144.2382002</v>
+        <v>5627101366.1607189</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.6353166265027651</v>
+        <v>0.67677809636153219</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>2286380159.9468575</v>
+        <v>1984803306.3652024</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>745795852.03530264</v>
+        <v>702639483.69444156</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>3032176011.9821606</v>
+        <v>2687442790.0596437</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>433168001.71173722</v>
+        <v>447907131.67660731</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23389,7 +23390,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>93180953.700000003</v>
+        <v>98131404.040000007</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23401,7 +23402,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>67853061.859999999</v>
+        <v>67898061.859999999</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23413,7 +23414,7 @@
       </c>
       <c r="D72" s="192">
         <f>IF(E22="",0,E22)</f>
-        <v>10414414.119999999</v>
+        <v>10814414.119999999</v>
       </c>
     </row>
     <row r="73" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23426,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>143479278.12</v>
+        <v>151076034.90000001</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23462,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>560156524.46994305</v>
+        <v>563406974.72994304</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23473,7 +23474,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>154821801.23991001</v>
+        <v>195682161.77985999</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23485,7 +23486,7 @@
       </c>
       <c r="D78" s="192">
         <f>IF(E23="",0,E23)</f>
-        <v>10180179.9</v>
+        <v>10300179.9</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23510,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>296580177.76995099</v>
+        <v>320141438.62991101</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23522,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>127412843.419999</v>
+        <v>127302032.61999901</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23545,7 +23546,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>44821622.519999996</v>
+        <v>45664865.779999994</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23556,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1576567344.075803</v>
+        <v>1658084055.3157127</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23569,13 +23570,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23617,19 +23618,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>213399540.74474099</v>
+        <v>223714856.18468201</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.76744586331460185</v>
+        <v>0.80454269180608051</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>64665077.159468561</v>
+        <v>54349761.719527543</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>9237868.1656383667</v>
+        <v>9058293.6199212577</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23647,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>313888308.08042198</v>
+        <v>319503064.902022</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.75161485447757292</v>
+        <v>0.76505955605694054</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>103730245.10609961</v>
+        <v>98115488.284499586</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>14818606.443728516</v>
+        <v>16352581.380749932</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23676,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>496893466.725613</v>
+        <v>526145889.32693201</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.45699944754518079</v>
+        <v>0.48390328481286415</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>590402085.58791173</v>
+        <v>561149662.98659277</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>84343155.083987385</v>
+        <v>93524943.831098795</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,24 +23761,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>1024181315.550776</v>
+        <v>1069363810.413636</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.57442150156189087</v>
+        <v>0.59976251896707489</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>758797407.85347986</v>
+        <v>713614912.9906199</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>108399629.69335426</v>
+        <v>118935818.83176999</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23785,11 +23791,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -24562,10 +24563,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -24592,7 +24593,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24627,7 +24628,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25626,13 +25627,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25835,6 +25836,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25842,11 +25848,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26619,10 +26620,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -26649,7 +26650,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26684,7 +26685,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27683,13 +27684,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27892,6 +27893,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27899,11 +27905,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 25 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 26 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1927,6 +1927,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1948,16 +1957,6 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3600,10 +3599,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -3630,7 +3629,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3665,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4664,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4873,11 +4872,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4885,6 +4879,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5657,10 +5656,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -5687,7 +5686,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5722,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6721,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6930,11 +6929,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6942,6 +6936,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7714,10 +7713,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -7744,7 +7743,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7779,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8778,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8987,11 +8986,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8999,6 +8993,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9771,10 +9770,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -9801,7 +9800,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9836,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10835,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11044,11 +11043,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11056,6 +11050,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11827,10 +11826,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -11857,7 +11856,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11892,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12877,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13086,11 +13085,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13098,6 +13092,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21662,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21744,11 +21743,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>223117130.28994101</v>
+        <v>254512394.267885</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>37340749.923455</v>
+        <v>37644371.543454997</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21766,11 +21765,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>434607754.903373</v>
+        <v>450163430.59335101</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>81416791.795083001</v>
+        <v>87396620.680083007</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21778,27 +21777,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>228377311.09677401</v>
+        <v>245904663.37819701</v>
       </c>
       <c r="D10" s="205">
-        <v>26505356.599342</v>
+        <v>30000486.200826</v>
       </c>
       <c r="E10" s="205">
-        <v>127302032.61999901</v>
+        <v>135459239.519999</v>
       </c>
       <c r="F10" s="205">
-        <v>382184700.31611502</v>
+        <v>411364389.09902197</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>504189113.04032397</v>
+        <v>531463288.50028402</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>23213884.341109</v>
+        <v>24103560.081103001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21806,23 +21805,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>309241696.54955202</v>
+        <v>328044269.38552397</v>
       </c>
       <c r="D11" s="205">
-        <v>76766000.904586002</v>
+        <v>83068874.754528001</v>
       </c>
       <c r="E11" s="205">
         <v>38843243.600000001</v>
       </c>
       <c r="F11" s="205">
-        <v>424850941.054138</v>
+        <v>449956387.74005198</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>284526373.39999801</v>
+        <v>314350697.279998</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -21834,27 +21833,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>233124411.38787901</v>
+        <v>244185492.48785701</v>
       </c>
       <c r="D12" s="205">
-        <v>52827652.705250002</v>
+        <v>58807481.59025</v>
       </c>
       <c r="E12" s="205">
         <v>37261125.280000001</v>
       </c>
       <c r="F12" s="205">
-        <v>323213189.37312901</v>
+        <v>340254099.35810697</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>354899621.00415897</v>
+        <v>364392495.68195301</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>55668901.179328002</v>
+        <v>57646324.609319001</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21862,27 +21861,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>201483343.51549399</v>
+        <v>205977938.10549399</v>
       </c>
       <c r="D13" s="205">
         <v>28589139.089832999</v>
       </c>
       <c r="E13" s="205">
-        <v>30636936.579999998</v>
+        <v>36852139.219999999</v>
       </c>
       <c r="F13" s="205">
-        <v>260709419.18532699</v>
+        <v>271419216.41532701</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>718450266.48923695</v>
+        <v>783530562.45213401</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>62114836.769892</v>
+        <v>63122836.769892</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21890,27 +21889,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>504189113.04032397</v>
+        <v>531463288.50028402</v>
       </c>
       <c r="D14" s="205">
-        <v>23213884.341109</v>
+        <v>24103560.081103001</v>
       </c>
       <c r="E14" s="205">
-        <v>151076034.90000001</v>
+        <v>185618737.74000001</v>
       </c>
       <c r="F14" s="205">
-        <v>678479032.28143299</v>
+        <v>741185586.32138705</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>321858844.71594501</v>
+        <v>333984691.930942</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>56383965.909757003</v>
+        <v>58336776.719756998</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21926,11 +21925,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>309241696.54955202</v>
+        <v>328044269.38552397</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>76766000.904586002</v>
+        <v>83068874.754528001</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21938,27 +21937,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>354899621.00415897</v>
+        <v>364392495.68195301</v>
       </c>
       <c r="D16" s="205">
-        <v>55668901.179328002</v>
+        <v>57646324.609319001</v>
       </c>
       <c r="E16" s="205">
-        <v>10797297.199999999</v>
+        <v>11608108</v>
       </c>
       <c r="F16" s="205">
-        <v>421365819.38348699</v>
+        <v>433646928.29127198</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>361445781.86299402</v>
+        <v>389025523.14936203</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>44903213.509947002</v>
+        <v>52235612.639940999</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21966,7 +21965,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>284526373.39999801</v>
+        <v>314350697.279998</v>
       </c>
       <c r="D17" s="205">
         <v>33550551.18</v>
@@ -21975,18 +21974,18 @@
         <v>169</v>
       </c>
       <c r="F17" s="205">
-        <v>318076924.57999802</v>
+        <v>347901248.45999801</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>228377311.09677401</v>
+        <v>245904663.37819701</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>26505356.599342</v>
+        <v>30000486.200826</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21994,27 +21993,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>874695319.674793</v>
+        <v>882983776.94476902</v>
       </c>
       <c r="D18" s="205">
-        <v>8457528.7219769992</v>
+        <v>8619114.3119760007</v>
       </c>
       <c r="E18" s="205">
-        <v>8274324.2400000002</v>
+        <v>10706756.74</v>
       </c>
       <c r="F18" s="205">
-        <v>891427172.63677001</v>
+        <v>902309647.99674499</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>567121972.41786301</v>
+        <v>585538328.93634605</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>168980267.45270899</v>
+        <v>172859916.172685</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22022,27 +22021,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>718450266.48923695</v>
+        <v>783530562.45213401</v>
       </c>
       <c r="D19" s="205">
-        <v>62114836.769892</v>
+        <v>63122836.769892</v>
       </c>
       <c r="E19" s="205">
-        <v>563406974.72994304</v>
+        <v>599431298.08994305</v>
       </c>
       <c r="F19" s="205">
-        <v>1343972077.9890721</v>
+        <v>1446084697.311969</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>194159528.81466299</v>
+        <v>202946310.76466301</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>105780820.960712</v>
+        <v>118446982.960512</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22050,23 +22049,23 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>153810634.81466299</v>
+        <v>158951496.76466301</v>
       </c>
       <c r="D20" s="205">
-        <v>28052299.959775999</v>
+        <v>28556299.959775999</v>
       </c>
       <c r="E20" s="205">
         <v>3816216.3</v>
       </c>
       <c r="F20" s="205">
-        <v>185679151.07443899</v>
+        <v>191324013.02443901</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
       <c r="J20" s="116"/>
       <c r="M20" s="14">
         <f>IFERROR(C31,0)+IFERROR(C15,0)+IFERROR(C36,0)</f>
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>120</v>
@@ -22077,23 +22076,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>40348894</v>
+        <v>43994814</v>
       </c>
       <c r="D21" s="205">
-        <v>77728521.000936002</v>
+        <v>89890683.000735998</v>
       </c>
       <c r="E21" s="205">
-        <v>41848649.479999997</v>
+        <v>48551352.280000001</v>
       </c>
       <c r="F21" s="205">
-        <v>159926064.48093599</v>
+        <v>182436849.280736</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>526145889.32693201</v>
+        <v>554303461.83272099</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22104,7 +22103,7 @@
         <v>173</v>
       </c>
       <c r="C22" s="205">
-        <v>149370505.80000001</v>
+        <v>211281605.80000001</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>169</v>
@@ -22113,7 +22112,7 @@
         <v>10814414.119999999</v>
       </c>
       <c r="F22" s="205">
-        <v>160184919.91999999</v>
+        <v>222096019.91999999</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -22124,7 +22123,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="205">
-        <v>203110125.249975</v>
+        <v>241460975.249975</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>169</v>
@@ -22133,7 +22132,7 @@
         <v>10300179.9</v>
       </c>
       <c r="F23" s="205">
-        <v>213410305.149975</v>
+        <v>251761155.149975</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22144,16 +22143,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>223117130.28994101</v>
+        <v>254512394.267885</v>
       </c>
       <c r="D24" s="205">
-        <v>37340749.923455</v>
+        <v>37644371.543454997</v>
       </c>
       <c r="E24" s="205">
-        <v>98131404.040000007</v>
+        <v>99482755.359999999</v>
       </c>
       <c r="F24" s="205">
-        <v>358589284.25339597</v>
+        <v>391639521.17133999</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22164,16 +22163,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>321858844.71594501</v>
+        <v>333984691.930942</v>
       </c>
       <c r="D25" s="205">
-        <v>56383965.909757003</v>
+        <v>58336776.719756998</v>
       </c>
       <c r="E25" s="205">
-        <v>195682161.77985999</v>
+        <v>208051531.43981999</v>
       </c>
       <c r="F25" s="205">
-        <v>573924972.40556204</v>
+        <v>600373000.09051895</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22184,16 +22183,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>361445781.86299402</v>
+        <v>389025523.14936203</v>
       </c>
       <c r="D26" s="205">
-        <v>44903213.509947002</v>
+        <v>52235612.639940999</v>
       </c>
       <c r="E26" s="205">
-        <v>320141438.62991101</v>
+        <v>368505403.31984103</v>
       </c>
       <c r="F26" s="205">
-        <v>726490434.00285196</v>
+        <v>809766539.10914397</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22204,16 +22203,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>567121972.41786301</v>
+        <v>585538328.93634605</v>
       </c>
       <c r="D27" s="205">
-        <v>168980267.45270899</v>
+        <v>172859916.172685</v>
       </c>
       <c r="E27" s="205">
         <v>18025946.155999999</v>
       </c>
       <c r="F27" s="205">
-        <v>754128186.02657199</v>
+        <v>776424191.26503098</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22260,7 +22259,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>223714856.18468201</v>
+        <v>233726396.70464301</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22271,7 +22270,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>319503064.902022</v>
+        <v>321596578.36200398</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22282,7 +22281,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>248720069.58996499</v>
+        <v>269880090.13584203</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22292,8 +22291,8 @@
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="248">
-        <v>277425819.73696703</v>
+      <c r="C35" s="205">
+        <v>283601371.69687903</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22304,7 +22303,7 @@
         <v>136</v>
       </c>
       <c r="C36" s="205">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="G36" s="116"/>
       <c r="H36" s="116"/>
@@ -22335,17 +22334,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="245" t="s">
+      <c r="B41" s="238" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="246"/>
-      <c r="D41" s="247"/>
+      <c r="C41" s="239"/>
+      <c r="D41" s="240"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.80645161290322576</v>
+        <v>0.83870967741935487</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22388,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>4854476025.634798</v>
+        <v>5236599237.3706141</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.70979350162251831</v>
+        <v>0.76566535495477173</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>1984803306.365202</v>
+        <v>1602680094.6293859</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>330800551.06086701</v>
+        <v>320536018.92587721</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22417,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>772625340.52591991</v>
+        <v>818412914.31210101</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.52371976057534753</v>
+        <v>0.5547566110678539</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>702639483.6944418</v>
+        <v>656851909.9082607</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>117106580.6157403</v>
+        <v>131370381.98165214</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22446,19 +22445,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1069363810.413636</v>
+        <v>1109626436.899368</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.59976251896707489</v>
+        <v>0.62234418298651883</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>713614912.9906199</v>
+        <v>673352286.50488782</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>118935818.83176999</v>
+        <v>134670457.30097756</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22473,19 +22472,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>6696465176.5743542</v>
+        <v>7164638588.5820837</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.6631790050297266</v>
+        <v>0.70954417969572692</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>3401057703.0502634</v>
+        <v>2932884291.0425348</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>566842950.50837719</v>
+        <v>586576858.20850694</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22506,10 +22505,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -22536,7 +22535,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22571,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22594,35 +22593,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>223117130.28994101</v>
+        <v>254512394.267885</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>37340749.923455</v>
+        <v>37644371.543454997</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>260457880.21339601</v>
+        <v>292156765.81133997</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.53707763021086696</v>
+        <v>0.60244237303730996</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>193566347.71005899</v>
+        <v>162171083.732115</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>30929651.297199309</v>
+        <v>30626029.677199312</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>224495999.0072583</v>
+        <v>192797113.40931433</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>37415999.834543049</v>
+        <v>38559422.681862868</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22646,35 +22645,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>434607754.903373</v>
+        <v>450163430.59335101</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>81416791.795083001</v>
+        <v>87396620.680083007</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>516024546.69845599</v>
+        <v>537560051.27343404</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.69104647012002096</v>
+        <v>0.71988625015375762</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>120574616.096627</v>
+        <v>105018940.40664899</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>110129992.204917</v>
+        <v>104150163.31991699</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>230704608.30154401</v>
+        <v>209169103.72656596</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>38450768.050257333</v>
+        <v>41833820.74531319</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22698,7 +22697,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>149370505.80000001</v>
+        <v>211281605.80000001</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22706,15 +22705,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>149370505.80000001</v>
+        <v>211281605.80000001</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.6185798827222565</v>
+        <v>0.87496892533876669</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>92102762.199999988</v>
+        <v>30191662.199999988</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22722,11 +22721,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>92102762.199999988</v>
+        <v>30191662.199999988</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>15350460.366666665</v>
+        <v>6038332.4399999976</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22750,35 +22749,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>504189113.04032397</v>
+        <v>531463288.50028402</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>23213884.341109</v>
+        <v>24103560.081103001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>527402997.38143295</v>
+        <v>555566848.58138704</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.80201881057964253</v>
+        <v>0.84484742276591906</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>106523358.95967603</v>
+        <v>79249183.499715984</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>23667942.47622589</v>
+        <v>22778266.73623189</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>130191301.43590194</v>
+        <v>102027450.23594785</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>21698550.239316989</v>
+        <v>20405490.047189571</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22802,7 +22801,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>284526373.39999801</v>
+        <v>314350697.279998</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -22810,15 +22809,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>318076924.57999802</v>
+        <v>347901248.45999801</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.6518870128928318</v>
+        <v>0.71301087288787446</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>120536910.60000199</v>
+        <v>90712586.720001996</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -22826,11 +22825,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>169855674.61152613</v>
+        <v>140031350.73152614</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>28309279.101921022</v>
+        <v>28006270.146305226</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22854,35 +22853,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>354899621.00415897</v>
+        <v>364392495.68195301</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>55668901.179328002</v>
+        <v>57646324.609319001</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>410568522.183487</v>
+        <v>422038820.29127204</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.7395522625161971</v>
+        <v>0.76021357593650984</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>119019210.99584103</v>
+        <v>109526336.31804699</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>25570492.943325602</v>
+        <v>23593069.513334602</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>144589703.93916661</v>
+        <v>133119405.83138156</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>24098283.989861101</v>
+        <v>26623881.166276313</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22906,35 +22905,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>718450266.48923695</v>
+        <v>783530562.45213401</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>62114836.769892</v>
+        <v>63122836.769892</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>780565103.25912893</v>
+        <v>846653399.22202599</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.74079414620339945</v>
+        <v>0.80351514484586517</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>243308078.51076305</v>
+        <v>178227782.54786599</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>29813739.56926439</v>
+        <v>28805739.56926439</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>273121818.08002746</v>
+        <v>207033522.1171304</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>45520303.01333791</v>
+        <v>41406704.423426077</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22958,35 +22957,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>321858844.71594501</v>
+        <v>333984691.930942</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>56383965.909757003</v>
+        <v>58336776.719756998</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>378242810.62570202</v>
+        <v>392321468.65069902</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.66467013236279449</v>
+        <v>0.68940996410602184</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>183428214.28405499</v>
+        <v>171302367.069058</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>7397438.0902429968</v>
+        <v>5444627.2802430019</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>190825652.37429798</v>
+        <v>176746994.34930098</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>31804275.395716328</v>
+        <v>35349398.869860195</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23010,7 +23009,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>203110125.249975</v>
+        <v>241460975.249975</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23018,15 +23017,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>203110125.249975</v>
+        <v>241460975.249975</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.50258155492331125</v>
+        <v>0.59747800482657887</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>201023538.750025</v>
+        <v>162672688.750025</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23034,11 +23033,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>201023538.750025</v>
+        <v>162672688.750025</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>33503923.125004169</v>
+        <v>32534537.750004999</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23062,35 +23061,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>309241696.54955202</v>
+        <v>328044269.38552397</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>76766000.904586002</v>
+        <v>83068874.754528001</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>386007697.45413804</v>
+        <v>411113144.14005196</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.71155893002580617</v>
+        <v>0.75783781228506808</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>94775612.450447977</v>
+        <v>75973039.614476025</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>61698389.313409403</v>
+        <v>55395515.463467404</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>156474001.76385736</v>
+        <v>131368555.07794344</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>26079000.293976229</v>
+        <v>26273711.01558869</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23114,35 +23113,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>361445781.86299402</v>
+        <v>389025523.14936203</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>44903213.509947002</v>
+        <v>52235612.639940999</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>406348995.37294102</v>
+        <v>441261135.789303</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.58859494336946538</v>
+        <v>0.63916504332114787</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>270183814.13700598</v>
+        <v>242604072.85063797</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>13838387.100678265</v>
+        <v>6505987.9706842676</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>284022201.23768425</v>
+        <v>249110060.82132226</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>47337033.539614044</v>
+        <v>49822012.164264455</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23166,35 +23165,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>228377311.09677401</v>
+        <v>245904663.37819701</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>26505356.599342</v>
+        <v>30000486.200826</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>254882667.696116</v>
+        <v>275905149.579023</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.56601955345563093</v>
+        <v>0.61270431203670028</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>158165711.90322599</v>
+        <v>140638359.62180299</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>37258798.200471804</v>
+        <v>33763668.598987803</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>195424510.10369781</v>
+        <v>174402028.2207908</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>32570751.683949634</v>
+        <v>34880405.644158162</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23218,35 +23217,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>567121972.41786301</v>
+        <v>585538328.93634605</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>168980267.45270899</v>
+        <v>172859916.172685</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>736102239.87057197</v>
+        <v>758398245.10903108</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.80610620611815675</v>
+        <v>0.83052258093794407</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>16228969.582136989</v>
+        <v>-2187386.9363460541</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>160826677.5400084</v>
+        <v>156947028.82003239</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>177055647.12214541</v>
+        <v>154759641.8836863</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>29509274.520357568</v>
+        <v>30951928.376737259</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23270,35 +23269,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>194159528.81466299</v>
+        <v>202946310.76466301</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>105780820.960712</v>
+        <v>118446982.960512</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>299940349.77537501</v>
+        <v>321393293.72517502</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.57959967137344515</v>
+        <v>0.6210549783123378</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>65366160.185337007</v>
+        <v>56579378.235336989</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>152189210.94717437</v>
+        <v>139523048.9473744</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>217555371.13251138</v>
+        <v>196102427.18271136</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>36259228.522085227</v>
+        <v>39220485.436542273</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23320,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>4854476025.634798</v>
+        <v>5236599237.3706141</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>772625340.52591991</v>
+        <v>818412914.31210101</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>5627101366.1607189</v>
+        <v>6055012151.6827154</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.67677809636153219</v>
+        <v>0.72824342957548394</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>1984803306.3652024</v>
+        <v>1602680094.6293859</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>702639483.69444156</v>
+        <v>656851909.90826058</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>2687442790.0596437</v>
+        <v>2259532004.5376463</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>447907131.67660731</v>
+        <v>451906400.90752923</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23390,7 +23389,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>98131404.040000007</v>
+        <v>99482755.359999999</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23402,7 +23401,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>67898061.859999999</v>
+        <v>74113264.5</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23426,7 +23425,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>151076034.90000001</v>
+        <v>185618737.74000001</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23450,7 +23449,7 @@
       </c>
       <c r="D75" s="192">
         <f>IF(E16="",0,E16)</f>
-        <v>10797297.199999999</v>
+        <v>11608108</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23462,7 +23461,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>563406974.72994304</v>
+        <v>599431298.08994305</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23474,7 +23473,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>195682161.77985999</v>
+        <v>208051531.43981999</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23510,7 +23509,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>320141438.62991101</v>
+        <v>368505403.31984103</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23522,7 +23521,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>127302032.61999901</v>
+        <v>135459239.519999</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23546,7 +23545,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>45664865.779999994</v>
+        <v>52367568.579999998</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23556,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1658084055.3157127</v>
+        <v>1812621690.3256028</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23570,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23618,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>223714856.18468201</v>
+        <v>233726396.70464301</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.80454269180608051</v>
+        <v>0.84054705868820534</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>54349761.719527543</v>
+        <v>44338221.199566543</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>9058293.6199212577</v>
+        <v>8867644.239913309</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23647,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>319503064.902022</v>
+        <v>321596578.36200398</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.76505955605694054</v>
+        <v>0.77007253606946158</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>98115488.284499586</v>
+        <v>96021974.824517608</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16352581.380749932</v>
+        <v>19204394.964903522</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23676,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>526145889.32693201</v>
+        <v>554303461.83272099</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.48390328481286415</v>
+        <v>0.50980017406792999</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>561149662.98659277</v>
+        <v>532992090.48080373</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>93524943.831098795</v>
+        <v>106598418.09616074</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23761,29 +23760,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>1069363810.413636</v>
+        <v>1109626436.899368</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.59976251896707489</v>
+        <v>0.62234418298651883</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>713614912.9906199</v>
+        <v>673352286.50488782</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>118935818.83176999</v>
+        <v>134670457.30097756</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23791,6 +23785,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -24563,10 +24562,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -24593,7 +24592,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24628,7 +24627,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25627,13 +25626,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25836,11 +25835,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25848,6 +25842,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26620,10 +26619,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -26650,7 +26649,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26685,7 +26684,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27684,13 +27683,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27893,11 +27892,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27905,6 +27899,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 26 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 28 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1927,15 +1927,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1955,6 +1946,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3599,10 +3599,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4663,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4872,6 +4872,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4879,11 +4884,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5656,10 +5656,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6720,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6929,6 +6929,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6936,11 +6941,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7713,10 +7713,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8777,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8986,6 +8986,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8993,11 +8998,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9770,10 +9770,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10834,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11043,6 +11043,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11050,11 +11055,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11826,10 +11826,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12876,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13085,6 +13085,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13092,11 +13097,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,11 +21743,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>254512394.267885</v>
+        <v>261505850.983055</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>37644371.543454997</v>
+        <v>39834299.483455002</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21765,11 +21765,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>450163430.59335101</v>
+        <v>460708655.93333304</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>87396620.680083007</v>
+        <v>89648571.110073</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21777,27 +21777,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>245904663.37819701</v>
+        <v>267709411.18987799</v>
       </c>
       <c r="D10" s="205">
-        <v>30000486.200826</v>
+        <v>30690071.790826</v>
       </c>
       <c r="E10" s="205">
-        <v>135459239.519999</v>
+        <v>144475455.58999899</v>
       </c>
       <c r="F10" s="205">
-        <v>411364389.09902197</v>
+        <v>442874938.57070303</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>531463288.50028402</v>
+        <v>551699592.62628102</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>24103560.081103001</v>
+        <v>24607560.081103001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21805,16 +21805,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>328044269.38552397</v>
+        <v>333945247.25051302</v>
       </c>
       <c r="D11" s="205">
-        <v>83068874.754528001</v>
+        <v>87481053.135527998</v>
       </c>
       <c r="E11" s="205">
         <v>38843243.600000001</v>
       </c>
       <c r="F11" s="205">
-        <v>449956387.74005198</v>
+        <v>460269543.98604101</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -21825,7 +21825,7 @@
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>33550551.18</v>
+        <v>42787524.299999997</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -21833,27 +21833,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>244185492.48785701</v>
+        <v>253037024.127839</v>
       </c>
       <c r="D12" s="205">
-        <v>58807481.59025</v>
+        <v>60194868.990249999</v>
       </c>
       <c r="E12" s="205">
         <v>37261125.280000001</v>
       </c>
       <c r="F12" s="205">
-        <v>340254099.35810697</v>
+        <v>350493018.39808899</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>364392495.68195301</v>
+        <v>383595443.10745603</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>57646324.609319001</v>
+        <v>58946522.809318997</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21861,27 +21861,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>205977938.10549399</v>
+        <v>207671631.80549401</v>
       </c>
       <c r="D13" s="205">
-        <v>28589139.089832999</v>
+        <v>29453702.119823001</v>
       </c>
       <c r="E13" s="205">
-        <v>36852139.219999999</v>
+        <v>39320607.640000001</v>
       </c>
       <c r="F13" s="205">
-        <v>271419216.41532701</v>
+        <v>276445941.56531698</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>783530562.45213401</v>
+        <v>821190758.40247202</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>63122836.769892</v>
+        <v>63431836.769892</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21889,27 +21889,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>531463288.50028402</v>
+        <v>551699592.62628102</v>
       </c>
       <c r="D14" s="205">
-        <v>24103560.081103001</v>
+        <v>24607560.081103001</v>
       </c>
       <c r="E14" s="205">
-        <v>185618737.74000001</v>
+        <v>194345764.74000001</v>
       </c>
       <c r="F14" s="205">
-        <v>741185586.32138705</v>
+        <v>770652917.447384</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>333984691.930942</v>
+        <v>351566039.30800402</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>58336776.719756998</v>
+        <v>59619663.229754999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21925,11 +21925,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>328044269.38552397</v>
+        <v>333945247.25051302</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>83068874.754528001</v>
+        <v>87481053.135527998</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21937,27 +21937,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>364392495.68195301</v>
+        <v>383595443.10745603</v>
       </c>
       <c r="D16" s="205">
-        <v>57646324.609319001</v>
+        <v>58946522.809318997</v>
       </c>
       <c r="E16" s="205">
         <v>11608108</v>
       </c>
       <c r="F16" s="205">
-        <v>433646928.29127198</v>
+        <v>454150073.91677499</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>389025523.14936203</v>
+        <v>411824973.570301</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>52235612.639940999</v>
+        <v>54983063.089941002</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21968,24 +21968,24 @@
         <v>314350697.279998</v>
       </c>
       <c r="D17" s="205">
-        <v>33550551.18</v>
+        <v>42787524.299999997</v>
       </c>
       <c r="E17" s="205" t="s">
         <v>169</v>
       </c>
       <c r="F17" s="205">
-        <v>347901248.45999801</v>
+        <v>357138221.57999802</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>245904663.37819701</v>
+        <v>267709411.18987799</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>30000486.200826</v>
+        <v>30690071.790826</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21993,27 +21993,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>882983776.94476902</v>
+        <v>904424153.65476894</v>
       </c>
       <c r="D18" s="205">
-        <v>8619114.3119760007</v>
+        <v>9022114.3119760007</v>
       </c>
       <c r="E18" s="205">
-        <v>10706756.74</v>
+        <v>10606756.74</v>
       </c>
       <c r="F18" s="205">
-        <v>902309647.99674499</v>
+        <v>924053024.70674503</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>585538328.93634605</v>
+        <v>635176158.95366597</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>172859916.172685</v>
+        <v>176805862.07262501</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22021,27 +22021,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>783530562.45213401</v>
+        <v>821190758.40247202</v>
       </c>
       <c r="D19" s="205">
-        <v>63122836.769892</v>
+        <v>63431836.769892</v>
       </c>
       <c r="E19" s="205">
-        <v>599431298.08994305</v>
+        <v>626249765.80992699</v>
       </c>
       <c r="F19" s="205">
-        <v>1446084697.311969</v>
+        <v>1510872360.982291</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>202946310.76466301</v>
+        <v>218820355.124603</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>118446982.960512</v>
+        <v>124629971.040492</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22049,7 +22049,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>158951496.76466301</v>
+        <v>168132261.124603</v>
       </c>
       <c r="D20" s="205">
         <v>28556299.959775999</v>
@@ -22058,14 +22058,14 @@
         <v>3816216.3</v>
       </c>
       <c r="F20" s="205">
-        <v>191324013.02443901</v>
+        <v>200504777.384379</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
       <c r="J20" s="116"/>
       <c r="M20" s="14">
         <f>IFERROR(C31,0)+IFERROR(C15,0)+IFERROR(C36,0)</f>
-        <v>822000</v>
+        <v>301003631.99519998</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>120</v>
@@ -22076,23 +22076,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>43994814</v>
+        <v>50688094</v>
       </c>
       <c r="D21" s="205">
-        <v>89890683.000735998</v>
+        <v>96073671.080715999</v>
       </c>
       <c r="E21" s="205">
-        <v>48551352.280000001</v>
+        <v>48789190.119999997</v>
       </c>
       <c r="F21" s="205">
-        <v>182436849.280736</v>
+        <v>195550955.20071599</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>554303461.83272099</v>
+        <v>860938548.95787692</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22103,7 +22103,7 @@
         <v>173</v>
       </c>
       <c r="C22" s="205">
-        <v>211281605.80000001</v>
+        <v>196977845.80000001</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>169</v>
@@ -22112,7 +22112,7 @@
         <v>10814414.119999999</v>
       </c>
       <c r="F22" s="205">
-        <v>222096019.91999999</v>
+        <v>207792259.91999999</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -22129,10 +22129,10 @@
         <v>169</v>
       </c>
       <c r="E23" s="205">
-        <v>10300179.9</v>
+        <v>12516396.060000001</v>
       </c>
       <c r="F23" s="205">
-        <v>251761155.149975</v>
+        <v>253977371.309975</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22143,16 +22143,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>254512394.267885</v>
+        <v>261505850.983055</v>
       </c>
       <c r="D24" s="205">
-        <v>37644371.543454997</v>
+        <v>39834299.483455002</v>
       </c>
       <c r="E24" s="205">
-        <v>99482755.359999999</v>
+        <v>109538611.08</v>
       </c>
       <c r="F24" s="205">
-        <v>391639521.17133999</v>
+        <v>410878761.54650998</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22163,16 +22163,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>333984691.930942</v>
+        <v>351566039.30800402</v>
       </c>
       <c r="D25" s="205">
-        <v>58336776.719756998</v>
+        <v>59619663.229754999</v>
       </c>
       <c r="E25" s="205">
-        <v>208051531.43981999</v>
+        <v>220811891.94979501</v>
       </c>
       <c r="F25" s="205">
-        <v>600373000.09051895</v>
+        <v>631997594.48755395</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22183,16 +22183,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>389025523.14936203</v>
+        <v>411824973.570301</v>
       </c>
       <c r="D26" s="205">
-        <v>52235612.639940999</v>
+        <v>54983063.089941002</v>
       </c>
       <c r="E26" s="205">
-        <v>368505403.31984103</v>
+        <v>412972069.489811</v>
       </c>
       <c r="F26" s="205">
-        <v>809766539.10914397</v>
+        <v>879780106.15005302</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22203,16 +22203,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>585538328.93634605</v>
+        <v>635176158.95366597</v>
       </c>
       <c r="D27" s="205">
-        <v>172859916.172685</v>
+        <v>176805862.07262501</v>
       </c>
       <c r="E27" s="205">
-        <v>18025946.155999999</v>
+        <v>18458378.596000001</v>
       </c>
       <c r="F27" s="205">
-        <v>776424191.26503098</v>
+        <v>830440399.62229097</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22259,7 +22259,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>233726396.70464301</v>
+        <v>246996964.26461601</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22270,7 +22270,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>321596578.36200398</v>
+        <v>332754930.021882</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22281,7 +22281,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>269880090.13584203</v>
+        <v>276229671.38579899</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22292,7 +22292,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>283601371.69687903</v>
+        <v>283705245.57687801</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22303,7 +22303,7 @@
         <v>136</v>
       </c>
       <c r="C36" s="205">
-        <v>822000</v>
+        <v>301003631.99519998</v>
       </c>
       <c r="G36" s="116"/>
       <c r="H36" s="116"/>
@@ -22334,17 +22334,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="238" t="s">
+      <c r="B41" s="245" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="239"/>
-      <c r="D41" s="240"/>
+      <c r="C41" s="246"/>
+      <c r="D41" s="247"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.83870967741935487</v>
+        <v>0.90322580645161288</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>5236599237.3706141</v>
+        <v>5450532004.7795343</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.76566535495477173</v>
+        <v>0.7969453710242953</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>1602680094.6293859</v>
+        <v>1388747327.2204657</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>320536018.92587721</v>
+        <v>462915775.74015522</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>818412914.31210101</v>
+        <v>853465998.91300893</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.5547566110678539</v>
+        <v>0.57851714817645916</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>656851909.9082607</v>
+        <v>621798825.30735278</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>131370381.98165214</v>
+        <v>207266275.10245094</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,19 +22445,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1109626436.899368</v>
+        <v>1440690443.244375</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.62234418298651883</v>
+        <v>0.8080244729413556</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>673352286.50488782</v>
+        <v>342288280.15988088</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>134670457.30097756</v>
+        <v>114096093.38662696</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22472,19 +22472,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>7164638588.5820837</v>
+        <v>7744688446.9369183</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.70954417969572692</v>
+        <v>0.76698894761254865</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>2932884291.0425348</v>
+        <v>2352834432.6876993</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>586576858.20850694</v>
+        <v>784278144.22923315</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22505,10 +22505,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22593,35 +22593,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>254512394.267885</v>
+        <v>261505850.983055</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>37644371.543454997</v>
+        <v>39834299.483455002</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>292156765.81133997</v>
+        <v>301340150.46651</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.60244237303730996</v>
+        <v>0.621378987525121</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>162171083.732115</v>
+        <v>155177627.016945</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>30626029.677199312</v>
+        <v>28436101.737199306</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>192797113.40931433</v>
+        <v>183613728.75414431</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>38559422.681862868</v>
+        <v>61204576.251381435</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22645,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>450163430.59335101</v>
+        <v>460708655.93333304</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>87396620.680083007</v>
+        <v>89648571.110073</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>537560051.27343404</v>
+        <v>550357227.04340601</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.71988625015375762</v>
+        <v>0.7370238906011457</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>105018940.40664899</v>
+        <v>94473715.066666961</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>104150163.31991699</v>
+        <v>101898212.889927</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>209169103.72656596</v>
+        <v>196371927.95659399</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>41833820.74531319</v>
+        <v>65457309.318864666</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>211281605.80000001</v>
+        <v>196977845.80000001</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22705,15 +22705,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>211281605.80000001</v>
+        <v>196977845.80000001</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.87496892533876669</v>
+        <v>0.81573354860961256</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>30191662.199999988</v>
+        <v>44495422.199999988</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22721,11 +22721,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>30191662.199999988</v>
+        <v>44495422.199999988</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>6038332.4399999976</v>
+        <v>14831807.399999997</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,35 +22749,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>531463288.50028402</v>
+        <v>551699592.62628102</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>24103560.081103001</v>
+        <v>24607560.081103001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>555566848.58138704</v>
+        <v>576307152.70738399</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.84484742276591906</v>
+        <v>0.87638708812387278</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>79249183.499715984</v>
+        <v>59012879.373718977</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>22778266.73623189</v>
+        <v>22274266.73623189</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>102027450.23594785</v>
+        <v>81287146.1099509</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>20405490.047189571</v>
+        <v>27095715.369983632</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>33550551.18</v>
+        <v>42787524.299999997</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>347901248.45999801</v>
+        <v>357138221.57999802</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.71301087288787446</v>
+        <v>0.73194171115386675</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
@@ -22821,15 +22821,15 @@
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>49318764.011524148</v>
+        <v>40081790.891524151</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>140031350.73152614</v>
+        <v>130794377.61152613</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>28006270.146305226</v>
+        <v>43598125.870508708</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22853,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>364392495.68195301</v>
+        <v>383595443.10745603</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>57646324.609319001</v>
+        <v>58946522.809318997</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>422038820.29127204</v>
+        <v>442541965.91677505</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.76021357593650984</v>
+        <v>0.79714565162365492</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>109526336.31804699</v>
+        <v>90323388.892543972</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>23593069.513334602</v>
+        <v>22292871.313334607</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>133119405.83138156</v>
+        <v>112616260.20587856</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>26623881.166276313</v>
+        <v>37538753.401959516</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,35 +22905,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>783530562.45213401</v>
+        <v>821190758.40247202</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>63122836.769892</v>
+        <v>63431836.769892</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>846653399.22202599</v>
+        <v>884622595.172364</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.80351514484586517</v>
+        <v>0.83954975359101502</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>178227782.54786599</v>
+        <v>140567586.59752798</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>28805739.56926439</v>
+        <v>28496739.56926439</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>207033522.1171304</v>
+        <v>169064326.16679239</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>41406704.423426077</v>
+        <v>56354775.388930798</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,35 +22957,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>333984691.930942</v>
+        <v>351566039.30800402</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>58336776.719756998</v>
+        <v>59619663.229754999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>392321468.65069902</v>
+        <v>411185702.53775901</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.68940996410602184</v>
+        <v>0.72255928639953293</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>171302367.069058</v>
+        <v>153721019.69199598</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>5444627.2802430019</v>
+        <v>4161740.7702450007</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>176746994.34930098</v>
+        <v>157882760.46224099</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>35349398.869860195</v>
+        <v>52627586.820746996</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23037,7 +23037,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>32534537.750004999</v>
+        <v>54224229.583341666</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,35 +23061,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>328044269.38552397</v>
+        <v>333945247.25051302</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>83068874.754528001</v>
+        <v>87481053.135527998</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>411113144.14005196</v>
+        <v>421426300.38604105</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.75783781228506808</v>
+        <v>0.77684887986735851</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>75973039.614476025</v>
+        <v>70072061.749486983</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>55395515.463467404</v>
+        <v>50983337.082467407</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>131368555.07794344</v>
+        <v>121055398.83195436</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>26273711.01558869</v>
+        <v>40351799.610651456</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23113,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>389025523.14936203</v>
+        <v>411824973.570301</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>52235612.639940999</v>
+        <v>54983063.089941002</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>441261135.789303</v>
+        <v>466808036.66024202</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.63916504332114787</v>
+        <v>0.67616963012367015</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>242604072.85063797</v>
+        <v>219804622.429699</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>6505987.9706842676</v>
+        <v>3758537.5206842646</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>249110060.82132226</v>
+        <v>223563159.95038325</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>49822012.164264455</v>
+        <v>74521053.31679441</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23165,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>245904663.37819701</v>
+        <v>267709411.18987799</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>30000486.200826</v>
+        <v>30690071.790826</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>275905149.579023</v>
+        <v>298399482.98070401</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.61270431203670028</v>
+        <v>0.66265762060172828</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>140638359.62180299</v>
+        <v>118833611.81012201</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>33763668.598987803</v>
+        <v>33074083.008987807</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>174402028.2207908</v>
+        <v>151907694.8191098</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>34880405.644158162</v>
+        <v>50635898.273036599</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23217,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>585538328.93634605</v>
+        <v>635176158.95366597</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>172859916.172685</v>
+        <v>176805862.07262501</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>758398245.10903108</v>
+        <v>811982021.02629101</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.83052258093794407</v>
+        <v>0.88920222076860489</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>-2187386.9363460541</v>
+        <v>-51825216.953665972</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>156947028.82003239</v>
+        <v>153001082.92009237</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>154759641.8836863</v>
+        <v>101175865.96642637</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>30951928.376737259</v>
+        <v>33725288.65547546</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23269,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>202946310.76466301</v>
+        <v>218820355.124603</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>118446982.960512</v>
+        <v>124629971.040492</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>321393293.72517502</v>
+        <v>343450326.16509497</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.6210549783123378</v>
+        <v>0.6636776156574804</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>56579378.235336989</v>
+        <v>40705333.875396997</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>139523048.9473744</v>
+        <v>133340060.86739439</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>196102427.18271136</v>
+        <v>174045394.74279141</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>39220485.436542273</v>
+        <v>58015131.580930471</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>5236599237.3706141</v>
+        <v>5450532004.7795343</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>818412914.31210101</v>
+        <v>853465998.91300893</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>6055012151.6827154</v>
+        <v>6303998003.6925449</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.72824342957548394</v>
+        <v>0.7581892506970852</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>1602680094.6293859</v>
+        <v>1388747327.2204649</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>656851909.90826058</v>
+        <v>621798825.30735254</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>2259532004.5376463</v>
+        <v>2010546152.5278175</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>451906400.90752923</v>
+        <v>670182050.84260583</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>99482755.359999999</v>
+        <v>109538611.08</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23401,7 +23401,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>74113264.5</v>
+        <v>76581732.920000002</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>185618737.74000001</v>
+        <v>194345764.74000001</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>599431298.08994305</v>
+        <v>626249765.80992699</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>208051531.43981999</v>
+        <v>220811891.94979501</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="D78" s="192">
         <f>IF(E23="",0,E23)</f>
-        <v>10300179.9</v>
+        <v>12516396.060000001</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>368505403.31984103</v>
+        <v>412972069.489811</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>135459239.519999</v>
+        <v>144475455.58999899</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23533,7 +23533,7 @@
       </c>
       <c r="D82" s="192">
         <f>IF(E27="",0,E27)</f>
-        <v>18025946.155999999</v>
+        <v>18458378.596000001</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>52367568.579999998</v>
+        <v>52605406.419999994</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1812621690.3256028</v>
+        <v>1929821238.3755317</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23569,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23617,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>233726396.70464301</v>
+        <v>246996964.26461601</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.84054705868820534</v>
+        <v>0.88827182014830797</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>44338221.199566543</v>
+        <v>31067653.639593542</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>8867644.239913309</v>
+        <v>10355884.54653118</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>321596578.36200398</v>
+        <v>332754930.021882</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.77007253606946158</v>
+        <v>0.79679153975054162</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>96021974.824517608</v>
+        <v>84863623.164639592</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>19204394.964903522</v>
+        <v>28287874.388213199</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>554303461.83272099</v>
+        <v>860938548.95787692</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.50980017406792999</v>
+        <v>0.79181649104145591</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>532992090.48080373</v>
+        <v>226357003.3556478</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>106598418.09616074</v>
+        <v>75452334.451882601</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,24 +23760,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>1109626436.899368</v>
+        <v>1440690443.244375</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.62234418298651883</v>
+        <v>0.8080244729413556</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>673352286.50488782</v>
+        <v>342288280.15988094</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>134670457.30097756</v>
+        <v>114096093.38662697</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23785,11 +23790,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -24562,10 +24562,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24627,7 +24627,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25626,13 +25626,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25835,6 +25835,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25842,11 +25847,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26619,10 +26619,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -26649,7 +26649,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26684,7 +26684,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27683,13 +27683,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27892,6 +27892,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27899,11 +27904,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 28 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 29 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -21661,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,11 +21743,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>261505850.983055</v>
+        <v>277572338.92065102</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>39834299.483455002</v>
+        <v>42987072.443455003</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21765,11 +21765,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>460708655.93333304</v>
+        <v>491408712.98569405</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>89648571.110073</v>
+        <v>95115098.150067002</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21777,27 +21777,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>267709411.18987799</v>
+        <v>284653659.37129903</v>
       </c>
       <c r="D10" s="205">
-        <v>30690071.790826</v>
+        <v>32538666.405825999</v>
       </c>
       <c r="E10" s="205">
-        <v>144475455.58999899</v>
+        <v>160988067.75999901</v>
       </c>
       <c r="F10" s="205">
-        <v>442874938.57070303</v>
+        <v>478180393.53712398</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>551699592.62628102</v>
+        <v>601791552.94577396</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>24607560.081103001</v>
+        <v>24913073.601101998</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21805,16 +21805,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>333945247.25051302</v>
+        <v>360481445.10647702</v>
       </c>
       <c r="D11" s="205">
-        <v>87481053.135527998</v>
+        <v>90194350.395528004</v>
       </c>
       <c r="E11" s="205">
         <v>38843243.600000001</v>
       </c>
       <c r="F11" s="205">
-        <v>460269543.98604101</v>
+        <v>489519039.102005</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -21833,27 +21833,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>253037024.127839</v>
+        <v>265036672.84783801</v>
       </c>
       <c r="D12" s="205">
-        <v>60194868.990249999</v>
+        <v>62694125.750248998</v>
       </c>
       <c r="E12" s="205">
-        <v>37261125.280000001</v>
+        <v>37747611.759999998</v>
       </c>
       <c r="F12" s="205">
-        <v>350493018.39808899</v>
+        <v>365478410.358087</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>383595443.10745603</v>
+        <v>401012002.879605</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>58946522.809318997</v>
+        <v>60954054.369306996</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21861,27 +21861,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>207671631.80549401</v>
+        <v>226372040.13785601</v>
       </c>
       <c r="D13" s="205">
-        <v>29453702.119823001</v>
+        <v>32420972.399817999</v>
       </c>
       <c r="E13" s="205">
-        <v>39320607.640000001</v>
+        <v>40862296.799999997</v>
       </c>
       <c r="F13" s="205">
-        <v>276445941.56531698</v>
+        <v>299655309.33767402</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>821190758.40247202</v>
+        <v>985018350.45224202</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>63431836.769892</v>
+        <v>73190755.369811997</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21889,27 +21889,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>551699592.62628102</v>
+        <v>601791552.94577396</v>
       </c>
       <c r="D14" s="205">
-        <v>24607560.081103001</v>
+        <v>24913073.601101998</v>
       </c>
       <c r="E14" s="205">
-        <v>194345764.74000001</v>
+        <v>212275674.66999999</v>
       </c>
       <c r="F14" s="205">
-        <v>770652917.447384</v>
+        <v>838980301.21687603</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>351566039.30800402</v>
+        <v>377190190.04997498</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>59619663.229754999</v>
+        <v>67775158.759754002</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21925,11 +21925,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>333945247.25051302</v>
+        <v>360481445.10647702</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>87481053.135527998</v>
+        <v>90194350.395528004</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21937,27 +21937,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>383595443.10745603</v>
+        <v>401012002.879605</v>
       </c>
       <c r="D16" s="205">
-        <v>58946522.809318997</v>
+        <v>60954054.369306996</v>
       </c>
       <c r="E16" s="205">
-        <v>11608108</v>
+        <v>11908108</v>
       </c>
       <c r="F16" s="205">
-        <v>454150073.91677499</v>
+        <v>473874165.24891198</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>411824973.570301</v>
+        <v>434780667.167575</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>54983063.089941002</v>
+        <v>55655063.089941002</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21981,11 +21981,11 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>267709411.18987799</v>
+        <v>284653659.37129903</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>30690071.790826</v>
+        <v>32538666.405825999</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21993,27 +21993,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>904424153.65476894</v>
+        <v>925109213.55476904</v>
       </c>
       <c r="D18" s="205">
-        <v>9022114.3119760007</v>
+        <v>9312204.4019750003</v>
       </c>
       <c r="E18" s="205">
-        <v>10606756.74</v>
+        <v>11243243.220000001</v>
       </c>
       <c r="F18" s="205">
-        <v>924053024.70674503</v>
+        <v>945664661.17674398</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>635176158.95366597</v>
+        <v>667336640.85745704</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>176805862.07262501</v>
+        <v>179744789.15262499</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22021,27 +22021,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>821190758.40247202</v>
+        <v>985018350.45224202</v>
       </c>
       <c r="D19" s="205">
-        <v>63431836.769892</v>
+        <v>73190755.369811997</v>
       </c>
       <c r="E19" s="205">
-        <v>626249765.80992699</v>
+        <v>634030850.76992702</v>
       </c>
       <c r="F19" s="205">
-        <v>1510872360.982291</v>
+        <v>1692239956.5919809</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>218820355.124603</v>
+        <v>237899949.77078599</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>124629971.040492</v>
+        <v>128164709.80047999</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22049,7 +22049,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>168132261.124603</v>
+        <v>177226855.77078599</v>
       </c>
       <c r="D20" s="205">
         <v>28556299.959775999</v>
@@ -22058,7 +22058,7 @@
         <v>3816216.3</v>
       </c>
       <c r="F20" s="205">
-        <v>200504777.384379</v>
+        <v>209599372.03056201</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22076,23 +22076,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>50688094</v>
+        <v>60673094</v>
       </c>
       <c r="D21" s="205">
-        <v>96073671.080715999</v>
+        <v>99608409.840703994</v>
       </c>
       <c r="E21" s="205">
-        <v>48789190.119999997</v>
+        <v>69318920.239999995</v>
       </c>
       <c r="F21" s="205">
-        <v>195550955.20071599</v>
+        <v>229600424.080704</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>860938548.95787692</v>
+        <v>935920708.75692701</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22129,10 +22129,10 @@
         <v>169</v>
       </c>
       <c r="E23" s="205">
-        <v>12516396.060000001</v>
+        <v>13813693.32</v>
       </c>
       <c r="F23" s="205">
-        <v>253977371.309975</v>
+        <v>255274668.56997499</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22143,16 +22143,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>261505850.983055</v>
+        <v>277572338.92065102</v>
       </c>
       <c r="D24" s="205">
-        <v>39834299.483455002</v>
+        <v>42987072.443455003</v>
       </c>
       <c r="E24" s="205">
-        <v>109538611.08</v>
+        <v>117989061.36</v>
       </c>
       <c r="F24" s="205">
-        <v>410878761.54650998</v>
+        <v>438548472.72410601</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22163,16 +22163,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>351566039.30800402</v>
+        <v>377190190.04997498</v>
       </c>
       <c r="D25" s="205">
-        <v>59619663.229754999</v>
+        <v>67775158.759754002</v>
       </c>
       <c r="E25" s="205">
-        <v>220811891.94979501</v>
+        <v>235065044.80979499</v>
       </c>
       <c r="F25" s="205">
-        <v>631997594.48755395</v>
+        <v>680030393.619524</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22183,16 +22183,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>411824973.570301</v>
+        <v>434780667.167575</v>
       </c>
       <c r="D26" s="205">
-        <v>54983063.089941002</v>
+        <v>55655063.089941002</v>
       </c>
       <c r="E26" s="205">
-        <v>412972069.489811</v>
+        <v>446908556.76973099</v>
       </c>
       <c r="F26" s="205">
-        <v>879780106.15005302</v>
+        <v>937344287.02724695</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22203,16 +22203,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>635176158.95366597</v>
+        <v>667336640.85745704</v>
       </c>
       <c r="D27" s="205">
-        <v>176805862.07262501</v>
+        <v>179744789.15262499</v>
       </c>
       <c r="E27" s="205">
         <v>18458378.596000001</v>
       </c>
       <c r="F27" s="205">
-        <v>830440399.62229097</v>
+        <v>865539808.60608196</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22259,7 +22259,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>246996964.26461601</v>
+        <v>276131649.54051697</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22270,7 +22270,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>332754930.021882</v>
+        <v>412946038.37677097</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22281,7 +22281,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>276229671.38579899</v>
+        <v>277029671.38579899</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22292,7 +22292,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>283705245.57687801</v>
+        <v>357887405.37592798</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22344,7 +22344,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.90322580645161288</v>
+        <v>0.93548387096774188</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>5450532004.7795343</v>
+        <v>5871935028.8375082</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.7969453710242953</v>
+        <v>0.85856049209213792</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>1388747327.2204657</v>
+        <v>967344303.1624918</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>462915775.74015522</v>
+        <v>483672151.5812459</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>853465998.91300893</v>
+        <v>894020315.83789694</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.57851714817645916</v>
+        <v>0.60600666481040988</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>621798825.30735278</v>
+        <v>581244508.38246477</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>207266275.10245094</v>
+        <v>290622254.19123238</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,19 +22445,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1440690443.244375</v>
+        <v>1624998396.6742148</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.8080244729413556</v>
+        <v>0.91139528214424914</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>342288280.15988088</v>
+        <v>157980326.73004103</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>114096093.38662696</v>
+        <v>78990163.365020514</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22472,19 +22472,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>7744688446.9369183</v>
+        <v>8390953741.3496208</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.76698894761254865</v>
+        <v>0.83099130760885775</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>2352834432.6876993</v>
+        <v>1706569138.2749977</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>784278144.22923315</v>
+        <v>853284569.13749886</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22593,35 +22593,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>261505850.983055</v>
+        <v>277572338.92065102</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>39834299.483455002</v>
+        <v>42987072.443455003</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>301340150.46651</v>
+        <v>320559411.364106</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.621378987525121</v>
+        <v>0.66101009827833812</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>155177627.016945</v>
+        <v>139111139.07934898</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>28436101.737199306</v>
+        <v>25283328.777199306</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>183613728.75414431</v>
+        <v>164394467.85654831</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>61204576.251381435</v>
+        <v>82197233.928274155</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22645,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>460708655.93333304</v>
+        <v>491408712.98569405</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>89648571.110073</v>
+        <v>95115098.150067002</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>550357227.04340601</v>
+        <v>586523811.13576102</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.7370238906011457</v>
+        <v>0.78545722663763007</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>94473715.066666961</v>
+        <v>63773658.014305949</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>101898212.889927</v>
+        <v>96431685.849932998</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>196371927.95659399</v>
+        <v>160205343.86423898</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>65457309.318864666</v>
+        <v>80102671.932119489</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22725,7 +22725,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>14831807.399999997</v>
+        <v>22247711.099999994</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,35 +22749,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>551699592.62628102</v>
+        <v>601791552.94577396</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>24607560.081103001</v>
+        <v>24913073.601101998</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>576307152.70738399</v>
+        <v>626704626.54687595</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.87638708812387278</v>
+        <v>0.95302624684244808</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>59012879.373718977</v>
+        <v>8920919.0542260408</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>22274266.73623189</v>
+        <v>21968753.216232892</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>81287146.1099509</v>
+        <v>30889672.270458937</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>27095715.369983632</v>
+        <v>15444836.135229468</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>43598125.870508708</v>
+        <v>65397188.805763066</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22853,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>383595443.10745603</v>
+        <v>401012002.879605</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>58946522.809318997</v>
+        <v>60954054.369306996</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>442541965.91677505</v>
+        <v>461966057.24891198</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.79714565162365492</v>
+        <v>0.83213403947084397</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>90323388.892543972</v>
+        <v>72906829.120395005</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>22292871.313334607</v>
+        <v>20285339.753346607</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>112616260.20587856</v>
+        <v>93192168.873741627</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>37538753.401959516</v>
+        <v>46596084.436870813</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,35 +22905,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>821190758.40247202</v>
+        <v>985018350.45224202</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>63431836.769892</v>
+        <v>73190755.369811997</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>884622595.172364</v>
+        <v>1058209105.822054</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.83954975359101502</v>
+        <v>1.0042917724338367</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>140567586.59752798</v>
+        <v>-23260005.452242017</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>28496739.56926439</v>
+        <v>18737820.969344392</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>169064326.16679239</v>
+        <v>-4522184.4828976393</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>56354775.388930798</v>
+        <v>-2261092.2414488196</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,35 +22957,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>351566039.30800402</v>
+        <v>377190190.04997498</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>59619663.229754999</v>
+        <v>67775158.759754002</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>411185702.53775901</v>
+        <v>444965348.80972898</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.72255928639953293</v>
+        <v>0.78191883356876335</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>153721019.69199598</v>
+        <v>128096868.95002502</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>4161740.7702450007</v>
+        <v>-3993754.7597540021</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>157882760.46224099</v>
+        <v>124103114.19027102</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>52627586.820746996</v>
+        <v>62051557.09513551</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23037,7 +23037,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>54224229.583341666</v>
+        <v>81336344.375012502</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,35 +23061,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>333945247.25051302</v>
+        <v>360481445.10647702</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>87481053.135527998</v>
+        <v>90194350.395528004</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>421426300.38604105</v>
+        <v>450675795.50200504</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.77684887986735851</v>
+        <v>0.83076681877318348</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>70072061.749486983</v>
+        <v>43535863.893522978</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>50983337.082467407</v>
+        <v>48270039.822467402</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>121055398.83195436</v>
+        <v>91805903.715990365</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>40351799.610651456</v>
+        <v>45902951.857995182</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23113,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>411824973.570301</v>
+        <v>434780667.167575</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>54983063.089941002</v>
+        <v>55655063.089941002</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>466808036.66024202</v>
+        <v>490435730.25751603</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.67616963012367015</v>
+        <v>0.71039425263584044</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>219804622.429699</v>
+        <v>196848928.832425</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>3758537.5206842646</v>
+        <v>3086537.5206842646</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>223563159.95038325</v>
+        <v>199935466.35310924</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>74521053.31679441</v>
+        <v>99967733.17655462</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23165,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>267709411.18987799</v>
+        <v>284653659.37129903</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>30690071.790826</v>
+        <v>32538666.405825999</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>298399482.98070401</v>
+        <v>317192325.777125</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.66265762060172828</v>
+        <v>0.70439100555073619</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>118833611.81012201</v>
+        <v>101889363.62870097</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>33074083.008987807</v>
+        <v>31225488.393987808</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>151907694.8191098</v>
+        <v>133114852.02268881</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>50635898.273036599</v>
+        <v>66557426.011344403</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23217,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>635176158.95366597</v>
+        <v>667336640.85745704</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>176805862.07262501</v>
+        <v>179744789.15262499</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>811982021.02629101</v>
+        <v>847081430.01008201</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.88920222076860489</v>
+        <v>0.92763961421803676</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>-51825216.953665972</v>
+        <v>-83985698.857457042</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>153001082.92009237</v>
+        <v>150062155.84009239</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>101175865.96642637</v>
+        <v>66076456.982635379</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>33725288.65547546</v>
+        <v>33038228.491317689</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23269,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>218820355.124603</v>
+        <v>237899949.77078599</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>124629971.040492</v>
+        <v>128164709.80047999</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>343450326.16509497</v>
+        <v>366064659.571266</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.6636776156574804</v>
+        <v>0.70737717198713812</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>40705333.875396997</v>
+        <v>21625739.229214013</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>133340060.86739439</v>
+        <v>129805322.10740639</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>174045394.74279141</v>
+        <v>151431061.33662039</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>58015131.580930471</v>
+        <v>75715530.668310195</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>5450532004.7795343</v>
+        <v>5871935028.8375082</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>853465998.91300893</v>
+        <v>894020315.83789694</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>6303998003.6925449</v>
+        <v>6765955344.6754055</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.7581892506970852</v>
+        <v>0.81374940316043531</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>1388747327.2204649</v>
+        <v>967344303.1624918</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>621798825.30735254</v>
+        <v>581244508.38246453</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>2010546152.5278175</v>
+        <v>1548588811.5449567</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>670182050.84260583</v>
+        <v>774294405.77247834</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>109538611.08</v>
+        <v>117989061.36</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23401,7 +23401,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>76581732.920000002</v>
+        <v>78609908.560000002</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>194345764.74000001</v>
+        <v>212275674.66999999</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23449,7 +23449,7 @@
       </c>
       <c r="D75" s="192">
         <f>IF(E16="",0,E16)</f>
-        <v>11608108</v>
+        <v>11908108</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>626249765.80992699</v>
+        <v>634030850.76992702</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>220811891.94979501</v>
+        <v>235065044.80979499</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="D78" s="192">
         <f>IF(E23="",0,E23)</f>
-        <v>12516396.060000001</v>
+        <v>13813693.32</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>412972069.489811</v>
+        <v>446908556.76973099</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>144475455.58999899</v>
+        <v>160988067.75999901</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>52605406.419999994</v>
+        <v>73135136.539999992</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1929821238.3755317</v>
+        <v>2052840138.8754518</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23617,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>246996964.26461601</v>
+        <v>276131649.54051697</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.88827182014830797</v>
+        <v>0.99304849218767388</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>31067653.639593542</v>
+        <v>1932968.3636925817</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>10355884.54653118</v>
+        <v>966484.18184629083</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>332754930.021882</v>
+        <v>412946038.37677097</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.79679153975054162</v>
+        <v>0.9888115248374425</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>84863623.164639592</v>
+        <v>4672514.8097506166</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>28287874.388213199</v>
+        <v>2336257.4048753083</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>860938548.95787692</v>
+        <v>935920708.75692701</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.79181649104145591</v>
+        <v>0.86077856822415444</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>226357003.3556478</v>
+        <v>151374843.55659771</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>75452334.451882601</v>
+        <v>75687421.778298855</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,19 +23760,19 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>1440690443.244375</v>
+        <v>1624998396.6742148</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.8080244729413556</v>
+        <v>0.91139528214424914</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>342288280.15988094</v>
+        <v>157980326.73004091</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>114096093.38662697</v>
+        <v>78990163.365020454</v>
       </c>
       <c r="I94" s="116"/>
     </row>

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 29 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1927,6 +1927,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1946,15 +1955,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3599,10 +3599,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4663,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4872,11 +4872,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4884,6 +4879,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5656,10 +5656,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6720,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6929,11 +6929,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6941,6 +6936,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7713,10 +7713,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8777,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8986,11 +8986,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8998,6 +8993,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9770,10 +9770,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10834,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11043,11 +11043,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11055,6 +11050,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11826,10 +11826,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12876,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13085,11 +13085,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13097,6 +13092,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,11 +21743,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>277572338.92065102</v>
+        <v>288424016.78064901</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>42987072.443455003</v>
+        <v>44585739.113441996</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21765,11 +21765,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>491408712.98569405</v>
+        <v>514873412.84566295</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>95115098.150067002</v>
+        <v>95906107.167067006</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21777,27 +21777,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>284653659.37129903</v>
+        <v>297882183.23181498</v>
       </c>
       <c r="D10" s="205">
-        <v>32538666.405825999</v>
+        <v>34050666.405826002</v>
       </c>
       <c r="E10" s="205">
-        <v>160988067.75999901</v>
+        <v>162788612.639999</v>
       </c>
       <c r="F10" s="205">
-        <v>478180393.53712398</v>
+        <v>494721462.27763999</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>601791552.94577396</v>
+        <v>670664362.43227303</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>24913073.601101998</v>
+        <v>27278643.871089</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21805,16 +21805,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>360481445.10647702</v>
+        <v>374466810.62618703</v>
       </c>
       <c r="D11" s="205">
-        <v>90194350.395528004</v>
+        <v>92402940.934527993</v>
       </c>
       <c r="E11" s="205">
-        <v>38843243.600000001</v>
+        <v>40868468.799999997</v>
       </c>
       <c r="F11" s="205">
-        <v>489519039.102005</v>
+        <v>507738220.36071497</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -21833,27 +21833,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>265036672.84783801</v>
+        <v>278227678.91783297</v>
       </c>
       <c r="D12" s="205">
-        <v>62694125.750248998</v>
+        <v>62708999.627249002</v>
       </c>
       <c r="E12" s="205">
-        <v>37747611.759999998</v>
+        <v>52162025.759999998</v>
       </c>
       <c r="F12" s="205">
-        <v>365478410.358087</v>
+        <v>393098704.30508202</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>401012002.879605</v>
+        <v>413013469.09840298</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>60954054.369306996</v>
+        <v>61457252.569306999</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21861,23 +21861,23 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>226372040.13785601</v>
+        <v>236645733.92783001</v>
       </c>
       <c r="D13" s="205">
-        <v>32420972.399817999</v>
+        <v>33197107.539818</v>
       </c>
       <c r="E13" s="205">
-        <v>40862296.799999997</v>
+        <v>41510945.439999998</v>
       </c>
       <c r="F13" s="205">
-        <v>299655309.33767402</v>
+        <v>311353786.90764803</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>985018350.45224202</v>
+        <v>1005613301.6380841</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
@@ -21889,27 +21889,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>601791552.94577396</v>
+        <v>670664362.43227303</v>
       </c>
       <c r="D14" s="205">
-        <v>24913073.601101998</v>
+        <v>27278643.871089</v>
       </c>
       <c r="E14" s="205">
-        <v>212275674.66999999</v>
+        <v>260324322.93000001</v>
       </c>
       <c r="F14" s="205">
-        <v>838980301.21687603</v>
+        <v>958267329.23336196</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>377190190.04997498</v>
+        <v>389875776.90495598</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>67775158.759754002</v>
+        <v>68378257.859753996</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21925,11 +21925,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>360481445.10647702</v>
+        <v>374466810.62618703</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>90194350.395528004</v>
+        <v>92402940.934527993</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21937,27 +21937,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>401012002.879605</v>
+        <v>413013469.09840298</v>
       </c>
       <c r="D16" s="205">
-        <v>60954054.369306996</v>
+        <v>61457252.569306999</v>
       </c>
       <c r="E16" s="205">
-        <v>11908108</v>
+        <v>14439639.5</v>
       </c>
       <c r="F16" s="205">
-        <v>473874165.24891198</v>
+        <v>488910361.16771001</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>434780667.167575</v>
+        <v>454249976.114806</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>55655063.089941002</v>
+        <v>58885063.089941002</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21981,11 +21981,11 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>284653659.37129903</v>
+        <v>297882183.23181498</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>32538666.405825999</v>
+        <v>34050666.405826002</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21993,27 +21993,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>925109213.55476904</v>
+        <v>976940398.98976696</v>
       </c>
       <c r="D18" s="205">
-        <v>9312204.4019750003</v>
+        <v>11562280.951971</v>
       </c>
       <c r="E18" s="205">
-        <v>11243243.220000001</v>
+        <v>11405405.380000001</v>
       </c>
       <c r="F18" s="205">
-        <v>945664661.17674398</v>
+        <v>999908085.321738</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>667336640.85745704</v>
+        <v>686645252.87729704</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>179744789.15262499</v>
+        <v>191906951.15242499</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22021,27 +22021,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>985018350.45224202</v>
+        <v>1005613301.6380841</v>
       </c>
       <c r="D19" s="205">
         <v>73190755.369811997</v>
       </c>
       <c r="E19" s="205">
-        <v>634030850.76992702</v>
+        <v>709237967.049927</v>
       </c>
       <c r="F19" s="205">
-        <v>1692239956.5919809</v>
+        <v>1788042024.0578229</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>237899949.77078599</v>
+        <v>298336622.32828599</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>128164709.80047999</v>
+        <v>128847592.67048</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22049,23 +22049,23 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>177226855.77078599</v>
+        <v>234281528.32828599</v>
       </c>
       <c r="D20" s="205">
-        <v>28556299.959775999</v>
+        <v>28741885.549775999</v>
       </c>
       <c r="E20" s="205">
         <v>3816216.3</v>
       </c>
       <c r="F20" s="205">
-        <v>209599372.03056201</v>
+        <v>266839630.17806199</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
       <c r="J20" s="116"/>
       <c r="M20" s="14">
         <f>IFERROR(C31,0)+IFERROR(C15,0)+IFERROR(C36,0)</f>
-        <v>301003631.99519998</v>
+        <v>296173392</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>120</v>
@@ -22076,23 +22076,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>60673094</v>
+        <v>64055094</v>
       </c>
       <c r="D21" s="205">
-        <v>99608409.840703994</v>
+        <v>100105707.120704</v>
       </c>
       <c r="E21" s="205">
-        <v>69318920.239999995</v>
+        <v>79070271.780000001</v>
       </c>
       <c r="F21" s="205">
-        <v>229600424.080704</v>
+        <v>243231072.900704</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>935920708.75692701</v>
+        <v>945630576.91965699</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22103,16 +22103,16 @@
         <v>173</v>
       </c>
       <c r="C22" s="205">
-        <v>196977845.80000001</v>
+        <v>197567845.80000001</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>169</v>
       </c>
       <c r="E22" s="205">
-        <v>10814414.119999999</v>
+        <v>12832432.08</v>
       </c>
       <c r="F22" s="205">
-        <v>207792259.91999999</v>
+        <v>210400277.88</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -22123,7 +22123,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="205">
-        <v>241460975.249975</v>
+        <v>300521523.82997501</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>169</v>
@@ -22132,7 +22132,7 @@
         <v>13813693.32</v>
       </c>
       <c r="F23" s="205">
-        <v>255274668.56997499</v>
+        <v>314335217.149975</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22143,16 +22143,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>277572338.92065102</v>
+        <v>288424016.78064901</v>
       </c>
       <c r="D24" s="205">
-        <v>42987072.443455003</v>
+        <v>44585739.113441996</v>
       </c>
       <c r="E24" s="205">
-        <v>117989061.36</v>
+        <v>126214286.45999999</v>
       </c>
       <c r="F24" s="205">
-        <v>438548472.72410601</v>
+        <v>459224042.35409099</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22163,16 +22163,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>377190190.04997498</v>
+        <v>389875776.90495598</v>
       </c>
       <c r="D25" s="205">
-        <v>67775158.759754002</v>
+        <v>68378257.859753996</v>
       </c>
       <c r="E25" s="205">
-        <v>235065044.80979499</v>
+        <v>247976756.949745</v>
       </c>
       <c r="F25" s="205">
-        <v>680030393.619524</v>
+        <v>706230791.71445501</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22183,16 +22183,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>434780667.167575</v>
+        <v>454249976.114806</v>
       </c>
       <c r="D26" s="205">
-        <v>55655063.089941002</v>
+        <v>58885063.089941002</v>
       </c>
       <c r="E26" s="205">
-        <v>446908556.76973099</v>
+        <v>469103962.04973102</v>
       </c>
       <c r="F26" s="205">
-        <v>937344287.02724695</v>
+        <v>982239001.25447798</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22203,16 +22203,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>667336640.85745704</v>
+        <v>686645252.87729704</v>
       </c>
       <c r="D27" s="205">
-        <v>179744789.15262499</v>
+        <v>191906951.15242499</v>
       </c>
       <c r="E27" s="205">
-        <v>18458378.596000001</v>
+        <v>19182702.936000001</v>
       </c>
       <c r="F27" s="205">
-        <v>865539808.60608196</v>
+        <v>897734906.96572196</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22259,7 +22259,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>276131649.54051697</v>
+        <v>291427595.82048202</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22270,7 +22270,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>412946038.37677097</v>
+        <v>436148035.92440403</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22281,7 +22281,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>277029671.38579899</v>
+        <v>135628039.89320499</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22292,7 +22292,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>357887405.37592798</v>
+        <v>513829145.026452</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22303,7 +22303,7 @@
         <v>136</v>
       </c>
       <c r="C36" s="205">
-        <v>301003631.99519998</v>
+        <v>296173392</v>
       </c>
       <c r="G36" s="116"/>
       <c r="H36" s="116"/>
@@ -22334,17 +22334,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="245" t="s">
+      <c r="B41" s="238" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="246"/>
-      <c r="D41" s="247"/>
+      <c r="C41" s="239"/>
+      <c r="D41" s="240"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.93548387096774188</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>5871935028.8375082</v>
+        <v>6206485251.788393</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.85856049209213792</v>
+        <v>0.90747649723109647</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>967344303.1624918</v>
+        <v>632794080.21160698</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>483672151.5812459</v>
+        <v>632794080.21160698</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>894020315.83789694</v>
+        <v>919677494.50367093</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.60600666481040988</v>
+        <v>0.62339823969550423</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>581244508.38246477</v>
+        <v>555587329.71669078</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>290622254.19123238</v>
+        <v>555587329.71669078</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,19 +22445,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1624998396.6742148</v>
+        <v>1673206208.6645432</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.91139528214424914</v>
+        <v>0.93843307645863372</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>157980326.73004103</v>
+        <v>109772514.73971272</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>78990163.365020514</v>
+        <v>109772514.73971272</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22472,19 +22472,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>8390953741.3496208</v>
+        <v>8799368954.9566078</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.83099130760885775</v>
+        <v>0.87143837749677178</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>1706569138.2749977</v>
+        <v>1298153924.6680105</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>853284569.13749886</v>
+        <v>1298153924.6680105</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22505,10 +22505,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22593,35 +22593,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>277572338.92065102</v>
+        <v>288424016.78064901</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>42987072.443455003</v>
+        <v>44585739.113441996</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>320559411.364106</v>
+        <v>333009755.89409101</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.66101009827833812</v>
+        <v>0.68668335312474404</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>139111139.07934898</v>
+        <v>128259461.21935099</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>25283328.777199306</v>
+        <v>23684662.107212313</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>164394467.85654831</v>
+        <v>151944123.3265633</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>82197233.928274155</v>
+        <v>151944123.3265633</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22645,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>491408712.98569405</v>
+        <v>514873412.84566295</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>95115098.150067002</v>
+        <v>95906107.167067006</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>586523811.13576102</v>
+        <v>610779520.01273</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.78545722663763007</v>
+        <v>0.81793983256583846</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>63773658.014305949</v>
+        <v>40308958.154337049</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>96431685.849932998</v>
+        <v>95640676.832932994</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>160205343.86423898</v>
+        <v>135949634.98727</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>80102671.932119489</v>
+        <v>135949634.98727</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>196977845.80000001</v>
+        <v>197567845.80000001</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22705,15 +22705,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>196977845.80000001</v>
+        <v>197567845.80000001</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.81573354860961256</v>
+        <v>0.81817688324821114</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>44495422.199999988</v>
+        <v>43905422.199999988</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22721,11 +22721,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>44495422.199999988</v>
+        <v>43905422.199999988</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>22247711.099999994</v>
+        <v>43905422.199999988</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,35 +22749,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>601791552.94577396</v>
+        <v>670664362.43227303</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>24913073.601101998</v>
+        <v>27278643.871089</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>626704626.54687595</v>
+        <v>697943006.30336201</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.95302624684244808</v>
+        <v>1.0613580555041204</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>8920919.0542260408</v>
+        <v>-59951890.43227303</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>21968753.216232892</v>
+        <v>19603182.94624589</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>30889672.270458937</v>
+        <v>-40348707.486027122</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>15444836.135229468</v>
+        <v>-40348707.486027122</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>65397188.805763066</v>
+        <v>130794377.61152613</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22853,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>401012002.879605</v>
+        <v>413013469.09840298</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>60954054.369306996</v>
+        <v>61457252.569306999</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>461966057.24891198</v>
+        <v>474470721.66770995</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.83213403947084397</v>
+        <v>0.85465854479274705</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>72906829.120395005</v>
+        <v>60905362.901597023</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>20285339.753346607</v>
+        <v>19782141.553346604</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>93192168.873741627</v>
+        <v>80687504.454943657</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>46596084.436870813</v>
+        <v>80687504.454943657</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>985018350.45224202</v>
+        <v>1005613301.6380841</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
@@ -22913,15 +22913,15 @@
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>1058209105.822054</v>
+        <v>1078804057.0078959</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>1.0042917724338367</v>
+        <v>1.0238373801174427</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>-23260005.452242017</v>
+        <v>-43854956.638084054</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
@@ -22929,11 +22929,11 @@
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>-4522184.4828976393</v>
+        <v>-25117135.668739557</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-2261092.2414488196</v>
+        <v>-25117135.668739557</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,35 +22957,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>377190190.04997498</v>
+        <v>389875776.90495598</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>67775158.759754002</v>
+        <v>68378257.859753996</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>444965348.80972898</v>
+        <v>458254034.76470995</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.78191883356876335</v>
+        <v>0.805270480723705</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>128096868.95002502</v>
+        <v>115411282.09504402</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>-3993754.7597540021</v>
+        <v>-4596853.8597539961</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>124103114.19027102</v>
+        <v>110814428.23529005</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>62051557.09513551</v>
+        <v>110814428.23529005</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>241460975.249975</v>
+        <v>300521523.82997501</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23017,15 +23017,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>241460975.249975</v>
+        <v>300521523.82997501</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.59747800482657887</v>
+        <v>0.74361913050127648</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>162672688.750025</v>
+        <v>103612140.17002499</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23033,11 +23033,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>162672688.750025</v>
+        <v>103612140.17002499</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>81336344.375012502</v>
+        <v>103612140.17002499</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,35 +23061,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>360481445.10647702</v>
+        <v>374466810.62618703</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>90194350.395528004</v>
+        <v>92402940.934527993</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>450675795.50200504</v>
+        <v>466869751.56071502</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.83076681877318348</v>
+        <v>0.86061843603889787</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>43535863.893522978</v>
+        <v>29550498.373812973</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>48270039.822467402</v>
+        <v>46061449.283467412</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>91805903.715990365</v>
+        <v>75611947.657280385</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>45902951.857995182</v>
+        <v>75611947.657280385</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23113,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>434780667.167575</v>
+        <v>454249976.114806</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>55655063.089941002</v>
+        <v>58885063.089941002</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>490435730.25751603</v>
+        <v>513135039.20474702</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.71039425263584044</v>
+        <v>0.74327411358408568</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>196848928.832425</v>
+        <v>177379619.885194</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>3086537.5206842646</v>
+        <v>-143462.4793157354</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>199935466.35310924</v>
+        <v>177236157.40587825</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>99967733.17655462</v>
+        <v>177236157.40587825</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23165,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>284653659.37129903</v>
+        <v>297882183.23181498</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>32538666.405825999</v>
+        <v>34050666.405826002</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>317192325.777125</v>
+        <v>331932849.63764095</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.70439100555073619</v>
+        <v>0.7371253801892611</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>101889363.62870097</v>
+        <v>88660839.768185019</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>31225488.393987808</v>
+        <v>29713488.393987805</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>133114852.02268881</v>
+        <v>118374328.16217285</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>66557426.011344403</v>
+        <v>118374328.16217285</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23217,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>667336640.85745704</v>
+        <v>686645252.87729704</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>179744789.15262499</v>
+        <v>191906951.15242499</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>847081430.01008201</v>
+        <v>878552204.02972198</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.92763961421803676</v>
+        <v>0.96210328634737907</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>-83985698.857457042</v>
+        <v>-103294310.87729704</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>150062155.84009239</v>
+        <v>137899993.84029239</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>66076456.982635379</v>
+        <v>34605682.96299541</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>33038228.491317689</v>
+        <v>34605682.96299541</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23269,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>237899949.77078599</v>
+        <v>298336622.32828599</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>128164709.80047999</v>
+        <v>128847592.67048</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>366064659.571266</v>
+        <v>427184214.99876601</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.70737717198713812</v>
+        <v>0.82548356969854886</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>21625739.229214013</v>
+        <v>-38810933.328285992</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>129805322.10740639</v>
+        <v>129122439.23740639</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>151431061.33662039</v>
+        <v>90311505.909120381</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>75715530.668310195</v>
+        <v>90311505.909120381</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>5871935028.8375082</v>
+        <v>6206485251.788393</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>894020315.83789694</v>
+        <v>919677494.50367093</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>6765955344.6754055</v>
+        <v>7126162746.2920628</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.81374940316043531</v>
+        <v>0.85707197080200292</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>967344303.1624918</v>
+        <v>632794080.21160793</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>581244508.38246453</v>
+        <v>555587329.71669066</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>1548588811.5449567</v>
+        <v>1188381409.9282987</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>774294405.77247834</v>
+        <v>1188381409.9282987</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>117989061.36</v>
+        <v>126214286.45999999</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23401,7 +23401,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>78609908.560000002</v>
+        <v>93672971.199999988</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="D72" s="192">
         <f>IF(E22="",0,E22)</f>
-        <v>10814414.119999999</v>
+        <v>12832432.08</v>
       </c>
     </row>
     <row r="73" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>212275674.66999999</v>
+        <v>260324322.93000001</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23449,7 +23449,7 @@
       </c>
       <c r="D75" s="192">
         <f>IF(E16="",0,E16)</f>
-        <v>11908108</v>
+        <v>14439639.5</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>634030850.76992702</v>
+        <v>709237967.049927</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>235065044.80979499</v>
+        <v>247976756.949745</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="D79" s="192">
         <f>IF(E11="",0,E11)</f>
-        <v>38843243.600000001</v>
+        <v>40868468.799999997</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>446908556.76973099</v>
+        <v>469103962.04973102</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>160988067.75999901</v>
+        <v>162788612.639999</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23533,7 +23533,7 @@
       </c>
       <c r="D82" s="192">
         <f>IF(E27="",0,E27)</f>
-        <v>18458378.596000001</v>
+        <v>19182702.936000001</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>73135136.539999992</v>
+        <v>82886488.079999998</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>2052840138.8754518</v>
+        <v>2253342303.9954014</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23569,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23617,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>276131649.54051697</v>
+        <v>291427595.82048202</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.99304849218767388</v>
+        <v>1.0480570955664552</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>1932968.3636925817</v>
+        <v>-13362977.916272461</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>966484.18184629083</v>
+        <v>-13362977.916272461</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>412946038.37677097</v>
+        <v>436148035.92440403</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.9888115248374425</v>
+        <v>1.0443693954602793</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>4672514.8097506166</v>
+        <v>-18529482.737882435</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>2336257.4048753083</v>
+        <v>-18529482.737882435</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>935920708.75692701</v>
+        <v>945630576.91965699</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.86077856822415444</v>
+        <v>0.86970886150280302</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>151374843.55659771</v>
+        <v>141664975.39386773</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>75687421.778298855</v>
+        <v>141664975.39386773</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,29 +23760,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>1624998396.6742148</v>
+        <v>1673206208.6645432</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.91139528214424914</v>
+        <v>0.93843307645863372</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>157980326.73004091</v>
+        <v>109772514.73971283</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>78990163.365020454</v>
+        <v>109772514.73971283</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23790,6 +23785,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -24562,10 +24562,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24627,7 +24627,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25626,13 +25626,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25835,11 +25835,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25847,6 +25842,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26619,10 +26619,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -26649,7 +26649,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26684,7 +26684,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27683,13 +27683,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27892,11 +27892,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27904,6 +27899,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9195" windowHeight="7290" tabRatio="500" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9195" windowHeight="7290" tabRatio="500" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -530,9 +530,6 @@
     <t>DATA PENCAPAIAN — JUNI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — JUNI 2026</t>
-  </si>
-  <si>
     <t>DATA PENCAPAIAN — JULI 2026</t>
   </si>
   <si>
@@ -603,6 +600,9 @@
   </si>
   <si>
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
+  </si>
+  <si>
+    <t>DATA PENCAPAIAN — GLOBAL — 02 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -2869,7 +2869,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -2967,7 +2967,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -3246,7 +3246,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B41" s="224" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C41" s="225"/>
       <c r="D41" s="226"/>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>176</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>177</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!R7</f>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!R13</f>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
@@ -4471,7 +4471,7 @@
       <c r="B69" s="223"/>
       <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -4500,10 +4500,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>176</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>177</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -4926,7 +4926,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -5024,7 +5024,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -5303,7 +5303,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -5315,7 +5315,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -5486,7 +5486,7 @@
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B41" s="224" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C41" s="225"/>
       <c r="D41" s="226"/>
@@ -5829,10 +5829,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>176</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>177</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!T7</f>
@@ -6141,10 +6141,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!T13</f>
@@ -6508,7 +6508,7 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
@@ -6528,7 +6528,7 @@
       <c r="B69" s="223"/>
       <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -6557,10 +6557,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>176</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>177</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -6629,10 +6629,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -6983,7 +6983,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -7081,7 +7081,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -7372,7 +7372,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -7543,7 +7543,7 @@
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B41" s="224" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C41" s="225"/>
       <c r="D41" s="226"/>
@@ -7886,10 +7886,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>176</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>177</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!V7</f>
@@ -8198,10 +8198,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!V13</f>
@@ -8565,7 +8565,7 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
@@ -8585,7 +8585,7 @@
       <c r="B69" s="223"/>
       <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -8614,10 +8614,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>176</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>177</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -9040,7 +9040,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -9138,7 +9138,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -9429,7 +9429,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B41" s="224" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C41" s="225"/>
       <c r="D41" s="226"/>
@@ -9943,10 +9943,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>176</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>177</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!X7</f>
@@ -10255,10 +10255,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!X13</f>
@@ -10622,7 +10622,7 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
@@ -10642,7 +10642,7 @@
       <c r="B69" s="223"/>
       <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -10671,10 +10671,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>176</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>177</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -11097,7 +11097,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -11195,7 +11195,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -11474,7 +11474,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -11486,7 +11486,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -11657,7 +11657,7 @@
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B41" s="224" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C41" s="225"/>
       <c r="D41" s="226"/>
@@ -11997,10 +11997,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>176</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>177</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!Z7</f>
@@ -12303,10 +12303,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!Z13</f>
@@ -12664,7 +12664,7 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
@@ -12684,7 +12684,7 @@
       <c r="B69" s="223"/>
       <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>176</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>177</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -12785,10 +12785,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -13125,11 +13125,10 @@
     <col min="4" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -13343,10 +13342,10 @@
         <v>68270401.220654309</v>
       </c>
       <c r="N5" s="7">
-        <v>0</v>
+        <v>451683478</v>
       </c>
       <c r="O5" s="7">
-        <v>0</v>
+        <v>101830423</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
@@ -13423,10 +13422,10 @@
         <v>191546784</v>
       </c>
       <c r="N6" s="7">
-        <v>0</v>
+        <v>590182371</v>
       </c>
       <c r="O6" s="7">
-        <v>0</v>
+        <v>225106806</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
@@ -13467,10 +13466,10 @@
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="145" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="146" t="s">
         <v>176</v>
-      </c>
-      <c r="C7" s="146" t="s">
-        <v>177</v>
       </c>
       <c r="D7" s="147">
         <v>241473268</v>
@@ -13500,7 +13499,9 @@
         <v>241473268</v>
       </c>
       <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+      <c r="N7" s="7">
+        <v>241473268</v>
+      </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
@@ -13553,10 +13554,10 @@
         <v>46881826.81733489</v>
       </c>
       <c r="N8" s="7">
-        <v>0</v>
+        <v>645712472</v>
       </c>
       <c r="O8" s="7">
-        <v>0</v>
+        <v>80441848</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
@@ -13633,10 +13634,10 @@
         <v>82869315.191524148</v>
       </c>
       <c r="N9" s="7">
-        <v>0</v>
+        <v>508918832</v>
       </c>
       <c r="O9" s="7">
-        <v>0</v>
+        <v>80519404</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
@@ -13713,10 +13714,10 @@
         <v>81239394.122653604</v>
       </c>
       <c r="N10" s="7">
-        <v>0</v>
+        <v>440063284</v>
       </c>
       <c r="O10" s="7">
-        <v>0</v>
+        <v>82149325</v>
       </c>
       <c r="P10" s="7">
         <v>0</v>
@@ -13793,10 +13794,10 @@
         <v>91928576.339156389</v>
       </c>
       <c r="N11" s="7">
-        <v>0</v>
+        <v>996758345</v>
       </c>
       <c r="O11" s="7">
-        <v>0</v>
+        <v>125488598</v>
       </c>
       <c r="P11" s="7">
         <v>0</v>
@@ -13873,10 +13874,10 @@
         <v>63781404</v>
       </c>
       <c r="N12" s="7">
-        <v>0</v>
+        <v>540287059</v>
       </c>
       <c r="O12" s="7">
-        <v>0</v>
+        <v>97341426</v>
       </c>
       <c r="P12" s="7">
         <v>0</v>
@@ -13917,10 +13918,10 @@
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" s="145" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C13" s="146" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D13" s="147">
         <v>404133664</v>
@@ -13950,7 +13951,9 @@
         <v>404133664</v>
       </c>
       <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
+      <c r="N13" s="7">
+        <v>404133664</v>
+      </c>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
@@ -14003,10 +14006,10 @@
         <v>138464390.21799541</v>
       </c>
       <c r="N14" s="7">
-        <v>0</v>
+        <v>439017309</v>
       </c>
       <c r="O14" s="7">
-        <v>0</v>
+        <v>172024412</v>
       </c>
       <c r="P14" s="7">
         <v>0</v>
@@ -14083,10 +14086,10 @@
         <v>58741600.610625267</v>
       </c>
       <c r="N15" s="7">
-        <v>0</v>
+        <v>666629596</v>
       </c>
       <c r="O15" s="7">
-        <v>0</v>
+        <v>92301622</v>
       </c>
       <c r="P15" s="7">
         <v>0</v>
@@ -14163,10 +14166,10 @@
         <v>63764154.799813807</v>
       </c>
       <c r="N16" s="7">
-        <v>0</v>
+        <v>421543023</v>
       </c>
       <c r="O16" s="7">
-        <v>0</v>
+        <v>97324176</v>
       </c>
       <c r="P16" s="7">
         <v>0</v>
@@ -14243,10 +14246,10 @@
         <v>329806944.99271739</v>
       </c>
       <c r="N17" s="7">
-        <v>0</v>
+        <v>618350942</v>
       </c>
       <c r="O17" s="7">
-        <v>0</v>
+        <v>363366966</v>
       </c>
       <c r="P17" s="7">
         <v>0</v>
@@ -14323,10 +14326,10 @@
         <v>257970031.90788639</v>
       </c>
       <c r="N18" s="7">
-        <v>0</v>
+        <v>294525689</v>
       </c>
       <c r="O18" s="7">
-        <v>0</v>
+        <v>291530053</v>
       </c>
       <c r="P18" s="7">
         <v>0</v>
@@ -14450,7 +14453,7 @@
         <v>278064617.90420955</v>
       </c>
       <c r="I22" s="7">
-        <v>0</v>
+        <v>285530553</v>
       </c>
       <c r="J22" s="7">
         <v>0</v>
@@ -14494,7 +14497,7 @@
         <v>417618553.18652159</v>
       </c>
       <c r="I23" s="7">
-        <v>0</v>
+        <v>428831462</v>
       </c>
       <c r="J23" s="7">
         <v>0</v>
@@ -14538,7 +14541,7 @@
         <v>1087295552.3135247</v>
       </c>
       <c r="I24" s="7">
-        <v>0</v>
+        <v>1116489049</v>
       </c>
       <c r="J24" s="7">
         <v>0</v>
@@ -14688,7 +14691,7 @@
   <sheetData>
     <row r="1" spans="2:17" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -16223,7 +16226,7 @@
   <sheetData>
     <row r="1" spans="2:17" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -17846,7 +17849,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C9" s="15">
         <v>188107.92</v>
@@ -17984,7 +17987,7 @@
         <v>282161.88</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E15" s="15">
         <v>282161.88</v>
@@ -18200,7 +18203,7 @@
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C29" s="15">
         <v>3087270.2699850001</v>
@@ -19617,7 +19620,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -19797,7 +19800,7 @@
       </c>
       <c r="C15" s="150"/>
       <c r="D15" s="150" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E15" s="150"/>
       <c r="F15" s="150"/>
@@ -19850,7 +19853,7 @@
         <v>44657675.509999998</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F17" s="15">
         <v>400283795.43999302</v>
@@ -19931,7 +19934,7 @@
         <v>16467727.799813</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F20" s="15">
         <v>121782785.42740899</v>
@@ -19957,7 +19960,7 @@
         <v>136240384.927111</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F21" s="15">
         <v>193600324.34711099</v>
@@ -19974,13 +19977,13 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="15">
         <v>38884328.600000001</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E22" s="15">
         <v>12315315.119999999</v>
@@ -19995,13 +19998,13 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="15">
         <v>120550492.72</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E23" s="15">
         <v>17151621.32</v>
@@ -20082,7 +20085,7 @@
         <v>200253231.98958299</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F27" s="15">
         <v>863813055.77967799</v>
@@ -20158,7 +20161,7 @@
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="224" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C41" s="225"/>
       <c r="D41" s="226"/>
@@ -20489,10 +20492,10 @@
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="187" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="188" t="s">
         <v>176</v>
-      </c>
-      <c r="C53" s="188" t="s">
-        <v>177</v>
       </c>
       <c r="D53" s="179">
         <f>TARGETS!J7</f>
@@ -20801,10 +20804,10 @@
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="187" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="188" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" s="179">
         <f>TARGETS!J13</f>
@@ -21163,7 +21166,7 @@
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
@@ -21189,7 +21192,7 @@
       <c r="B69" s="223"/>
       <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
@@ -21221,10 +21224,10 @@
     </row>
     <row r="72" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="185" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="186" t="s">
         <v>176</v>
-      </c>
-      <c r="C72" s="186" t="s">
-        <v>177</v>
       </c>
       <c r="D72" s="192">
         <f>IF(E22="",0,E22)</f>
@@ -21292,10 +21295,10 @@
     </row>
     <row r="78" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="185" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" s="186" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D78" s="192">
         <f>IF(E23="",0,E23)</f>
@@ -21661,14 +21664,14 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
         <f ca="1">DAY(EOMONTH(TODAY(),0))</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -21733,7 +21736,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -21971,7 +21974,7 @@
         <v>42787524.299999997</v>
       </c>
       <c r="E17" s="205" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F17" s="205">
         <v>357138221.57999802</v>
@@ -22100,13 +22103,13 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="205">
         <v>197567845.80000001</v>
       </c>
       <c r="D22" s="205" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E22" s="205">
         <v>12832432.08</v>
@@ -22120,13 +22123,13 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="205">
         <v>300521523.82997501</v>
       </c>
       <c r="D23" s="205" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E23" s="205">
         <v>13813693.32</v>
@@ -22335,7 +22338,7 @@
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="238" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C41" s="239"/>
       <c r="D41" s="240"/>
@@ -22344,7 +22347,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.967741935483871</v>
+        <v>1</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22399,7 +22402,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>632794080.21160698</v>
+        <v>25311763.20846428</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22428,7 +22431,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>555587329.71669078</v>
+        <v>22223493.188667633</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22457,7 +22460,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>109772514.73971272</v>
+        <v>4390900.5895885089</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22484,7 +22487,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>1298153924.6680105</v>
+        <v>51926156.98672042</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22621,7 +22624,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>151944123.3265633</v>
+        <v>6077764.933062532</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22673,15 +22676,15 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>135949634.98727</v>
+        <v>5437985.3994907998</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>176</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>177</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!L7</f>
@@ -22725,7 +22728,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>43905422.199999988</v>
+        <v>1756216.8879999996</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22777,7 +22780,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-40348707.486027122</v>
+        <v>-1613948.299441085</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22829,7 +22832,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>130794377.61152613</v>
+        <v>5231775.104461045</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22881,7 +22884,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>80687504.454943657</v>
+        <v>3227500.1781977462</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22933,7 +22936,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-25117135.668739557</v>
+        <v>-1004685.4267495823</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22985,15 +22988,15 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>110814428.23529005</v>
+        <v>4432577.1294116024</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!L13</f>
@@ -23037,7 +23040,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>103612140.17002499</v>
+        <v>4144485.6068009995</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23089,7 +23092,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>75611947.657280385</v>
+        <v>3024477.9062912152</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23141,7 +23144,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>177236157.40587825</v>
+        <v>7089446.2962351302</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23193,7 +23196,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>118374328.16217285</v>
+        <v>4734973.1264869142</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23245,7 +23248,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>34605682.96299541</v>
+        <v>1384227.3185198165</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23297,7 +23300,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>90311505.909120381</v>
+        <v>3612460.2363648154</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23347,7 +23350,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>1188381409.9282987</v>
+        <v>47535256.39713195</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23357,7 +23360,7 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
@@ -23377,7 +23380,7 @@
       <c r="B69" s="223"/>
       <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23406,10 +23409,10 @@
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="201" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="202" t="s">
         <v>176</v>
-      </c>
-      <c r="C72" s="202" t="s">
-        <v>177</v>
       </c>
       <c r="D72" s="192">
         <f>IF(E22="",0,E22)</f>
@@ -23478,10 +23481,10 @@
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="201" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" s="202" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D78" s="192">
         <f>IF(E23="",0,E23)</f>
@@ -23629,7 +23632,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-13362977.916272461</v>
+        <v>-534519.11665089848</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23658,7 +23661,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-18529482.737882435</v>
+        <v>-741179.30951529741</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23687,7 +23690,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>141664975.39386773</v>
+        <v>5666599.015754709</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23772,7 +23775,7 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>109772514.73971283</v>
+        <v>4390900.5895885136</v>
       </c>
       <c r="I94" s="116"/>
     </row>
@@ -23813,15 +23816,15 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" customWidth="1"/>
     <col min="11" max="11" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -23858,7 +23861,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23930,7 +23933,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -23940,11 +23943,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>0</v>
+        <v>15565960.869789001</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>0</v>
+        <v>1540540.52</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23962,107 +23965,147 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>0</v>
+        <v>15107693.889947999</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>0</v>
+        <v>6064027.9354969999</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
+      <c r="C10" s="205">
+        <v>10209497.789187999</v>
+      </c>
+      <c r="D10" s="205">
+        <v>0</v>
+      </c>
+      <c r="E10" s="205">
+        <v>3279279.22</v>
+      </c>
+      <c r="F10" s="205">
+        <v>13488777.009188</v>
+      </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>0</v>
+        <v>39950331.5</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>0</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
+      <c r="C11" s="205">
+        <v>40538550.981369004</v>
+      </c>
+      <c r="D11" s="205">
+        <v>4228378.3199399998</v>
+      </c>
+      <c r="E11" s="205" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="205">
+        <v>44766929.301308997</v>
+      </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>0</v>
+        <v>282000</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="C12" s="205">
+        <v>2065000</v>
+      </c>
+      <c r="D12" s="205">
+        <v>5678149.5554999998</v>
+      </c>
+      <c r="E12" s="205" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12" s="205">
+        <v>7743149.5554999998</v>
+      </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>0</v>
+        <v>33187180.708790999</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>0</v>
+        <v>773810.81</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="C13" s="205">
+        <v>13042693.889947999</v>
+      </c>
+      <c r="D13" s="205">
+        <v>385878.37999699998</v>
+      </c>
+      <c r="E13" s="205" t="s">
+        <v>168</v>
+      </c>
+      <c r="F13" s="205">
+        <v>13428572.269944999</v>
+      </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>0</v>
+        <v>33289730.151946001</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>0</v>
+        <v>14591959.959952001</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="C14" s="205">
+        <v>39950331.5</v>
+      </c>
+      <c r="D14" s="205">
+        <v>420000</v>
+      </c>
+      <c r="E14" s="205">
+        <v>9360360.2599999998</v>
+      </c>
+      <c r="F14" s="205">
+        <v>49730691.759999998</v>
+      </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>0</v>
+        <v>17738173.430498999</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
@@ -24082,47 +24125,63 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>0</v>
+        <v>40538550.981369004</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>0</v>
+        <v>4228378.3199399998</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
+      <c r="C16" s="205">
+        <v>33187180.708790999</v>
+      </c>
+      <c r="D16" s="205">
+        <v>773810.81</v>
+      </c>
+      <c r="E16" s="205">
+        <v>810810.8</v>
+      </c>
+      <c r="F16" s="205">
+        <v>34771802.318791002</v>
+      </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>0</v>
+        <v>34306915.179871</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>0</v>
+        <v>2431800</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
+      <c r="C17" s="205">
+        <v>1500000</v>
+      </c>
+      <c r="D17" s="205">
+        <v>282000</v>
+      </c>
+      <c r="E17" s="205" t="s">
+        <v>168</v>
+      </c>
+      <c r="F17" s="205">
+        <v>1782000</v>
+      </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>0</v>
+        <v>10209497.789187999</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
@@ -24133,16 +24192,24 @@
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
+      <c r="C18" s="205">
+        <v>42189230.339962997</v>
+      </c>
+      <c r="D18" s="205">
+        <v>0</v>
+      </c>
+      <c r="E18" s="205">
+        <v>5189189.12</v>
+      </c>
+      <c r="F18" s="205">
+        <v>47378419.459963001</v>
+      </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>0</v>
+        <v>10305210.84</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
@@ -24153,16 +24220,24 @@
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
+      <c r="C19" s="205">
+        <v>33289730.151946001</v>
+      </c>
+      <c r="D19" s="205">
+        <v>14591959.959952001</v>
+      </c>
+      <c r="E19" s="205">
+        <v>284636047.89999998</v>
+      </c>
+      <c r="F19" s="205">
+        <v>332517738.01189798</v>
+      </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>0</v>
+        <v>930000</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
@@ -24174,7 +24249,9 @@
         <v>123</v>
       </c>
       <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
+      <c r="D20" s="15">
+        <v>0</v>
+      </c>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
       <c r="H20" s="116"/>
@@ -24192,16 +24269,24 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
+      <c r="C21" s="205">
+        <v>930000</v>
+      </c>
+      <c r="D21" s="205">
+        <v>0</v>
+      </c>
+      <c r="E21" s="205" t="s">
+        <v>168</v>
+      </c>
+      <c r="F21" s="205">
+        <v>930000</v>
+      </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>0</v>
+        <v>22380806.529866003</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24209,7 +24294,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -24221,12 +24306,20 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>174</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
+        <v>173</v>
+      </c>
+      <c r="C23" s="205">
+        <v>63811629.899999999</v>
+      </c>
+      <c r="D23" s="205">
+        <v>0</v>
+      </c>
+      <c r="E23" s="205">
+        <v>1927927.88</v>
+      </c>
+      <c r="F23" s="205">
+        <v>65739557.780000001</v>
+      </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
       <c r="J23" s="116"/>
@@ -24235,10 +24328,18 @@
       <c r="B24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
+      <c r="C24" s="205">
+        <v>15565960.869789001</v>
+      </c>
+      <c r="D24" s="205">
+        <v>1540540.52</v>
+      </c>
+      <c r="E24" s="205">
+        <v>6677477.4199999999</v>
+      </c>
+      <c r="F24" s="205">
+        <v>23783978.809788998</v>
+      </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
       <c r="J24" s="116"/>
@@ -24247,10 +24348,18 @@
       <c r="B25" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
+      <c r="C25" s="205">
+        <v>17738173.430498999</v>
+      </c>
+      <c r="D25" s="205">
+        <v>0</v>
+      </c>
+      <c r="E25" s="205">
+        <v>11945946.749915</v>
+      </c>
+      <c r="F25" s="205">
+        <v>29684120.180413999</v>
+      </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
       <c r="J25" s="116"/>
@@ -24259,10 +24368,18 @@
       <c r="B26" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="C26" s="205">
+        <v>34306915.179871</v>
+      </c>
+      <c r="D26" s="205">
+        <v>2431800</v>
+      </c>
+      <c r="E26" s="205">
+        <v>35648648.749954998</v>
+      </c>
+      <c r="F26" s="205">
+        <v>72387363.929826006</v>
+      </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
       <c r="J26" s="116"/>
@@ -24271,10 +24388,18 @@
       <c r="B27" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
+      <c r="C27" s="205">
+        <v>10305210.84</v>
+      </c>
+      <c r="D27" s="205">
+        <v>0</v>
+      </c>
+      <c r="E27" s="205" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27" s="205">
+        <v>10305210.84</v>
+      </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
       <c r="J27" s="116"/>
@@ -24315,8 +24440,8 @@
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="15">
-        <v>0</v>
+      <c r="C32" s="205">
+        <v>1374000</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24326,8 +24451,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="15">
-        <v>0</v>
+      <c r="C33" s="205">
+        <v>1197747.618</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24337,8 +24462,8 @@
       <c r="B34" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="15">
-        <v>0</v>
+      <c r="C34" s="205">
+        <v>7647500</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24348,8 +24473,8 @@
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="15">
-        <v>0</v>
+      <c r="C35" s="205">
+        <v>14733306.529866001</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24390,9 +24515,9 @@
       <c r="H40" s="116"/>
       <c r="I40" s="116"/>
     </row>
-    <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="224" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="C41" s="225"/>
       <c r="D41" s="226"/>
@@ -24401,13 +24526,13 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
       <c r="I41" s="116"/>
     </row>
-    <row r="42" spans="2:14" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="69" t="s">
         <v>137</v>
       </c>
@@ -24431,7 +24556,7 @@
       </c>
       <c r="I42" s="116"/>
     </row>
-    <row r="43" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="114" t="s">
         <v>143</v>
       </c>
@@ -24440,27 +24565,27 @@
       </c>
       <c r="D43" s="45">
         <f>SUM(TARGETS!N5:N7,TARGETS!N8:N13,TARGETS!N14:N18)</f>
-        <v>0</v>
+        <v>7259279332</v>
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>0</v>
+        <v>316440875.24140102</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0</v>
+        <v>4.3591224523690915E-2</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>0</v>
+        <v>6942838456.7585993</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>0</v>
+        <v>277713538.27034396</v>
       </c>
       <c r="I43" s="116"/>
     </row>
-    <row r="44" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="114" t="s">
         <v>111</v>
       </c>
@@ -24469,27 +24594,27 @@
       </c>
       <c r="D44" s="45">
         <f>SUM(TARGETS!O5:O6,TARGETS!O8:O12,TARGETS!O14:O18)</f>
-        <v>0</v>
+        <v>1809425059</v>
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>0</v>
+        <v>30332517.545389004</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0</v>
+        <v>1.6763621899960106E-2</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>0</v>
+        <v>1779092541.4546111</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>0</v>
+        <v>71163701.658184439</v>
       </c>
       <c r="I44" s="116"/>
     </row>
-    <row r="45" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="114" t="s">
         <v>145</v>
       </c>
@@ -24498,23 +24623,23 @@
       </c>
       <c r="D45" s="45">
         <f>SUM(TARGETS!I22:I26)</f>
-        <v>0</v>
+        <v>1830851064</v>
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>0</v>
+        <v>24952554.147866003</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0</v>
+        <v>1.3628937185829991E-2</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>0</v>
+        <v>1805898509.852134</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>0</v>
+        <v>72235940.394085363</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24525,23 +24650,23 @@
       <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
-        <v>0</v>
+        <v>10899555455</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>0</v>
+        <v>371725946.93465602</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0</v>
+        <v>3.4104688807664409E-2</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>0</v>
+        <v>10527829508.065346</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>0</v>
+        <v>421113180.32261384</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24567,7 +24692,7 @@
       <c r="M48" s="245"/>
       <c r="N48" s="246"/>
     </row>
-    <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
@@ -24596,7 +24721,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="223"/>
       <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
@@ -24629,7 +24754,7 @@
       </c>
       <c r="N50" s="247"/>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
         <v>67</v>
       </c>
@@ -24638,50 +24763,50 @@
       </c>
       <c r="D51" s="127">
         <f>TARGETS!N5</f>
-        <v>0</v>
+        <v>451683478</v>
       </c>
       <c r="E51" s="127">
         <f>TARGETS!O5</f>
-        <v>0</v>
+        <v>101830423</v>
       </c>
       <c r="F51" s="127">
         <f t="shared" ref="F51:F64" si="0">D51+E51</f>
-        <v>0</v>
+        <v>553513901</v>
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>0</v>
+        <v>15565960.869789001</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>0</v>
+        <v>1540540.52</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>0</v>
+        <v>17106501.389789</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0</v>
+        <v>3.0905278727207611E-2</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>0</v>
+        <v>436117517.130211</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>100289882.48</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>536407399.61021101</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+        <v>21456295.984408442</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="53" t="s">
         <v>69</v>
       </c>
@@ -24690,59 +24815,59 @@
       </c>
       <c r="D52" s="128">
         <f>TARGETS!N6</f>
-        <v>0</v>
+        <v>590182371</v>
       </c>
       <c r="E52" s="128">
         <f>TARGETS!O6</f>
-        <v>0</v>
+        <v>225106806</v>
       </c>
       <c r="F52" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>815289177</v>
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>0</v>
+        <v>15107693.889947999</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>0</v>
+        <v>6064027.9354969999</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21171721.825445</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.5968358740330735E-2</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>575074677.11005199</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>219042778.06450301</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>794117455.17455494</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+        <v>31764698.206982199</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>176</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>177</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!N7</f>
-        <v>0</v>
+        <v>241473268</v>
       </c>
       <c r="E53" s="157">
         <f>TARGETS!O7</f>
@@ -24750,7 +24875,7 @@
       </c>
       <c r="F53" s="157">
         <f>D53+E53</f>
-        <v>0</v>
+        <v>241473268</v>
       </c>
       <c r="G53" s="122">
         <f>C22</f>
@@ -24770,7 +24895,7 @@
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>0</v>
+        <v>241473268</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -24778,14 +24903,14 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>0</v>
+        <v>241473268</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+        <v>9658930.7200000007</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="53" t="s">
         <v>71</v>
       </c>
@@ -24794,50 +24919,50 @@
       </c>
       <c r="D54" s="128">
         <f>TARGETS!N8</f>
-        <v>0</v>
+        <v>645712472</v>
       </c>
       <c r="E54" s="128">
         <f>TARGETS!O8</f>
-        <v>0</v>
+        <v>80441848</v>
       </c>
       <c r="F54" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>726154320</v>
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>0</v>
+        <v>39950331.5</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>0</v>
+        <v>420000</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40370331.5</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.5594699897950066E-2</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>0</v>
+        <v>605762140.5</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>80021848</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>685783988.5</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+        <v>27431359.539999999</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="50" t="s">
         <v>73</v>
       </c>
@@ -24846,50 +24971,50 @@
       </c>
       <c r="D55" s="127">
         <f>TARGETS!N9</f>
-        <v>0</v>
+        <v>508918832</v>
       </c>
       <c r="E55" s="127">
         <f>TARGETS!O9</f>
-        <v>0</v>
+        <v>80519404</v>
       </c>
       <c r="F55" s="127">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>589438236</v>
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>282000</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1782000</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.0232175165507925E-3</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>507418832</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>80237404</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>587656236</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+        <v>23506249.440000001</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="53" t="s">
         <v>75</v>
       </c>
@@ -24898,50 +25023,50 @@
       </c>
       <c r="D56" s="128">
         <f>TARGETS!N10</f>
-        <v>0</v>
+        <v>440063284</v>
       </c>
       <c r="E56" s="128">
         <f>TARGETS!O10</f>
-        <v>0</v>
+        <v>82149325</v>
       </c>
       <c r="F56" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>522212609</v>
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>0</v>
+        <v>33187180.708790999</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>773810.81</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>33960991.518790998</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.5032883031728939E-2</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>406876103.29120898</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>81375514.189999998</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>488251617.48120898</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+        <v>19530064.699248359</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="50" t="s">
         <v>76</v>
       </c>
@@ -24950,50 +25075,50 @@
       </c>
       <c r="D57" s="127">
         <f>TARGETS!N11</f>
-        <v>0</v>
+        <v>996758345</v>
       </c>
       <c r="E57" s="127">
         <f>TARGETS!O11</f>
-        <v>0</v>
+        <v>125488598</v>
       </c>
       <c r="F57" s="127">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1122246943</v>
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>0</v>
+        <v>33289730.151946001</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14591959.959952001</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>47881690.111898005</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.2665912712491129E-2</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>963468614.84805405</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>110896638.040048</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1074365252.8881021</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
+        <v>42974610.115524083</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="53" t="s">
         <v>78</v>
       </c>
@@ -25002,19 +25127,19 @@
       </c>
       <c r="D58" s="128">
         <f>TARGETS!N12</f>
-        <v>0</v>
+        <v>540287059</v>
       </c>
       <c r="E58" s="128">
         <f>TARGETS!O12</f>
-        <v>0</v>
+        <v>97341426</v>
       </c>
       <c r="F58" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>637628485</v>
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>0</v>
+        <v>17738173.430498999</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
@@ -25022,39 +25147,39 @@
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>0</v>
+        <v>17738173.430498999</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0</v>
+        <v>2.7818978994482969E-2</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>522548885.56950098</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>97341426</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>619890311.56950104</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
+        <v>24795612.462780043</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!N13</f>
-        <v>0</v>
+        <v>404133664</v>
       </c>
       <c r="E59" s="157">
         <f>TARGETS!O13</f>
@@ -25062,11 +25187,11 @@
       </c>
       <c r="F59" s="157">
         <f>D59+E59</f>
-        <v>0</v>
+        <v>404133664</v>
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>0</v>
+        <v>63811629.899999999</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25074,15 +25199,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>0</v>
+        <v>63811629.899999999</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0</v>
+        <v>0.1578973383914882</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>0</v>
+        <v>340322034.10000002</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25090,14 +25215,14 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>0</v>
+        <v>340322034.10000002</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
+        <v>13612881.364</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="53" t="s">
         <v>80</v>
       </c>
@@ -25106,50 +25231,50 @@
       </c>
       <c r="D60" s="128">
         <f>TARGETS!N14</f>
-        <v>0</v>
+        <v>439017309</v>
       </c>
       <c r="E60" s="128">
         <f>TARGETS!O14</f>
-        <v>0</v>
+        <v>172024412</v>
       </c>
       <c r="F60" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>611041721</v>
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>0</v>
+        <v>40538550.981369004</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>0</v>
+        <v>4228378.3199399998</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>44766929.301309004</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.3263294080878325E-2</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>398478758.01863098</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>167796033.68006</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>566274791.69869101</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+        <v>22650991.667947639</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="50" t="s">
         <v>82</v>
       </c>
@@ -25158,50 +25283,50 @@
       </c>
       <c r="D61" s="127">
         <f>TARGETS!N15</f>
-        <v>0</v>
+        <v>666629596</v>
       </c>
       <c r="E61" s="127">
         <f>TARGETS!O15</f>
-        <v>0</v>
+        <v>92301622</v>
       </c>
       <c r="F61" s="127">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>758931218</v>
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>0</v>
+        <v>34306915.179871</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2431800</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>36738715.179871</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.8408491189343858E-2</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>632322680.82012904</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>89869822</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>722192502.82012904</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+        <v>28887700.112805162</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="53" t="s">
         <v>84</v>
       </c>
@@ -25210,19 +25335,19 @@
       </c>
       <c r="D62" s="128">
         <f>TARGETS!N16</f>
-        <v>0</v>
+        <v>421543023</v>
       </c>
       <c r="E62" s="128">
         <f>TARGETS!O16</f>
-        <v>0</v>
+        <v>97324176</v>
       </c>
       <c r="F62" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>518867199</v>
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>0</v>
+        <v>10209497.789187999</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
@@ -25230,30 +25355,30 @@
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10209497.789187999</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.967651416174411E-2</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>411333525.21081197</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>97324176</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>508657701.21081197</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+        <v>20346308.048432481</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="50" t="s">
         <v>86</v>
       </c>
@@ -25262,19 +25387,19 @@
       </c>
       <c r="D63" s="127">
         <f>TARGETS!N17</f>
-        <v>0</v>
+        <v>618350942</v>
       </c>
       <c r="E63" s="127">
         <f>TARGETS!O17</f>
-        <v>0</v>
+        <v>363366966</v>
       </c>
       <c r="F63" s="127">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>981717908</v>
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>0</v>
+        <v>10305210.84</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
@@ -25282,30 +25407,30 @@
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10305210.84</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.0497120156434999E-2</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>608045731.15999997</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>363366966</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>971412697.15999997</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
+        <v>38856507.886399999</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="53" t="s">
         <v>88</v>
       </c>
@@ -25314,19 +25439,19 @@
       </c>
       <c r="D64" s="128">
         <f>TARGETS!N18</f>
-        <v>0</v>
+        <v>294525689</v>
       </c>
       <c r="E64" s="128">
         <f>TARGETS!O18</f>
-        <v>0</v>
+        <v>291530053</v>
       </c>
       <c r="F64" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>586055742</v>
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>0</v>
+        <v>930000</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
@@ -25334,77 +25459,77 @@
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>930000</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.5868797681705847E-3</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>293595689</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>291530053</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>585125742</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
+        <v>23405029.68</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="57" t="s">
         <v>152</v>
       </c>
       <c r="C65" s="58"/>
       <c r="D65" s="151">
         <f>SUM(D51:D64)</f>
-        <v>0</v>
+        <v>7259279332</v>
       </c>
       <c r="E65" s="151">
         <f t="shared" ref="E65" si="6">SUM(E51:E52,E54:E58,E60:E64)</f>
-        <v>0</v>
+        <v>1809425059</v>
       </c>
       <c r="F65" s="151">
         <f>SUM(F51:F64)</f>
-        <v>0</v>
+        <v>9068704391</v>
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>0</v>
+        <v>316440875.24140102</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>0</v>
+        <v>30332517.545389004</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>0</v>
+        <v>346773392.78679001</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0</v>
+        <v>3.8238471322423549E-2</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>0</v>
+        <v>6942838456.7585993</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>0</v>
+        <v>1779092541.4546111</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>0</v>
+        <v>8721930998.2132111</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>0</v>
+        <v>348877239.92852843</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25414,7 +25539,7 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
@@ -25434,10 +25559,10 @@
       <c r="B69" s="223"/>
       <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="50" t="s">
         <v>67</v>
       </c>
@@ -25446,10 +25571,10 @@
       </c>
       <c r="D70" s="148">
         <f>IF(E24="",0,E24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
+        <v>6677477.4199999999</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="53" t="s">
         <v>69</v>
       </c>
@@ -25461,19 +25586,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>176</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>177</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="50" t="s">
         <v>71</v>
       </c>
@@ -25482,10 +25607,10 @@
       </c>
       <c r="D73" s="148">
         <f>IF(E14="",0,E14)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
+        <v>9360360.2599999998</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="53" t="s">
         <v>73</v>
       </c>
@@ -25497,7 +25622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="50" t="s">
         <v>75</v>
       </c>
@@ -25509,7 +25634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="53" t="s">
         <v>76</v>
       </c>
@@ -25518,10 +25643,10 @@
       </c>
       <c r="D76" s="149">
         <f>IF(E19="",0,E19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
+        <v>284636047.89999998</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="50" t="s">
         <v>78</v>
       </c>
@@ -25530,22 +25655,22 @@
       </c>
       <c r="D77" s="148">
         <f>IF(E25="",0,E25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
+        <v>11945946.749915</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
+        <v>1927927.88</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="53" t="s">
         <v>80</v>
       </c>
@@ -25557,7 +25682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="50" t="s">
         <v>82</v>
       </c>
@@ -25566,10 +25691,10 @@
       </c>
       <c r="D80" s="148">
         <f>IF(E26="",0,E26)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+        <v>35648648.749954998</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="53" t="s">
         <v>84</v>
       </c>
@@ -25578,10 +25703,10 @@
       </c>
       <c r="D81" s="149">
         <f>IF(E10="",0,E10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+        <v>3279279.22</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="50" t="s">
         <v>86</v>
       </c>
@@ -25593,7 +25718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="53" t="s">
         <v>88</v>
       </c>
@@ -25605,14 +25730,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="57" t="s">
         <v>152</v>
       </c>
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>0</v>
+        <v>353475688.17987001</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25637,7 +25762,7 @@
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
     </row>
-    <row r="88" spans="2:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="75" t="s">
         <v>153</v>
       </c>
@@ -25661,7 +25786,7 @@
       </c>
       <c r="I88" s="116"/>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="50" t="s">
         <v>92</v>
       </c>
@@ -25670,27 +25795,27 @@
       </c>
       <c r="D89" s="125">
         <f>TARGETS!I22</f>
-        <v>0</v>
+        <v>285530553</v>
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>0</v>
+        <v>1374000</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0</v>
+        <v>4.8120944871353228E-3</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>0</v>
+        <v>284156553</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>0</v>
+        <v>11366262.119999999</v>
       </c>
       <c r="I89" s="116"/>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="53" t="s">
         <v>94</v>
       </c>
@@ -25699,27 +25824,27 @@
       </c>
       <c r="D90" s="126">
         <f>TARGETS!I23</f>
-        <v>0</v>
+        <v>428831462</v>
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>0</v>
+        <v>1197747.618</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.793049773945924E-3</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>0</v>
+        <v>427633714.38200003</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>0</v>
+        <v>17105348.57528</v>
       </c>
       <c r="I90" s="116"/>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="50" t="s">
         <v>96</v>
       </c>
@@ -25728,27 +25853,27 @@
       </c>
       <c r="D91" s="125">
         <f>TARGETS!I24</f>
-        <v>0</v>
+        <v>1116489049</v>
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>0</v>
+        <v>22380806.529866003</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.0045701791622322E-2</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>0</v>
+        <v>1094108242.470134</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>0</v>
+        <v>43764329.698805362</v>
       </c>
       <c r="I91" s="116"/>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="53" t="s">
         <v>98</v>
       </c>
@@ -25777,7 +25902,7 @@
       </c>
       <c r="I92" s="116"/>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="50" t="s">
         <v>100</v>
       </c>
@@ -25806,30 +25931,30 @@
       </c>
       <c r="I93" s="116"/>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="57" t="s">
         <v>152</v>
       </c>
       <c r="C94" s="58"/>
       <c r="D94" s="123">
         <f>SUM(D89:D93)</f>
-        <v>0</v>
+        <v>1830851064</v>
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>0</v>
+        <v>24952554.147866003</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.3628937185829991E-2</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>0</v>
+        <v>1805898509.852134</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>0</v>
+        <v>72235940.394085363</v>
       </c>
       <c r="I94" s="116"/>
     </row>
@@ -25860,7 +25985,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -25889,7 +26014,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -25987,7 +26112,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -26266,7 +26391,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -26278,7 +26403,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -26449,7 +26574,7 @@
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B41" s="224" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C41" s="225"/>
       <c r="D41" s="226"/>
@@ -26792,10 +26917,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>176</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>177</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!P7</f>
@@ -27104,10 +27229,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!P13</f>
@@ -27471,7 +27596,7 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
@@ -27491,7 +27616,7 @@
       <c r="B69" s="223"/>
       <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -27520,10 +27645,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>176</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>177</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -27592,10 +27717,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 03 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 04 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1831,6 +1831,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1957,7 +1958,6 @@
     <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2713,16 +2713,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="206" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="206"/>
+      <c r="B1" s="207" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="207"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="207"/>
+      <c r="C3" s="208"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2773,10 +2773,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="208"/>
+      <c r="C11" s="209"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -3429,11 +3429,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3557,10 +3557,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3589,40 +3589,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3630,13 +3630,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3655,7 +3655,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3665,7 +3665,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4458,10 +4458,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4469,8 +4469,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -4664,13 +4664,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -5486,11 +5486,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5614,10 +5614,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5646,40 +5646,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5687,13 +5687,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5712,7 +5712,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5722,7 +5722,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6515,10 +6515,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6526,8 +6526,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -6721,13 +6721,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -7543,11 +7543,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7671,10 +7671,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7703,40 +7703,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7744,13 +7744,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7769,7 +7769,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7779,7 +7779,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8572,10 +8572,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8583,8 +8583,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -8778,13 +8778,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -9600,11 +9600,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9728,10 +9728,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9760,40 +9760,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9801,13 +9801,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9826,7 +9826,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9836,7 +9836,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10629,10 +10629,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10640,8 +10640,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -10835,13 +10835,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11657,11 +11657,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11784,10 +11784,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11816,40 +11816,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11857,13 +11857,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11882,7 +11882,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11892,7 +11892,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12671,10 +12671,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12682,8 +12682,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -12877,13 +12877,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13172,10 +13172,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="208" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="207"/>
+      <c r="C3" s="208"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14652,13 +14652,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="209" t="s">
+      <c r="B29" s="210" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="209"/>
-      <c r="D29" s="209"/>
-      <c r="E29" s="209"/>
-      <c r="F29" s="209"/>
+      <c r="C29" s="210"/>
+      <c r="D29" s="210"/>
+      <c r="E29" s="210"/>
+      <c r="F29" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15190,10 +15190,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="211" t="s">
+      <c r="B44" s="212" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="212"/>
+      <c r="C44" s="213"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15233,23 +15233,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="214" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="213" t="s">
+      <c r="C47" s="214" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="214" t="s">
+      <c r="D47" s="215" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="215"/>
-      <c r="F47" s="216"/>
+      <c r="E47" s="216"/>
+      <c r="F47" s="217"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="213" t="s">
+      <c r="J47" s="214" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15257,13 +15257,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="210" t="s">
+      <c r="N47" s="211" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
+      <c r="B48" s="214"/>
+      <c r="C48" s="214"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15282,7 +15282,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="213"/>
+      <c r="J48" s="214"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15292,7 +15292,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16725,10 +16725,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="211" t="s">
+      <c r="B44" s="212" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="212"/>
+      <c r="C44" s="213"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16768,23 +16768,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="214" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="213" t="s">
+      <c r="C47" s="214" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="214" t="s">
+      <c r="D47" s="215" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="215"/>
-      <c r="F47" s="216"/>
+      <c r="E47" s="216"/>
+      <c r="F47" s="217"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="213" t="s">
+      <c r="J47" s="214" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16792,13 +16792,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="210" t="s">
+      <c r="N47" s="211" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
+      <c r="B48" s="214"/>
+      <c r="C48" s="214"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16817,7 +16817,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="213"/>
+      <c r="J48" s="214"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16827,7 +16827,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -18412,10 +18412,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="221" t="s">
+      <c r="B44" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="222"/>
+      <c r="C44" s="223"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18480,23 +18480,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="223" t="s">
+      <c r="B47" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="223" t="s">
+      <c r="C47" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="218" t="s">
+      <c r="D47" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="219"/>
-      <c r="F47" s="220"/>
+      <c r="E47" s="220"/>
+      <c r="F47" s="221"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="223" t="s">
+      <c r="J47" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18504,13 +18504,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="217" t="s">
+      <c r="N47" s="218" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="223"/>
-      <c r="C48" s="223"/>
+      <c r="B48" s="224"/>
+      <c r="C48" s="224"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18529,7 +18529,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="223"/>
+      <c r="J48" s="224"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18539,7 +18539,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="217"/>
+      <c r="N48" s="218"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -20161,11 +20161,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20283,10 +20283,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20309,40 +20309,40 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="235"/>
-      <c r="L48" s="236"/>
-      <c r="M48" s="236"/>
-      <c r="N48" s="237"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="236"/>
+      <c r="L48" s="237"/>
+      <c r="M48" s="237"/>
+      <c r="N48" s="238"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="234" t="s">
+      <c r="B49" s="235" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="234" t="s">
+      <c r="C49" s="235" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="231" t="s">
+      <c r="D49" s="232" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="232"/>
-      <c r="F49" s="233"/>
+      <c r="E49" s="233"/>
+      <c r="F49" s="234"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="234" t="s">
+      <c r="J49" s="235" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20350,13 +20350,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="227" t="s">
+      <c r="N49" s="228" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="234"/>
-      <c r="C50" s="234"/>
+      <c r="B50" s="235"/>
+      <c r="C50" s="235"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20375,7 +20375,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="234"/>
+      <c r="J50" s="235"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20385,7 +20385,7 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="227"/>
+      <c r="N50" s="228"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="183" t="s">
@@ -21176,10 +21176,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21190,8 +21190,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -21377,13 +21377,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="228" t="s">
+      <c r="B87" s="229" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="229"/>
-      <c r="D87" s="229"/>
-      <c r="E87" s="229"/>
-      <c r="F87" s="230"/>
+      <c r="C87" s="230"/>
+      <c r="D87" s="230"/>
+      <c r="E87" s="230"/>
+      <c r="F87" s="231"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22338,17 +22338,16 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="245" t="s">
+      <c r="B41" s="246" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="246"/>
-      <c r="D41" s="247"/>
+      <c r="C41" s="247"/>
+      <c r="D41" s="248"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
-        <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22403,7 +22402,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>26366420.008816957</v>
+        <v>27512786.096156824</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22432,7 +22431,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>23149472.071528781</v>
+        <v>24155970.857247423</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22461,15 +22460,15 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>4573854.7808213634</v>
+        <v>4772718.0321614221</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
@@ -22488,7 +22487,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>54089746.861167103</v>
+        <v>56441474.98556567</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22498,40 +22497,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22539,13 +22538,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22564,7 +22563,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22574,7 +22573,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22625,7 +22624,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>6331005.1386068044</v>
+        <v>6606266.2315897085</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22677,7 +22676,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>5664568.1244695829</v>
+        <v>5910853.6950986953</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22729,7 +22728,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>1829392.5916666661</v>
+        <v>1908931.3999999994</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22781,7 +22780,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-1681196.14525113</v>
+        <v>-1754291.6298272661</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22833,7 +22832,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>5449765.7338135885</v>
+        <v>5686712.0700663533</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22885,7 +22884,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>3361979.352289319</v>
+        <v>3508152.3676062459</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22937,7 +22936,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-1046547.3195308149</v>
+        <v>-1092049.37690172</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22989,7 +22988,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>4617267.8431370854</v>
+        <v>4818018.6189256543</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23041,7 +23040,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>4317172.5070843743</v>
+        <v>4504875.6595663037</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23093,7 +23092,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>3150497.8190533496</v>
+        <v>3287475.9850991471</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23145,7 +23144,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>7384839.8919115933</v>
+        <v>7705919.8872120976</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23197,7 +23196,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>4932263.6734238686</v>
+        <v>5146709.9200944724</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23249,7 +23248,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>1441903.4567914754</v>
+        <v>1504594.9114345831</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23301,7 +23300,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>3762979.412880016</v>
+        <v>3926587.2134400164</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23351,7 +23350,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>49515892.08034578</v>
+        <v>51668756.953404292</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23367,10 +23366,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23378,8 +23377,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -23573,13 +23572,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23633,7 +23632,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-556790.7465113526</v>
+        <v>-580999.03983793315</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23662,7 +23661,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-772061.78074510151</v>
+        <v>-805629.68425575807</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23691,7 +23690,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>5902707.3080778224</v>
+        <v>6159346.7562551191</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23776,7 +23775,7 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>4573854.7808213681</v>
+        <v>4772718.0321614277</v>
       </c>
       <c r="I94" s="116"/>
     </row>
@@ -23862,7 +23861,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23944,11 +23943,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>42324438.906558998</v>
+        <v>60029869.416492999</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>7900090.0700000003</v>
+        <v>17068869.389989998</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23966,11 +23965,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>91530233.793256</v>
+        <v>112771179.493204</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>18598016.016090002</v>
+        <v>24938191.736076999</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23978,27 +23977,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>44512904.037834004</v>
+        <v>51927985.045832001</v>
       </c>
       <c r="D10" s="205">
-        <v>6076871.6917989999</v>
+        <v>9516671.6917989999</v>
       </c>
       <c r="E10" s="205">
-        <v>19039638.91</v>
+        <v>24331530.75</v>
       </c>
       <c r="F10" s="205">
-        <v>69629414.639633</v>
+        <v>85776187.487630993</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>99515831.717950001</v>
+        <v>136651201.12355</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>3202914.2803969998</v>
+        <v>5076049.4275939995</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24006,16 +24005,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>67645862.483296007</v>
+        <v>75073920.303231999</v>
       </c>
       <c r="D11" s="205">
-        <v>12952457.544438001</v>
+        <v>15760757.544438001</v>
       </c>
       <c r="E11" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F11" s="205">
-        <v>80598320.027733997</v>
+        <v>90834677.847670004</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -24034,27 +24033,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>51881305.323743001</v>
+        <v>60940764.683730997</v>
       </c>
       <c r="D12" s="205">
-        <v>16256610.616095001</v>
-      </c>
-      <c r="E12" s="205" t="s">
-        <v>168</v>
+        <v>22596786.336082</v>
+      </c>
+      <c r="E12" s="205">
+        <v>810810.8</v>
       </c>
       <c r="F12" s="205">
-        <v>68137915.939838007</v>
+        <v>84348361.819812998</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>68535804.870348006</v>
+        <v>84660301.410301</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>12666684.409902999</v>
+        <v>27898513.309893001</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24062,27 +24061,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>39648928.469512999</v>
+        <v>51830414.809473</v>
       </c>
       <c r="D13" s="205">
         <v>2341405.3999950001</v>
       </c>
       <c r="E13" s="205">
-        <v>1621621.6</v>
+        <v>3711711.64</v>
       </c>
       <c r="F13" s="205">
-        <v>43611955.469508</v>
+        <v>57883531.849468</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>72712611.853913993</v>
+        <v>110075179.547778</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>17340651.849943999</v>
+        <v>27142821.109944001</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24090,27 +24089,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>99515831.717950001</v>
+        <v>136651201.12355</v>
       </c>
       <c r="D14" s="205">
-        <v>3202914.2803969998</v>
+        <v>5076049.4275939995</v>
       </c>
       <c r="E14" s="205">
-        <v>26479279.379999999</v>
+        <v>34320720.909999996</v>
       </c>
       <c r="F14" s="205">
-        <v>129198025.37834699</v>
+        <v>176047971.461144</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>59839203.868955001</v>
+        <v>80813416.962354004</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>9378523.4799959995</v>
+        <v>12619226.239995999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24126,11 +24125,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>67645862.483296007</v>
+        <v>75073920.303231999</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>12952457.544438001</v>
+        <v>15760757.544438001</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24138,27 +24137,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>68535804.870348006</v>
+        <v>84660301.410301</v>
       </c>
       <c r="D16" s="205">
-        <v>12666684.409902999</v>
+        <v>27898513.309893001</v>
       </c>
       <c r="E16" s="205">
         <v>7693693.5999999996</v>
       </c>
       <c r="F16" s="205">
-        <v>88896182.880251005</v>
+        <v>120252508.32019401</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>70627705.995001003</v>
+        <v>89344117.566962004</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>5540529.7199879996</v>
+        <v>10307464.799968001</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24182,11 +24181,11 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>44512904.037834004</v>
+        <v>51927985.045832001</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>6076871.6917989999</v>
+        <v>9516671.6917989999</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24194,7 +24193,7 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>85406364.739962995</v>
+        <v>90114096.079950005</v>
       </c>
       <c r="D18" s="205">
         <v>198198.2</v>
@@ -24203,18 +24202,18 @@
         <v>6237837.7599999998</v>
       </c>
       <c r="F18" s="205">
-        <v>91842400.699963003</v>
+        <v>96550132.039949998</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>99847748.039975002</v>
+        <v>165714161.38511801</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>4005189.12</v>
+        <v>4924989.12</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24222,27 +24221,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>72712611.853913993</v>
+        <v>110075179.547778</v>
       </c>
       <c r="D19" s="205">
-        <v>17340651.849943999</v>
+        <v>27142821.109944001</v>
       </c>
       <c r="E19" s="205">
-        <v>289356769.69999999</v>
+        <v>310744157.09998</v>
       </c>
       <c r="F19" s="205">
-        <v>379410033.40385801</v>
+        <v>447962157.75770199</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>26482162.15989</v>
+        <v>29018929.859889999</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>4160802.5199480001</v>
+        <v>8315629.5999480002</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24250,16 +24249,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>16843042.15989</v>
+        <v>17547729.859889999</v>
       </c>
       <c r="D20" s="205">
-        <v>0</v>
+        <v>4154827.08</v>
       </c>
       <c r="E20" s="205">
         <v>1945946</v>
       </c>
       <c r="F20" s="205">
-        <v>18788988.15989</v>
+        <v>23648502.939890001</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24277,23 +24276,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>9639120</v>
+        <v>11471200</v>
       </c>
       <c r="D21" s="205">
         <v>4160802.5199480001</v>
       </c>
       <c r="E21" s="205">
-        <v>2972973</v>
+        <v>9524324.4600000009</v>
       </c>
       <c r="F21" s="205">
-        <v>16772895.519948</v>
+        <v>25156326.979947999</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>68193346.882744998</v>
+        <v>83852981.795613006</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24306,8 +24305,8 @@
       <c r="C22" s="205">
         <v>29394090</v>
       </c>
-      <c r="D22" s="205">
-        <v>0</v>
+      <c r="D22" s="205" t="s">
+        <v>168</v>
       </c>
       <c r="E22" s="205" t="s">
         <v>168</v>
@@ -24326,8 +24325,8 @@
       <c r="C23" s="205">
         <v>72519364.939999998</v>
       </c>
-      <c r="D23" s="205">
-        <v>0</v>
+      <c r="D23" s="205" t="s">
+        <v>168</v>
       </c>
       <c r="E23" s="205">
         <v>1927927.88</v>
@@ -24344,16 +24343,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>42324438.906558998</v>
+        <v>60029869.416492999</v>
       </c>
       <c r="D24" s="205">
-        <v>7900090.0700000003</v>
+        <v>17068869.389989998</v>
       </c>
       <c r="E24" s="205">
-        <v>18533333.059999999</v>
+        <v>20130630.34</v>
       </c>
       <c r="F24" s="205">
-        <v>68757862.036559001</v>
+        <v>97229369.146483004</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24364,16 +24363,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>59839203.868955001</v>
+        <v>80813416.962354004</v>
       </c>
       <c r="D25" s="205">
-        <v>9378523.4799959995</v>
+        <v>12619226.239995999</v>
       </c>
       <c r="E25" s="205">
-        <v>35945946.749885</v>
+        <v>53549550.189884998</v>
       </c>
       <c r="F25" s="205">
-        <v>105163674.098836</v>
+        <v>146982193.39223501</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24384,16 +24383,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>70627705.995001003</v>
+        <v>89344117.566962004</v>
       </c>
       <c r="D26" s="205">
-        <v>5540529.7199879996</v>
+        <v>10307464.799968001</v>
       </c>
       <c r="E26" s="205">
-        <v>75185406.199884996</v>
+        <v>121198019.099865</v>
       </c>
       <c r="F26" s="205">
-        <v>151353641.91487399</v>
+        <v>220849601.466795</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24404,16 +24403,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>99847748.039975002</v>
+        <v>165714161.38511801</v>
       </c>
       <c r="D27" s="205">
-        <v>4005189.12</v>
+        <v>4924989.12</v>
       </c>
       <c r="E27" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F27" s="205">
-        <v>103852937.15997501</v>
+        <v>170639150.50511801</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24456,7 +24455,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>18227851.429972</v>
+        <v>27648554.289969001</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24466,8 +24465,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="248">
-        <v>23951450.718766998</v>
+      <c r="C33" s="206">
+        <v>25558117.405960999</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24478,7 +24477,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>22819806.153243002</v>
+        <v>23757801.634229999</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24489,7 +24488,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>45373540.729502</v>
+        <v>60095180.161383003</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24531,17 +24530,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.1</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24584,19 +24583,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>882123097.16697824</v>
+        <v>1134628851.5547142</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.12151662125446067</v>
+        <v>0.156300481034405</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>6377156234.8330221</v>
+        <v>6124650480.4452858</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>265714843.11804259</v>
+        <v>266289151.32370809</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24613,19 +24612,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>105748122.70250301</v>
+        <v>167494575.96964699</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>5.844294140645203E-2</v>
+        <v>9.2567843656489887E-2</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1703676936.297497</v>
+        <v>1641930483.0303531</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>70986539.01239571</v>
+        <v>71388281.87088491</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24642,46 +24641,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>110372649.03148399</v>
+        <v>137059653.49154299</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>6.0284886740237867E-2</v>
+        <v>7.4861170406782473E-2</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1720478414.9685161</v>
+        <v>1693791410.5084569</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>71686600.623688176</v>
+        <v>73643104.804715514</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10899555455</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>1098243868.9009652</v>
+        <v>1439183081.0159042</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.10076042765553003</v>
+        <v>0.13204053018104528</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>9801311586.0990353</v>
+        <v>9460372373.9840965</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>408387982.75412649</v>
+        <v>411320537.99930853</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24691,40 +24690,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24732,13 +24731,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24757,7 +24756,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24767,7 +24766,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24790,35 +24789,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>42324438.906558998</v>
+        <v>60029869.416492999</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>7900090.0700000003</v>
+        <v>17068869.389989998</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>50224528.976558998</v>
+        <v>77098738.806483001</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>9.0737610899782981E-2</v>
+        <v>0.13928961615452365</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>409359039.09344101</v>
+        <v>391653608.583507</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>93930332.930000007</v>
+        <v>84761553.610009998</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>503289372.02344102</v>
+        <v>476415162.19351697</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>20970390.500976708</v>
+        <v>20713702.704065956</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24842,35 +24841,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>91530233.793256</v>
+        <v>112771179.493204</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>18598016.016090002</v>
+        <v>24938191.736076999</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>110128249.80934601</v>
+        <v>137709371.22928101</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.13507875845302189</v>
+        <v>0.16890862176780866</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>498652137.20674402</v>
+        <v>477411191.506796</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>206508789.98390999</v>
+        <v>200168614.26392299</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>705160927.19065404</v>
+        <v>677579805.77071905</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>29381705.299610585</v>
+        <v>29459991.555248655</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24922,7 +24921,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>8836632.416666666</v>
+        <v>9220833.826086957</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24946,35 +24945,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>99515831.717950001</v>
+        <v>136651201.12355</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>3202914.2803969998</v>
+        <v>5076049.4275939995</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>102718745.998347</v>
+        <v>141727250.551144</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.14145580790367948</v>
+        <v>0.19517511174641777</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>546196640.28205001</v>
+        <v>509061270.87645</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>77238933.719603002</v>
+        <v>75365798.572405994</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>623435574.00165296</v>
+        <v>584427069.448856</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>25976482.250068873</v>
+        <v>25409872.584732868</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25026,7 +25025,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>22869904.5625</v>
+        <v>23864248.239130434</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25050,35 +25049,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>68535804.870348006</v>
+        <v>84660301.410301</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>12666684.409902999</v>
+        <v>27898513.309893001</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>81202489.280251011</v>
+        <v>112558814.720194</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.15549699084391699</v>
+        <v>0.21554212361079547</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>371527479.12965202</v>
+        <v>355402982.58969903</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>69482640.590096995</v>
+        <v>54250811.690107003</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>441010119.71974897</v>
+        <v>409653794.27980602</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>18375421.654989541</v>
+        <v>17811034.533904608</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25102,35 +25101,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>72712611.853913993</v>
+        <v>110075179.547778</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>17340651.849943999</v>
+        <v>27142821.109944001</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>90053263.703857988</v>
+        <v>137218000.657722</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>8.0243714866468557E-2</v>
+        <v>0.12227077250120164</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>924045733.14608598</v>
+        <v>886683165.45222199</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>108147946.150056</v>
+        <v>98345776.890055999</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>1032193679.296142</v>
+        <v>985028942.342278</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>43008069.970672585</v>
+        <v>42827345.319229476</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25154,35 +25153,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>59839203.868955001</v>
+        <v>80813416.962354004</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>9378523.4799959995</v>
+        <v>12619226.239995999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>69217727.348950997</v>
+        <v>93432643.202350006</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.10855494849630345</v>
+        <v>0.1465314762441173</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>480447855.13104498</v>
+        <v>459473642.037646</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>87962902.520004004</v>
+        <v>84722199.760003999</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>568410757.65104902</v>
+        <v>544195841.79764998</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>23683781.56879371</v>
+        <v>23660688.773810867</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25234,7 +25233,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>13817262.460833333</v>
+        <v>14418013.002608696</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25258,35 +25257,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>67645862.483296007</v>
+        <v>75073920.303231999</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>12952457.544438001</v>
+        <v>15760757.544438001</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>80598320.027734011</v>
+        <v>90834677.847670004</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.13190313731087114</v>
+        <v>0.14865544319791218</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>371371446.51670396</v>
+        <v>363943388.69676799</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>159071954.455562</v>
+        <v>156263654.455562</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>530443400.97226596</v>
+        <v>520207043.15232998</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>22101808.373844415</v>
+        <v>22617697.528362174</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25310,35 +25309,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>70627705.995001003</v>
+        <v>89344117.566962004</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>5540529.7199879996</v>
+        <v>10307464.799968001</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>76168235.714989007</v>
+        <v>99651582.366930008</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.10036250177679344</v>
+        <v>0.13130515651937513</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>596001890.00499904</v>
+        <v>577285478.433038</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>86761092.280011997</v>
+        <v>81994157.200031996</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>682762982.28501105</v>
+        <v>659279635.63306999</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>28448457.595208794</v>
+        <v>28664331.984046523</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25362,35 +25361,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>44512904.037834004</v>
+        <v>51927985.045832001</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>6076871.6917989999</v>
+        <v>9516671.6917989999</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>50589775.729633003</v>
+        <v>61444656.737631001</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>9.7500431376532248E-2</v>
+        <v>0.11842077675376624</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>377030118.96216601</v>
+        <v>369615037.95416802</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>91247304.308201</v>
+        <v>87807504.308201</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>468277423.27036703</v>
+        <v>457422542.26236898</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>19511559.302931961</v>
+        <v>19887936.620102998</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25414,35 +25413,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>99847748.039975002</v>
+        <v>165714161.38511801</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>4005189.12</v>
+        <v>4924989.12</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>103852937.15997501</v>
+        <v>170639150.50511801</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.10578694379890542</v>
+        <v>0.17381688682113561</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>518503193.96002501</v>
+        <v>452636780.61488199</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>359361776.88</v>
+        <v>358441976.88</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>877864970.84002495</v>
+        <v>811078757.49488199</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>36577707.118334375</v>
+        <v>35264293.804125302</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25466,35 +25465,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>26482162.15989</v>
+        <v>29018929.859889999</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>4160802.5199480001</v>
+        <v>8315629.5999480002</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>30642964.679838002</v>
+        <v>37334559.459838003</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>5.2286774932473919E-2</v>
+        <v>6.3704792538041552E-2</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>268043526.84011</v>
+        <v>265506759.14011002</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>287369250.48005199</v>
+        <v>283214423.40005201</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>555412777.32016206</v>
+        <v>548721182.54016197</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>23142199.055006754</v>
+        <v>23857442.719137479</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25516,35 +25515,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>882123097.16697824</v>
+        <v>1134628851.5547142</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>105748122.70250301</v>
+        <v>167494575.96964699</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>987871219.86948109</v>
+        <v>1302123427.5243607</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.10893190220753785</v>
+        <v>0.14358428408104462</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>6377156234.8330212</v>
+        <v>6124650480.4452858</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1703676936.297497</v>
+        <v>1641930483.0303531</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>8080833171.1305189</v>
+        <v>7766580963.4756403</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>336701382.13043827</v>
+        <v>337677433.19459307</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25560,10 +25559,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25571,8 +25570,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -25586,7 +25585,7 @@
       </c>
       <c r="D70" s="148">
         <f>IF(E24="",0,E24)</f>
-        <v>18533333.059999999</v>
+        <v>20130630.34</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25598,7 +25597,7 @@
       </c>
       <c r="D71" s="149">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>1621621.6</v>
+        <v>4522522.4400000004</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25622,7 +25621,7 @@
       </c>
       <c r="D73" s="148">
         <f>IF(E14="",0,E14)</f>
-        <v>26479279.379999999</v>
+        <v>34320720.909999996</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25645,8 +25644,7 @@
         <v>74</v>
       </c>
       <c r="D75" s="148">
-        <f>0</f>
-        <v>0</v>
+        <v>7693693.5999999996</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25658,7 +25656,7 @@
       </c>
       <c r="D76" s="149">
         <f>IF(E19="",0,E19)</f>
-        <v>289356769.69999999</v>
+        <v>310744157.09998</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25670,7 +25668,7 @@
       </c>
       <c r="D77" s="148">
         <f>IF(E25="",0,E25)</f>
-        <v>35945946.749885</v>
+        <v>53549550.189884998</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25706,7 +25704,7 @@
       </c>
       <c r="D80" s="148">
         <f>IF(E26="",0,E26)</f>
-        <v>75185406.199884996</v>
+        <v>121198019.099865</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25718,7 +25716,7 @@
       </c>
       <c r="D81" s="149">
         <f>IF(E10="",0,E10)</f>
-        <v>19039638.91</v>
+        <v>24331530.75</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25728,8 +25726,8 @@
       <c r="C82" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="148">
-        <f>0</f>
+      <c r="D82" s="149">
+        <f t="shared" ref="D82:D83" si="7">IF(E11="",0,E11)</f>
         <v>0</v>
       </c>
     </row>
@@ -25741,8 +25739,7 @@
         <v>89</v>
       </c>
       <c r="D83" s="149">
-        <f>0</f>
-        <v>0</v>
+        <v>11470270.460000001</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25752,7 +25749,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>468089923.47977006</v>
+        <v>589889022.76973009</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25766,13 +25763,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25814,19 +25811,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>18227851.429972</v>
+        <v>27648554.289969001</v>
       </c>
       <c r="F89" s="61">
-        <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>6.383853229875544E-2</v>
+        <f t="shared" ref="F89:F94" si="8">IFERROR(E89/D89,0)</f>
+        <v>9.6832209371194689E-2</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>267302701.57002801</v>
+        <v>257881998.710031</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>11137612.565417834</v>
+        <v>11212260.813479608</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25843,19 +25840,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>23951450.718766998</v>
+        <v>25558117.405960999</v>
       </c>
       <c r="F90" s="61">
-        <f t="shared" si="7"/>
-        <v>5.5852829937107086E-2</v>
+        <f t="shared" si="8"/>
+        <v>5.9599445634800463E-2</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>404880011.28123301</v>
+        <v>403273344.59403902</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16870000.470051374</v>
+        <v>17533623.678001698</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25872,19 +25869,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>68193346.882744998</v>
+        <v>83852981.795613006</v>
       </c>
       <c r="F91" s="61">
-        <f t="shared" si="7"/>
-        <v>6.1078384014445444E-2</v>
+        <f t="shared" si="8"/>
+        <v>7.5104168617432632E-2</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>1048295702.117255</v>
+        <v>1032636067.2043869</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>43678987.588218957</v>
+        <v>44897220.313234217</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25904,7 +25901,7 @@
         <v>0</v>
       </c>
       <c r="F92" s="61">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G92" s="126">
@@ -25933,7 +25930,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="61">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G93" s="125">
@@ -25957,19 +25954,19 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>110372649.03148399</v>
+        <v>137059653.49154299</v>
       </c>
       <c r="F94" s="43">
-        <f t="shared" si="7"/>
-        <v>6.0284886740237867E-2</v>
+        <f t="shared" si="8"/>
+        <v>7.4861170406782473E-2</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1720478414.9685159</v>
+        <v>1693791410.5084569</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>71686600.623688161</v>
+        <v>73643104.804715514</v>
       </c>
       <c r="I94" s="116"/>
     </row>
@@ -26588,11 +26585,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26716,10 +26713,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26748,40 +26745,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26789,13 +26786,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26814,7 +26811,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26824,7 +26821,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27617,10 +27614,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27628,8 +27625,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -27823,13 +27820,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 04 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 05 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>27512786.096156824</v>
+        <v>28763367.282345772</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22431,7 +22431,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>24155970.857247423</v>
+        <v>25253969.532576855</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22460,7 +22460,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>4772718.0321614221</v>
+        <v>4989659.7608960327</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22487,7 +22487,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>56441474.98556567</v>
+        <v>59006996.575818658</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22624,7 +22624,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>6606266.2315897085</v>
+        <v>6906551.060298332</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>5910853.6950986953</v>
+        <v>6179528.863057727</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>1908931.3999999994</v>
+        <v>1995701.0090909086</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22780,7 +22780,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-1754291.6298272661</v>
+        <v>-1834032.1584557781</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>5686712.0700663533</v>
+        <v>5945198.982342097</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>3508152.3676062459</v>
+        <v>3667613.8388610752</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-1092049.37690172</v>
+        <v>-1141687.9849427072</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22988,7 +22988,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>4818018.6189256543</v>
+        <v>5037019.4652404571</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>4504875.6595663037</v>
+        <v>4709642.7350011356</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>3287475.9850991471</v>
+        <v>3436906.7116945628</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23144,7 +23144,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>7705919.8872120976</v>
+        <v>8056188.9729944654</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>5146709.9200944724</v>
+        <v>5380651.2800987661</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>1504594.9114345831</v>
+        <v>1572985.589227064</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>3926587.2134400164</v>
+        <v>4105068.4504145626</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>51668756.953404292</v>
+        <v>54017336.814922668</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23632,7 +23632,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-580999.03983793315</v>
+        <v>-607408.08710329374</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-805629.68425575807</v>
+        <v>-842249.21535829257</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23690,7 +23690,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>6159346.7562551191</v>
+        <v>6439317.0633576242</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>4772718.0321614277</v>
+        <v>4989659.7608960383</v>
       </c>
       <c r="I94" s="116"/>
     </row>
@@ -23825,7 +23825,7 @@
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" customWidth="1"/>
     <col min="10" max="10" width="9.28515625" customWidth="1"/>
-    <col min="11" max="11" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" customWidth="1"/>
     <col min="12" max="12" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
@@ -23861,7 +23861,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23943,11 +23943,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>60029869.416492999</v>
+        <v>81414157.224280998</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>17068869.389989998</v>
+        <v>22378576.639989998</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23965,11 +23965,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>112771179.493204</v>
+        <v>128198477.063154</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>24938191.736076999</v>
+        <v>26460601.666076999</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23977,23 +23977,23 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>51927985.045832001</v>
+        <v>58290237.251025997</v>
       </c>
       <c r="D10" s="205">
-        <v>9516671.6917989999</v>
+        <v>10524671.691799</v>
       </c>
       <c r="E10" s="205">
-        <v>24331530.75</v>
+        <v>27427197.370000001</v>
       </c>
       <c r="F10" s="205">
-        <v>85776187.487630993</v>
+        <v>96242106.312824994</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>136651201.12355</v>
+        <v>188735680.79965001</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
@@ -24005,23 +24005,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>75073920.303231999</v>
+        <v>93761492.889708996</v>
       </c>
       <c r="D11" s="205">
-        <v>15760757.544438001</v>
+        <v>18421257.544438001</v>
       </c>
       <c r="E11" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F11" s="205">
-        <v>90834677.847670004</v>
+        <v>112182750.434147</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>36635134.5</v>
+        <v>39283783.140000001</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24033,27 +24033,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>60940764.683730997</v>
+        <v>64165359.283730999</v>
       </c>
       <c r="D12" s="205">
-        <v>22596786.336082</v>
+        <v>23569628.696082</v>
       </c>
       <c r="E12" s="205">
-        <v>810810.8</v>
+        <v>1859459.44</v>
       </c>
       <c r="F12" s="205">
-        <v>84348361.819812998</v>
+        <v>89594447.419813007</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>84660301.410301</v>
+        <v>141386234.56545201</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>27898513.309893001</v>
+        <v>33458193.469863001</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24061,27 +24061,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>51830414.809473</v>
+        <v>64033117.779422998</v>
       </c>
       <c r="D13" s="205">
-        <v>2341405.3999950001</v>
+        <v>2890972.9699949999</v>
       </c>
       <c r="E13" s="205">
-        <v>3711711.64</v>
+        <v>4570360.28</v>
       </c>
       <c r="F13" s="205">
-        <v>57883531.849468</v>
+        <v>71494451.029418007</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>110075179.547778</v>
+        <v>173025435.4937</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>27142821.109944001</v>
+        <v>27394821.109944001</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24089,27 +24089,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>136651201.12355</v>
+        <v>188735680.79965001</v>
       </c>
       <c r="D14" s="205">
         <v>5076049.4275939995</v>
       </c>
       <c r="E14" s="205">
-        <v>34320720.909999996</v>
+        <v>43971171.439999998</v>
       </c>
       <c r="F14" s="205">
-        <v>176047971.461144</v>
+        <v>237782901.66724399</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>80813416.962354004</v>
+        <v>94384464.072352007</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>12619226.239995999</v>
+        <v>14537892.899995999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24125,11 +24125,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>75073920.303231999</v>
+        <v>93761492.889708996</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>15760757.544438001</v>
+        <v>18421257.544438001</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24137,23 +24137,23 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>84660301.410301</v>
+        <v>141386234.56545201</v>
       </c>
       <c r="D16" s="205">
-        <v>27898513.309893001</v>
+        <v>33458193.469863001</v>
       </c>
       <c r="E16" s="205">
-        <v>7693693.5999999996</v>
+        <v>7963693.5999999996</v>
       </c>
       <c r="F16" s="205">
-        <v>120252508.32019401</v>
+        <v>182808121.635315</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>89344117.566962004</v>
+        <v>117382243.771851</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
@@ -24165,7 +24165,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>36635134.5</v>
+        <v>39283783.140000001</v>
       </c>
       <c r="D17" s="205">
         <v>3925392</v>
@@ -24174,18 +24174,18 @@
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>40560526.5</v>
+        <v>43209175.140000001</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>51927985.045832001</v>
+        <v>58290237.251025997</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>9516671.6917989999</v>
+        <v>10524671.691799</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24193,27 +24193,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>90114096.079950005</v>
+        <v>127815836.09394801</v>
       </c>
       <c r="D18" s="205">
-        <v>198198.2</v>
+        <v>297297.3</v>
       </c>
       <c r="E18" s="205">
         <v>6237837.7599999998</v>
       </c>
       <c r="F18" s="205">
-        <v>96550132.039949998</v>
+        <v>134350971.15394801</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>165714161.38511801</v>
+        <v>210565565.854633</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>4924989.12</v>
+        <v>7459839.1200000001</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24221,27 +24221,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>110075179.547778</v>
+        <v>173025435.4937</v>
       </c>
       <c r="D19" s="205">
-        <v>27142821.109944001</v>
+        <v>27394821.109944001</v>
       </c>
       <c r="E19" s="205">
-        <v>310744157.09998</v>
+        <v>366397128.41997999</v>
       </c>
       <c r="F19" s="205">
-        <v>447962157.75770199</v>
+        <v>566817385.02362394</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>29018929.859889999</v>
+        <v>35415225.659889996</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>8315629.5999480002</v>
+        <v>10206534.879948001</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24249,7 +24249,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>17547729.859889999</v>
+        <v>21758537.65989</v>
       </c>
       <c r="D20" s="205">
         <v>4154827.08</v>
@@ -24258,7 +24258,7 @@
         <v>1945946</v>
       </c>
       <c r="F20" s="205">
-        <v>23648502.939890001</v>
+        <v>27859310.739890002</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24276,23 +24276,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>11471200</v>
+        <v>13656688</v>
       </c>
       <c r="D21" s="205">
-        <v>4160802.5199480001</v>
+        <v>6051707.7999480003</v>
       </c>
       <c r="E21" s="205">
-        <v>9524324.4600000009</v>
+        <v>10735135.300000001</v>
       </c>
       <c r="F21" s="205">
-        <v>25156326.979947999</v>
+        <v>30443531.099948</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>83852981.795613006</v>
+        <v>90820756.643530995</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24303,7 +24303,7 @@
         <v>172</v>
       </c>
       <c r="C22" s="205">
-        <v>29394090</v>
+        <v>35091520</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>168</v>
@@ -24312,7 +24312,7 @@
         <v>168</v>
       </c>
       <c r="F22" s="205">
-        <v>29394090</v>
+        <v>35091520</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24329,10 +24329,10 @@
         <v>168</v>
       </c>
       <c r="E23" s="205">
-        <v>1927927.88</v>
+        <v>1957927.88</v>
       </c>
       <c r="F23" s="205">
-        <v>74447292.819999993</v>
+        <v>74477292.819999993</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24343,16 +24343,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>60029869.416492999</v>
+        <v>81414157.224280998</v>
       </c>
       <c r="D24" s="205">
-        <v>17068869.389989998</v>
+        <v>22378576.639989998</v>
       </c>
       <c r="E24" s="205">
-        <v>20130630.34</v>
+        <v>94584054.779899999</v>
       </c>
       <c r="F24" s="205">
-        <v>97229369.146483004</v>
+        <v>198376788.644171</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24363,16 +24363,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>80813416.962354004</v>
+        <v>94384464.072352007</v>
       </c>
       <c r="D25" s="205">
-        <v>12619226.239995999</v>
+        <v>14537892.899995999</v>
       </c>
       <c r="E25" s="205">
-        <v>53549550.189884998</v>
+        <v>63175226.039860003</v>
       </c>
       <c r="F25" s="205">
-        <v>146982193.39223501</v>
+        <v>172097583.01220801</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24383,16 +24383,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>89344117.566962004</v>
+        <v>117382243.771851</v>
       </c>
       <c r="D26" s="205">
         <v>10307464.799968001</v>
       </c>
       <c r="E26" s="205">
-        <v>121198019.099865</v>
+        <v>146977208.35986501</v>
       </c>
       <c r="F26" s="205">
-        <v>220849601.466795</v>
+        <v>274666916.93168402</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24403,16 +24403,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>165714161.38511801</v>
+        <v>210565565.854633</v>
       </c>
       <c r="D27" s="205">
-        <v>4924989.12</v>
+        <v>7459839.1200000001</v>
       </c>
       <c r="E27" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F27" s="205">
-        <v>170639150.50511801</v>
+        <v>218025404.97463301</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24455,7 +24455,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>27648554.289969001</v>
+        <v>34371437.009887002</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24466,7 +24466,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>25558117.405960999</v>
+        <v>47089037.045641005</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24477,7 +24477,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>23757801.634229999</v>
+        <v>26435846.722212002</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24488,7 +24488,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>60095180.161383003</v>
+        <v>64384909.921319</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24540,7 +24540,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.13333333333333333</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24583,19 +24583,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>1134628851.5547142</v>
+        <v>1469453882.725698</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.156300481034405</v>
+        <v>0.20242420983142545</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>6124650480.4452858</v>
+        <v>5789825449.2743015</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>266289151.32370809</v>
+        <v>263173884.05792281</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24612,19 +24612,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>167494575.96964699</v>
+        <v>190151295.24961701</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>9.2567843656489887E-2</v>
+        <v>0.10508934553758549</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1641930483.0303531</v>
+        <v>1619273763.7503829</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>71388281.87088491</v>
+        <v>73603352.897744671</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24641,19 +24641,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>137059653.49154299</v>
+        <v>172281230.69905901</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>7.4861170406782473E-2</v>
+        <v>9.4098987124962022E-2</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1693791410.5084569</v>
+        <v>1658569833.300941</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>73643104.804715514</v>
+        <v>75389537.877315506</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24668,19 +24668,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>1439183081.0159042</v>
+        <v>1831886408.6743741</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.13204053018104528</v>
+        <v>0.16806982782348476</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>9460372373.9840965</v>
+        <v>9067669046.3256264</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>411320537.99930853</v>
+        <v>412166774.83298302</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24789,35 +24789,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>60029869.416492999</v>
+        <v>81414157.224280998</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>17068869.389989998</v>
+        <v>22378576.639989998</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>77098738.806483001</v>
+        <v>103792733.864271</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.13928961615452365</v>
+        <v>0.18751603830862235</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>391653608.583507</v>
+        <v>370269320.77571899</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>84761553.610009998</v>
+        <v>79451846.360009998</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>476415162.19351697</v>
+        <v>449721167.13572901</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>20713702.704065956</v>
+        <v>20441871.233442228</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24841,35 +24841,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>112771179.493204</v>
+        <v>128198477.063154</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>24938191.736076999</v>
+        <v>26460601.666076999</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>137709371.22928101</v>
+        <v>154659078.729231</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.16890862176780866</v>
+        <v>0.18969843227690855</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>477411191.506796</v>
+        <v>461983893.93684602</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>200168614.26392299</v>
+        <v>198646204.33392301</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>677579805.77071905</v>
+        <v>660630098.270769</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>29459991.555248655</v>
+        <v>30028640.830489501</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>29394090</v>
+        <v>35091520</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -24901,15 +24901,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>29394090</v>
+        <v>35091520</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.12172813265607521</v>
+        <v>0.14532258701199174</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>212079178</v>
+        <v>206381748</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -24917,11 +24917,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>212079178</v>
+        <v>206381748</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>9220833.826086957</v>
+        <v>9380988.5454545449</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24945,7 +24945,7 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>136651201.12355</v>
+        <v>188735680.79965001</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
@@ -24953,15 +24953,15 @@
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>141727250.551144</v>
+        <v>193811730.22724402</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.19517511174641777</v>
+        <v>0.26690157297039013</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>509061270.87645</v>
+        <v>456976791.20034999</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
@@ -24969,11 +24969,11 @@
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>584427069.448856</v>
+        <v>532342589.77275598</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>25409872.584732868</v>
+        <v>24197390.444216181</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>36635134.5</v>
+        <v>39283783.140000001</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25005,15 +25005,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>40560526.5</v>
+        <v>43209175.140000001</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>6.8812174071449281E-2</v>
+        <v>7.3305687519056709E-2</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>472283697.5</v>
+        <v>469635048.86000001</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25021,11 +25021,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>548877709.5</v>
+        <v>546229060.86000001</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>23864248.239130434</v>
+        <v>24828593.675454546</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25049,35 +25049,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>84660301.410301</v>
+        <v>141386234.56545201</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>27898513.309893001</v>
+        <v>33458193.469863001</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>112558814.720194</v>
+        <v>174844428.03531501</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.21554212361079547</v>
+        <v>0.33481464258423338</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>355402982.58969903</v>
+        <v>298677049.43454802</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>54250811.690107003</v>
+        <v>48691131.530137002</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>409653794.27980602</v>
+        <v>347368180.96468496</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>17811034.533904608</v>
+        <v>15789462.771122044</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25101,35 +25101,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>110075179.547778</v>
+        <v>173025435.4937</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>27142821.109944001</v>
+        <v>27394821.109944001</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>137218000.657722</v>
+        <v>200420256.60364401</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.12227077250120164</v>
+        <v>0.17858837384566972</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>886683165.45222199</v>
+        <v>823732909.50629997</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>98345776.890055999</v>
+        <v>98093776.890055999</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>985028942.342278</v>
+        <v>921826686.39635599</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>42827345.319229476</v>
+        <v>41901213.018016182</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25153,35 +25153,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>80813416.962354004</v>
+        <v>94384464.072352007</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>12619226.239995999</v>
+        <v>14537892.899995999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>93432643.202350006</v>
+        <v>108922356.972348</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.1465314762441173</v>
+        <v>0.17082417039814024</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>459473642.037646</v>
+        <v>445902594.92764801</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>84722199.760003999</v>
+        <v>82803533.100004002</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>544195841.79764998</v>
+        <v>528706128.02765203</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>23660688.773810867</v>
+        <v>24032096.728529636</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>14418013.002608696</v>
+        <v>15073377.23</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25257,35 +25257,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>75073920.303231999</v>
+        <v>93761492.889708996</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>15760757.544438001</v>
+        <v>18421257.544438001</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>90834677.847670004</v>
+        <v>112182750.434147</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.14865544319791218</v>
+        <v>0.18359261991235948</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>363943388.69676799</v>
+        <v>345255816.110291</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>156263654.455562</v>
+        <v>153603154.455562</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>520207043.15232998</v>
+        <v>498858970.565853</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>22617697.528362174</v>
+        <v>22675407.752993319</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25309,7 +25309,7 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>89344117.566962004</v>
+        <v>117382243.771851</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
@@ -25317,15 +25317,15 @@
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>99651582.366930008</v>
+        <v>127689708.57181901</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.13130515651937513</v>
+        <v>0.16824938221452765</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>577285478.433038</v>
+        <v>549247352.22814894</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
@@ -25333,11 +25333,11 @@
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>659279635.63306999</v>
+        <v>631241509.42818093</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>28664331.984046523</v>
+        <v>28692795.883099135</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25361,35 +25361,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>51927985.045832001</v>
+        <v>58290237.251025997</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>9516671.6917989999</v>
+        <v>10524671.691799</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>61444656.737631001</v>
+        <v>68814908.94282499</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.11842077675376624</v>
+        <v>0.13262528268398979</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>369615037.95416802</v>
+        <v>363252785.74897403</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>87807504.308201</v>
+        <v>86799504.308201</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>457422542.26236898</v>
+        <v>450052290.05717504</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>19887936.620102998</v>
+        <v>20456922.275326136</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25413,35 +25413,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>165714161.38511801</v>
+        <v>210565565.854633</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>4924989.12</v>
+        <v>7459839.1200000001</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>170639150.50511801</v>
+        <v>218025404.97463301</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.17381688682113561</v>
+        <v>0.22208559424041088</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>452636780.61488199</v>
+        <v>407785376.14536703</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>358441976.88</v>
+        <v>355907126.88</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>811078757.49488199</v>
+        <v>763692503.02536702</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>35264293.804125302</v>
+        <v>34713295.592062138</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25465,35 +25465,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>29018929.859889999</v>
+        <v>35415225.659889996</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>8315629.5999480002</v>
+        <v>10206534.879948001</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>37334559.459838003</v>
+        <v>45621760.539838001</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>6.3704792538041552E-2</v>
+        <v>7.7845428805367808E-2</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>265506759.14011002</v>
+        <v>259110463.34011</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>283214423.40005201</v>
+        <v>281323518.12005198</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>548721182.54016197</v>
+        <v>540433981.46016204</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>23857442.719137479</v>
+        <v>24565180.975461911</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25515,35 +25515,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>1134628851.5547142</v>
+        <v>1469453882.725698</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>167494575.96964699</v>
+        <v>190151295.24961701</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>1302123427.5243607</v>
+        <v>1659605177.9753151</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.14358428408104462</v>
+        <v>0.18300355887907727</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>6124650480.4452858</v>
+        <v>5789825449.2743006</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1641930483.0303531</v>
+        <v>1619273763.7503829</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>7766580963.4756403</v>
+        <v>7409099213.0246849</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>337677433.19459307</v>
+        <v>336777236.9556675</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="D70" s="148">
         <f>IF(E24="",0,E24)</f>
-        <v>20130630.34</v>
+        <v>94584054.779899999</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25597,7 +25597,7 @@
       </c>
       <c r="D71" s="149">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>4522522.4400000004</v>
+        <v>6429819.7200000007</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25621,7 +25621,7 @@
       </c>
       <c r="D73" s="148">
         <f>IF(E14="",0,E14)</f>
-        <v>34320720.909999996</v>
+        <v>43971171.439999998</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25656,7 +25656,7 @@
       </c>
       <c r="D76" s="149">
         <f>IF(E19="",0,E19)</f>
-        <v>310744157.09998</v>
+        <v>366397128.41997999</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="D77" s="148">
         <f>IF(E25="",0,E25)</f>
-        <v>53549550.189884998</v>
+        <v>63175226.039860003</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
-        <v>1927927.88</v>
+        <v>1957927.88</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="D80" s="148">
         <f>IF(E26="",0,E26)</f>
-        <v>121198019.099865</v>
+        <v>146977208.35986501</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25716,7 +25716,7 @@
       </c>
       <c r="D81" s="149">
         <f>IF(E10="",0,E10)</f>
-        <v>24331530.75</v>
+        <v>27427197.370000001</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25727,7 +25727,7 @@
         <v>87</v>
       </c>
       <c r="D82" s="149">
-        <f t="shared" ref="D82:D83" si="7">IF(E11="",0,E11)</f>
+        <f t="shared" ref="D82" si="7">IF(E11="",0,E11)</f>
         <v>0</v>
       </c>
     </row>
@@ -25739,7 +25739,7 @@
         <v>89</v>
       </c>
       <c r="D83" s="149">
-        <v>11470270.460000001</v>
+        <v>12681081.300000001</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25749,7 +25749,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>589889022.76973009</v>
+        <v>771294508.90960491</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25811,19 +25811,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>27648554.289969001</v>
+        <v>34371437.009887002</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="8">IFERROR(E89/D89,0)</f>
-        <v>9.6832209371194689E-2</v>
+        <v>0.12037743999286479</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>257881998.710031</v>
+        <v>251159115.99011299</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>11212260.813479608</v>
+        <v>11416323.454096045</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25840,19 +25840,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>25558117.405960999</v>
+        <v>47089037.045641005</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="8"/>
-        <v>5.9599445634800463E-2</v>
+        <v>0.10980779447950348</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>403273344.59403902</v>
+        <v>381742424.95435899</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>17533623.678001698</v>
+        <v>17351928.407016318</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25869,19 +25869,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>83852981.795613006</v>
+        <v>90820756.643530995</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="8"/>
-        <v>7.5104168617432632E-2</v>
+        <v>8.1344959652650387E-2</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>1032636067.2043869</v>
+        <v>1025668292.356469</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>44897220.313234217</v>
+        <v>46621286.016203135</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25954,19 +25954,19 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>137059653.49154299</v>
+        <v>172281230.69905901</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="8"/>
-        <v>7.4861170406782473E-2</v>
+        <v>9.4098987124962022E-2</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1693791410.5084569</v>
+        <v>1658569833.300941</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>73643104.804715514</v>
+        <v>75389537.877315506</v>
       </c>
       <c r="I94" s="116"/>
     </row>

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 05 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 06 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1928,6 +1928,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1947,15 +1956,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3600,10 +3600,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4664,13 +4664,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4873,11 +4873,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4885,6 +4880,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5657,10 +5657,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6721,13 +6721,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6930,11 +6930,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6942,6 +6937,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7714,10 +7714,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8778,13 +8778,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8987,11 +8987,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8999,6 +8994,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9771,10 +9771,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10835,13 +10835,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11044,11 +11044,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11056,6 +11051,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11827,10 +11827,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12877,13 +12877,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13086,11 +13086,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13098,6 +13093,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22338,11 +22338,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="246" t="s">
+      <c r="B41" s="239" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="247"/>
-      <c r="D41" s="248"/>
+      <c r="C41" s="240"/>
+      <c r="D41" s="241"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>28763367.282345772</v>
+        <v>30133051.438647952</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22431,7 +22431,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>25253969.532576855</v>
+        <v>26456539.510318607</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22460,7 +22460,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>4989659.7608960327</v>
+        <v>5227262.6066529863</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22487,7 +22487,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>59006996.575818658</v>
+        <v>61816853.555619545</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22508,10 +22508,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22573,7 +22573,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>6906551.060298332</v>
+        <v>7235434.4441220621</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>6179528.863057727</v>
+        <v>6473792.1422509523</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>1995701.0090909086</v>
+        <v>2090734.39047619</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22780,7 +22780,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-1834032.1584557781</v>
+        <v>-1921367.0231441488</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>5945198.982342097</v>
+        <v>6228303.6957869586</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>3667613.8388610752</v>
+        <v>3842262.116902079</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-1141687.9849427072</v>
+        <v>-1196054.0794637885</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22988,7 +22988,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>5037019.4652404571</v>
+        <v>5276877.5350138117</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>4709642.7350011356</v>
+        <v>4933911.4366678568</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>3436906.7116945628</v>
+        <v>3600568.9360609706</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23144,7 +23144,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>8056188.9729944654</v>
+        <v>8439817.0193275362</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>5380651.2800987661</v>
+        <v>5636872.7696272787</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>1572985.589227064</v>
+        <v>1647889.6649045434</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>4105068.4504145626</v>
+        <v>4300547.900434304</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>54017336.814922668</v>
+        <v>56589590.948966607</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23572,13 +23572,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-607408.08710329374</v>
+        <v>-636332.2817272601</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-842249.21535829257</v>
+        <v>-882356.3208515445</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23690,7 +23690,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>6439317.0633576242</v>
+        <v>6745951.2092317967</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23775,17 +23775,12 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>4989659.7608960383</v>
+        <v>5227262.6066529918</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23793,6 +23788,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23861,7 +23861,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23943,11 +23943,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>81414157.224280998</v>
+        <v>85072270.124280006</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>22378576.639989998</v>
+        <v>24342576.659990001</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23965,11 +23965,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>128198477.063154</v>
+        <v>149603134.68308198</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>26460601.666076999</v>
+        <v>27944511.576076999</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23977,27 +23977,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>58290237.251025997</v>
+        <v>68630018.114123002</v>
       </c>
       <c r="D10" s="205">
-        <v>10524671.691799</v>
+        <v>11028671.691799</v>
       </c>
       <c r="E10" s="205">
-        <v>27427197.370000001</v>
+        <v>40349719.649999999</v>
       </c>
       <c r="F10" s="205">
-        <v>96242106.312824994</v>
+        <v>120008409.45592199</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>188735680.79965001</v>
+        <v>228165305.08983999</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>5076049.4275939995</v>
+        <v>6480445.8275939999</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24005,23 +24005,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>93761492.889708996</v>
+        <v>104622545.667676</v>
       </c>
       <c r="D11" s="205">
-        <v>18421257.544438001</v>
+        <v>19232014.304437999</v>
       </c>
       <c r="E11" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F11" s="205">
-        <v>112182750.434147</v>
+        <v>123854559.972114</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>39283783.140000001</v>
+        <v>69734233.040000007</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24033,27 +24033,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>64165359.283730999</v>
+        <v>72797179.063658997</v>
       </c>
       <c r="D12" s="205">
-        <v>23569628.696082</v>
+        <v>25053538.606082</v>
       </c>
       <c r="E12" s="205">
         <v>1859459.44</v>
       </c>
       <c r="F12" s="205">
-        <v>89594447.419813007</v>
+        <v>99710177.109741002</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>141386234.56545201</v>
+        <v>143216240.83604801</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>33458193.469863001</v>
+        <v>33998734.009856999</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24061,27 +24061,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>64033117.779422998</v>
+        <v>76805955.619423002</v>
       </c>
       <c r="D13" s="205">
         <v>2890972.9699949999</v>
       </c>
       <c r="E13" s="205">
-        <v>4570360.28</v>
+        <v>5381171.0800000001</v>
       </c>
       <c r="F13" s="205">
-        <v>71494451.029418007</v>
+        <v>85078099.669418007</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>173025435.4937</v>
+        <v>187530673.70565599</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>27394821.109944001</v>
+        <v>30024821.109944001</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24089,27 +24089,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>188735680.79965001</v>
+        <v>228165305.08983999</v>
       </c>
       <c r="D14" s="205">
-        <v>5076049.4275939995</v>
+        <v>6480445.8275939999</v>
       </c>
       <c r="E14" s="205">
-        <v>43971171.439999998</v>
+        <v>66451712.039999999</v>
       </c>
       <c r="F14" s="205">
-        <v>237782901.66724399</v>
+        <v>301097462.957434</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>94384464.072352007</v>
+        <v>113083899.692844</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>14537892.899995999</v>
+        <v>15654556.019983999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24125,11 +24125,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>93761492.889708996</v>
+        <v>104622545.667676</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>18421257.544438001</v>
+        <v>19232014.304437999</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24137,27 +24137,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>141386234.56545201</v>
+        <v>143216240.83604801</v>
       </c>
       <c r="D16" s="205">
-        <v>33458193.469863001</v>
+        <v>33998734.009856999</v>
       </c>
       <c r="E16" s="205">
         <v>7963693.5999999996</v>
       </c>
       <c r="F16" s="205">
-        <v>182808121.635315</v>
+        <v>185178668.445905</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>117382243.771851</v>
+        <v>136943853.57716101</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>10307464.799968001</v>
+        <v>11584324.495468</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24165,7 +24165,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>39283783.140000001</v>
+        <v>69734233.040000007</v>
       </c>
       <c r="D17" s="205">
         <v>3925392</v>
@@ -24174,18 +24174,18 @@
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>43209175.140000001</v>
+        <v>73659625.040000007</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>58290237.251025997</v>
+        <v>68630018.114123002</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>10524671.691799</v>
+        <v>11028671.691799</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24193,27 +24193,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>127815836.09394801</v>
+        <v>131301106.353948</v>
       </c>
       <c r="D18" s="205">
-        <v>297297.3</v>
+        <v>531441.44999800005</v>
       </c>
       <c r="E18" s="205">
         <v>6237837.7599999998</v>
       </c>
       <c r="F18" s="205">
-        <v>134350971.15394801</v>
+        <v>138070385.56394601</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>210565565.854633</v>
+        <v>215334935.084598</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>7459839.1200000001</v>
+        <v>11198866.199999999</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24221,23 +24221,23 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>173025435.4937</v>
+        <v>187530673.70565599</v>
       </c>
       <c r="D19" s="205">
-        <v>27394821.109944001</v>
+        <v>30024821.109944001</v>
       </c>
       <c r="E19" s="205">
-        <v>366397128.41997999</v>
+        <v>390736047.13998002</v>
       </c>
       <c r="F19" s="205">
-        <v>566817385.02362394</v>
+        <v>608291541.95558</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>35415225.659889996</v>
+        <v>43742360.789889999</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
@@ -24249,7 +24249,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>21758537.65989</v>
+        <v>29893672.789889999</v>
       </c>
       <c r="D20" s="205">
         <v>4154827.08</v>
@@ -24258,7 +24258,7 @@
         <v>1945946</v>
       </c>
       <c r="F20" s="205">
-        <v>27859310.739890002</v>
+        <v>35994445.869889997</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24276,7 +24276,7 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>13656688</v>
+        <v>13848688</v>
       </c>
       <c r="D21" s="205">
         <v>6051707.7999480003</v>
@@ -24285,14 +24285,14 @@
         <v>10735135.300000001</v>
       </c>
       <c r="F21" s="205">
-        <v>30443531.099948</v>
+        <v>30635531.099948</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>90820756.643530995</v>
+        <v>99533143.973503992</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24323,7 +24323,7 @@
         <v>173</v>
       </c>
       <c r="C23" s="205">
-        <v>72519364.939999998</v>
+        <v>92325602.239999995</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>168</v>
@@ -24332,7 +24332,7 @@
         <v>1957927.88</v>
       </c>
       <c r="F23" s="205">
-        <v>74477292.819999993</v>
+        <v>94283530.120000005</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24343,16 +24343,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>81414157.224280998</v>
+        <v>85072270.124280006</v>
       </c>
       <c r="D24" s="205">
-        <v>22378576.639989998</v>
+        <v>24342576.659990001</v>
       </c>
       <c r="E24" s="205">
-        <v>94584054.779899999</v>
+        <v>140854325.09990001</v>
       </c>
       <c r="F24" s="205">
-        <v>198376788.644171</v>
+        <v>250269171.88417</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24363,16 +24363,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>94384464.072352007</v>
+        <v>113083899.692844</v>
       </c>
       <c r="D25" s="205">
-        <v>14537892.899995999</v>
+        <v>15654556.019983999</v>
       </c>
       <c r="E25" s="205">
-        <v>63175226.039860003</v>
+        <v>71769820.739840001</v>
       </c>
       <c r="F25" s="205">
-        <v>172097583.01220801</v>
+        <v>200508276.45266801</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24383,16 +24383,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>117382243.771851</v>
+        <v>136943853.57716101</v>
       </c>
       <c r="D26" s="205">
-        <v>10307464.799968001</v>
+        <v>11584324.495468</v>
       </c>
       <c r="E26" s="205">
-        <v>146977208.35986501</v>
+        <v>167189100.54982001</v>
       </c>
       <c r="F26" s="205">
-        <v>274666916.93168402</v>
+        <v>315717278.62244898</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24403,16 +24403,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>210565565.854633</v>
+        <v>215334935.084598</v>
       </c>
       <c r="D27" s="205">
-        <v>7459839.1200000001</v>
+        <v>11198866.199999999</v>
       </c>
       <c r="E27" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F27" s="205">
-        <v>218025404.97463301</v>
+        <v>226533801.28459799</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24455,7 +24455,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>34371437.009887002</v>
+        <v>55119391.829728998</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24466,7 +24466,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>47089037.045641005</v>
+        <v>75442010.825186998</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24477,7 +24477,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>26435846.722212002</v>
+        <v>30812864.572184999</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24488,7 +24488,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>64384909.921319</v>
+        <v>68720279.401318997</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24540,7 +24540,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.16666666666666666</v>
+        <v>0.2</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24583,19 +24583,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>1469453882.725698</v>
+        <v>1673096592.6451981</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.20242420983142545</v>
+        <v>0.23047695454698039</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>5789825449.2743015</v>
+        <v>5586182739.3548021</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>263173884.05792281</v>
+        <v>266008701.87403819</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24612,19 +24612,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>190151295.24961701</v>
+        <v>205621448.77509895</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.10508934553758549</v>
+        <v>0.11363910749016488</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1619273763.7503829</v>
+        <v>1603803610.224901</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>73603352.897744671</v>
+        <v>76371600.486900046</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24641,19 +24641,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>172281230.69905901</v>
+        <v>230094546.62842</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>9.4098987124962022E-2</v>
+        <v>0.12567627763544834</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1658569833.300941</v>
+        <v>1600756517.3715801</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>75389537.877315506</v>
+        <v>76226500.8272181</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24668,19 +24668,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>1831886408.6743741</v>
+        <v>2108812588.048717</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.16806982782348476</v>
+        <v>0.19347693552780013</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>9067669046.3256264</v>
+        <v>8790742866.9512825</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>412166774.83298302</v>
+        <v>418606803.18815631</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24701,10 +24701,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24789,35 +24789,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>81414157.224280998</v>
+        <v>85072270.124280006</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>22378576.639989998</v>
+        <v>24342576.659990001</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>103792733.864271</v>
+        <v>109414846.78427</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.18751603830862235</v>
+        <v>0.19767316879774263</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>370269320.77571899</v>
+        <v>366611207.87572002</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>79451846.360009998</v>
+        <v>77487846.340010002</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>449721167.13572901</v>
+        <v>444099054.21573001</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>20441871.233442228</v>
+        <v>21147574.010272857</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24841,35 +24841,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>128198477.063154</v>
+        <v>149603134.68308198</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>26460601.666076999</v>
+        <v>27944511.576076999</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>154659078.729231</v>
+        <v>177547646.25915897</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.18969843227690855</v>
+        <v>0.21777260298300141</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>461983893.93684602</v>
+        <v>440579236.31691802</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>198646204.33392301</v>
+        <v>197162294.42392302</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>660630098.270769</v>
+        <v>637741530.74084103</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>30028640.830489501</v>
+        <v>30368644.320992429</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24921,7 +24921,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>9380988.5454545449</v>
+        <v>9827702.2857142854</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24945,35 +24945,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>188735680.79965001</v>
+        <v>228165305.08983999</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>5076049.4275939995</v>
+        <v>6480445.8275939999</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>193811730.22724402</v>
+        <v>234645750.91743401</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.26690157297039013</v>
+        <v>0.32313482748051958</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>456976791.20034999</v>
+        <v>417547166.91016001</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>75365798.572405994</v>
+        <v>73961402.172406003</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>532342589.77275598</v>
+        <v>491508569.08256602</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>24197390.444216181</v>
+        <v>23405169.956312668</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>39283783.140000001</v>
+        <v>69734233.040000007</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25005,15 +25005,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>43209175.140000001</v>
+        <v>73659625.040000007</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>7.3305687519056709E-2</v>
+        <v>0.1249658073420266</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>469635048.86000001</v>
+        <v>439184598.95999998</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25021,11 +25021,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>546229060.86000001</v>
+        <v>515778610.95999998</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>24828593.675454546</v>
+        <v>24560886.236190476</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25049,35 +25049,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>141386234.56545201</v>
+        <v>143216240.83604801</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>33458193.469863001</v>
+        <v>33998734.009856999</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>174844428.03531501</v>
+        <v>177214974.84590501</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.33481464258423338</v>
+        <v>0.33935407110383464</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>298677049.43454802</v>
+        <v>296847043.16395199</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>48691131.530137002</v>
+        <v>48150590.990143001</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>347368180.96468496</v>
+        <v>344997634.15409499</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>15789462.771122044</v>
+        <v>16428458.769242618</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25101,35 +25101,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>173025435.4937</v>
+        <v>187530673.70565599</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>27394821.109944001</v>
+        <v>30024821.109944001</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>200420256.60364401</v>
+        <v>217555494.81559998</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.17858837384566972</v>
+        <v>0.1938570616499331</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>823732909.50629997</v>
+        <v>809227671.29434395</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>98093776.890055999</v>
+        <v>95463776.890055999</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>921826686.39635599</v>
+        <v>904691448.18440008</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>41901213.018016182</v>
+        <v>43080545.151638098</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25153,35 +25153,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>94384464.072352007</v>
+        <v>113083899.692844</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>14537892.899995999</v>
+        <v>15654556.019983999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>108922356.972348</v>
+        <v>128738455.71282801</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.17082417039814024</v>
+        <v>0.20190198327295245</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>445902594.92764801</v>
+        <v>427203159.30715597</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>82803533.100004002</v>
+        <v>81686869.980015993</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>528706128.02765203</v>
+        <v>508890029.28717196</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>24032096.728529636</v>
+        <v>24232858.537484378</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>72519364.939999998</v>
+        <v>92325602.239999995</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25213,15 +25213,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>72519364.939999998</v>
+        <v>92325602.239999995</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.17944400924739592</v>
+        <v>0.2284531343570527</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>331614299.06</v>
+        <v>311808061.75999999</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25229,11 +25229,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>331614299.06</v>
+        <v>311808061.75999999</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>15073377.23</v>
+        <v>14848002.940952381</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25257,35 +25257,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>93761492.889708996</v>
+        <v>104622545.667676</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>18421257.544438001</v>
+        <v>19232014.304437999</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>112182750.434147</v>
+        <v>123854559.972114</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.18359261991235948</v>
+        <v>0.20269411353683001</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>345255816.110291</v>
+        <v>334394763.33232403</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>153603154.455562</v>
+        <v>152792397.69556201</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>498858970.565853</v>
+        <v>487187161.02788603</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>22675407.752993319</v>
+        <v>23199388.620375525</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25309,35 +25309,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>117382243.771851</v>
+        <v>136943853.57716101</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>10307464.799968001</v>
+        <v>11584324.495468</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>127689708.57181901</v>
+        <v>148528178.072629</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.16824938221452765</v>
+        <v>0.19570703451103655</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>549247352.22814894</v>
+        <v>529685742.42283899</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>81994157.200031996</v>
+        <v>80717297.504531994</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>631241509.42818093</v>
+        <v>610403039.92737103</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>28692795.883099135</v>
+        <v>29066811.425112907</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25361,35 +25361,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>58290237.251025997</v>
+        <v>68630018.114123002</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>10524671.691799</v>
+        <v>11028671.691799</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>68814908.94282499</v>
+        <v>79658689.805922002</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.13262528268398979</v>
+        <v>0.15352423502477366</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>363252785.74897403</v>
+        <v>352913004.88587701</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>86799504.308201</v>
+        <v>86295504.308201</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>450052290.05717504</v>
+        <v>439208509.19407797</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>20456922.275326136</v>
+        <v>20914690.914003711</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25413,35 +25413,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>210565565.854633</v>
+        <v>215334935.084598</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>7459839.1200000001</v>
+        <v>11198866.199999999</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>218025404.97463301</v>
+        <v>226533801.28459799</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.22208559424041088</v>
+        <v>0.23075243859623878</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>407785376.14536703</v>
+        <v>403016006.915402</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>355907126.88</v>
+        <v>352168099.80000001</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>763692503.02536702</v>
+        <v>755184106.71540201</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>34713295.592062138</v>
+        <v>35961147.938828669</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25465,7 +25465,7 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>35415225.659889996</v>
+        <v>43742360.789889999</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
@@ -25473,15 +25473,15 @@
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>45621760.539838001</v>
+        <v>53948895.669837996</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>7.7845428805367808E-2</v>
+        <v>9.205420543399094E-2</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>259110463.34011</v>
+        <v>250783328.21011001</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
@@ -25489,11 +25489,11 @@
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>540433981.46016204</v>
+        <v>532106846.33016199</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>24565180.975461911</v>
+        <v>25338421.253817238</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25515,35 +25515,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>1469453882.725698</v>
+        <v>1673096592.6451981</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>190151295.24961701</v>
+        <v>205621448.77509895</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>1659605177.9753151</v>
+        <v>1878718041.4202967</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.18300355887907727</v>
+        <v>0.20716498856052487</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>5789825449.2743006</v>
+        <v>5586182739.3548021</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1619273763.7503829</v>
+        <v>1603803610.2249007</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>7409099213.0246849</v>
+        <v>7189986349.5797033</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>336777236.9556675</v>
+        <v>342380302.36093825</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="D70" s="148">
         <f>IF(E24="",0,E24)</f>
-        <v>94584054.779899999</v>
+        <v>140854325.09990001</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25597,7 +25597,7 @@
       </c>
       <c r="D71" s="149">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>6429819.7200000007</v>
+        <v>7240630.5199999996</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25621,7 +25621,7 @@
       </c>
       <c r="D73" s="148">
         <f>IF(E14="",0,E14)</f>
-        <v>43971171.439999998</v>
+        <v>66451712.039999999</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25644,7 +25644,7 @@
         <v>74</v>
       </c>
       <c r="D75" s="148">
-        <v>7693693.5999999996</v>
+        <v>7963693.5999999996</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25655,8 +25655,7 @@
         <v>77</v>
       </c>
       <c r="D76" s="149">
-        <f>IF(E19="",0,E19)</f>
-        <v>366397128.41997999</v>
+        <v>390736047.13998002</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25667,8 +25666,7 @@
         <v>79</v>
       </c>
       <c r="D77" s="148">
-        <f>IF(E25="",0,E25)</f>
-        <v>63175226.039860003</v>
+        <v>71769820.739840001</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25679,7 +25677,6 @@
         <v>177</v>
       </c>
       <c r="D78" s="149">
-        <f>IF(E23="",0,E23)</f>
         <v>1957927.88</v>
       </c>
     </row>
@@ -25703,8 +25700,7 @@
         <v>83</v>
       </c>
       <c r="D80" s="148">
-        <f>IF(E26="",0,E26)</f>
-        <v>146977208.35986501</v>
+        <v>167189100.54982001</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25715,8 +25711,7 @@
         <v>85</v>
       </c>
       <c r="D81" s="149">
-        <f>IF(E10="",0,E10)</f>
-        <v>27427197.370000001</v>
+        <v>40349719.649999999</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25749,7 +25744,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>771294508.90960491</v>
+        <v>907194058.51953995</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25763,13 +25758,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25811,19 +25806,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>34371437.009887002</v>
+        <v>55119391.829728998</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="8">IFERROR(E89/D89,0)</f>
-        <v>0.12037743999286479</v>
+        <v>0.193042009867606</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>251159115.99011299</v>
+        <v>230411161.17027101</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>11416323.454096045</v>
+        <v>10971960.055727191</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25840,19 +25835,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>47089037.045641005</v>
+        <v>75442010.825186998</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="8"/>
-        <v>0.10980779447950348</v>
+        <v>0.17592461726883976</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>381742424.95435899</v>
+        <v>353389451.17481303</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>17351928.407016318</v>
+        <v>16828069.103562526</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25869,19 +25864,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>90820756.643530995</v>
+        <v>99533143.973503992</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="8"/>
-        <v>8.1344959652650387E-2</v>
+        <v>8.9148338770230068E-2</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>1025668292.356469</v>
+        <v>1016955905.0264961</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>46621286.016203135</v>
+        <v>48426471.667928383</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25954,29 +25949,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>172281230.69905901</v>
+        <v>230094546.62842</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="8"/>
-        <v>9.4098987124962022E-2</v>
+        <v>0.12567627763544834</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1658569833.300941</v>
+        <v>1600756517.3715801</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>75389537.877315506</v>
+        <v>76226500.8272181</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25984,6 +25974,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26756,10 +26751,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -26786,7 +26781,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26821,7 +26816,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27820,13 +27815,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28029,11 +28024,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28041,6 +28031,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 06 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 08 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1831,7 +1831,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1928,15 +1927,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1956,6 +1946,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2713,16 +2712,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="207" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="207"/>
+      <c r="B1" s="206" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="206"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="208"/>
+      <c r="C3" s="207"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2773,10 +2772,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="209" t="s">
+      <c r="B11" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="209"/>
+      <c r="C11" s="208"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -3429,11 +3428,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3557,10 +3556,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3589,40 +3588,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3630,13 +3629,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3655,7 +3654,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3665,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4458,10 +4457,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4469,8 +4468,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -4664,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4873,6 +4872,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4880,11 +4884,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5486,11 +5485,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5614,10 +5613,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5646,40 +5645,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5687,13 +5686,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5712,7 +5711,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5722,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6515,10 +6514,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6526,8 +6525,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -6721,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6930,6 +6929,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6937,11 +6941,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7543,11 +7542,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7671,10 +7670,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7703,40 +7702,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7744,13 +7743,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7769,7 +7768,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7779,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8572,10 +8571,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8583,8 +8582,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -8778,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8987,6 +8986,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8994,11 +8998,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9600,11 +9599,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9728,10 +9727,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9760,40 +9759,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9801,13 +9800,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9826,7 +9825,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9836,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10629,10 +10628,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10640,8 +10639,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -10835,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11044,6 +11043,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11051,11 +11055,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11657,11 +11656,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11784,10 +11783,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11816,40 +11815,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11857,13 +11856,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11882,7 +11881,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11892,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12671,10 +12670,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12682,8 +12681,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -12877,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13086,6 +13085,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13093,11 +13097,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -13172,10 +13171,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="207" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="208"/>
+      <c r="C3" s="207"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14652,13 +14651,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="210" t="s">
+      <c r="B29" s="209" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="210"/>
-      <c r="D29" s="210"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="210"/>
+      <c r="C29" s="209"/>
+      <c r="D29" s="209"/>
+      <c r="E29" s="209"/>
+      <c r="F29" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15190,10 +15189,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="212" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="213"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15233,23 +15232,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="214" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="214" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="215" t="s">
+      <c r="D47" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="216"/>
-      <c r="F47" s="217"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="216"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="214" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15257,13 +15256,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="211" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="214"/>
-      <c r="C48" s="214"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15282,7 +15281,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="214"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15292,7 +15291,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="211"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16725,10 +16724,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="212" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="213"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16768,23 +16767,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="214" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="214" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="215" t="s">
+      <c r="D47" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="216"/>
-      <c r="F47" s="217"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="216"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="214" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16792,13 +16791,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="211" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="214"/>
-      <c r="C48" s="214"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16817,7 +16816,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="214"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16827,7 +16826,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="211"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -18412,10 +18411,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="222" t="s">
+      <c r="B44" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="223"/>
+      <c r="C44" s="222"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18480,23 +18479,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="224" t="s">
+      <c r="B47" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="224" t="s">
+      <c r="C47" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="219" t="s">
+      <c r="D47" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="220"/>
-      <c r="F47" s="221"/>
+      <c r="E47" s="219"/>
+      <c r="F47" s="220"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="224" t="s">
+      <c r="J47" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18504,13 +18503,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="218" t="s">
+      <c r="N47" s="217" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="224"/>
-      <c r="C48" s="224"/>
+      <c r="B48" s="223"/>
+      <c r="C48" s="223"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18529,7 +18528,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="224"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18539,7 +18538,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="218"/>
+      <c r="N48" s="217"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -20161,11 +20160,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20283,10 +20282,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20309,40 +20308,40 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="236"/>
-      <c r="L48" s="237"/>
-      <c r="M48" s="237"/>
-      <c r="N48" s="238"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="235"/>
+      <c r="L48" s="236"/>
+      <c r="M48" s="236"/>
+      <c r="N48" s="237"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="235" t="s">
+      <c r="B49" s="234" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="235" t="s">
+      <c r="C49" s="234" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="232" t="s">
+      <c r="D49" s="231" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="233"/>
-      <c r="F49" s="234"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="233"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="235" t="s">
+      <c r="J49" s="234" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20350,13 +20349,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="228" t="s">
+      <c r="N49" s="227" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="235"/>
-      <c r="C50" s="235"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="234"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20375,7 +20374,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="235"/>
+      <c r="J50" s="234"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20385,7 +20384,7 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="228"/>
+      <c r="N50" s="227"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="183" t="s">
@@ -21176,10 +21175,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21190,8 +21189,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -21377,13 +21376,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="229" t="s">
+      <c r="B87" s="228" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="230"/>
-      <c r="D87" s="230"/>
-      <c r="E87" s="230"/>
-      <c r="F87" s="231"/>
+      <c r="C87" s="229"/>
+      <c r="D87" s="229"/>
+      <c r="E87" s="229"/>
+      <c r="F87" s="230"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21665,7 +21664,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22338,11 +22337,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="239" t="s">
+      <c r="B41" s="245" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="240"/>
-      <c r="D41" s="241"/>
+      <c r="C41" s="246"/>
+      <c r="D41" s="247"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22402,7 +22401,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>30133051.438647952</v>
+        <v>31639704.01058035</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22431,7 +22430,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>26456539.510318607</v>
+        <v>27779366.485834539</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22460,15 +22459,15 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>5227262.6066529863</v>
+        <v>5488625.7369856359</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
@@ -22487,7 +22486,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>61816853.555619545</v>
+        <v>64907696.233400524</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22497,40 +22496,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22538,13 +22537,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22563,7 +22562,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22573,7 +22572,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22624,7 +22623,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>7235434.4441220621</v>
+        <v>7597206.1663281647</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22676,7 +22675,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>6473792.1422509523</v>
+        <v>6797481.7493634997</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22728,7 +22727,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>2090734.39047619</v>
+        <v>2195271.1099999994</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22780,7 +22779,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-1921367.0231441488</v>
+        <v>-2017435.374301356</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22832,7 +22831,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>6228303.6957869586</v>
+        <v>6539718.880576307</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22884,7 +22883,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>3842262.116902079</v>
+        <v>4034375.2227471829</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22936,7 +22935,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-1196054.0794637885</v>
+        <v>-1255856.7834369778</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22988,7 +22987,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>5276877.5350138117</v>
+        <v>5540721.4117645025</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23040,7 +23039,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>4933911.4366678568</v>
+        <v>5180607.0085012494</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23092,7 +23091,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>3600568.9360609706</v>
+        <v>3780597.3828640194</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23144,7 +23143,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>8439817.0193275362</v>
+        <v>8861807.8702939115</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23196,7 +23195,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>5636872.7696272787</v>
+        <v>5918716.4081086423</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23248,7 +23247,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>1647889.6649045434</v>
+        <v>1730284.1481497705</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23300,7 +23299,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>4300547.900434304</v>
+        <v>4515575.2954560192</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23350,7 +23349,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>56589590.948966607</v>
+        <v>59419070.496414937</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23366,10 +23365,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23377,8 +23376,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -23572,13 +23571,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23632,7 +23631,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-636332.2817272601</v>
+        <v>-668148.89581362309</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23661,7 +23660,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-882356.3208515445</v>
+        <v>-926474.13689412177</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23690,7 +23689,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>6745951.2092317967</v>
+        <v>7083248.7696933867</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23775,12 +23774,17 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>5227262.6066529918</v>
+        <v>5488625.7369856415</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23788,11 +23792,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23861,7 +23860,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23943,11 +23942,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>85072270.124280006</v>
+        <v>92363992.324272007</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>24342576.659990001</v>
+        <v>26055169.459989998</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23965,11 +23964,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>149603134.68308198</v>
+        <v>166454827.28515399</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>27944511.576076999</v>
+        <v>37813286.126001999</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23977,27 +23976,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>68630018.114123002</v>
+        <v>71727112.708320007</v>
       </c>
       <c r="D10" s="205">
-        <v>11028671.691799</v>
+        <v>11772770.791799</v>
       </c>
       <c r="E10" s="205">
-        <v>40349719.649999999</v>
+        <v>41971341.25</v>
       </c>
       <c r="F10" s="205">
-        <v>120008409.45592199</v>
+        <v>125471224.750119</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>228165305.08983999</v>
+        <v>270811727.06423998</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>6480445.8275939999</v>
+        <v>7184072.0075920001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24005,27 +24004,27 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>104622545.667676</v>
+        <v>119278251.877675</v>
       </c>
       <c r="D11" s="205">
-        <v>19232014.304437999</v>
+        <v>19707239.534437999</v>
       </c>
       <c r="E11" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F11" s="205">
-        <v>123854559.972114</v>
+        <v>138985491.41211301</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>69734233.040000007</v>
+        <v>93157656.040000007</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>3925392</v>
+        <v>33673767.340000004</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -24033,7 +24032,7 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>72797179.063658997</v>
+        <v>81171393.985780999</v>
       </c>
       <c r="D12" s="205">
         <v>25053538.606082</v>
@@ -24042,18 +24041,18 @@
         <v>1859459.44</v>
       </c>
       <c r="F12" s="205">
-        <v>99710177.109741002</v>
+        <v>108084392.031863</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>143216240.83604801</v>
+        <v>166183439.07484499</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>33998734.009856999</v>
+        <v>35733598.889857002</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24061,27 +24060,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>76805955.619423002</v>
+        <v>85283433.299373001</v>
       </c>
       <c r="D13" s="205">
-        <v>2890972.9699949999</v>
+        <v>12759747.519920001</v>
       </c>
       <c r="E13" s="205">
-        <v>5381171.0800000001</v>
+        <v>6426216.0999999996</v>
       </c>
       <c r="F13" s="205">
-        <v>85078099.669418007</v>
+        <v>104469396.919293</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>187530673.70565599</v>
+        <v>225173461.261388</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>30024821.109944001</v>
+        <v>31810496.829944</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24089,27 +24088,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>228165305.08983999</v>
+        <v>270811727.06423998</v>
       </c>
       <c r="D14" s="205">
-        <v>6480445.8275939999</v>
+        <v>7184072.0075920001</v>
       </c>
       <c r="E14" s="205">
-        <v>66451712.039999999</v>
+        <v>71471531.810000002</v>
       </c>
       <c r="F14" s="205">
-        <v>301097462.957434</v>
+        <v>349467330.881832</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>113083899.692844</v>
+        <v>114934350.132837</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>15654556.019983999</v>
+        <v>16357258.739984</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24125,11 +24124,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>104622545.667676</v>
+        <v>119278251.877675</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>19232014.304437999</v>
+        <v>19707239.534437999</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24137,27 +24136,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>143216240.83604801</v>
+        <v>166183439.07484499</v>
       </c>
       <c r="D16" s="205">
-        <v>33998734.009856999</v>
+        <v>35733598.889857002</v>
       </c>
       <c r="E16" s="205">
         <v>7963693.5999999996</v>
       </c>
       <c r="F16" s="205">
-        <v>185178668.445905</v>
+        <v>209880731.564702</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>136943853.57716101</v>
+        <v>152773967.65607199</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>11584324.495468</v>
+        <v>11866324.495468</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24165,27 +24164,27 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>69734233.040000007</v>
+        <v>93157656.040000007</v>
       </c>
       <c r="D17" s="205">
-        <v>3925392</v>
+        <v>33673767.340000004</v>
       </c>
       <c r="E17" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>73659625.040000007</v>
+        <v>126831423.38</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>68630018.114123002</v>
+        <v>71727112.708320007</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>11028671.691799</v>
+        <v>11772770.791799</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24193,23 +24192,23 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>131301106.353948</v>
+        <v>134560565.819148</v>
       </c>
       <c r="D18" s="205">
-        <v>531441.44999800005</v>
+        <v>612409.019998</v>
       </c>
       <c r="E18" s="205">
-        <v>6237837.7599999998</v>
+        <v>6662162.0800000001</v>
       </c>
       <c r="F18" s="205">
-        <v>138070385.56394601</v>
+        <v>141835136.919146</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>215334935.084598</v>
+        <v>223158538.444594</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
@@ -24221,27 +24220,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>187530673.70565599</v>
+        <v>225173461.261388</v>
       </c>
       <c r="D19" s="205">
-        <v>30024821.109944001</v>
+        <v>31810496.829944</v>
       </c>
       <c r="E19" s="205">
-        <v>390736047.13998002</v>
+        <v>413706317.48997998</v>
       </c>
       <c r="F19" s="205">
-        <v>608291541.95558</v>
+        <v>670690275.58131194</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>43742360.789889999</v>
+        <v>44742360.789889999</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>10206534.879948001</v>
+        <v>11183358.439948</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24249,7 +24248,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>29893672.789889999</v>
+        <v>30893672.789889999</v>
       </c>
       <c r="D20" s="205">
         <v>4154827.08</v>
@@ -24258,7 +24257,7 @@
         <v>1945946</v>
       </c>
       <c r="F20" s="205">
-        <v>35994445.869889997</v>
+        <v>36994445.869889997</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24279,20 +24278,20 @@
         <v>13848688</v>
       </c>
       <c r="D21" s="205">
-        <v>6051707.7999480003</v>
+        <v>7028531.3599479999</v>
       </c>
       <c r="E21" s="205">
-        <v>10735135.300000001</v>
+        <v>11383783.960000001</v>
       </c>
       <c r="F21" s="205">
-        <v>30635531.099948</v>
+        <v>32261003.319947999</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>99533143.973503992</v>
+        <v>215640573.270042</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24329,10 +24328,10 @@
         <v>168</v>
       </c>
       <c r="E23" s="205">
-        <v>1957927.88</v>
+        <v>3687657.56</v>
       </c>
       <c r="F23" s="205">
-        <v>94283530.120000005</v>
+        <v>96013259.799999997</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24343,16 +24342,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>85072270.124280006</v>
+        <v>92363992.324272007</v>
       </c>
       <c r="D24" s="205">
-        <v>24342576.659990001</v>
+        <v>26055169.459989998</v>
       </c>
       <c r="E24" s="205">
-        <v>140854325.09990001</v>
+        <v>144205676.39989999</v>
       </c>
       <c r="F24" s="205">
-        <v>250269171.88417</v>
+        <v>262624838.18416199</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24363,16 +24362,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>113083899.692844</v>
+        <v>114934350.132837</v>
       </c>
       <c r="D25" s="205">
-        <v>15654556.019983999</v>
+        <v>16357258.739984</v>
       </c>
       <c r="E25" s="205">
-        <v>71769820.739840001</v>
+        <v>78310361.589805007</v>
       </c>
       <c r="F25" s="205">
-        <v>200508276.45266801</v>
+        <v>209601970.46262601</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24383,16 +24382,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>136943853.57716101</v>
+        <v>152773967.65607199</v>
       </c>
       <c r="D26" s="205">
-        <v>11584324.495468</v>
+        <v>11866324.495468</v>
       </c>
       <c r="E26" s="205">
-        <v>167189100.54982001</v>
+        <v>185059370.96979001</v>
       </c>
       <c r="F26" s="205">
-        <v>315717278.62244898</v>
+        <v>349699663.12133002</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24403,7 +24402,7 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>215334935.084598</v>
+        <v>223158538.444594</v>
       </c>
       <c r="D27" s="205">
         <v>11198866.199999999</v>
@@ -24412,7 +24411,7 @@
         <v>168</v>
       </c>
       <c r="F27" s="205">
-        <v>226533801.28459799</v>
+        <v>234357404.64459401</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24455,7 +24454,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>55119391.829728998</v>
+        <v>57713265.689695001</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24465,8 +24464,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="206">
-        <v>75442010.825186998</v>
+      <c r="C33" s="205">
+        <v>75575344.161186993</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24477,7 +24476,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>30812864.572184999</v>
+        <v>34766242.950185001</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24488,7 +24487,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>68720279.401318997</v>
+        <v>180874330.319857</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24530,17 +24529,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.2</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24583,19 +24582,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>1673096592.6451981</v>
+        <v>1868176806.8992867</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.23047695454698039</v>
+        <v>0.25735017505995134</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>5586182739.3548021</v>
+        <v>5391102525.1007137</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>266008701.87403819</v>
+        <v>269555126.2550357</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24612,19 +24611,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>205621448.77509895</v>
+        <v>254356208.85502195</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.11363910749016488</v>
+        <v>0.14057294475384069</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1603803610.224901</v>
+        <v>1555068850.144978</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>76371600.486900046</v>
+        <v>77753442.507248908</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24641,46 +24640,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>230094546.62842</v>
+        <v>348929183.120924</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.12567627763544834</v>
+        <v>0.19058305177407045</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1600756517.3715801</v>
+        <v>1481921880.879076</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>76226500.8272181</v>
+        <v>74096094.043953806</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10899555455</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>2108812588.048717</v>
+        <v>2471462198.8752327</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.19347693552780013</v>
+        <v>0.22674889898757183</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>8790742866.9512825</v>
+        <v>8428093256.1247673</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>418606803.18815631</v>
+        <v>421404662.80623835</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24690,40 +24689,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24731,13 +24730,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24756,7 +24755,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24766,7 +24765,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24789,35 +24788,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>85072270.124280006</v>
+        <v>92363992.324272007</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>24342576.659990001</v>
+        <v>26055169.459989998</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>109414846.78427</v>
+        <v>118419161.784262</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.19767316879774263</v>
+        <v>0.21394071868894582</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>366611207.87572002</v>
+        <v>359319485.67572796</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>77487846.340010002</v>
+        <v>75775253.540010005</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>444099054.21573001</v>
+        <v>435094739.215738</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>21147574.010272857</v>
+        <v>21754736.960786901</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24841,35 +24840,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>149603134.68308198</v>
+        <v>166454827.28515399</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>27944511.576076999</v>
+        <v>37813286.126001999</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>177547646.25915897</v>
+        <v>204268113.411156</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.21777260298300141</v>
+        <v>0.25054682335266176</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>440579236.31691802</v>
+        <v>423727543.71484601</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>197162294.42392302</v>
+        <v>187293519.87399799</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>637741530.74084103</v>
+        <v>611021063.58884406</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>30368644.320992429</v>
+        <v>30551053.179442205</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24921,7 +24920,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>9827702.2857142854</v>
+        <v>10319087.4</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24945,35 +24944,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>228165305.08983999</v>
+        <v>270811727.06423998</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>6480445.8275939999</v>
+        <v>7184072.0075920001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>234645750.91743401</v>
+        <v>277995799.071832</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.32313482748051958</v>
+        <v>0.38283294805962459</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>417547166.91016001</v>
+        <v>374900744.93576002</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>73961402.172406003</v>
+        <v>73257775.992408007</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>491508569.08256602</v>
+        <v>448158520.928168</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>23405169.956312668</v>
+        <v>22407926.0464084</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24997,35 +24996,35 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>69734233.040000007</v>
+        <v>93157656.040000007</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>3925392</v>
+        <v>33673767.340000004</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>73659625.040000007</v>
+        <v>126831423.38000001</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.1249658073420266</v>
+        <v>0.21517338990543533</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>439184598.95999998</v>
+        <v>415761175.95999998</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>76594012</v>
+        <v>46845636.659999996</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>515778610.95999998</v>
+        <v>462606812.62</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>24560886.236190476</v>
+        <v>23130340.631000001</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25049,35 +25048,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>143216240.83604801</v>
+        <v>166183439.07484499</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>33998734.009856999</v>
+        <v>35733598.889857002</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>177214974.84590501</v>
+        <v>201917037.96470198</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.33935407110383464</v>
+        <v>0.38665676485935246</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>296847043.16395199</v>
+        <v>273879844.92515504</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>48150590.990143001</v>
+        <v>46415726.110142998</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>344997634.15409499</v>
+        <v>320295571.03529799</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>16428458.769242618</v>
+        <v>16014778.5517649</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25101,35 +25100,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>187530673.70565599</v>
+        <v>225173461.261388</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>30024821.109944001</v>
+        <v>31810496.829944</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>217555494.81559998</v>
+        <v>256983958.09133202</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.1938570616499331</v>
+        <v>0.22899056192067704</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>809227671.29434395</v>
+        <v>771584883.73861194</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>95463776.890055999</v>
+        <v>93678101.170056</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>904691448.18440008</v>
+        <v>865262984.90866804</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>43080545.151638098</v>
+        <v>43263149.245433405</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25153,35 +25152,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>113083899.692844</v>
+        <v>114934350.132837</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>15654556.019983999</v>
+        <v>16357258.739984</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>128738455.71282801</v>
+        <v>131291608.872821</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.20190198327295245</v>
+        <v>0.20590612239166353</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>427203159.30715597</v>
+        <v>425352708.867163</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>81686869.980015993</v>
+        <v>80984167.260015994</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>508890029.28717196</v>
+        <v>506336876.12717903</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>24232858.537484378</v>
+        <v>25316843.806358952</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25233,7 +25232,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>14848002.940952381</v>
+        <v>15590403.088</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25257,35 +25256,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>104622545.667676</v>
+        <v>119278251.877675</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>19232014.304437999</v>
+        <v>19707239.534437999</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>123854559.972114</v>
+        <v>138985491.41211301</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.20269411353683001</v>
+        <v>0.22745663125041016</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>334394763.33232403</v>
+        <v>319739057.122325</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>152792397.69556201</v>
+        <v>152317172.46556199</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>487187161.02788603</v>
+        <v>472056229.58788699</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>23199388.620375525</v>
+        <v>23602811.47939435</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25309,35 +25308,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>136943853.57716101</v>
+        <v>152773967.65607199</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>11584324.495468</v>
+        <v>11866324.495468</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>148528178.072629</v>
+        <v>164640292.15153998</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.19570703451103655</v>
+        <v>0.21693704020426788</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>529685742.42283899</v>
+        <v>513855628.34392798</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>80717297.504531994</v>
+        <v>80435297.504531994</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>610403039.92737103</v>
+        <v>594290925.84845996</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>29066811.425112907</v>
+        <v>29714546.292422999</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25361,35 +25360,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>68630018.114123002</v>
+        <v>71727112.708320007</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>11028671.691799</v>
+        <v>11772770.791799</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>79658689.805922002</v>
+        <v>83499883.500119001</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.15352423502477366</v>
+        <v>0.16092727322337252</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>352913004.88587701</v>
+        <v>349815910.29167998</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>86295504.308201</v>
+        <v>85551405.208201006</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>439208509.19407797</v>
+        <v>435367315.49988103</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>20914690.914003711</v>
+        <v>21768365.774994053</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25413,7 +25412,7 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>215334935.084598</v>
+        <v>223158538.444594</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
@@ -25421,15 +25420,15 @@
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>226533801.28459799</v>
+        <v>234357404.64459398</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.23075243859623878</v>
+        <v>0.23872173741032948</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>403016006.915402</v>
+        <v>395192403.55540597</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
@@ -25437,11 +25436,11 @@
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>755184106.71540201</v>
+        <v>747360503.35540605</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>35961147.938828669</v>
+        <v>37368025.167770304</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25465,35 +25464,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>43742360.789889999</v>
+        <v>44742360.789889999</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>10206534.879948001</v>
+        <v>11183358.439948</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>53948895.669837996</v>
+        <v>55925719.229837999</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>9.205420543399094E-2</v>
+        <v>9.5427303619589815E-2</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>250783328.21011001</v>
+        <v>249783328.21011001</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>281323518.12005198</v>
+        <v>280346694.56005198</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>532106846.33016199</v>
+        <v>530130022.77016199</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>25338421.253817238</v>
+        <v>26506501.1385081</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25515,35 +25514,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>1673096592.6451981</v>
+        <v>1868176806.8992867</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>205621448.77509895</v>
+        <v>254356208.85502195</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>1878718041.4202967</v>
+        <v>2122533015.7543089</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.20716498856052487</v>
+        <v>0.23405030357597295</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>5586182739.3548021</v>
+        <v>5391102525.1007128</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1603803610.2249007</v>
+        <v>1555068850.144978</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>7189986349.5797033</v>
+        <v>6946171375.2456903</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>342380302.36093825</v>
+        <v>347308568.76228452</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25559,10 +25558,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25570,8 +25569,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -25584,8 +25583,7 @@
         <v>68</v>
       </c>
       <c r="D70" s="148">
-        <f>IF(E24="",0,E24)</f>
-        <v>140854325.09990001</v>
+        <v>144205676.39989999</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25596,8 +25594,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="149">
-        <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>7240630.5199999996</v>
+        <v>8285675.5399999991</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25620,8 +25617,7 @@
         <v>72</v>
       </c>
       <c r="D73" s="148">
-        <f>IF(E14="",0,E14)</f>
-        <v>66451712.039999999</v>
+        <v>71471531.810000002</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25655,7 +25651,7 @@
         <v>77</v>
       </c>
       <c r="D76" s="149">
-        <v>390736047.13998002</v>
+        <v>413706317.48997998</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25666,7 +25662,7 @@
         <v>79</v>
       </c>
       <c r="D77" s="148">
-        <v>71769820.739840001</v>
+        <v>78310361.589805007</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25677,7 +25673,7 @@
         <v>177</v>
       </c>
       <c r="D78" s="149">
-        <v>1957927.88</v>
+        <v>3687657.56</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25700,7 +25696,7 @@
         <v>83</v>
       </c>
       <c r="D80" s="148">
-        <v>167189100.54982001</v>
+        <v>185059370.96979001</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25711,7 +25707,7 @@
         <v>85</v>
       </c>
       <c r="D81" s="149">
-        <v>40349719.649999999</v>
+        <v>41971341.25</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25734,7 +25730,7 @@
         <v>89</v>
       </c>
       <c r="D83" s="149">
-        <v>12681081.300000001</v>
+        <v>13329729.960000001</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25744,7 +25740,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>907194058.51953995</v>
+        <v>967991356.16947496</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25758,13 +25754,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25806,19 +25802,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>55119391.829728998</v>
+        <v>57713265.689695001</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="8">IFERROR(E89/D89,0)</f>
-        <v>0.193042009867606</v>
+        <v>0.20212641023286571</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>230411161.17027101</v>
+        <v>227817287.310305</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>10971960.055727191</v>
+        <v>11390864.365515251</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25835,19 +25831,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>75442010.825186998</v>
+        <v>75575344.161186993</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="8"/>
-        <v>0.17592461726883976</v>
+        <v>0.17623553973562461</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>353389451.17481303</v>
+        <v>353256117.83881301</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16828069.103562526</v>
+        <v>17662805.89194065</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25864,19 +25860,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>99533143.973503992</v>
+        <v>215640573.270042</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="8"/>
-        <v>8.9148338770230068E-2</v>
+        <v>0.19314168236865709</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>1016955905.0264961</v>
+        <v>900848475.72995806</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>48426471.667928383</v>
+        <v>45042423.786497906</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25949,24 +25945,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>230094546.62842</v>
+        <v>348929183.120924</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="8"/>
-        <v>0.12567627763544834</v>
+        <v>0.19058305177407045</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1600756517.3715801</v>
+        <v>1481921880.879076</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>76226500.8272181</v>
+        <v>74096094.043953806</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25974,11 +25975,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26580,11 +26576,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="224" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26708,10 +26704,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26740,40 +26736,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26781,13 +26777,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26806,7 +26802,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26816,7 +26812,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27609,10 +27605,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27620,8 +27616,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -27815,13 +27811,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28024,6 +28020,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28031,11 +28032,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9195" windowHeight="7290" tabRatio="500" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9195" windowHeight="7290" tabRatio="500" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 08 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 09 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -21664,7 +21664,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>31639704.01058035</v>
+        <v>33304951.590084579</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22430,7 +22430,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>27779366.485834539</v>
+        <v>29241438.40614162</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22459,7 +22459,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>5488625.7369856359</v>
+        <v>5777500.7757743532</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22486,7 +22486,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>64907696.233400524</v>
+        <v>68323890.772000551</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22623,7 +22623,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>7597206.1663281647</v>
+        <v>7997059.1224507</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22675,7 +22675,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>6797481.7493634997</v>
+        <v>7155243.9466984207</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22727,7 +22727,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>2195271.1099999994</v>
+        <v>2310811.6947368416</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22779,7 +22779,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-2017435.374301356</v>
+        <v>-2123616.1834751116</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22831,7 +22831,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>6539718.880576307</v>
+        <v>6883914.6111329542</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>4034375.2227471829</v>
+        <v>4246710.7607865082</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-1255856.7834369778</v>
+        <v>-1321954.5088810294</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>5540721.4117645025</v>
+        <v>5832338.3281731606</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23039,7 +23039,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>5180607.0085012494</v>
+        <v>5453270.5352644734</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23091,7 +23091,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>3780597.3828640194</v>
+        <v>3979576.1924884412</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23143,7 +23143,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>8861807.8702939115</v>
+        <v>9328218.8108356968</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23195,7 +23195,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>5918716.4081086423</v>
+        <v>6230227.7980090976</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>1730284.1481497705</v>
+        <v>1821351.7348944952</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>4515575.2954560192</v>
+        <v>4753237.1531115994</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23349,7 +23349,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>59419070.496414937</v>
+        <v>62546389.996226251</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-668148.89581362309</v>
+        <v>-703314.62717223482</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23660,7 +23660,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-926474.13689412177</v>
+        <v>-975235.93357275974</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23689,7 +23689,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>7083248.7696933867</v>
+        <v>7456051.336519354</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23774,7 +23774,7 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>5488625.7369856415</v>
+        <v>5777500.7757743597</v>
       </c>
       <c r="I94" s="116"/>
     </row>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23942,11 +23942,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>92363992.324272007</v>
+        <v>117735656.850054</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>26055169.459989998</v>
+        <v>28298292.88899</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23964,11 +23964,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>166454827.28515399</v>
+        <v>199743705.26072901</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>37813286.126001999</v>
+        <v>39590277.125999004</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23976,27 +23976,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>71727112.708320007</v>
+        <v>96238037.215053007</v>
       </c>
       <c r="D10" s="205">
-        <v>11772770.791799</v>
+        <v>12766305.931799</v>
       </c>
       <c r="E10" s="205">
-        <v>41971341.25</v>
+        <v>49164133.729999997</v>
       </c>
       <c r="F10" s="205">
-        <v>125471224.750119</v>
+        <v>158168476.87685201</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>270811727.06423998</v>
+        <v>314777079.08607203</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>7184072.0075920001</v>
+        <v>8677783.7175789997</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24004,23 +24004,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>119278251.877675</v>
+        <v>124568945.48766901</v>
       </c>
       <c r="D11" s="205">
-        <v>19707239.534437999</v>
+        <v>29348863.854412999</v>
       </c>
       <c r="E11" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F11" s="205">
-        <v>138985491.41211301</v>
+        <v>153917809.34208199</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>93157656.040000007</v>
+        <v>100441439.8</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24032,27 +24032,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>81171393.985780999</v>
+        <v>107551650.422556</v>
       </c>
       <c r="D12" s="205">
-        <v>25053538.606082</v>
+        <v>26558998.066082001</v>
       </c>
       <c r="E12" s="205">
-        <v>1859459.44</v>
+        <v>2670270.2400000002</v>
       </c>
       <c r="F12" s="205">
-        <v>108084392.031863</v>
+        <v>136780918.72863799</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>166183439.07484499</v>
+        <v>183969906.55358899</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>35733598.889857002</v>
+        <v>37583798.459847003</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24060,27 +24060,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>85283433.299373001</v>
+        <v>92192054.838173002</v>
       </c>
       <c r="D13" s="205">
-        <v>12759747.519920001</v>
+        <v>13031279.059916999</v>
       </c>
       <c r="E13" s="205">
-        <v>6426216.0999999996</v>
+        <v>8372162</v>
       </c>
       <c r="F13" s="205">
-        <v>104469396.919293</v>
+        <v>113595495.89809</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>225173461.261388</v>
+        <v>262119110.493633</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>31810496.829944</v>
+        <v>32287974.319944002</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24088,27 +24088,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>270811727.06423998</v>
+        <v>314777079.08607203</v>
       </c>
       <c r="D14" s="205">
-        <v>7184072.0075920001</v>
+        <v>8677783.7175789997</v>
       </c>
       <c r="E14" s="205">
-        <v>71471531.810000002</v>
+        <v>82001802.109999999</v>
       </c>
       <c r="F14" s="205">
-        <v>349467330.881832</v>
+        <v>405456664.91365099</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>114934350.132837</v>
+        <v>153628801.92758399</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>16357258.739984</v>
+        <v>20698577.639975999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24124,11 +24124,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>119278251.877675</v>
+        <v>124568945.48766901</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>19707239.534437999</v>
+        <v>29348863.854412999</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24136,27 +24136,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>166183439.07484499</v>
+        <v>183969906.55358899</v>
       </c>
       <c r="D16" s="205">
-        <v>35733598.889857002</v>
+        <v>37583798.459847003</v>
       </c>
       <c r="E16" s="205">
-        <v>7963693.5999999996</v>
+        <v>9495225.0999999996</v>
       </c>
       <c r="F16" s="205">
-        <v>209880731.564702</v>
+        <v>231048930.11343601</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>152773967.65607199</v>
+        <v>183317238.90193999</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>11866324.495468</v>
+        <v>15736126.305468</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24164,7 +24164,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>93157656.040000007</v>
+        <v>100441439.8</v>
       </c>
       <c r="D17" s="205">
         <v>33673767.340000004</v>
@@ -24173,18 +24173,18 @@
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>126831423.38</v>
+        <v>134115207.14</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>71727112.708320007</v>
+        <v>96238037.215053007</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>11772770.791799</v>
+        <v>12766305.931799</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24192,27 +24192,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>134560565.819148</v>
+        <v>146236600.41912001</v>
       </c>
       <c r="D18" s="205">
-        <v>612409.019998</v>
+        <v>783513.519998</v>
       </c>
       <c r="E18" s="205">
-        <v>6662162.0800000001</v>
+        <v>6824324.2400000002</v>
       </c>
       <c r="F18" s="205">
-        <v>141835136.919146</v>
+        <v>153844438.17911801</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>223158538.444594</v>
+        <v>252347348.71590301</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>11198866.199999999</v>
+        <v>11359406.759997001</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24220,27 +24220,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>225173461.261388</v>
+        <v>262119110.493633</v>
       </c>
       <c r="D19" s="205">
-        <v>31810496.829944</v>
+        <v>32287974.319944002</v>
       </c>
       <c r="E19" s="205">
-        <v>413706317.48997998</v>
+        <v>486263072.48997998</v>
       </c>
       <c r="F19" s="205">
-        <v>670690275.58131194</v>
+        <v>780670157.30355704</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>44742360.789889999</v>
+        <v>58853093.639789999</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>11183358.439948</v>
+        <v>32604979.759608001</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24248,16 +24248,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>30893672.789889999</v>
+        <v>41008455.639789999</v>
       </c>
       <c r="D20" s="205">
-        <v>4154827.08</v>
+        <v>12668340.47986</v>
       </c>
       <c r="E20" s="205">
         <v>1945946</v>
       </c>
       <c r="F20" s="205">
-        <v>36994445.869889997</v>
+        <v>55622742.119649999</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24275,23 +24275,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>13848688</v>
+        <v>17844638</v>
       </c>
       <c r="D21" s="205">
-        <v>7028531.3599479999</v>
+        <v>19936639.279748</v>
       </c>
       <c r="E21" s="205">
-        <v>11383783.960000001</v>
+        <v>15762162.460000001</v>
       </c>
       <c r="F21" s="205">
-        <v>32261003.319947999</v>
+        <v>53543439.739748001</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>215640573.270042</v>
+        <v>275337806.31482899</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24342,16 +24342,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>92363992.324272007</v>
+        <v>117735656.850054</v>
       </c>
       <c r="D24" s="205">
-        <v>26055169.459989998</v>
+        <v>28298292.88899</v>
       </c>
       <c r="E24" s="205">
-        <v>144205676.39989999</v>
+        <v>150475946.51989999</v>
       </c>
       <c r="F24" s="205">
-        <v>262624838.18416199</v>
+        <v>296509896.25894397</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24362,16 +24362,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>114934350.132837</v>
+        <v>153628801.92758399</v>
       </c>
       <c r="D25" s="205">
-        <v>16357258.739984</v>
+        <v>20698577.639975999</v>
       </c>
       <c r="E25" s="205">
-        <v>78310361.589805007</v>
+        <v>93887839.209775001</v>
       </c>
       <c r="F25" s="205">
-        <v>209601970.46262601</v>
+        <v>268215218.77733499</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24382,16 +24382,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>152773967.65607199</v>
+        <v>183317238.90193999</v>
       </c>
       <c r="D26" s="205">
-        <v>11866324.495468</v>
+        <v>15736126.305468</v>
       </c>
       <c r="E26" s="205">
-        <v>185059370.96979001</v>
+        <v>210438650.29978001</v>
       </c>
       <c r="F26" s="205">
-        <v>349699663.12133002</v>
+        <v>409492015.50718802</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24402,16 +24402,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>223158538.444594</v>
+        <v>252347348.71590301</v>
       </c>
       <c r="D27" s="205">
-        <v>11198866.199999999</v>
-      </c>
-      <c r="E27" s="205" t="s">
-        <v>168</v>
+        <v>11359406.759997001</v>
+      </c>
+      <c r="E27" s="205">
+        <v>1902162.2150000001</v>
       </c>
       <c r="F27" s="205">
-        <v>234357404.64459401</v>
+        <v>265608917.6909</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24454,7 +24454,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>57713265.689695001</v>
+        <v>80412292.329539001</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24465,7 +24465,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>75575344.161186993</v>
+        <v>121443345.52067301</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24476,7 +24476,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>34766242.950185001</v>
+        <v>58423675.421282999</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24487,7 +24487,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>180874330.319857</v>
+        <v>216914130.89354599</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24539,7 +24539,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.26666666666666666</v>
+        <v>0.3</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24582,19 +24582,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>1868176806.8992867</v>
+        <v>2175157486.1720157</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.25735017505995134</v>
+        <v>0.29963821292612242</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>5391102525.1007137</v>
+        <v>5084121845.8279839</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>269555126.2550357</v>
+        <v>267585360.30673599</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24611,19 +24611,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>254356208.85502195</v>
+        <v>302626154.10361993</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.14057294475384069</v>
+        <v>0.16724989664444562</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1555068850.144978</v>
+        <v>1506798904.8963799</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>77753442.507248908</v>
+        <v>79305205.520862103</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24640,19 +24640,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>348929183.120924</v>
+        <v>477193444.16504097</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.19058305177407045</v>
+        <v>0.26064023095493088</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1481921880.879076</v>
+        <v>1353657619.834959</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>74096094.043953806</v>
+        <v>71245137.886050478</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24667,19 +24667,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>2471462198.8752327</v>
+        <v>2954977084.4406767</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.22674889898757183</v>
+        <v>0.27110987201639747</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>8428093256.1247673</v>
+        <v>7944578370.5593224</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>421404662.80623835</v>
+        <v>418135703.71364856</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24788,35 +24788,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>92363992.324272007</v>
+        <v>117735656.850054</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>26055169.459989998</v>
+        <v>28298292.88899</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>118419161.784262</v>
+        <v>146033949.73904401</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.21394071868894582</v>
+        <v>0.26383068153340561</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>359319485.67572796</v>
+        <v>333947821.14994597</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>75775253.540010005</v>
+        <v>73532130.11101</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>435094739.215738</v>
+        <v>407479951.26095599</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>21754736.960786901</v>
+        <v>21446313.224260841</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24840,35 +24840,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>166454827.28515399</v>
+        <v>199743705.26072901</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>37813286.126001999</v>
+        <v>39590277.125999004</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>204268113.411156</v>
+        <v>239333982.38672802</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.25054682335266176</v>
+        <v>0.29355716859556447</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>423727543.71484601</v>
+        <v>390438665.73927099</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>187293519.87399799</v>
+        <v>185516528.874001</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>611021063.58884406</v>
+        <v>575955194.61327195</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>30551053.179442205</v>
+        <v>30313431.295435365</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24920,7 +24920,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>10319087.4</v>
+        <v>10862197.263157895</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24944,35 +24944,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>270811727.06423998</v>
+        <v>314777079.08607203</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>7184072.0075920001</v>
+        <v>8677783.7175789997</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>277995799.071832</v>
+        <v>323454862.80365103</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.38283294805962459</v>
+        <v>0.44543543141580572</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>374900744.93576002</v>
+        <v>330935392.91392797</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>73257775.992408007</v>
+        <v>71764064.282420993</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>448158520.928168</v>
+        <v>402699457.19634897</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>22407926.0464084</v>
+        <v>21194708.273492049</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>93157656.040000007</v>
+        <v>100441439.8</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25004,15 +25004,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>126831423.38000001</v>
+        <v>134115207.14</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.21517338990543533</v>
+        <v>0.22753055188635574</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>415761175.95999998</v>
+        <v>408477392.19999999</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25020,11 +25020,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>462606812.62</v>
+        <v>455323028.86000001</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>23130340.631000001</v>
+        <v>23964369.940000001</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25048,35 +25048,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>166183439.07484499</v>
+        <v>183969906.55358899</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>35733598.889857002</v>
+        <v>37583798.459847003</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>201917037.96470198</v>
+        <v>221553705.01343599</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.38665676485935246</v>
+        <v>0.42425958545446762</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>273879844.92515504</v>
+        <v>256093377.44641101</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>46415726.110142998</v>
+        <v>44565526.540152997</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>320295571.03529799</v>
+        <v>300658903.98656404</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>16014778.5517649</v>
+        <v>15824152.841398107</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25100,35 +25100,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>225173461.261388</v>
+        <v>262119110.493633</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>31810496.829944</v>
+        <v>32287974.319944002</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>256983958.09133202</v>
+        <v>294407084.813577</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.22899056192067704</v>
+        <v>0.26233716799135626</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>771584883.73861194</v>
+        <v>734639234.50636697</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>93678101.170056</v>
+        <v>93200623.680056006</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>865262984.90866804</v>
+        <v>827839858.18642306</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>43263149.245433405</v>
+        <v>43570518.851917006</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25152,35 +25152,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>114934350.132837</v>
+        <v>153628801.92758399</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>16357258.739984</v>
+        <v>20698577.639975999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>131291608.872821</v>
+        <v>174327379.56755999</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.20590612239166353</v>
+        <v>0.27339961069581137</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>425352708.867163</v>
+        <v>386658257.07241601</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>80984167.260015994</v>
+        <v>76642848.360024005</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>506336876.12717903</v>
+        <v>463301105.43244004</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>25316843.806358952</v>
+        <v>24384268.706970528</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25232,7 +25232,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>15590403.088</v>
+        <v>16410950.618947368</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25256,35 +25256,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>119278251.877675</v>
+        <v>124568945.48766901</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>19707239.534437999</v>
+        <v>29348863.854412999</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>138985491.41211301</v>
+        <v>153917809.34208199</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.22745663125041016</v>
+        <v>0.25189410813092744</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>319739057.122325</v>
+        <v>314448363.51233101</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>152317172.46556199</v>
+        <v>142675548.145587</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>472056229.58788699</v>
+        <v>457123911.65791798</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>23602811.47939435</v>
+        <v>24059153.245153576</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25308,35 +25308,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>152773967.65607199</v>
+        <v>183317238.90193999</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>11866324.495468</v>
+        <v>15736126.305468</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>164640292.15153998</v>
+        <v>199053365.20740798</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.21693704020426788</v>
+        <v>0.26228116657524025</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>513855628.34392798</v>
+        <v>483312357.09806001</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>80435297.504531994</v>
+        <v>76565495.694532007</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>594290925.84845996</v>
+        <v>559877852.79259205</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>29714546.292422999</v>
+        <v>29467255.410136424</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25360,35 +25360,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>71727112.708320007</v>
+        <v>96238037.215053007</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>11772770.791799</v>
+        <v>12766305.931799</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>83499883.500119001</v>
+        <v>109004343.146852</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.16092727322337252</v>
+        <v>0.21008139145610552</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>349815910.29167998</v>
+        <v>325304985.78494698</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>85551405.208201006</v>
+        <v>84557870.068201005</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>435367315.49988103</v>
+        <v>409862855.85314798</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>21768365.774994053</v>
+        <v>21571729.255428839</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25412,35 +25412,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>223158538.444594</v>
+        <v>252347348.71590301</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>11198866.199999999</v>
+        <v>11359406.759997001</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>234357404.64459398</v>
+        <v>263706755.47590002</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.23872173741032948</v>
+        <v>0.26861764803000826</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>395192403.55540597</v>
+        <v>366003593.28409696</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>352168099.80000001</v>
+        <v>352007559.24000299</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>747360503.35540605</v>
+        <v>718011152.52409995</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>37368025.167770304</v>
+        <v>37790060.659163155</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25464,35 +25464,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>44742360.789889999</v>
+        <v>58853093.639789999</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>11183358.439948</v>
+        <v>32604979.759608001</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>55925719.229837999</v>
+        <v>91458073.399397999</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>9.5427303619589815E-2</v>
+        <v>0.15605695302512368</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>249783328.21011001</v>
+        <v>235672595.36021</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>280346694.56005198</v>
+        <v>258925073.240392</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>530130022.77016199</v>
+        <v>494597668.60060203</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>26506501.1385081</v>
+        <v>26031456.242136948</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25514,35 +25514,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>1868176806.8992867</v>
+        <v>2175157486.1720157</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>254356208.85502195</v>
+        <v>302626154.10361993</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>2122533015.7543089</v>
+        <v>2477783640.2756357</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.23405030357597295</v>
+        <v>0.27322355360206113</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>5391102525.1007128</v>
+        <v>5084121845.8279839</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1555068850.144978</v>
+        <v>1506798904.8963797</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>6946171375.2456903</v>
+        <v>6590920750.7243652</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>347308568.76228452</v>
+        <v>346890565.82759815</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25582,8 +25582,9 @@
       <c r="C70" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="148">
-        <v>144205676.39989999</v>
+      <c r="D70" s="191">
+        <f>IF(E24="",0,E24)</f>
+        <v>150475946.51989999</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25593,8 +25594,9 @@
       <c r="C71" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="149">
-        <v>8285675.5399999991</v>
+      <c r="D71" s="192">
+        <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
+        <v>11042432.24</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25604,7 +25606,7 @@
       <c r="C72" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="D72" s="149">
+      <c r="D72" s="192">
         <f>IF(E22="",0,E22)</f>
         <v>0</v>
       </c>
@@ -25616,8 +25618,9 @@
       <c r="C73" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="D73" s="148">
-        <v>71471531.810000002</v>
+      <c r="D73" s="191">
+        <f>IF(E14="",0,E14)</f>
+        <v>82001802.109999999</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25627,7 +25630,7 @@
       <c r="C74" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="D74" s="149">
+      <c r="D74" s="192">
         <f>0</f>
         <v>0</v>
       </c>
@@ -25639,8 +25642,9 @@
       <c r="C75" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="148">
-        <v>7963693.5999999996</v>
+      <c r="D75" s="192">
+        <f>IF(E16="",0,E16)</f>
+        <v>9495225.0999999996</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25650,8 +25654,9 @@
       <c r="C76" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="D76" s="149">
-        <v>413706317.48997998</v>
+      <c r="D76" s="192">
+        <f>IF(E19="",0,E19)</f>
+        <v>486263072.48997998</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25661,8 +25666,9 @@
       <c r="C77" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="D77" s="148">
-        <v>78310361.589805007</v>
+      <c r="D77" s="191">
+        <f>IF(E25="",0,E25)</f>
+        <v>93887839.209775001</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25672,7 +25678,8 @@
       <c r="C78" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="D78" s="149">
+      <c r="D78" s="192">
+        <f>IF(E23="",0,E23)</f>
         <v>3687657.56</v>
       </c>
     </row>
@@ -25683,7 +25690,7 @@
       <c r="C79" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="D79" s="149">
+      <c r="D79" s="192">
         <f>IF(E11="",0,E11)</f>
         <v>0</v>
       </c>
@@ -25695,8 +25702,9 @@
       <c r="C80" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="D80" s="148">
-        <v>185059370.96979001</v>
+      <c r="D80" s="191">
+        <f>IF(E26="",0,E26)</f>
+        <v>210438650.29978001</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25706,8 +25714,9 @@
       <c r="C81" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="D81" s="149">
-        <v>41971341.25</v>
+      <c r="D81" s="192">
+        <f>IF(E10="",0,E10)</f>
+        <v>49164133.729999997</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25717,9 +25726,9 @@
       <c r="C82" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="149">
-        <f t="shared" ref="D82" si="7">IF(E11="",0,E11)</f>
-        <v>0</v>
+      <c r="D82" s="192">
+        <f>IF(E27="",0,E27)</f>
+        <v>1902162.2150000001</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25729,8 +25738,9 @@
       <c r="C83" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="D83" s="149">
-        <v>13329729.960000001</v>
+      <c r="D83" s="192">
+        <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
+        <v>17708108.460000001</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25740,7 +25750,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>967991356.16947496</v>
+        <v>1116067029.9344349</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25802,19 +25812,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>57713265.689695001</v>
+        <v>80412292.329539001</v>
       </c>
       <c r="F89" s="61">
-        <f t="shared" ref="F89:F94" si="8">IFERROR(E89/D89,0)</f>
-        <v>0.20212641023286571</v>
+        <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
+        <v>0.28162412563092332</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>227817287.310305</v>
+        <v>205118260.670461</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>11390864.365515251</v>
+        <v>10795697.930024263</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25831,19 +25841,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>75575344.161186993</v>
+        <v>121443345.52067301</v>
       </c>
       <c r="F90" s="61">
-        <f t="shared" si="8"/>
-        <v>0.17623553973562461</v>
+        <f t="shared" si="7"/>
+        <v>0.28319597856528772</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>353256117.83881301</v>
+        <v>307388116.47932696</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>17662805.89194065</v>
+        <v>16178321.919964576</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25860,19 +25870,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>215640573.270042</v>
+        <v>275337806.31482899</v>
       </c>
       <c r="F91" s="61">
-        <f t="shared" si="8"/>
-        <v>0.19314168236865709</v>
+        <f t="shared" si="7"/>
+        <v>0.24661039583096617</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>900848475.72995806</v>
+        <v>841151242.68517101</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>45042423.786497906</v>
+        <v>44271118.03606163</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25892,7 +25902,7 @@
         <v>0</v>
       </c>
       <c r="F92" s="61">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G92" s="126">
@@ -25921,7 +25931,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="61">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G93" s="125">
@@ -25945,19 +25955,19 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>348929183.120924</v>
+        <v>477193444.16504097</v>
       </c>
       <c r="F94" s="43">
-        <f t="shared" si="8"/>
-        <v>0.19058305177407045</v>
+        <f t="shared" si="7"/>
+        <v>0.26064023095493088</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1481921880.879076</v>
+        <v>1353657619.834959</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>74096094.043953806</v>
+        <v>71245137.886050478</v>
       </c>
       <c r="I94" s="116"/>
     </row>

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 09 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 10 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1927,6 +1927,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1946,15 +1955,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3599,10 +3599,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4663,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4872,11 +4872,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4884,6 +4879,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5656,10 +5656,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6720,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6929,11 +6929,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6941,6 +6936,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7713,10 +7713,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8777,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8986,11 +8986,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8998,6 +8993,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9770,10 +9770,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10834,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11043,11 +11043,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11055,6 +11050,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11826,10 +11826,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12876,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13085,11 +13085,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13097,6 +13092,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22337,11 +22337,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="245" t="s">
+      <c r="B41" s="238" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="246"/>
-      <c r="D41" s="247"/>
+      <c r="C41" s="239"/>
+      <c r="D41" s="240"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>33304951.590084579</v>
+        <v>35155226.678422607</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22430,7 +22430,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>29241438.40614162</v>
+        <v>30865962.762038376</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22459,7 +22459,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>5777500.7757743532</v>
+        <v>6098473.0410951506</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22486,7 +22486,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>68323890.772000551</v>
+        <v>72119662.481556132</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22507,10 +22507,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22572,7 +22572,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>7997059.1224507</v>
+        <v>8441340.1848090719</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22675,7 +22675,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>7155243.9466984207</v>
+        <v>7552757.4992927779</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22727,7 +22727,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>2310811.6947368416</v>
+        <v>2439190.1222222215</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22779,7 +22779,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-2123616.1834751116</v>
+        <v>-2241594.8603348401</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22831,7 +22831,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>6883914.6111329542</v>
+        <v>7266354.3117514513</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>4246710.7607865082</v>
+        <v>4482639.1363857584</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-1321954.5088810294</v>
+        <v>-1395396.4260410864</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>5832338.3281731606</v>
+        <v>6156357.1241827803</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23039,7 +23039,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>5453270.5352644734</v>
+        <v>5756230.009445833</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23091,7 +23091,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>3979576.1924884412</v>
+        <v>4200663.7587377988</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23143,7 +23143,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>9328218.8108356968</v>
+        <v>9846453.1892154589</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23195,7 +23195,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>6230227.7980090976</v>
+        <v>6576351.5645651584</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>1821351.7348944952</v>
+        <v>1922537.942388634</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>4753237.1531115994</v>
+        <v>5017305.8838400207</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23349,7 +23349,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>62546389.996226251</v>
+        <v>66021189.44046104</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23571,13 +23571,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23631,7 +23631,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-703314.62717223482</v>
+        <v>-742387.6620151368</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23660,7 +23660,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-975235.93357275974</v>
+        <v>-1029415.7076601353</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23689,7 +23689,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>7456051.336519354</v>
+        <v>7870276.4107704293</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23774,17 +23774,12 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>5777500.7757743597</v>
+        <v>6098473.0410951572</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23792,6 +23787,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23860,7 +23860,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23942,11 +23942,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>117735656.850054</v>
+        <v>131003162.560046</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>28298292.88899</v>
+        <v>30741238.848979998</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23964,11 +23964,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>199743705.26072901</v>
+        <v>234820630.080697</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>39590277.125999004</v>
+        <v>66215972.277888998</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23976,27 +23976,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>96238037.215053007</v>
+        <v>106446757.925051</v>
       </c>
       <c r="D10" s="205">
-        <v>12766305.931799</v>
+        <v>20384697.426798999</v>
       </c>
       <c r="E10" s="205">
-        <v>49164133.729999997</v>
+        <v>57238908.399999999</v>
       </c>
       <c r="F10" s="205">
-        <v>158168476.87685201</v>
+        <v>184070363.75185001</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>314777079.08607203</v>
+        <v>362230308.49726498</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>8677783.7175789997</v>
+        <v>11191243.147555999</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24004,16 +24004,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>124568945.48766901</v>
+        <v>133760703.15766799</v>
       </c>
       <c r="D11" s="205">
-        <v>29348863.854412999</v>
-      </c>
-      <c r="E11" s="205" t="s">
-        <v>168</v>
+        <v>34246061.990364</v>
+      </c>
+      <c r="E11" s="205">
+        <v>1783783.8</v>
       </c>
       <c r="F11" s="205">
-        <v>153917809.34208199</v>
+        <v>169790548.94803199</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -24024,7 +24024,7 @@
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>33673767.340000004</v>
+        <v>37956650.210000001</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -24032,27 +24032,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>107551650.422556</v>
+        <v>124706041.402551</v>
       </c>
       <c r="D12" s="205">
-        <v>26558998.066082001</v>
+        <v>39332135.068071999</v>
       </c>
       <c r="E12" s="205">
         <v>2670270.2400000002</v>
       </c>
       <c r="F12" s="205">
-        <v>136780918.72863799</v>
+        <v>166708446.710623</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>183969906.55358899</v>
+        <v>194596923.17355201</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>37583798.459847003</v>
+        <v>40895843.640844002</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24060,27 +24060,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>92192054.838173002</v>
+        <v>110114588.678146</v>
       </c>
       <c r="D13" s="205">
-        <v>13031279.059916999</v>
+        <v>26883837.209817</v>
       </c>
       <c r="E13" s="205">
-        <v>8372162</v>
+        <v>10318107.92</v>
       </c>
       <c r="F13" s="205">
-        <v>113595495.89809</v>
+        <v>147316533.80796301</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>262119110.493633</v>
+        <v>289820795.27350301</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>32287974.319944002</v>
+        <v>32833974.319944002</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24088,27 +24088,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>314777079.08607203</v>
+        <v>362230308.49726498</v>
       </c>
       <c r="D14" s="205">
-        <v>8677783.7175789997</v>
+        <v>11191243.147555999</v>
       </c>
       <c r="E14" s="205">
-        <v>82001802.109999999</v>
+        <v>88542342.609999999</v>
       </c>
       <c r="F14" s="205">
-        <v>405456664.91365099</v>
+        <v>461963894.254821</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>153628801.92758399</v>
+        <v>181134992.25664401</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>20698577.639975999</v>
+        <v>23568577.639975999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24124,11 +24124,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>124568945.48766901</v>
+        <v>133760703.15766799</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>29348863.854412999</v>
+        <v>34246061.990364</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24136,27 +24136,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>183969906.55358899</v>
+        <v>194596923.17355201</v>
       </c>
       <c r="D16" s="205">
-        <v>37583798.459847003</v>
+        <v>40895843.640844002</v>
       </c>
       <c r="E16" s="205">
         <v>9495225.0999999996</v>
       </c>
       <c r="F16" s="205">
-        <v>231048930.11343601</v>
+        <v>244987991.91439599</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>183317238.90193999</v>
+        <v>213854001.74483201</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>15736126.305468</v>
+        <v>18407221.805468</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24167,24 +24167,24 @@
         <v>100441439.8</v>
       </c>
       <c r="D17" s="205">
-        <v>33673767.340000004</v>
+        <v>37956650.210000001</v>
       </c>
       <c r="E17" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>134115207.14</v>
+        <v>138398090.00999999</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>96238037.215053007</v>
+        <v>106446757.925051</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>12766305.931799</v>
+        <v>20384697.426798999</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24192,27 +24192,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>146236600.41912001</v>
+        <v>205933716.21912</v>
       </c>
       <c r="D18" s="205">
-        <v>783513.519998</v>
+        <v>1115504.509997</v>
       </c>
       <c r="E18" s="205">
         <v>6824324.2400000002</v>
       </c>
       <c r="F18" s="205">
-        <v>153844438.17911801</v>
+        <v>213873544.96911699</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>252347348.71590301</v>
+        <v>303643157.845487</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>11359406.759997001</v>
+        <v>41052595.559517004</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24220,27 +24220,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>262119110.493633</v>
+        <v>289820795.27350301</v>
       </c>
       <c r="D19" s="205">
-        <v>32287974.319944002</v>
+        <v>32833974.319944002</v>
       </c>
       <c r="E19" s="205">
-        <v>486263072.48997998</v>
+        <v>528253164.88998002</v>
       </c>
       <c r="F19" s="205">
-        <v>780670157.30355704</v>
+        <v>850907934.48342705</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>58853093.639789999</v>
+        <v>69453418.021081001</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>32604979.759608001</v>
+        <v>70097685.959368005</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24248,16 +24248,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>41008455.639789999</v>
+        <v>44172780.021081001</v>
       </c>
       <c r="D20" s="205">
-        <v>12668340.47986</v>
+        <v>13884556.67984</v>
       </c>
       <c r="E20" s="205">
         <v>1945946</v>
       </c>
       <c r="F20" s="205">
-        <v>55622742.119649999</v>
+        <v>60003282.700920999</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24275,23 +24275,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>17844638</v>
+        <v>25280638</v>
       </c>
       <c r="D21" s="205">
-        <v>19936639.279748</v>
+        <v>56213129.279527999</v>
       </c>
       <c r="E21" s="205">
-        <v>15762162.460000001</v>
+        <v>16627027.34</v>
       </c>
       <c r="F21" s="205">
-        <v>53543439.739748001</v>
+        <v>98120794.619527996</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>275337806.31482899</v>
+        <v>304509189.634718</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24302,7 +24302,7 @@
         <v>172</v>
       </c>
       <c r="C22" s="205">
-        <v>35091520</v>
+        <v>60385505.920000002</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>168</v>
@@ -24311,7 +24311,7 @@
         <v>168</v>
       </c>
       <c r="F22" s="205">
-        <v>35091520</v>
+        <v>60385505.920000002</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24322,7 +24322,7 @@
         <v>173</v>
       </c>
       <c r="C23" s="205">
-        <v>92325602.239999995</v>
+        <v>123341852.23999999</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>168</v>
@@ -24331,7 +24331,7 @@
         <v>3687657.56</v>
       </c>
       <c r="F23" s="205">
-        <v>96013259.799999997</v>
+        <v>127029509.8</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24342,16 +24342,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>117735656.850054</v>
+        <v>131003162.560046</v>
       </c>
       <c r="D24" s="205">
-        <v>28298292.88899</v>
+        <v>30741238.848979998</v>
       </c>
       <c r="E24" s="205">
-        <v>150475946.51989999</v>
+        <v>155959369.87990001</v>
       </c>
       <c r="F24" s="205">
-        <v>296509896.25894397</v>
+        <v>317703771.28892601</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24362,16 +24362,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>153628801.92758399</v>
+        <v>181134992.25664401</v>
       </c>
       <c r="D25" s="205">
-        <v>20698577.639975999</v>
+        <v>23568577.639975999</v>
       </c>
       <c r="E25" s="205">
-        <v>93887839.209775001</v>
+        <v>97941893.209775001</v>
       </c>
       <c r="F25" s="205">
-        <v>268215218.77733499</v>
+        <v>302645463.10639501</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24382,16 +24382,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>183317238.90193999</v>
+        <v>213854001.74483201</v>
       </c>
       <c r="D26" s="205">
-        <v>15736126.305468</v>
+        <v>18407221.805468</v>
       </c>
       <c r="E26" s="205">
-        <v>210438650.29978001</v>
+        <v>211962974.69977999</v>
       </c>
       <c r="F26" s="205">
-        <v>409492015.50718802</v>
+        <v>444224198.25007999</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24402,16 +24402,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>252347348.71590301</v>
+        <v>303643157.845487</v>
       </c>
       <c r="D27" s="205">
-        <v>11359406.759997001</v>
+        <v>41052595.559517004</v>
       </c>
       <c r="E27" s="205">
         <v>1902162.2150000001</v>
       </c>
       <c r="F27" s="205">
-        <v>265608917.6909</v>
+        <v>346597915.620004</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24454,7 +24454,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>80412292.329539001</v>
+        <v>81758283.299530998</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24465,7 +24465,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>121443345.52067301</v>
+        <v>126042913.180613</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24476,7 +24476,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>58423675.421282999</v>
+        <v>60934053.821280003</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24487,7 +24487,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>216914130.89354599</v>
+        <v>243575135.813438</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24539,7 +24539,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.3</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24582,19 +24582,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>2175157486.1720157</v>
+        <v>2504933648.4958258</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.29963821292612242</v>
+        <v>0.34506643620306771</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>5084121845.8279839</v>
+        <v>4754345683.5041742</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>267585360.30673599</v>
+        <v>264130315.75023189</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24611,19 +24611,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>302626154.10361993</v>
+        <v>427591762.82670504</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.16724989664444562</v>
+        <v>0.2363136072974576</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1506798904.8963799</v>
+        <v>1381833296.173295</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>79305205.520862103</v>
+        <v>76768516.454071939</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24640,19 +24640,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>477193444.16504097</v>
+        <v>512310386.11486197</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.26064023095493088</v>
+        <v>0.27982089651551362</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1353657619.834959</v>
+        <v>1318540677.885138</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>71245137.886050478</v>
+        <v>73252259.882507667</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24667,19 +24667,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>2954977084.4406767</v>
+        <v>3444835797.4373927</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.27110987201639747</v>
+        <v>0.31605287129918019</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>7944578370.5593224</v>
+        <v>7454719657.5626068</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>418135703.71364856</v>
+        <v>414151092.08681148</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24700,10 +24700,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24765,7 +24765,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24788,35 +24788,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>117735656.850054</v>
+        <v>131003162.560046</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>28298292.88899</v>
+        <v>30741238.848979998</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>146033949.73904401</v>
+        <v>161744401.409026</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.26383068153340561</v>
+        <v>0.29221380188792401</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>333947821.14994597</v>
+        <v>320680315.43995398</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>73532130.11101</v>
+        <v>71089184.151020005</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>407479951.26095599</v>
+        <v>391769499.59097397</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>21446313.224260841</v>
+        <v>21764972.199498553</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24840,35 +24840,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>199743705.26072901</v>
+        <v>234820630.080697</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>39590277.125999004</v>
+        <v>66215972.277888998</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>239333982.38672802</v>
+        <v>301036602.35858601</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.29355716859556447</v>
+        <v>0.36923905143240482</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>390438665.73927099</v>
+        <v>355361740.919303</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>185516528.874001</v>
+        <v>158890833.72211099</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>575955194.61327195</v>
+        <v>514252574.64141399</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>30313431.295435365</v>
+        <v>28569587.480078556</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>35091520</v>
+        <v>60385505.920000002</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -24900,15 +24900,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>35091520</v>
+        <v>60385505.920000002</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.14532258701199174</v>
+        <v>0.25007118353158664</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>206381748</v>
+        <v>181087762.07999998</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -24916,11 +24916,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>206381748</v>
+        <v>181087762.07999998</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>10862197.263157895</v>
+        <v>10060431.226666667</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24944,35 +24944,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>314777079.08607203</v>
+        <v>362230308.49726498</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>8677783.7175789997</v>
+        <v>11191243.147555999</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>323454862.80365103</v>
+        <v>373421551.64482099</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.44543543141580572</v>
+        <v>0.51424544529986549</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>330935392.91392797</v>
+        <v>283482163.50273502</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>71764064.282420993</v>
+        <v>69250604.852443993</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>402699457.19634897</v>
+        <v>352732768.35517901</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>21194708.273492049</v>
+        <v>19596264.908621058</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25000,15 +25000,15 @@
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>33673767.340000004</v>
+        <v>37956650.210000001</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>134115207.14</v>
+        <v>138398090.00999999</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.22753055188635574</v>
+        <v>0.23479659370112527</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
@@ -25016,15 +25016,15 @@
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>46845636.659999996</v>
+        <v>42562753.789999999</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>455323028.86000001</v>
+        <v>451040145.99000001</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>23964369.940000001</v>
+        <v>25057785.888333336</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25048,35 +25048,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>183969906.55358899</v>
+        <v>194596923.17355201</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>37583798.459847003</v>
+        <v>40895843.640844002</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>221553705.01343599</v>
+        <v>235492766.81439602</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.42425958545446762</v>
+        <v>0.45095189728441815</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>256093377.44641101</v>
+        <v>245466360.82644799</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>44565526.540152997</v>
+        <v>41253481.359155998</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>300658903.98656404</v>
+        <v>286719842.18560398</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>15824152.841398107</v>
+        <v>15928880.121422444</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25100,35 +25100,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>262119110.493633</v>
+        <v>289820795.27350301</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>32287974.319944002</v>
+        <v>32833974.319944002</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>294407084.813577</v>
+        <v>322654769.59344703</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.26233716799135626</v>
+        <v>0.28750781778110579</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>734639234.50636697</v>
+        <v>706937549.72649693</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>93200623.680056006</v>
+        <v>92654623.680056006</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>827839858.18642306</v>
+        <v>799592173.40655303</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>43570518.851917006</v>
+        <v>44421787.411475167</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25152,35 +25152,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>153628801.92758399</v>
+        <v>181134992.25664401</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>20698577.639975999</v>
+        <v>23568577.639975999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>174327379.56755999</v>
+        <v>204703569.89662001</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.27339961069581137</v>
+        <v>0.32103893522984628</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>386658257.07241601</v>
+        <v>359152066.74335599</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>76642848.360024005</v>
+        <v>73772848.360024005</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>463301105.43244004</v>
+        <v>432924915.10337996</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>24384268.706970528</v>
+        <v>24051384.172409996</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25204,7 +25204,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>92325602.239999995</v>
+        <v>123341852.23999999</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25212,15 +25212,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>92325602.239999995</v>
+        <v>123341852.23999999</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.2284531343570527</v>
+        <v>0.30520063837097222</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>311808061.75999999</v>
+        <v>280791811.75999999</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25228,11 +25228,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>311808061.75999999</v>
+        <v>280791811.75999999</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>16410950.618947368</v>
+        <v>15599545.097777776</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25256,35 +25256,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>124568945.48766901</v>
+        <v>133760703.15766799</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>29348863.854412999</v>
+        <v>34246061.990364</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>153917809.34208199</v>
+        <v>168006765.14803201</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.25189410813092744</v>
+        <v>0.27495138118078194</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>314448363.51233101</v>
+        <v>305256605.84233201</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>142675548.145587</v>
+        <v>137778350.00963598</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>457123911.65791798</v>
+        <v>443034955.85196799</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>24059153.245153576</v>
+        <v>24613053.102887109</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25308,35 +25308,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>183317238.90193999</v>
+        <v>213854001.74483201</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>15736126.305468</v>
+        <v>18407221.805468</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>199053365.20740798</v>
+        <v>232261223.5503</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.26228116657524025</v>
+        <v>0.3060372508623041</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>483312357.09806001</v>
+        <v>452775594.25516796</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>76565495.694532007</v>
+        <v>73894400.194532007</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>559877852.79259205</v>
+        <v>526669994.4497</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>29467255.410136424</v>
+        <v>29259444.136094444</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25360,35 +25360,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>96238037.215053007</v>
+        <v>106446757.925051</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>12766305.931799</v>
+        <v>20384697.426798999</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>109004343.146852</v>
+        <v>126831455.35185</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.21008139145610552</v>
+        <v>0.2444391466569657</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>325304985.78494698</v>
+        <v>315096265.07494903</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>84557870.068201005</v>
+        <v>76939478.573201001</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>409862855.85314798</v>
+        <v>392035743.64814997</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>21571729.255428839</v>
+        <v>21779763.536008332</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25412,35 +25412,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>252347348.71590301</v>
+        <v>303643157.845487</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>11359406.759997001</v>
+        <v>41052595.559517004</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>263706755.47590002</v>
+        <v>344695753.40500402</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.26861764803000826</v>
+        <v>0.35111486771921452</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>366003593.28409696</v>
+        <v>314707784.154513</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>352007559.24000299</v>
+        <v>322314370.44048297</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>718011152.52409995</v>
+        <v>637022154.59499598</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>37790060.659163155</v>
+        <v>35390119.699721999</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25464,35 +25464,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>58853093.639789999</v>
+        <v>69453418.021081001</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>32604979.759608001</v>
+        <v>70097685.959368005</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>91458073.399397999</v>
+        <v>139551103.98044902</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.15605695302512368</v>
+        <v>0.23811916508864958</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>235672595.36021</v>
+        <v>225072270.978919</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>258925073.240392</v>
+        <v>221432367.04063201</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>494597668.60060203</v>
+        <v>446504638.01955098</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>26031456.242136948</v>
+        <v>24805813.223308388</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25514,35 +25514,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>2175157486.1720157</v>
+        <v>2504933648.4958258</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>302626154.10361993</v>
+        <v>427591762.82670504</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>2477783640.2756357</v>
+        <v>2932525411.3225312</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.27322355360206113</v>
+        <v>0.32336762616640585</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>5084121845.8279839</v>
+        <v>4754345683.5041742</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1506798904.8963797</v>
+        <v>1381833296.1732953</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>6590920750.7243652</v>
+        <v>6136178979.6774702</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>346890565.82759815</v>
+        <v>340898832.20430392</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25584,7 +25584,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>150475946.51989999</v>
+        <v>155959369.87990001</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25596,7 +25596,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>11042432.24</v>
+        <v>12988378.16</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>82001802.109999999</v>
+        <v>88542342.609999999</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25656,7 +25656,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>486263072.48997998</v>
+        <v>528253164.88998002</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>93887839.209775001</v>
+        <v>97941893.209775001</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="D79" s="192">
         <f>IF(E11="",0,E11)</f>
-        <v>0</v>
+        <v>1783783.8</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>210438650.29978001</v>
+        <v>211962974.69977999</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25716,7 +25716,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>49164133.729999997</v>
+        <v>57238908.399999999</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25740,7 +25740,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>17708108.460000001</v>
+        <v>18572973.34</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25750,7 +25750,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1116067029.9344349</v>
+        <v>1188328833.8644347</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25764,13 +25764,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25812,19 +25812,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>80412292.329539001</v>
+        <v>81758283.299530998</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.28162412563092332</v>
+        <v>0.28633812543182025</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>205118260.670461</v>
+        <v>203772269.70046902</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>10795697.930024263</v>
+        <v>11320681.650026057</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25841,19 +25841,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>121443345.52067301</v>
+        <v>126042913.180613</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.28319597856528772</v>
+        <v>0.29392179527306461</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>307388116.47932696</v>
+        <v>302788548.81938702</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16178321.919964576</v>
+        <v>16821586.045521501</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25870,19 +25870,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>275337806.31482899</v>
+        <v>304509189.634718</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.24661039583096617</v>
+        <v>0.27273817858532173</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>841151242.68517101</v>
+        <v>811979859.36528206</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>44271118.03606163</v>
+        <v>45109992.186960116</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25955,29 +25955,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>477193444.16504097</v>
+        <v>512310386.11486197</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.26064023095493088</v>
+        <v>0.27982089651551362</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1353657619.834959</v>
+        <v>1318540677.885138</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>71245137.886050478</v>
+        <v>73252259.882507667</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25985,6 +25980,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26757,10 +26757,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26822,7 +26822,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27821,13 +27821,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28030,11 +28030,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28042,6 +28037,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 10 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 11 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1927,15 +1927,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1957,6 +1948,16 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3599,10 +3600,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -3629,7 +3630,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3664,7 +3665,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4663,13 +4664,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4872,6 +4873,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4879,11 +4885,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5656,10 +5657,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -5686,7 +5687,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5721,7 +5722,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6720,13 +6721,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6929,6 +6930,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6936,11 +6942,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7713,10 +7714,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -7743,7 +7744,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7778,7 +7779,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8777,13 +8778,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8986,6 +8987,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8993,11 +8999,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9770,10 +9771,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -9800,7 +9801,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9835,7 +9836,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10834,13 +10835,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11043,6 +11044,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11050,11 +11056,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11826,10 +11827,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -11856,7 +11857,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11891,7 +11892,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12876,13 +12877,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13085,6 +13086,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13092,11 +13098,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21664,7 +21665,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22337,11 +22338,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="238" t="s">
+      <c r="B41" s="245" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="239"/>
-      <c r="D41" s="240"/>
+      <c r="C41" s="246"/>
+      <c r="D41" s="247"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22401,7 +22402,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>35155226.678422607</v>
+        <v>37223181.188918054</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22430,7 +22431,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>30865962.762038376</v>
+        <v>32681607.630393576</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22459,7 +22460,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>6098473.0410951506</v>
+        <v>6457206.7493948657</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22486,7 +22487,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>72119662.481556132</v>
+        <v>76361995.568706498</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22507,10 +22508,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -22537,7 +22538,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22572,7 +22573,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22623,7 +22624,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>8441340.1848090719</v>
+        <v>8937889.6074448992</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22675,7 +22676,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>7552757.4992927779</v>
+        <v>7997037.3521923525</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22727,7 +22728,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>2439190.1222222215</v>
+        <v>2582671.8941176464</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22779,7 +22780,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-2241594.8603348401</v>
+        <v>-2373453.3815310071</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22831,7 +22832,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>7266354.3117514513</v>
+        <v>7693786.9183250666</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22883,7 +22884,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>4482639.1363857584</v>
+        <v>4746323.7914672736</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22935,7 +22936,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-1395396.4260410864</v>
+        <v>-1477478.5687493857</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22987,7 +22988,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>6156357.1241827803</v>
+        <v>6518495.7785464739</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23039,7 +23040,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>5756230.009445833</v>
+        <v>6094831.7747073527</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23091,7 +23092,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>4200663.7587377988</v>
+        <v>4447761.6268988466</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23143,7 +23144,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>9846453.1892154589</v>
+        <v>10425656.317992838</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23195,7 +23196,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>6576351.5645651584</v>
+        <v>6963195.7742454624</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23247,7 +23248,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>1922537.942388634</v>
+        <v>2035628.4095879653</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23299,7 +23300,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>5017305.8838400207</v>
+        <v>5312441.5240659043</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23349,7 +23350,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>66021189.44046104</v>
+        <v>69904788.819311693</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23571,13 +23572,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23631,7 +23632,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-742387.6620151368</v>
+        <v>-786057.52448661532</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23660,7 +23661,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-1029415.7076601353</v>
+        <v>-1089969.5728166138</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23689,7 +23690,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>7870276.4107704293</v>
+        <v>8333233.8466981016</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23774,12 +23775,17 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>6098473.0410951572</v>
+        <v>6457206.7493948722</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23787,11 +23793,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23860,7 +23861,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23942,11 +23943,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>131003162.560046</v>
+        <v>135378995.011134</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>30741238.848979998</v>
+        <v>32185396.508979999</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23964,11 +23965,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>234820630.080697</v>
+        <v>245043404.90069699</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>66215972.277888998</v>
+        <v>67522165.977889001</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23976,23 +23977,23 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>106446757.925051</v>
+        <v>119515303.00117099</v>
       </c>
       <c r="D10" s="205">
-        <v>20384697.426798999</v>
+        <v>21722428.966798998</v>
       </c>
       <c r="E10" s="205">
-        <v>57238908.399999999</v>
+        <v>58860530</v>
       </c>
       <c r="F10" s="205">
-        <v>184070363.75185001</v>
+        <v>200098261.96797001</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>362230308.49726498</v>
+        <v>406728427.45804399</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
@@ -24004,27 +24005,27 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>133760703.15766799</v>
+        <v>136023172.067651</v>
       </c>
       <c r="D11" s="205">
-        <v>34246061.990364</v>
+        <v>35515061.990364</v>
       </c>
       <c r="E11" s="205">
         <v>1783783.8</v>
       </c>
       <c r="F11" s="205">
-        <v>169790548.94803199</v>
+        <v>173322017.858015</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>100441439.8</v>
+        <v>124315313.7999</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>37956650.210000001</v>
+        <v>46234425.210000001</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -24032,27 +24033,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>124706041.402551</v>
+        <v>128161861.222551</v>
       </c>
       <c r="D12" s="205">
-        <v>39332135.068071999</v>
+        <v>40638328.768072002</v>
       </c>
       <c r="E12" s="205">
-        <v>2670270.2400000002</v>
+        <v>24940539.879999999</v>
       </c>
       <c r="F12" s="205">
-        <v>166708446.710623</v>
+        <v>193740729.87062299</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>194596923.17355201</v>
+        <v>201880098.311389</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>40895843.640844002</v>
+        <v>44391483.320831999</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24060,27 +24061,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>110114588.678146</v>
+        <v>116881543.678146</v>
       </c>
       <c r="D13" s="205">
         <v>26883837.209817</v>
       </c>
       <c r="E13" s="205">
-        <v>10318107.92</v>
+        <v>11615405.199999999</v>
       </c>
       <c r="F13" s="205">
-        <v>147316533.80796301</v>
+        <v>155380786.08796301</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>289820795.27350301</v>
+        <v>336029619.6706</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>32833974.319944002</v>
+        <v>33785325.679941997</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24088,27 +24089,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>362230308.49726498</v>
+        <v>406728427.45804399</v>
       </c>
       <c r="D14" s="205">
         <v>11191243.147555999</v>
       </c>
       <c r="E14" s="205">
-        <v>88542342.609999999</v>
+        <v>93474955.230000004</v>
       </c>
       <c r="F14" s="205">
-        <v>461963894.254821</v>
+        <v>511394625.83560002</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>181134992.25664401</v>
+        <v>191861943.63743401</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>23568577.639975999</v>
+        <v>30404159.599975999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24124,11 +24125,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>133760703.15766799</v>
+        <v>136023172.067651</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>34246061.990364</v>
+        <v>35515061.990364</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24136,27 +24137,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>194596923.17355201</v>
+        <v>201880098.311389</v>
       </c>
       <c r="D16" s="205">
-        <v>40895843.640844002</v>
+        <v>44391483.320831999</v>
       </c>
       <c r="E16" s="205">
-        <v>9495225.0999999996</v>
+        <v>14360089.9</v>
       </c>
       <c r="F16" s="205">
-        <v>244987991.91439599</v>
+        <v>260631671.53222099</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>213854001.74483201</v>
+        <v>233680095.40669799</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>18407221.805468</v>
+        <v>19663021.805468</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24164,27 +24165,27 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>100441439.8</v>
+        <v>124315313.7999</v>
       </c>
       <c r="D17" s="205">
-        <v>37956650.210000001</v>
+        <v>46234425.210000001</v>
       </c>
       <c r="E17" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>138398090.00999999</v>
+        <v>170549739.0099</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>106446757.925051</v>
+        <v>119515303.00117099</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>20384697.426798999</v>
+        <v>21722428.966798998</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24192,27 +24193,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>205933716.21912</v>
+        <v>211337932.37909099</v>
       </c>
       <c r="D18" s="205">
         <v>1115504.509997</v>
       </c>
       <c r="E18" s="205">
-        <v>6824324.2400000002</v>
+        <v>6986486.4000000004</v>
       </c>
       <c r="F18" s="205">
-        <v>213873544.96911699</v>
+        <v>219439923.28908801</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>303643157.845487</v>
+        <v>318172326.70523697</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>41052595.559517004</v>
+        <v>45108379.445509002</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24220,27 +24221,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>289820795.27350301</v>
+        <v>336029619.6706</v>
       </c>
       <c r="D19" s="205">
-        <v>32833974.319944002</v>
+        <v>33785325.679941997</v>
       </c>
       <c r="E19" s="205">
-        <v>528253164.88998002</v>
+        <v>569969388.88997996</v>
       </c>
       <c r="F19" s="205">
-        <v>850907934.48342705</v>
+        <v>939784334.24052203</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>69453418.021081001</v>
+        <v>75958599.120931</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>70097685.959368005</v>
+        <v>72286875.119332001</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24248,23 +24249,23 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>44172780.021081001</v>
+        <v>48987961.120931</v>
       </c>
       <c r="D20" s="205">
-        <v>13884556.67984</v>
+        <v>16073745.839803999</v>
       </c>
       <c r="E20" s="205">
         <v>1945946</v>
       </c>
       <c r="F20" s="205">
-        <v>60003282.700920999</v>
+        <v>67007652.960735001</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
       <c r="J20" s="116"/>
       <c r="M20" s="14">
         <f>IFERROR(C31,0)+IFERROR(C15,0)+IFERROR(C36,0)</f>
-        <v>0</v>
+        <v>411000</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>120</v>
@@ -24275,7 +24276,7 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>25280638</v>
+        <v>26970638</v>
       </c>
       <c r="D21" s="205">
         <v>56213129.279527999</v>
@@ -24284,14 +24285,14 @@
         <v>16627027.34</v>
       </c>
       <c r="F21" s="205">
-        <v>98120794.619527996</v>
+        <v>99810794.619527996</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>304509189.634718</v>
+        <v>373557754.84487098</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24307,11 +24308,11 @@
       <c r="D22" s="205" t="s">
         <v>168</v>
       </c>
-      <c r="E22" s="205" t="s">
-        <v>168</v>
+      <c r="E22" s="205">
+        <v>4684684.5599999996</v>
       </c>
       <c r="F22" s="205">
-        <v>60385505.920000002</v>
+        <v>65070190.479999997</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24322,16 +24323,16 @@
         <v>173</v>
       </c>
       <c r="C23" s="205">
-        <v>123341852.23999999</v>
+        <v>152812172.24000001</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>168</v>
       </c>
       <c r="E23" s="205">
-        <v>3687657.56</v>
+        <v>5129098.96</v>
       </c>
       <c r="F23" s="205">
-        <v>127029509.8</v>
+        <v>157941271.19999999</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24342,16 +24343,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>131003162.560046</v>
+        <v>135378995.011134</v>
       </c>
       <c r="D24" s="205">
-        <v>30741238.848979998</v>
+        <v>32185396.508979999</v>
       </c>
       <c r="E24" s="205">
-        <v>155959369.87990001</v>
+        <v>196175586.27990001</v>
       </c>
       <c r="F24" s="205">
-        <v>317703771.28892601</v>
+        <v>363739977.80001402</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24362,16 +24363,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>181134992.25664401</v>
+        <v>191861943.63743401</v>
       </c>
       <c r="D25" s="205">
-        <v>23568577.639975999</v>
+        <v>30404159.599975999</v>
       </c>
       <c r="E25" s="205">
-        <v>97941893.209775001</v>
+        <v>105378830.049775</v>
       </c>
       <c r="F25" s="205">
-        <v>302645463.10639501</v>
+        <v>327644933.28718501</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24382,16 +24383,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>213854001.74483201</v>
+        <v>233680095.40669799</v>
       </c>
       <c r="D26" s="205">
-        <v>18407221.805468</v>
+        <v>19663021.805468</v>
       </c>
       <c r="E26" s="205">
-        <v>211962974.69977999</v>
+        <v>263548744.42969999</v>
       </c>
       <c r="F26" s="205">
-        <v>444224198.25007999</v>
+        <v>516891861.64186603</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24402,16 +24403,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>303643157.845487</v>
+        <v>318172326.70523697</v>
       </c>
       <c r="D27" s="205">
-        <v>41052595.559517004</v>
+        <v>45108379.445509002</v>
       </c>
       <c r="E27" s="205">
         <v>1902162.2150000001</v>
       </c>
       <c r="F27" s="205">
-        <v>346597915.620004</v>
+        <v>365182868.36574602</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24454,7 +24455,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>81758283.299530998</v>
+        <v>83483688.659519002</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24464,8 +24465,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="205">
-        <v>126042913.180613</v>
+      <c r="C33" s="248">
+        <v>153267348.45391101</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24476,7 +24477,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>60934053.821280003</v>
+        <v>67689999.712246999</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24487,7 +24488,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>243575135.813438</v>
+        <v>305456755.13262397</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24497,8 +24498,8 @@
       <c r="B36" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="C36" s="15">
-        <v>0</v>
+      <c r="C36" s="205">
+        <v>411000</v>
       </c>
       <c r="G36" s="116"/>
       <c r="H36" s="116"/>
@@ -24539,7 +24540,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.33333333333333331</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24582,19 +24583,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>2504933648.4958258</v>
+        <v>2737784977.250886</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.34506643620306771</v>
+        <v>0.37714280606097028</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>4754345683.5041742</v>
+        <v>4521494354.749114</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>264130315.75023189</v>
+        <v>265970256.16171259</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24611,19 +24612,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>427591762.82670504</v>
+        <v>460009966.77264714</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.2363136072974576</v>
+        <v>0.25422990827090514</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1381833296.173295</v>
+        <v>1349415092.2273529</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>76768516.454071939</v>
+        <v>79377358.366314873</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24640,19 +24641,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>512310386.11486197</v>
+        <v>610308791.95830107</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.27982089651551362</v>
+        <v>0.33334704496657031</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1318540677.885138</v>
+        <v>1220542272.0416989</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>73252259.882507667</v>
+        <v>71796604.237746999</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24667,19 +24668,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>3444835797.4373927</v>
+        <v>3808103735.9818339</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.31605287129918019</v>
+        <v>0.34938156438618112</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>7454719657.5626068</v>
+        <v>7091451719.0181656</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>414151092.08681148</v>
+        <v>417144218.76577443</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24700,10 +24701,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -24730,7 +24731,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24765,7 +24766,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24788,35 +24789,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>131003162.560046</v>
+        <v>135378995.011134</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>30741238.848979998</v>
+        <v>32185396.508979999</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>161744401.409026</v>
+        <v>167564391.520114</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.29221380188792401</v>
+        <v>0.30272842509896425</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>320680315.43995398</v>
+        <v>316304482.98886597</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>71089184.151020005</v>
+        <v>69645026.491019994</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>391769499.59097397</v>
+        <v>385949509.479886</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>21764972.199498553</v>
+        <v>22702912.322346237</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24840,35 +24841,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>234820630.080697</v>
+        <v>245043404.90069699</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>66215972.277888998</v>
+        <v>67522165.977889001</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>301036602.35858601</v>
+        <v>312565570.87858599</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.36923905143240482</v>
+        <v>0.38338000760506352</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>355361740.919303</v>
+        <v>345138966.09930301</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>158890833.72211099</v>
+        <v>157584640.022111</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>514252574.64141399</v>
+        <v>502723606.12141401</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>28569587.480078556</v>
+        <v>29571976.830671411</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24920,7 +24921,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>10060431.226666667</v>
+        <v>10652221.298823528</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24944,7 +24945,7 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>362230308.49726498</v>
+        <v>406728427.45804399</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
@@ -24952,15 +24953,15 @@
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>373421551.64482099</v>
+        <v>417919670.6056</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.51424544529986549</v>
+        <v>0.57552459455945948</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>283482163.50273502</v>
+        <v>238984044.54195601</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
@@ -24968,11 +24969,11 @@
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>352732768.35517901</v>
+        <v>308234649.3944</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>19596264.908621058</v>
+        <v>18131449.964376472</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24996,35 +24997,35 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>100441439.8</v>
+        <v>124315313.7999</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>37956650.210000001</v>
+        <v>46234425.210000001</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>138398090.00999999</v>
+        <v>170549739.0099</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.23479659370112527</v>
+        <v>0.28934284984169234</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>408477392.19999999</v>
+        <v>384603518.2001</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>42562753.789999999</v>
+        <v>34284978.789999999</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>451040145.99000001</v>
+        <v>418888496.99010003</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>25057785.888333336</v>
+        <v>24640499.822947059</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25048,35 +25049,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>194596923.17355201</v>
+        <v>201880098.311389</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>40895843.640844002</v>
+        <v>44391483.320831999</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>235492766.81439602</v>
+        <v>246271581.63222098</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.45095189728441815</v>
+        <v>0.47159256093761032</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>245466360.82644799</v>
+        <v>238183185.688611</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>41253481.359155998</v>
+        <v>37757841.679168001</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>286719842.18560398</v>
+        <v>275941027.36777902</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>15928880.121422444</v>
+        <v>16231825.139281118</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25100,35 +25101,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>289820795.27350301</v>
+        <v>336029619.6706</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>32833974.319944002</v>
+        <v>33785325.679941997</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>322654769.59344703</v>
+        <v>369814945.35054201</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.28750781778110579</v>
+        <v>0.32953081107260546</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>706937549.72649693</v>
+        <v>660728725.32940006</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>92654623.680056006</v>
+        <v>91703272.320058003</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>799592173.40655303</v>
+        <v>752431997.64945793</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>44421787.411475167</v>
+        <v>44260705.744085759</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25152,35 +25153,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>181134992.25664401</v>
+        <v>191861943.63743401</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>23568577.639975999</v>
+        <v>30404159.599975999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>204703569.89662001</v>
+        <v>222266103.23741001</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.32103893522984628</v>
+        <v>0.34858245587539899</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>359152066.74335599</v>
+        <v>348425115.36256599</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>73772848.360024005</v>
+        <v>66937266.400023997</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>432924915.10337996</v>
+        <v>415362381.76258999</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>24051384.172409996</v>
+        <v>24433081.280152351</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25204,7 +25205,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>123341852.23999999</v>
+        <v>152812172.24000001</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25212,15 +25213,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>123341852.23999999</v>
+        <v>152812172.24000001</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.30520063837097222</v>
+        <v>0.37812284858308665</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>280791811.75999999</v>
+        <v>251321491.75999999</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25228,11 +25229,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>280791811.75999999</v>
+        <v>251321491.75999999</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>15599545.097777776</v>
+        <v>14783617.16235294</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25256,35 +25257,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>133760703.15766799</v>
+        <v>136023172.067651</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>34246061.990364</v>
+        <v>35515061.990364</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>168006765.14803201</v>
+        <v>171538234.05801499</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.27495138118078194</v>
+        <v>0.28073080472685924</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>305256605.84233201</v>
+        <v>302994136.93234897</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>137778350.00963598</v>
+        <v>136509350.00963598</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>443034955.85196799</v>
+        <v>439503486.94198501</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>24613053.102887109</v>
+        <v>25853146.290704999</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25308,35 +25309,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>213854001.74483201</v>
+        <v>233680095.40669799</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>18407221.805468</v>
+        <v>19663021.805468</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>232261223.5503</v>
+        <v>253343117.21216598</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.3060372508623041</v>
+        <v>0.33381564917015444</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>452775594.25516796</v>
+        <v>432949500.59330201</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>73894400.194532007</v>
+        <v>72638600.194532007</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>526669994.4497</v>
+        <v>505588100.78783405</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>29259444.136094444</v>
+        <v>29740476.516931415</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25360,35 +25361,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>106446757.925051</v>
+        <v>119515303.00117099</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>20384697.426798999</v>
+        <v>21722428.966798998</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>126831455.35185</v>
+        <v>141237731.96796998</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.2444391466569657</v>
+        <v>0.27220400950411588</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>315096265.07494903</v>
+        <v>302027719.99882901</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>76939478.573201001</v>
+        <v>75601747.033201009</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>392035743.64814997</v>
+        <v>377629467.03202999</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>21779763.536008332</v>
+        <v>22213498.060707647</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25412,35 +25413,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>303643157.845487</v>
+        <v>318172326.70523697</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>41052595.559517004</v>
+        <v>45108379.445509002</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>344695753.40500402</v>
+        <v>363280706.15074599</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.35111486771921452</v>
+        <v>0.37004591969890599</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>314707784.154513</v>
+        <v>300178615.29476303</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>322314370.44048297</v>
+        <v>318258586.55449098</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>637022154.59499598</v>
+        <v>618437201.84925401</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>35390119.699721999</v>
+        <v>36378658.932309061</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25464,35 +25465,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>69453418.021081001</v>
+        <v>75958599.120931</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>70097685.959368005</v>
+        <v>72286875.119332001</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>139551103.98044902</v>
+        <v>148245474.24026299</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.23811916508864958</v>
+        <v>0.25295456322013649</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>225072270.978919</v>
+        <v>218567089.879069</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>221432367.04063201</v>
+        <v>219243177.88066798</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>446504638.01955098</v>
+        <v>437810267.75973701</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>24805813.223308388</v>
+        <v>25753545.162337471</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25514,35 +25515,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>2504933648.4958258</v>
+        <v>2737784977.250886</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>427591762.82670504</v>
+        <v>460009966.77264714</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>2932525411.3225312</v>
+        <v>3197794944.0235329</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.32336762616640585</v>
+        <v>0.35261872105976916</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>4754345683.5041742</v>
+        <v>4521494354.749114</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1381833296.1732953</v>
+        <v>1349415092.2273529</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>6136178979.6774702</v>
+        <v>5870909446.9764662</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>340898832.20430392</v>
+        <v>345347614.52802742</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25584,7 +25585,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>155959369.87990001</v>
+        <v>196175586.27990001</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25596,7 +25597,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>12988378.16</v>
+        <v>36555945.079999998</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25608,7 +25609,7 @@
       </c>
       <c r="D72" s="192">
         <f>IF(E22="",0,E22)</f>
-        <v>0</v>
+        <v>4684684.5599999996</v>
       </c>
     </row>
     <row r="73" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25620,7 +25621,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>88542342.609999999</v>
+        <v>93474955.230000004</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25644,7 +25645,7 @@
       </c>
       <c r="D75" s="192">
         <f>IF(E16="",0,E16)</f>
-        <v>9495225.0999999996</v>
+        <v>14360089.9</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25656,7 +25657,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>528253164.88998002</v>
+        <v>569969388.88997996</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25668,7 +25669,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>97941893.209775001</v>
+        <v>105378830.049775</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25680,7 +25681,7 @@
       </c>
       <c r="D78" s="192">
         <f>IF(E23="",0,E23)</f>
-        <v>3687657.56</v>
+        <v>5129098.96</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25704,7 +25705,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>211962974.69977999</v>
+        <v>263548744.42969999</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25716,7 +25717,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>57238908.399999999</v>
+        <v>58860530</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25750,7 +25751,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1188328833.8644347</v>
+        <v>1370396772.7343547</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25764,13 +25765,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25812,19 +25813,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>81758283.299530998</v>
+        <v>83483688.659519002</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.28633812543182025</v>
+        <v>0.29238093010494398</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>203772269.70046902</v>
+        <v>202046864.34048098</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>11320681.650026057</v>
+        <v>11885109.667087117</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25841,19 +25842,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>126042913.180613</v>
+        <v>153267348.45391101</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.29392179527306461</v>
+        <v>0.35740695829335162</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>302788548.81938702</v>
+        <v>275564113.54608899</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16821586.045521501</v>
+        <v>16209653.738005236</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25870,19 +25871,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>304509189.634718</v>
+        <v>373557754.84487098</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.27273817858532173</v>
+        <v>0.33458255159730721</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>811979859.36528206</v>
+        <v>742931294.15512896</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>45109992.186960116</v>
+        <v>43701840.832654648</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25955,24 +25956,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>512310386.11486197</v>
+        <v>610308791.95830107</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.27982089651551362</v>
+        <v>0.33334704496657031</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1318540677.885138</v>
+        <v>1220542272.0416989</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>73252259.882507667</v>
+        <v>71796604.237746999</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25980,11 +25986,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26757,10 +26758,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -26787,7 +26788,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26822,7 +26823,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27821,13 +27822,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28030,6 +28031,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28037,11 +28043,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 11 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 12 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1831,6 +1831,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1927,6 +1928,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1948,16 +1958,6 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2713,16 +2713,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="206" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="206"/>
+      <c r="B1" s="207" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="207"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="207"/>
+      <c r="C3" s="208"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2773,10 +2773,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="208"/>
+      <c r="C11" s="209"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -3429,11 +3429,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3557,10 +3557,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3589,40 +3589,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3630,13 +3630,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3655,7 +3655,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3665,7 +3665,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4458,10 +4458,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4469,8 +4469,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -4664,13 +4664,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4873,11 +4873,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4885,6 +4880,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5486,11 +5486,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5614,10 +5614,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5646,40 +5646,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5687,13 +5687,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5712,7 +5712,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5722,7 +5722,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6515,10 +6515,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6526,8 +6526,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -6721,13 +6721,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6930,11 +6930,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6942,6 +6937,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7543,11 +7543,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7671,10 +7671,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7703,40 +7703,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7744,13 +7744,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7769,7 +7769,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7779,7 +7779,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8572,10 +8572,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8583,8 +8583,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -8778,13 +8778,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8987,11 +8987,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8999,6 +8994,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9600,11 +9600,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9728,10 +9728,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9760,40 +9760,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9801,13 +9801,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9826,7 +9826,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9836,7 +9836,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10629,10 +10629,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10640,8 +10640,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -10835,13 +10835,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11044,11 +11044,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11056,6 +11051,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11657,11 +11657,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11784,10 +11784,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11816,40 +11816,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11857,13 +11857,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11882,7 +11882,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11892,7 +11892,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12671,10 +12671,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12682,8 +12682,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -12877,13 +12877,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13086,11 +13086,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13098,6 +13093,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -13172,10 +13172,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="208" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="207"/>
+      <c r="C3" s="208"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14652,13 +14652,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="209" t="s">
+      <c r="B29" s="210" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="209"/>
-      <c r="D29" s="209"/>
-      <c r="E29" s="209"/>
-      <c r="F29" s="209"/>
+      <c r="C29" s="210"/>
+      <c r="D29" s="210"/>
+      <c r="E29" s="210"/>
+      <c r="F29" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15190,10 +15190,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="211" t="s">
+      <c r="B44" s="212" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="212"/>
+      <c r="C44" s="213"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15233,23 +15233,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="214" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="213" t="s">
+      <c r="C47" s="214" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="214" t="s">
+      <c r="D47" s="215" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="215"/>
-      <c r="F47" s="216"/>
+      <c r="E47" s="216"/>
+      <c r="F47" s="217"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="213" t="s">
+      <c r="J47" s="214" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15257,13 +15257,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="210" t="s">
+      <c r="N47" s="211" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
+      <c r="B48" s="214"/>
+      <c r="C48" s="214"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15282,7 +15282,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="213"/>
+      <c r="J48" s="214"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15292,7 +15292,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16725,10 +16725,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="211" t="s">
+      <c r="B44" s="212" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="212"/>
+      <c r="C44" s="213"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16768,23 +16768,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="214" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="213" t="s">
+      <c r="C47" s="214" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="214" t="s">
+      <c r="D47" s="215" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="215"/>
-      <c r="F47" s="216"/>
+      <c r="E47" s="216"/>
+      <c r="F47" s="217"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="213" t="s">
+      <c r="J47" s="214" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16792,13 +16792,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="210" t="s">
+      <c r="N47" s="211" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
+      <c r="B48" s="214"/>
+      <c r="C48" s="214"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16817,7 +16817,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="213"/>
+      <c r="J48" s="214"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16827,7 +16827,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -18412,10 +18412,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="221" t="s">
+      <c r="B44" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="222"/>
+      <c r="C44" s="223"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18480,23 +18480,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="223" t="s">
+      <c r="B47" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="223" t="s">
+      <c r="C47" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="218" t="s">
+      <c r="D47" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="219"/>
-      <c r="F47" s="220"/>
+      <c r="E47" s="220"/>
+      <c r="F47" s="221"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="223" t="s">
+      <c r="J47" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18504,13 +18504,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="217" t="s">
+      <c r="N47" s="218" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="223"/>
-      <c r="C48" s="223"/>
+      <c r="B48" s="224"/>
+      <c r="C48" s="224"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18529,7 +18529,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="223"/>
+      <c r="J48" s="224"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18539,7 +18539,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="217"/>
+      <c r="N48" s="218"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -20161,11 +20161,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20283,10 +20283,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20309,40 +20309,40 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="235"/>
-      <c r="L48" s="236"/>
-      <c r="M48" s="236"/>
-      <c r="N48" s="237"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="236"/>
+      <c r="L48" s="237"/>
+      <c r="M48" s="237"/>
+      <c r="N48" s="238"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="234" t="s">
+      <c r="B49" s="235" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="234" t="s">
+      <c r="C49" s="235" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="231" t="s">
+      <c r="D49" s="232" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="232"/>
-      <c r="F49" s="233"/>
+      <c r="E49" s="233"/>
+      <c r="F49" s="234"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="234" t="s">
+      <c r="J49" s="235" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20350,13 +20350,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="227" t="s">
+      <c r="N49" s="228" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="234"/>
-      <c r="C50" s="234"/>
+      <c r="B50" s="235"/>
+      <c r="C50" s="235"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20375,7 +20375,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="234"/>
+      <c r="J50" s="235"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20385,7 +20385,7 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="227"/>
+      <c r="N50" s="228"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="183" t="s">
@@ -21176,10 +21176,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21190,8 +21190,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -21377,13 +21377,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="228" t="s">
+      <c r="B87" s="229" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="229"/>
-      <c r="D87" s="229"/>
-      <c r="E87" s="229"/>
-      <c r="F87" s="230"/>
+      <c r="C87" s="230"/>
+      <c r="D87" s="230"/>
+      <c r="E87" s="230"/>
+      <c r="F87" s="231"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22338,11 +22338,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="245" t="s">
+      <c r="B41" s="239" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="246"/>
-      <c r="D41" s="247"/>
+      <c r="C41" s="240"/>
+      <c r="D41" s="241"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>37223181.188918054</v>
+        <v>39549630.013225436</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22431,7 +22431,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>32681607.630393576</v>
+        <v>34724208.107293174</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22460,15 +22460,15 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>6457206.7493948657</v>
+        <v>6860782.1712320447</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
@@ -22487,7 +22487,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>76361995.568706498</v>
+        <v>81134620.291750655</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22497,40 +22497,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22538,13 +22538,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22563,7 +22563,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22573,7 +22573,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>8937889.6074448992</v>
+        <v>9496507.7079102062</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>7997037.3521923525</v>
+        <v>8496852.1867043748</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>2582671.8941176464</v>
+        <v>2744088.8874999993</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22780,7 +22780,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-2373453.3815310071</v>
+        <v>-2521794.2178766951</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>7693786.9183250666</v>
+        <v>8174648.6007203832</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>4746323.7914672736</v>
+        <v>5042969.0284339786</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-1477478.5687493857</v>
+        <v>-1569820.9792962223</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22988,7 +22988,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>6518495.7785464739</v>
+        <v>6925901.7647056282</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>6094831.7747073527</v>
+        <v>6475758.7606265619</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>4447761.6268988466</v>
+        <v>4725746.7285800241</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23144,7 +23144,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>10425656.317992838</v>
+        <v>11077259.83786739</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>6963195.7742454624</v>
+        <v>7398395.5101358034</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>2035628.4095879653</v>
+        <v>2162855.1851872131</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>5312441.5240659043</v>
+        <v>5644469.1193200238</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>69904788.819311693</v>
+        <v>74273838.120518669</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23366,10 +23366,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23377,8 +23377,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -23572,13 +23572,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-786057.52448661532</v>
+        <v>-835186.11976702884</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-1089969.5728166138</v>
+        <v>-1158092.6711176522</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23690,7 +23690,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>8333233.8466981016</v>
+        <v>8854060.9621167332</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23775,17 +23775,12 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>6457206.7493948722</v>
+        <v>6860782.1712320521</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23793,6 +23788,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23861,7 +23861,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23943,11 +23943,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>135378995.011134</v>
+        <v>153195189.70111299</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>32185396.508979999</v>
+        <v>32846204.848972</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23965,11 +23965,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>245043404.90069699</v>
+        <v>250627839.900662</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>67522165.977889001</v>
+        <v>71329116.45788601</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23977,27 +23977,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>119515303.00117099</v>
+        <v>122607705.239004</v>
       </c>
       <c r="D10" s="205">
         <v>21722428.966798998</v>
       </c>
       <c r="E10" s="205">
-        <v>58860530</v>
+        <v>66503547.659999996</v>
       </c>
       <c r="F10" s="205">
-        <v>200098261.96797001</v>
+        <v>210833681.865803</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>406728427.45804399</v>
+        <v>433215286.78540802</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>11191243.147555999</v>
+        <v>12320972.887556</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24005,23 +24005,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>136023172.067651</v>
+        <v>151713072.94364899</v>
       </c>
       <c r="D11" s="205">
-        <v>35515061.990364</v>
+        <v>43101386.330268003</v>
       </c>
       <c r="E11" s="205">
         <v>1783783.8</v>
       </c>
       <c r="F11" s="205">
-        <v>173322017.858015</v>
+        <v>196598243.073917</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>124315313.7999</v>
+        <v>130317566.0399</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24033,27 +24033,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>128161861.222551</v>
+        <v>125164944.162646</v>
       </c>
       <c r="D12" s="205">
-        <v>40638328.768072002</v>
+        <v>42800238.698071003</v>
       </c>
       <c r="E12" s="205">
-        <v>24940539.879999999</v>
+        <v>29383539.879999999</v>
       </c>
       <c r="F12" s="205">
-        <v>193740729.87062299</v>
+        <v>197348722.74071699</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>201880098.311389</v>
+        <v>214201356.280561</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>44391483.320831999</v>
+        <v>48462348.180826001</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24061,27 +24061,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>116881543.678146</v>
+        <v>125462895.73801599</v>
       </c>
       <c r="D13" s="205">
-        <v>26883837.209817</v>
+        <v>28528877.759815</v>
       </c>
       <c r="E13" s="205">
-        <v>11615405.199999999</v>
+        <v>13913657.4</v>
       </c>
       <c r="F13" s="205">
-        <v>155380786.08796301</v>
+        <v>167905430.89783099</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>336029619.6706</v>
+        <v>399622960.05156302</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>33785325.679941997</v>
+        <v>37956947.329939</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24089,27 +24089,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>406728427.45804399</v>
+        <v>433215286.78540802</v>
       </c>
       <c r="D14" s="205">
-        <v>11191243.147555999</v>
+        <v>12320972.887556</v>
       </c>
       <c r="E14" s="205">
-        <v>93474955.230000004</v>
+        <v>103404684.89</v>
       </c>
       <c r="F14" s="205">
-        <v>511394625.83560002</v>
+        <v>548940944.56296396</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>191861943.63743401</v>
+        <v>196317107.082434</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>30404159.599975999</v>
+        <v>31250892.939971998</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24125,11 +24125,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>136023172.067651</v>
+        <v>151713072.94364899</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>35515061.990364</v>
+        <v>43101386.330268003</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24137,27 +24137,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>201880098.311389</v>
+        <v>214201356.280561</v>
       </c>
       <c r="D16" s="205">
-        <v>44391483.320831999</v>
+        <v>48462348.180826001</v>
       </c>
       <c r="E16" s="205">
-        <v>14360089.9</v>
+        <v>17069909.699999999</v>
       </c>
       <c r="F16" s="205">
-        <v>260631671.53222099</v>
+        <v>279733614.16138703</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>233680095.40669799</v>
+        <v>245320660.21154699</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>19663021.805468</v>
+        <v>23709940.735466</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24165,7 +24165,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>124315313.7999</v>
+        <v>130317566.0399</v>
       </c>
       <c r="D17" s="205">
         <v>46234425.210000001</v>
@@ -24174,14 +24174,14 @@
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>170549739.0099</v>
+        <v>176551991.24990001</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>119515303.00117099</v>
+        <v>122607705.239004</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
@@ -24193,27 +24193,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>211337932.37909099</v>
+        <v>225060686.539051</v>
       </c>
       <c r="D18" s="205">
-        <v>1115504.509997</v>
+        <v>1380603.6099970001</v>
       </c>
       <c r="E18" s="205">
-        <v>6986486.4000000004</v>
+        <v>5040540.4800000004</v>
       </c>
       <c r="F18" s="205">
-        <v>219439923.28908801</v>
+        <v>231481830.62904799</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>318172326.70523697</v>
+        <v>354627359.49477702</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>45108379.445509002</v>
+        <v>45812379.445509002</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24221,27 +24221,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>336029619.6706</v>
+        <v>399622960.05156302</v>
       </c>
       <c r="D19" s="205">
-        <v>33785325.679941997</v>
+        <v>37956947.329939</v>
       </c>
       <c r="E19" s="205">
-        <v>569969388.88997996</v>
+        <v>624812631.81997001</v>
       </c>
       <c r="F19" s="205">
-        <v>939784334.24052203</v>
+        <v>1062392539.201472</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>75958599.120931</v>
+        <v>81600040.120931</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>72286875.119332001</v>
+        <v>73847317.379317999</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24249,16 +24249,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>48987961.120931</v>
+        <v>54959402.120931</v>
       </c>
       <c r="D20" s="205">
         <v>16073745.839803999</v>
       </c>
       <c r="E20" s="205">
-        <v>1945946</v>
+        <v>3048648.72</v>
       </c>
       <c r="F20" s="205">
-        <v>67007652.960735001</v>
+        <v>74081796.680735007</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24276,23 +24276,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>26970638</v>
+        <v>26640638</v>
       </c>
       <c r="D21" s="205">
-        <v>56213129.279527999</v>
+        <v>57773571.539513998</v>
       </c>
       <c r="E21" s="205">
         <v>16627027.34</v>
       </c>
       <c r="F21" s="205">
-        <v>99810794.619527996</v>
+        <v>101041236.87951399</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>373557754.84487098</v>
+        <v>393152452.68463802</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24303,7 +24303,7 @@
         <v>172</v>
       </c>
       <c r="C22" s="205">
-        <v>60385505.920000002</v>
+        <v>67149256.400000006</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>168</v>
@@ -24312,7 +24312,7 @@
         <v>4684684.5599999996</v>
       </c>
       <c r="F22" s="205">
-        <v>65070190.479999997</v>
+        <v>71833940.959999993</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24323,7 +24323,7 @@
         <v>173</v>
       </c>
       <c r="C23" s="205">
-        <v>152812172.24000001</v>
+        <v>153956388.84</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>168</v>
@@ -24332,7 +24332,7 @@
         <v>5129098.96</v>
       </c>
       <c r="F23" s="205">
-        <v>157941271.19999999</v>
+        <v>159085487.80000001</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24343,16 +24343,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>135378995.011134</v>
+        <v>153195189.70111299</v>
       </c>
       <c r="D24" s="205">
-        <v>32185396.508979999</v>
+        <v>32846204.848972</v>
       </c>
       <c r="E24" s="205">
-        <v>196175586.27990001</v>
+        <v>156876401.39989999</v>
       </c>
       <c r="F24" s="205">
-        <v>363739977.80001402</v>
+        <v>342917795.94998503</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24363,16 +24363,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>191861943.63743401</v>
+        <v>196317107.082434</v>
       </c>
       <c r="D25" s="205">
-        <v>30404159.599975999</v>
+        <v>31250892.939971998</v>
       </c>
       <c r="E25" s="205">
-        <v>105378830.049775</v>
+        <v>120445452.11972</v>
       </c>
       <c r="F25" s="205">
-        <v>327644933.28718501</v>
+        <v>348013452.14212602</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24383,16 +24383,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>233680095.40669799</v>
+        <v>245320660.21154699</v>
       </c>
       <c r="D26" s="205">
-        <v>19663021.805468</v>
+        <v>23709940.735466</v>
       </c>
       <c r="E26" s="205">
-        <v>263548744.42969999</v>
+        <v>271402077.39973497</v>
       </c>
       <c r="F26" s="205">
-        <v>516891861.64186603</v>
+        <v>540432678.34674799</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24403,16 +24403,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>318172326.70523697</v>
+        <v>354627359.49477702</v>
       </c>
       <c r="D27" s="205">
-        <v>45108379.445509002</v>
+        <v>45812379.445509002</v>
       </c>
       <c r="E27" s="205">
-        <v>1902162.2150000001</v>
+        <v>5677297.4550000001</v>
       </c>
       <c r="F27" s="205">
-        <v>365182868.36574602</v>
+        <v>406117036.39528602</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24455,7 +24455,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>83483688.659519002</v>
+        <v>91679166.169450998</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24465,8 +24465,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="248">
-        <v>153267348.45391101</v>
+      <c r="C33" s="206">
+        <v>160538546.797405</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24477,7 +24477,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>67689999.712246999</v>
+        <v>79474968.432062</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24488,7 +24488,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>305456755.13262397</v>
+        <v>313266484.25257599</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24530,17 +24530,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.36666666666666664</v>
+        <v>0.4</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24583,19 +24583,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>2737784977.250886</v>
+        <v>2954471789.0915494</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.37714280606097028</v>
+        <v>0.40699243739909435</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>4521494354.749114</v>
+        <v>4304807542.9084511</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>265970256.16171259</v>
+        <v>269050471.43177819</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24612,19 +24612,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>460009966.77264714</v>
+        <v>488594360.71251106</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.25422990827090514</v>
+        <v>0.27002740913875617</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1349415092.2273529</v>
+        <v>1320830698.2874889</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>79377358.366314873</v>
+        <v>82551918.642968059</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24641,46 +24641,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>610308791.95830107</v>
+        <v>645370165.65149403</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.33334704496657031</v>
+        <v>0.35249735947472677</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1220542272.0416989</v>
+        <v>1185480898.348506</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>71796604.237746999</v>
+        <v>74092556.146781623</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10899555455</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>3808103735.9818339</v>
+        <v>4088436315.4555545</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.34938156438618112</v>
+        <v>0.3751011986071458</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>7091451719.0181656</v>
+        <v>6811119139.544446</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>417144218.76577443</v>
+        <v>425694946.22152787</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24690,40 +24690,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24731,13 +24731,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24756,7 +24756,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24766,7 +24766,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24789,35 +24789,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>135378995.011134</v>
+        <v>153195189.70111299</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>32185396.508979999</v>
+        <v>32846204.848972</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>167564391.520114</v>
+        <v>186041394.55008498</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.30272842509896425</v>
+        <v>0.33610970603263129</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>316304482.98886597</v>
+        <v>298488288.29888701</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>69645026.491019994</v>
+        <v>68984218.151028007</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>385949509.479886</v>
+        <v>367472506.44991505</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>22702912.322346237</v>
+        <v>22967031.653119691</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24841,35 +24841,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>245043404.90069699</v>
+        <v>250627839.900662</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>67522165.977889001</v>
+        <v>71329116.45788601</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>312565570.87858599</v>
+        <v>321956956.35854805</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.38338000760506352</v>
+        <v>0.39489909278968394</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>345138966.09930301</v>
+        <v>339554531.099338</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>157584640.022111</v>
+        <v>153777689.54211399</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>502723606.12141401</v>
+        <v>493332220.64145195</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>29571976.830671411</v>
+        <v>30833263.790090747</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>60385505.920000002</v>
+        <v>67149256.400000006</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -24901,15 +24901,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>60385505.920000002</v>
+        <v>67149256.400000006</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.25007118353158664</v>
+        <v>0.27808153240382699</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>181087762.07999998</v>
+        <v>174324011.59999999</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -24917,11 +24917,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>181087762.07999998</v>
+        <v>174324011.59999999</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>10652221.298823528</v>
+        <v>10895250.725</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24945,35 +24945,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>406728427.45804399</v>
+        <v>433215286.78540802</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>11191243.147555999</v>
+        <v>12320972.887556</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>417919670.6056</v>
+        <v>445536259.67296404</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.57552459455945948</v>
+        <v>0.61355588943265393</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>238984044.54195601</v>
+        <v>212497185.21459198</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>69250604.852443993</v>
+        <v>68120875.112443998</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>308234649.3944</v>
+        <v>280618060.32703596</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>18131449.964376472</v>
+        <v>17538628.770439748</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>124315313.7999</v>
+        <v>130317566.0399</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25005,15 +25005,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>170549739.0099</v>
+        <v>176551991.24990001</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.28934284984169234</v>
+        <v>0.29952585439316498</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>384603518.2001</v>
+        <v>378601265.9601</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25021,11 +25021,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>418888496.99010003</v>
+        <v>412886244.75010002</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>24640499.822947059</v>
+        <v>25805390.296881251</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25049,35 +25049,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>201880098.311389</v>
+        <v>214201356.280561</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>44391483.320831999</v>
+        <v>48462348.180826001</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>246271581.63222098</v>
+        <v>262663704.46138701</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.47159256093761032</v>
+        <v>0.5029823101444626</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>238183185.688611</v>
+        <v>225861927.719439</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>37757841.679168001</v>
+        <v>33686976.819173999</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>275941027.36777902</v>
+        <v>259548904.53861299</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>16231825.139281118</v>
+        <v>16221806.533663312</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25101,35 +25101,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>336029619.6706</v>
+        <v>399622960.05156302</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>33785325.679941997</v>
+        <v>37956947.329939</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>369814945.35054201</v>
+        <v>437579907.38150203</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.32953081107260546</v>
+        <v>0.38991410055594333</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>660728725.32940006</v>
+        <v>597135384.94843698</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>91703272.320058003</v>
+        <v>87531650.670060992</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>752431997.64945793</v>
+        <v>684667035.61849797</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>44260705.744085759</v>
+        <v>42791689.726156123</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25153,35 +25153,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>191861943.63743401</v>
+        <v>196317107.082434</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>30404159.599975999</v>
+        <v>31250892.939971998</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>222266103.23741001</v>
+        <v>227568000.02240598</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.34858245587539899</v>
+        <v>0.35689748086208223</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>348425115.36256599</v>
+        <v>343969951.917566</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>66937266.400023997</v>
+        <v>66090533.060028002</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>415362381.76258999</v>
+        <v>410060484.97759402</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>24433081.280152351</v>
+        <v>25628780.311099626</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>152812172.24000001</v>
+        <v>153956388.84</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25213,15 +25213,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>152812172.24000001</v>
+        <v>153956388.84</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.37812284858308665</v>
+        <v>0.38095413115597321</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>251321491.75999999</v>
+        <v>250177275.16</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25229,11 +25229,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>251321491.75999999</v>
+        <v>250177275.16</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>14783617.16235294</v>
+        <v>15636079.6975</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25257,35 +25257,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>136023172.067651</v>
+        <v>151713072.94364899</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>35515061.990364</v>
+        <v>43101386.330268003</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>171538234.05801499</v>
+        <v>194814459.27391699</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.28073080472685924</v>
+        <v>0.31882349859039655</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>302994136.93234897</v>
+        <v>287304236.05635101</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>136509350.00963598</v>
+        <v>128923025.669732</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>439503486.94198501</v>
+        <v>416227261.72608304</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>25853146.290704999</v>
+        <v>26014203.85788019</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25309,35 +25309,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>233680095.40669799</v>
+        <v>245320660.21154699</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>19663021.805468</v>
+        <v>23709940.735466</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>253343117.21216598</v>
+        <v>269030600.94701296</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.33381564917015444</v>
+        <v>0.35448614389059557</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>432949500.59330201</v>
+        <v>421308935.78845298</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>72638600.194532007</v>
+        <v>68591681.264533997</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>505588100.78783405</v>
+        <v>489900617.05298704</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>29740476.516931415</v>
+        <v>30618788.56581169</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25361,7 +25361,7 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>119515303.00117099</v>
+        <v>122607705.239004</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
@@ -25369,15 +25369,15 @@
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>141237731.96796998</v>
+        <v>144330134.20580301</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.27220400950411588</v>
+        <v>0.27816392033253773</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>302027719.99882901</v>
+        <v>298935317.76099598</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
@@ -25385,11 +25385,11 @@
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>377629467.03202999</v>
+        <v>374537064.79419696</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>22213498.060707647</v>
+        <v>23408566.54963731</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25413,35 +25413,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>318172326.70523697</v>
+        <v>354627359.49477702</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>45108379.445509002</v>
+        <v>45812379.445509002</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>363280706.15074599</v>
+        <v>400439738.94028604</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.37004591969890599</v>
+        <v>0.40789694847889646</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>300178615.29476303</v>
+        <v>263723582.50522298</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>318258586.55449098</v>
+        <v>317554586.55449098</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>618437201.84925401</v>
+        <v>581278169.05971396</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>36378658.932309061</v>
+        <v>36329885.566232122</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25465,35 +25465,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>75958599.120931</v>
+        <v>81600040.120931</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>72286875.119332001</v>
+        <v>73847317.379317999</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>148245474.24026299</v>
+        <v>155447357.500249</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.25295456322013649</v>
+        <v>0.26524329745454317</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>218567089.879069</v>
+        <v>212925648.879069</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>219243177.88066798</v>
+        <v>217682735.620682</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>437810267.75973701</v>
+        <v>430608384.49975097</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>25753545.162337471</v>
+        <v>26913024.031234436</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25515,35 +25515,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>2737784977.250886</v>
+        <v>2954471789.0915494</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>460009966.77264714</v>
+        <v>488594360.71251106</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>3197794944.0235329</v>
+        <v>3443066149.8040605</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.35261872105976916</v>
+        <v>0.37966461374802801</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>4521494354.749114</v>
+        <v>4304807542.9084511</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1349415092.2273529</v>
+        <v>1320830698.2874889</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>5870909446.9764662</v>
+        <v>5625638241.195941</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>345347614.52802742</v>
+        <v>351602390.07474631</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25559,10 +25559,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25570,8 +25570,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>196175586.27990001</v>
+        <v>156876401.39989999</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25597,7 +25597,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>36555945.079999998</v>
+        <v>43297197.280000001</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25621,7 +25621,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>93474955.230000004</v>
+        <v>103404684.89</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25645,7 +25645,7 @@
       </c>
       <c r="D75" s="192">
         <f>IF(E16="",0,E16)</f>
-        <v>14360089.9</v>
+        <v>17069909.699999999</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>569969388.88997996</v>
+        <v>624812631.81997001</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>105378830.049775</v>
+        <v>120445452.11972</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>263548744.42969999</v>
+        <v>271402077.39973497</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25717,7 +25717,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>58860530</v>
+        <v>66503547.659999996</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="D82" s="192">
         <f>IF(E27="",0,E27)</f>
-        <v>1902162.2150000001</v>
+        <v>5677297.4550000001</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>18572973.34</v>
+        <v>19675676.059999999</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25751,7 +25751,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1370396772.7343547</v>
+        <v>1440762443.1043248</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25765,13 +25765,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25813,19 +25813,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>83483688.659519002</v>
+        <v>91679166.169450998</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.29238093010494398</v>
+        <v>0.32108355903142527</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>202046864.34048098</v>
+        <v>193851386.830549</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>11885109.667087117</v>
+        <v>12115711.676909313</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25842,19 +25842,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>153267348.45391101</v>
+        <v>160538546.797405</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.35740695829335162</v>
+        <v>0.37436279989504362</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>275564113.54608899</v>
+        <v>268292915.202595</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16209653.738005236</v>
+        <v>16768307.200162187</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25871,19 +25871,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>373557754.84487098</v>
+        <v>393152452.68463802</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.33458255159730721</v>
+        <v>0.35213283375844201</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>742931294.15512896</v>
+        <v>723336596.31536198</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>43701840.832654648</v>
+        <v>45208537.269710124</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25956,29 +25956,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>610308791.95830107</v>
+        <v>645370165.65149403</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.33334704496657031</v>
+        <v>0.35249735947472677</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1220542272.0416989</v>
+        <v>1185480898.348506</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>71796604.237746999</v>
+        <v>74092556.146781623</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25986,6 +25981,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26587,11 +26587,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26715,10 +26715,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26747,40 +26747,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26788,13 +26788,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26813,7 +26813,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26823,7 +26823,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27616,10 +27616,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27627,8 +27627,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -27822,13 +27822,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28031,11 +28031,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28043,6 +28038,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -1928,15 +1928,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1956,6 +1947,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3600,10 +3600,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4664,13 +4664,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4873,6 +4873,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4880,11 +4885,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5657,10 +5657,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6721,13 +6721,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6930,6 +6930,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6937,11 +6942,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7714,10 +7714,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8778,13 +8778,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8987,6 +8987,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8994,11 +8999,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9771,10 +9771,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10835,13 +10835,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11044,6 +11044,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11051,11 +11056,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11827,10 +11827,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12877,13 +12877,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13086,6 +13086,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13093,11 +13098,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -22338,11 +22338,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="239" t="s">
+      <c r="B41" s="246" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="240"/>
-      <c r="D41" s="241"/>
+      <c r="C41" s="247"/>
+      <c r="D41" s="248"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22508,10 +22508,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22573,7 +22573,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -23572,13 +23572,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23781,6 +23781,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23788,11 +23793,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23977,7 +23977,7 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>122607705.239004</v>
+        <v>130839777.299004</v>
       </c>
       <c r="D10" s="205">
         <v>21722428.966798998</v>
@@ -23986,7 +23986,7 @@
         <v>66503547.659999996</v>
       </c>
       <c r="F10" s="205">
-        <v>210833681.865803</v>
+        <v>219065753.92580301</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
@@ -24005,7 +24005,7 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>151713072.94364899</v>
+        <v>152764829.66363701</v>
       </c>
       <c r="D11" s="205">
         <v>43101386.330268003</v>
@@ -24014,7 +24014,7 @@
         <v>1783783.8</v>
       </c>
       <c r="F11" s="205">
-        <v>196598243.073917</v>
+        <v>197649999.79390499</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -24049,7 +24049,7 @@
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>214201356.280561</v>
+        <v>222105140.284545</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
@@ -24077,7 +24077,7 @@
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>399622960.05156302</v>
+        <v>428096248.31151998</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
@@ -24095,17 +24095,17 @@
         <v>12320972.887556</v>
       </c>
       <c r="E14" s="205">
-        <v>103404684.89</v>
+        <v>106215495.69</v>
       </c>
       <c r="F14" s="205">
-        <v>548940944.56296396</v>
+        <v>551751755.36296403</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>196317107.082434</v>
+        <v>204127917.982434</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
@@ -24125,7 +24125,7 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>151713072.94364899</v>
+        <v>152764829.66363701</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
@@ -24137,7 +24137,7 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>214201356.280561</v>
+        <v>222105140.284545</v>
       </c>
       <c r="D16" s="205">
         <v>48462348.180826001</v>
@@ -24146,18 +24146,18 @@
         <v>17069909.699999999</v>
       </c>
       <c r="F16" s="205">
-        <v>279733614.16138703</v>
+        <v>287637398.165371</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>245320660.21154699</v>
+        <v>253752191.761547</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>23709940.735466</v>
+        <v>25221940.735466</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24181,7 +24181,7 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>122607705.239004</v>
+        <v>130839777.299004</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
@@ -24209,7 +24209,7 @@
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>354627359.49477702</v>
+        <v>379735850.517847</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
@@ -24221,7 +24221,7 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>399622960.05156302</v>
+        <v>428096248.31151998</v>
       </c>
       <c r="D19" s="205">
         <v>37956947.329939</v>
@@ -24230,7 +24230,7 @@
         <v>624812631.81997001</v>
       </c>
       <c r="F19" s="205">
-        <v>1062392539.201472</v>
+        <v>1090865827.4614291</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
@@ -24349,10 +24349,10 @@
         <v>32846204.848972</v>
       </c>
       <c r="E24" s="205">
-        <v>156876401.39989999</v>
+        <v>166606130.99990001</v>
       </c>
       <c r="F24" s="205">
-        <v>342917795.94998503</v>
+        <v>352647525.54998499</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24363,7 +24363,7 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>196317107.082434</v>
+        <v>204127917.982434</v>
       </c>
       <c r="D25" s="205">
         <v>31250892.939971998</v>
@@ -24372,7 +24372,7 @@
         <v>120445452.11972</v>
       </c>
       <c r="F25" s="205">
-        <v>348013452.14212602</v>
+        <v>355824263.042126</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24383,16 +24383,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>245320660.21154699</v>
+        <v>253752191.761547</v>
       </c>
       <c r="D26" s="205">
-        <v>23709940.735466</v>
+        <v>25221940.735466</v>
       </c>
       <c r="E26" s="205">
         <v>271402077.39973497</v>
       </c>
       <c r="F26" s="205">
-        <v>540432678.34674799</v>
+        <v>550376209.89674795</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24403,7 +24403,7 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>354627359.49477702</v>
+        <v>379735850.517847</v>
       </c>
       <c r="D27" s="205">
         <v>45812379.445509002</v>
@@ -24412,7 +24412,7 @@
         <v>5677297.4550000001</v>
       </c>
       <c r="F27" s="205">
-        <v>406117036.39528602</v>
+        <v>431225527.418356</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24466,7 +24466,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>160538546.797405</v>
+        <v>162873681.99740502</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24583,19 +24583,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>2954471789.0915494</v>
+        <v>3041483523.6085486</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.40699243739909435</v>
+        <v>0.41897871462270775</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>4304807542.9084511</v>
+        <v>4217795808.3914514</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>269050471.43177819</v>
+        <v>263612238.02446571</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24612,19 +24612,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>488594360.71251106</v>
+        <v>490106360.71251106</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.27002740913875617</v>
+        <v>0.27086303368837727</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1320830698.2874889</v>
+        <v>1319318698.2874889</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>82551918.642968059</v>
+        <v>82457418.642968059</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24641,19 +24641,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>645370165.65149403</v>
+        <v>647705300.85149407</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.35249735947472677</v>
+        <v>0.35377279648099985</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1185480898.348506</v>
+        <v>1183145763.1485059</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>74092556.146781623</v>
+        <v>73946610.19678162</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24668,19 +24668,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>4088436315.4555545</v>
+        <v>4179295185.172554</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.3751011986071458</v>
+        <v>0.38343721470359304</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>6811119139.544446</v>
+        <v>6720260269.827446</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>425694946.22152787</v>
+        <v>420016266.86421537</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24701,10 +24701,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25049,7 +25049,7 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>214201356.280561</v>
+        <v>222105140.284545</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
@@ -25057,15 +25057,15 @@
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>262663704.46138701</v>
+        <v>270567488.46537101</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.5029823101444626</v>
+        <v>0.51811749429698473</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>225861927.719439</v>
+        <v>217958143.715455</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
@@ -25073,11 +25073,11 @@
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>259548904.53861299</v>
+        <v>251645120.53462899</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>16221806.533663312</v>
+        <v>15727820.033414312</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25101,7 +25101,7 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>399622960.05156302</v>
+        <v>428096248.31151998</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
@@ -25109,15 +25109,15 @@
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>437579907.38150203</v>
+        <v>466053195.64145899</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.38991410055594333</v>
+        <v>0.41528577872139411</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>597135384.94843698</v>
+        <v>568662096.68848002</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
@@ -25125,11 +25125,11 @@
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>684667035.61849797</v>
+        <v>656193747.35854101</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>42791689.726156123</v>
+        <v>41012109.209908813</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25153,7 +25153,7 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>196317107.082434</v>
+        <v>204127917.982434</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
@@ -25161,15 +25161,15 @@
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>227568000.02240598</v>
+        <v>235378810.92240602</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.35689748086208223</v>
+        <v>0.369147264370421</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>343969951.917566</v>
+        <v>336159141.01756597</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
@@ -25177,11 +25177,11 @@
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>410060484.97759402</v>
+        <v>402249674.07759398</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>25628780.311099626</v>
+        <v>25140604.629849624</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>151713072.94364899</v>
+        <v>152764829.66363701</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
@@ -25265,15 +25265,15 @@
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>194814459.27391699</v>
+        <v>195866215.99390501</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.31882349859039655</v>
+        <v>0.32054475048505732</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>287304236.05635101</v>
+        <v>286252479.33636296</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
@@ -25281,11 +25281,11 @@
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>416227261.72608304</v>
+        <v>415175505.00609499</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>26014203.85788019</v>
+        <v>25948469.062880937</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25309,35 +25309,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>245320660.21154699</v>
+        <v>253752191.761547</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>23709940.735466</v>
+        <v>25221940.735466</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>269030600.94701296</v>
+        <v>278974132.49701297</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.35448614389059557</v>
+        <v>0.36758816330179339</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>421308935.78845298</v>
+        <v>412877404.23845303</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>68591681.264533997</v>
+        <v>67079681.264533997</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>489900617.05298704</v>
+        <v>479957085.50298703</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>30618788.56581169</v>
+        <v>29997317.843936689</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25361,7 +25361,7 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>122607705.239004</v>
+        <v>130839777.299004</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
@@ -25369,15 +25369,15 @@
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>144330134.20580301</v>
+        <v>152562206.26580301</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.27816392033253773</v>
+        <v>0.29402939048726223</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>298935317.76099598</v>
+        <v>290703245.70099598</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
@@ -25385,11 +25385,11 @@
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>374537064.79419696</v>
+        <v>366304992.73419702</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>23408566.54963731</v>
+        <v>22894062.045887314</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25413,7 +25413,7 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>354627359.49477702</v>
+        <v>379735850.517847</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
@@ -25421,15 +25421,15 @@
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>400439738.94028604</v>
+        <v>425548229.96335602</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.40789694847889646</v>
+        <v>0.43347302366145285</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>263723582.50522298</v>
+        <v>238615091.482153</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
@@ -25437,11 +25437,11 @@
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>581278169.05971396</v>
+        <v>556169678.03664398</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>36329885.566232122</v>
+        <v>34760604.877290249</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25515,35 +25515,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>2954471789.0915494</v>
+        <v>3041483523.6085486</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>488594360.71251106</v>
+        <v>490106360.71251106</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>3443066149.8040605</v>
+        <v>3531589884.3210592</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.37966461374802801</v>
+        <v>0.38942606706046057</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>4304807542.9084511</v>
+        <v>4217795808.3914518</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1320830698.2874889</v>
+        <v>1319318698.2874889</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>5625638241.195941</v>
+        <v>5537114506.6789408</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>351602390.07474631</v>
+        <v>346069656.6674338</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>156876401.39989999</v>
+        <v>166606130.99990001</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25621,7 +25621,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>103404684.89</v>
+        <v>106215495.69</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25751,7 +25751,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1440762443.1043248</v>
+        <v>1453302983.5043249</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25765,13 +25765,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25842,19 +25842,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>160538546.797405</v>
+        <v>162873681.99740502</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.37436279989504362</v>
+        <v>0.37980814476108804</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>268292915.202595</v>
+        <v>265957780.00259498</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16768307.200162187</v>
+        <v>16622361.250162186</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25956,24 +25956,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>645370165.65149403</v>
+        <v>647705300.85149407</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.35249735947472677</v>
+        <v>0.35377279648099985</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1185480898.348506</v>
+        <v>1183145763.1485059</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>74092556.146781623</v>
+        <v>73946610.19678162</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25981,11 +25986,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26758,10 +26758,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27822,13 +27822,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28031,6 +28031,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28038,11 +28043,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 12 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 13 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1928,6 +1928,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1947,15 +1956,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3600,10 +3600,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4664,13 +4664,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4873,11 +4873,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4885,6 +4880,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5657,10 +5657,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6721,13 +6721,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6930,11 +6930,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6942,6 +6937,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7714,10 +7714,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8778,13 +8778,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8987,11 +8987,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8999,6 +8994,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9771,10 +9771,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10835,13 +10835,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11044,11 +11044,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11056,6 +11051,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11827,10 +11827,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12877,13 +12877,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13086,11 +13086,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13098,6 +13093,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22338,11 +22338,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="246" t="s">
+      <c r="B41" s="239" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="247"/>
-      <c r="D41" s="248"/>
+      <c r="C41" s="240"/>
+      <c r="D41" s="241"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>39549630.013225436</v>
+        <v>42186272.01410713</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22431,7 +22431,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>34724208.107293174</v>
+        <v>37039155.314446054</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22460,7 +22460,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>6860782.1712320447</v>
+        <v>7318167.6493141809</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22487,7 +22487,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>81134620.291750655</v>
+        <v>86543594.977867365</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22508,10 +22508,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22573,7 +22573,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>9496507.7079102062</v>
+        <v>10129608.221770886</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>8496852.1867043748</v>
+        <v>9063308.9991513323</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>2744088.8874999993</v>
+        <v>2927028.146666666</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22780,7 +22780,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-2521794.2178766951</v>
+        <v>-2689913.8324018079</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>8174648.6007203832</v>
+        <v>8719625.174101742</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>5042969.0284339786</v>
+        <v>5379166.9636629103</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-1569820.9792962223</v>
+        <v>-1674475.7112493038</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22988,7 +22988,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>6925901.7647056282</v>
+        <v>7387628.5490193367</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>6475758.7606265619</v>
+        <v>6907476.0113349995</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>4725746.7285800241</v>
+        <v>5040796.5104853595</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23144,7 +23144,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>11077259.83786739</v>
+        <v>11815743.82705855</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>7398395.5101358034</v>
+        <v>7891621.8774781907</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>2162855.1851872131</v>
+        <v>2307045.5308663608</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>5644469.1193200238</v>
+        <v>6020767.0606080256</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>74273838.120518669</v>
+        <v>79225427.328553244</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23572,13 +23572,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-835186.11976702884</v>
+        <v>-890865.19441816409</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-1158092.6711176522</v>
+        <v>-1235298.8491921623</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23690,7 +23690,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>8854060.9621167332</v>
+        <v>9444331.6929245163</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23775,17 +23775,12 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>6860782.1712320521</v>
+        <v>7318167.6493141893</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23793,6 +23788,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23861,7 +23861,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23943,11 +23943,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>153195189.70111299</v>
+        <v>182652151.89806399</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>32846204.848972</v>
+        <v>34358204.848972</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23965,11 +23965,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>250627839.900662</v>
+        <v>264848838.000655</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>71329116.45788601</v>
+        <v>77604053.417861998</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23977,27 +23977,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>130839777.299004</v>
+        <v>151710781.81419799</v>
       </c>
       <c r="D10" s="205">
-        <v>21722428.966798998</v>
+        <v>23935450.952498998</v>
       </c>
       <c r="E10" s="205">
-        <v>66503547.659999996</v>
+        <v>77206250.260000005</v>
       </c>
       <c r="F10" s="205">
-        <v>219065753.92580301</v>
+        <v>252852483.02669701</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>433215286.78540802</v>
+        <v>481942612.94040698</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>12320972.887556</v>
+        <v>15260820.285153</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24005,23 +24005,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>152764829.66363701</v>
+        <v>187934863.95361799</v>
       </c>
       <c r="D11" s="205">
-        <v>43101386.330268003</v>
+        <v>48022944.660267003</v>
       </c>
       <c r="E11" s="205">
         <v>1783783.8</v>
       </c>
       <c r="F11" s="205">
-        <v>197649999.79390499</v>
+        <v>237741592.413885</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>130317566.0399</v>
+        <v>149416665.23982</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24033,27 +24033,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>125164944.162646</v>
+        <v>128751027.032639</v>
       </c>
       <c r="D12" s="205">
-        <v>42800238.698071003</v>
+        <v>49075175.658046998</v>
       </c>
       <c r="E12" s="205">
-        <v>29383539.879999999</v>
+        <v>29707864.199999999</v>
       </c>
       <c r="F12" s="205">
-        <v>197348722.74071699</v>
+        <v>207534066.89068601</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>222105140.284545</v>
+        <v>246394866.224498</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>48462348.180826001</v>
+        <v>52194708.560814001</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24061,7 +24061,7 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>125462895.73801599</v>
+        <v>136097810.968016</v>
       </c>
       <c r="D13" s="205">
         <v>28528877.759815</v>
@@ -24070,18 +24070,18 @@
         <v>13913657.4</v>
       </c>
       <c r="F13" s="205">
-        <v>167905430.89783099</v>
+        <v>178540346.12783101</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>428096248.31151998</v>
+        <v>446511323.25056702</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>37956947.329939</v>
+        <v>38460947.329939</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24089,27 +24089,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>433215286.78540802</v>
+        <v>481942612.94040698</v>
       </c>
       <c r="D14" s="205">
-        <v>12320972.887556</v>
+        <v>15260820.285153</v>
       </c>
       <c r="E14" s="205">
-        <v>106215495.69</v>
+        <v>128026306.64</v>
       </c>
       <c r="F14" s="205">
-        <v>551751755.36296403</v>
+        <v>625229739.86556005</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>204127917.982434</v>
+        <v>235880756.900805</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>31250892.939971998</v>
+        <v>31460892.939971998</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24125,11 +24125,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>152764829.66363701</v>
+        <v>187934863.95361799</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>43101386.330268003</v>
+        <v>48022944.660267003</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24137,27 +24137,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>222105140.284545</v>
+        <v>246394866.224498</v>
       </c>
       <c r="D16" s="205">
-        <v>48462348.180826001</v>
+        <v>52194708.560814001</v>
       </c>
       <c r="E16" s="205">
         <v>17069909.699999999</v>
       </c>
       <c r="F16" s="205">
-        <v>287637398.165371</v>
+        <v>315659484.48531199</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>253752191.761547</v>
+        <v>278243843.15952998</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>25221940.735466</v>
+        <v>26733940.735466</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24165,7 +24165,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>130317566.0399</v>
+        <v>149416665.23982</v>
       </c>
       <c r="D17" s="205">
         <v>46234425.210000001</v>
@@ -24174,18 +24174,18 @@
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>176551991.24990001</v>
+        <v>195651090.44982001</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>130839777.299004</v>
+        <v>151710781.81419799</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>21722428.966798998</v>
+        <v>23935450.952498998</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24193,27 +24193,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>225060686.539051</v>
+        <v>234109007.198033</v>
       </c>
       <c r="D18" s="205">
-        <v>1380603.6099970001</v>
+        <v>1777900.9299969999</v>
       </c>
       <c r="E18" s="205">
-        <v>5040540.4800000004</v>
+        <v>5689189.1200000001</v>
       </c>
       <c r="F18" s="205">
-        <v>231481830.62904799</v>
+        <v>241576097.24803001</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>379735850.517847</v>
+        <v>384460553.55784702</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>45812379.445509002</v>
+        <v>50952055.171508998</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24221,27 +24221,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>428096248.31151998</v>
+        <v>446511323.25056702</v>
       </c>
       <c r="D19" s="205">
-        <v>37956947.329939</v>
+        <v>38460947.329939</v>
       </c>
       <c r="E19" s="205">
-        <v>624812631.81997001</v>
+        <v>698069386.81997001</v>
       </c>
       <c r="F19" s="205">
-        <v>1090865827.4614291</v>
+        <v>1183041657.400476</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>81600040.120931</v>
+        <v>90238958.720900998</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>73847317.379317999</v>
+        <v>89768479.319114</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24249,16 +24249,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>54959402.120931</v>
+        <v>63598320.720900998</v>
       </c>
       <c r="D20" s="205">
-        <v>16073745.839803999</v>
+        <v>19557070.13978</v>
       </c>
       <c r="E20" s="205">
         <v>3048648.72</v>
       </c>
       <c r="F20" s="205">
-        <v>74081796.680735007</v>
+        <v>86204039.580680996</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24279,20 +24279,20 @@
         <v>26640638</v>
       </c>
       <c r="D21" s="205">
-        <v>57773571.539513998</v>
+        <v>70211409.179334</v>
       </c>
       <c r="E21" s="205">
         <v>16627027.34</v>
       </c>
       <c r="F21" s="205">
-        <v>101041236.87951399</v>
+        <v>113479074.519334</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>393152452.68463802</v>
+        <v>419040028.12441802</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24303,7 +24303,7 @@
         <v>172</v>
       </c>
       <c r="C22" s="205">
-        <v>67149256.400000006</v>
+        <v>92198236.400000006</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>168</v>
@@ -24312,7 +24312,7 @@
         <v>4684684.5599999996</v>
       </c>
       <c r="F22" s="205">
-        <v>71833940.959999993</v>
+        <v>96882920.959999993</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24323,7 +24323,7 @@
         <v>173</v>
       </c>
       <c r="C23" s="205">
-        <v>153956388.84</v>
+        <v>190630278.84</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>168</v>
@@ -24332,7 +24332,7 @@
         <v>5129098.96</v>
       </c>
       <c r="F23" s="205">
-        <v>159085487.80000001</v>
+        <v>195759377.80000001</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24343,16 +24343,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>153195189.70111299</v>
+        <v>182652151.89806399</v>
       </c>
       <c r="D24" s="205">
-        <v>32846204.848972</v>
+        <v>34358204.848972</v>
       </c>
       <c r="E24" s="205">
-        <v>166606130.99990001</v>
+        <v>167092617.4799</v>
       </c>
       <c r="F24" s="205">
-        <v>352647525.54998499</v>
+        <v>384102974.22693598</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24363,16 +24363,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>204127917.982434</v>
+        <v>235880756.900805</v>
       </c>
       <c r="D25" s="205">
-        <v>31250892.939971998</v>
+        <v>31460892.939971998</v>
       </c>
       <c r="E25" s="205">
-        <v>120445452.11972</v>
+        <v>130529236.16968501</v>
       </c>
       <c r="F25" s="205">
-        <v>355824263.042126</v>
+        <v>397870886.01046199</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24383,16 +24383,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>253752191.761547</v>
+        <v>278243843.15952998</v>
       </c>
       <c r="D26" s="205">
-        <v>25221940.735466</v>
+        <v>26733940.735466</v>
       </c>
       <c r="E26" s="205">
-        <v>271402077.39973497</v>
+        <v>314650726.179685</v>
       </c>
       <c r="F26" s="205">
-        <v>550376209.89674795</v>
+        <v>619628510.07468104</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24403,16 +24403,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>379735850.517847</v>
+        <v>384460553.55784702</v>
       </c>
       <c r="D27" s="205">
-        <v>45812379.445509002</v>
+        <v>50952055.171508998</v>
       </c>
       <c r="E27" s="205">
         <v>5677297.4550000001</v>
       </c>
       <c r="F27" s="205">
-        <v>431225527.418356</v>
+        <v>441089906.18435597</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24455,7 +24455,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>91679166.169450998</v>
+        <v>92875238.249441996</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24466,7 +24466,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>162873681.99740502</v>
+        <v>167127682.15738502</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24477,7 +24477,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>79474968.432062</v>
+        <v>85859981.992045999</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24488,7 +24488,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>313266484.25257599</v>
+        <v>332769046.13237202</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24540,7 +24540,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.4</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24583,19 +24583,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>3041483523.6085486</v>
+        <v>3383064730.9009104</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.41897871462270775</v>
+        <v>0.46603313857724826</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>4217795808.3914514</v>
+        <v>3876214601.0990896</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>263612238.02446571</v>
+        <v>258414306.7399393</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24612,19 +24612,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>490106360.71251106</v>
+        <v>534986923.43156695</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.27086303368837727</v>
+        <v>0.2956668035355019</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1319318698.2874889</v>
+        <v>1274438135.568433</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>82457418.642968059</v>
+        <v>84962542.371228874</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24641,19 +24641,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>647705300.85149407</v>
+        <v>679042948.53124499</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.35377279648099985</v>
+        <v>0.37088923391053341</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1183145763.1485059</v>
+        <v>1151808115.468755</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>73946610.19678162</v>
+        <v>76787207.697916999</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24668,19 +24668,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>4179295185.172554</v>
+        <v>4597094602.8637228</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.38343721470359304</v>
+        <v>0.42176899983153698</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>6720260269.827446</v>
+        <v>6302460852.1362772</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>420016266.86421537</v>
+        <v>420164056.80908513</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24701,10 +24701,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24789,35 +24789,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>153195189.70111299</v>
+        <v>182652151.89806399</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>32846204.848972</v>
+        <v>34358204.848972</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>186041394.55008498</v>
+        <v>217010356.74703598</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.33610970603263129</v>
+        <v>0.39205945208417808</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>298488288.29888701</v>
+        <v>269031326.10193598</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>68984218.151028007</v>
+        <v>67472218.151028007</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>367472506.44991505</v>
+        <v>336503544.25296402</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>22967031.653119691</v>
+        <v>22433569.616864268</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24841,35 +24841,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>250627839.900662</v>
+        <v>264848838.000655</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>71329116.45788601</v>
+        <v>77604053.417861998</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>321956956.35854805</v>
+        <v>342452891.41851699</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.39489909278968394</v>
+        <v>0.42003855942088264</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>339554531.099338</v>
+        <v>325333532.999345</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>153777689.54211399</v>
+        <v>147502752.582138</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>493332220.64145195</v>
+        <v>472836285.58148301</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>30833263.790090747</v>
+        <v>31522419.038765535</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>67149256.400000006</v>
+        <v>92198236.400000006</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -24901,15 +24901,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>67149256.400000006</v>
+        <v>92198236.400000006</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.27808153240382699</v>
+        <v>0.38181549934545966</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>174324011.59999999</v>
+        <v>149275031.59999999</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -24917,11 +24917,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>174324011.59999999</v>
+        <v>149275031.59999999</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>10895250.725</v>
+        <v>9951668.7733333334</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24945,35 +24945,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>433215286.78540802</v>
+        <v>481942612.94040698</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>12320972.887556</v>
+        <v>15260820.285153</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>445536259.67296404</v>
+        <v>497203433.22555995</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.61355588943265393</v>
+        <v>0.68470767098866803</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>212497185.21459198</v>
+        <v>163769859.05959302</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>68120875.112443998</v>
+        <v>65181027.714846998</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>280618060.32703596</v>
+        <v>228950886.77444005</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>17538628.770439748</v>
+        <v>15263392.451629337</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>130317566.0399</v>
+        <v>149416665.23982</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25005,15 +25005,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>176551991.24990001</v>
+        <v>195651090.44982001</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.29952585439316498</v>
+        <v>0.33192806048269324</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>378601265.9601</v>
+        <v>359502166.76018</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25021,11 +25021,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>412886244.75010002</v>
+        <v>393787145.55017996</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>25805390.296881251</v>
+        <v>26252476.370011996</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25049,35 +25049,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>222105140.284545</v>
+        <v>246394866.224498</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>48462348.180826001</v>
+        <v>52194708.560814001</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>270567488.46537101</v>
+        <v>298589574.785312</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.51811749429698473</v>
+        <v>0.57177779632148251</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>217958143.715455</v>
+        <v>193668417.775502</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>33686976.819173999</v>
+        <v>29954616.439185999</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>251645120.53462899</v>
+        <v>223623034.214688</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>15727820.033414312</v>
+        <v>14908202.280979199</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25101,35 +25101,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>428096248.31151998</v>
+        <v>446511323.25056702</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>37956947.329939</v>
+        <v>38460947.329939</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>466053195.64145899</v>
+        <v>484972270.58050603</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.41528577872139411</v>
+        <v>0.43214398899058176</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>568662096.68848002</v>
+        <v>550247021.74943304</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>87531650.670060992</v>
+        <v>87027650.670060992</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>656193747.35854101</v>
+        <v>637274672.41949391</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>41012109.209908813</v>
+        <v>42484978.161299594</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25153,35 +25153,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>204127917.982434</v>
+        <v>235880756.900805</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>31250892.939971998</v>
+        <v>31460892.939971998</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>235378810.92240602</v>
+        <v>267341649.84077698</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.369147264370421</v>
+        <v>0.41927494792014658</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>336159141.01756597</v>
+        <v>304406302.099195</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>66090533.060028002</v>
+        <v>65880533.060028002</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>402249674.07759398</v>
+        <v>370286835.15922302</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>25140604.629849624</v>
+        <v>24685789.010614868</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>153956388.84</v>
+        <v>190630278.84</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25213,15 +25213,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>153956388.84</v>
+        <v>190630278.84</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.38095413115597321</v>
+        <v>0.47170106284439595</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>250177275.16</v>
+        <v>213503385.16</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25229,11 +25229,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>250177275.16</v>
+        <v>213503385.16</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>15636079.6975</v>
+        <v>14233559.010666667</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25257,35 +25257,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>152764829.66363701</v>
+        <v>187934863.95361799</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>43101386.330268003</v>
+        <v>48022944.660267003</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>195866215.99390501</v>
+        <v>235957808.61388499</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.32054475048505732</v>
+        <v>0.38615662483361751</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>286252479.33636296</v>
+        <v>251082445.04638201</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>128923025.669732</v>
+        <v>124001467.339733</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>415175505.00609499</v>
+        <v>375083912.38611501</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>25948469.062880937</v>
+        <v>25005594.159074333</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25309,35 +25309,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>253752191.761547</v>
+        <v>278243843.15952998</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>25221940.735466</v>
+        <v>26733940.735466</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>278974132.49701297</v>
+        <v>304977783.89499599</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.36758816330179339</v>
+        <v>0.40185167859967513</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>412877404.23845303</v>
+        <v>388385752.84047002</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>67079681.264533997</v>
+        <v>65567681.264533997</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>479957085.50298703</v>
+        <v>453953434.10500401</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>29997317.843936689</v>
+        <v>30263562.273666933</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25361,35 +25361,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>130839777.299004</v>
+        <v>151710781.81419799</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>21722428.966798998</v>
+        <v>23935450.952498998</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>152562206.26580301</v>
+        <v>175646232.76669699</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.29402939048726223</v>
+        <v>0.33851866740702757</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>290703245.70099598</v>
+        <v>269832241.18580198</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>75601747.033201009</v>
+        <v>73388725.047500998</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>366304992.73419702</v>
+        <v>343220966.23330301</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>22894062.045887314</v>
+        <v>22881397.748886868</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25413,35 +25413,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>379735850.517847</v>
+        <v>384460553.55784702</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>45812379.445509002</v>
+        <v>50952055.171508998</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>425548229.96335602</v>
+        <v>435412608.72935605</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.43347302366145285</v>
+        <v>0.44352110232602182</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>238615091.482153</v>
+        <v>233890388.44215298</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>317554586.55449098</v>
+        <v>312414910.82849097</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>556169678.03664398</v>
+        <v>546305299.27064395</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>34760604.877290249</v>
+        <v>36420353.284709595</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25465,35 +25465,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>81600040.120931</v>
+        <v>90238958.720900998</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>73847317.379317999</v>
+        <v>89768479.319114</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>155447357.500249</v>
+        <v>180007438.04001498</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.26524329745454317</v>
+        <v>0.30715071133969879</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>212925648.879069</v>
+        <v>204286730.27909899</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>217682735.620682</v>
+        <v>201761573.680886</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>430608384.49975097</v>
+        <v>406048303.95998502</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>26913024.031234436</v>
+        <v>27069886.930665668</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25515,35 +25515,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>3041483523.6085486</v>
+        <v>3383064730.9009104</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>490106360.71251106</v>
+        <v>534986923.43156695</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>3531589884.3210592</v>
+        <v>3918051654.3324776</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.38942606706046057</v>
+        <v>0.4320409493357007</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>4217795808.3914518</v>
+        <v>3876214601.0990896</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1319318698.2874889</v>
+        <v>1274438135.5684328</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>5537114506.6789408</v>
+        <v>5150652736.6675224</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>346069656.6674338</v>
+        <v>343376849.11116815</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>166606130.99990001</v>
+        <v>167092617.4799</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25597,7 +25597,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>43297197.280000001</v>
+        <v>43621521.600000001</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25621,7 +25621,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>106215495.69</v>
+        <v>128026306.64</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>624812631.81997001</v>
+        <v>698069386.81997001</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>120445452.11972</v>
+        <v>130529236.16968501</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>271402077.39973497</v>
+        <v>314650726.179685</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25717,7 +25717,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>66503547.659999996</v>
+        <v>77206250.260000005</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25751,7 +25751,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1453302983.5043249</v>
+        <v>1613216495.6842396</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25765,13 +25765,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25813,19 +25813,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>91679166.169450998</v>
+        <v>92875238.249441996</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.32108355903142527</v>
+        <v>0.32527250507388605</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>193851386.830549</v>
+        <v>192655314.75055802</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>12115711.676909313</v>
+        <v>12843687.650037201</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25842,19 +25842,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>162873681.99740502</v>
+        <v>167127682.15738502</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.37980814476108804</v>
+        <v>0.38972812623851982</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>265957780.00259498</v>
+        <v>261703779.84261498</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16622361.250162186</v>
+        <v>17446918.656174332</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25871,19 +25871,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>393152452.68463802</v>
+        <v>419040028.12441802</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.35213283375844201</v>
+        <v>0.37531942521042855</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>723336596.31536198</v>
+        <v>697449020.87558198</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>45208537.269710124</v>
+        <v>46496601.391705468</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25956,29 +25956,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>647705300.85149407</v>
+        <v>679042948.53124499</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.35377279648099985</v>
+        <v>0.37088923391053341</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1183145763.1485059</v>
+        <v>1151808115.468755</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>73946610.19678162</v>
+        <v>76787207.697916999</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25986,6 +25981,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26758,10 +26758,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27822,13 +27822,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28031,11 +28031,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28043,6 +28038,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/randy/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF84DF2E-261F-0343-B7D9-56E9F9D1B169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B69C843-D7BA-5B40-815C-4B05E0CAD9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="600" windowWidth="21780" windowHeight="16380" tabRatio="500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="600" windowWidth="18360" windowHeight="16340" tabRatio="500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -603,7 +603,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 13 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 17 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1829,30 +1829,6 @@
     <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1884,6 +1860,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3426,11 +3426,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="205" t="s">
+      <c r="B41" s="216" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="206"/>
-      <c r="D41" s="207"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3554,10 +3554,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="211" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="212"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3586,40 +3586,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="208" t="s">
+      <c r="B48" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="209"/>
-      <c r="D48" s="209"/>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="210"/>
-      <c r="K48" s="217"/>
-      <c r="L48" s="218"/>
-      <c r="M48" s="218"/>
-      <c r="N48" s="219"/>
+      <c r="C48" s="220"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="220"/>
+      <c r="F48" s="220"/>
+      <c r="G48" s="220"/>
+      <c r="H48" s="220"/>
+      <c r="I48" s="220"/>
+      <c r="J48" s="221"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="210"/>
+      <c r="M48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="213" t="s">
+      <c r="B49" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="213" t="s">
+      <c r="C49" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="213"/>
+      <c r="F49" s="214"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="213" t="s">
+      <c r="J49" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3627,13 +3627,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="223" t="s">
+      <c r="N49" s="215" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="213"/>
-      <c r="C50" s="213"/>
+      <c r="B50" s="205"/>
+      <c r="C50" s="205"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3652,7 +3652,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="213"/>
+      <c r="J50" s="205"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3662,7 +3662,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="223"/>
+      <c r="N50" s="215"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -4455,10 +4455,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="213" t="s">
+      <c r="B68" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="213" t="s">
+      <c r="C68" s="205" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4466,8 +4466,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="213"/>
-      <c r="C69" s="213"/>
+      <c r="B69" s="205"/>
+      <c r="C69" s="205"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -4661,13 +4661,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="214" t="s">
+      <c r="B87" s="206" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="215"/>
-      <c r="D87" s="215"/>
-      <c r="E87" s="215"/>
-      <c r="F87" s="216"/>
+      <c r="C87" s="207"/>
+      <c r="D87" s="207"/>
+      <c r="E87" s="207"/>
+      <c r="F87" s="208"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4870,6 +4870,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4877,11 +4882,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5483,11 +5483,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="205" t="s">
+      <c r="B41" s="216" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="206"/>
-      <c r="D41" s="207"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5611,10 +5611,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="211" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="212"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5643,40 +5643,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="208" t="s">
+      <c r="B48" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="209"/>
-      <c r="D48" s="209"/>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="210"/>
-      <c r="K48" s="217"/>
-      <c r="L48" s="218"/>
-      <c r="M48" s="218"/>
-      <c r="N48" s="219"/>
+      <c r="C48" s="220"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="220"/>
+      <c r="F48" s="220"/>
+      <c r="G48" s="220"/>
+      <c r="H48" s="220"/>
+      <c r="I48" s="220"/>
+      <c r="J48" s="221"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="210"/>
+      <c r="M48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="213" t="s">
+      <c r="B49" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="213" t="s">
+      <c r="C49" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="213"/>
+      <c r="F49" s="214"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="213" t="s">
+      <c r="J49" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5684,13 +5684,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="223" t="s">
+      <c r="N49" s="215" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="213"/>
-      <c r="C50" s="213"/>
+      <c r="B50" s="205"/>
+      <c r="C50" s="205"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5709,7 +5709,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="213"/>
+      <c r="J50" s="205"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5719,7 +5719,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="223"/>
+      <c r="N50" s="215"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -6512,10 +6512,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="213" t="s">
+      <c r="B68" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="213" t="s">
+      <c r="C68" s="205" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6523,8 +6523,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="213"/>
-      <c r="C69" s="213"/>
+      <c r="B69" s="205"/>
+      <c r="C69" s="205"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -6718,13 +6718,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="214" t="s">
+      <c r="B87" s="206" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="215"/>
-      <c r="D87" s="215"/>
-      <c r="E87" s="215"/>
-      <c r="F87" s="216"/>
+      <c r="C87" s="207"/>
+      <c r="D87" s="207"/>
+      <c r="E87" s="207"/>
+      <c r="F87" s="208"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6927,6 +6927,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6934,11 +6939,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7540,11 +7540,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="205" t="s">
+      <c r="B41" s="216" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="206"/>
-      <c r="D41" s="207"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7668,10 +7668,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="211" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="212"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7700,40 +7700,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="208" t="s">
+      <c r="B48" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="209"/>
-      <c r="D48" s="209"/>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="210"/>
-      <c r="K48" s="217"/>
-      <c r="L48" s="218"/>
-      <c r="M48" s="218"/>
-      <c r="N48" s="219"/>
+      <c r="C48" s="220"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="220"/>
+      <c r="F48" s="220"/>
+      <c r="G48" s="220"/>
+      <c r="H48" s="220"/>
+      <c r="I48" s="220"/>
+      <c r="J48" s="221"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="210"/>
+      <c r="M48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="213" t="s">
+      <c r="B49" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="213" t="s">
+      <c r="C49" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="213"/>
+      <c r="F49" s="214"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="213" t="s">
+      <c r="J49" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7741,13 +7741,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="223" t="s">
+      <c r="N49" s="215" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="213"/>
-      <c r="C50" s="213"/>
+      <c r="B50" s="205"/>
+      <c r="C50" s="205"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7766,7 +7766,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="213"/>
+      <c r="J50" s="205"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7776,7 +7776,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="223"/>
+      <c r="N50" s="215"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -8569,10 +8569,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="213" t="s">
+      <c r="B68" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="213" t="s">
+      <c r="C68" s="205" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8580,8 +8580,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="213"/>
-      <c r="C69" s="213"/>
+      <c r="B69" s="205"/>
+      <c r="C69" s="205"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -8775,13 +8775,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="214" t="s">
+      <c r="B87" s="206" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="215"/>
-      <c r="D87" s="215"/>
-      <c r="E87" s="215"/>
-      <c r="F87" s="216"/>
+      <c r="C87" s="207"/>
+      <c r="D87" s="207"/>
+      <c r="E87" s="207"/>
+      <c r="F87" s="208"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8984,6 +8984,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8991,11 +8996,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9597,11 +9597,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="205" t="s">
+      <c r="B41" s="216" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="206"/>
-      <c r="D41" s="207"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9725,10 +9725,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="211" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="212"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9757,40 +9757,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="208" t="s">
+      <c r="B48" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="209"/>
-      <c r="D48" s="209"/>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="210"/>
-      <c r="K48" s="217"/>
-      <c r="L48" s="218"/>
-      <c r="M48" s="218"/>
-      <c r="N48" s="219"/>
+      <c r="C48" s="220"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="220"/>
+      <c r="F48" s="220"/>
+      <c r="G48" s="220"/>
+      <c r="H48" s="220"/>
+      <c r="I48" s="220"/>
+      <c r="J48" s="221"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="210"/>
+      <c r="M48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="213" t="s">
+      <c r="B49" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="213" t="s">
+      <c r="C49" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="213"/>
+      <c r="F49" s="214"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="213" t="s">
+      <c r="J49" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9798,13 +9798,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="223" t="s">
+      <c r="N49" s="215" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="213"/>
-      <c r="C50" s="213"/>
+      <c r="B50" s="205"/>
+      <c r="C50" s="205"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9823,7 +9823,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="213"/>
+      <c r="J50" s="205"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9833,7 +9833,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="223"/>
+      <c r="N50" s="215"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -10626,10 +10626,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="213" t="s">
+      <c r="B68" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="213" t="s">
+      <c r="C68" s="205" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10637,8 +10637,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="213"/>
-      <c r="C69" s="213"/>
+      <c r="B69" s="205"/>
+      <c r="C69" s="205"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -10832,13 +10832,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="214" t="s">
+      <c r="B87" s="206" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="215"/>
-      <c r="D87" s="215"/>
-      <c r="E87" s="215"/>
-      <c r="F87" s="216"/>
+      <c r="C87" s="207"/>
+      <c r="D87" s="207"/>
+      <c r="E87" s="207"/>
+      <c r="F87" s="208"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11041,6 +11041,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11048,11 +11053,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11654,11 +11654,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="205" t="s">
+      <c r="B41" s="216" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="206"/>
-      <c r="D41" s="207"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11781,10 +11781,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="211" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="212"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11813,40 +11813,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="208" t="s">
+      <c r="B48" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="209"/>
-      <c r="D48" s="209"/>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="210"/>
-      <c r="K48" s="217"/>
-      <c r="L48" s="218"/>
-      <c r="M48" s="218"/>
-      <c r="N48" s="219"/>
+      <c r="C48" s="220"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="220"/>
+      <c r="F48" s="220"/>
+      <c r="G48" s="220"/>
+      <c r="H48" s="220"/>
+      <c r="I48" s="220"/>
+      <c r="J48" s="221"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="210"/>
+      <c r="M48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="213" t="s">
+      <c r="B49" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="213" t="s">
+      <c r="C49" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="213"/>
+      <c r="F49" s="214"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="213" t="s">
+      <c r="J49" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11854,13 +11854,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="223" t="s">
+      <c r="N49" s="215" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="213"/>
-      <c r="C50" s="213"/>
+      <c r="B50" s="205"/>
+      <c r="C50" s="205"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11879,7 +11879,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="213"/>
+      <c r="J50" s="205"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11889,7 +11889,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="223"/>
+      <c r="N50" s="215"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -12668,10 +12668,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="213" t="s">
+      <c r="B68" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="213" t="s">
+      <c r="C68" s="205" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12679,8 +12679,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="213"/>
-      <c r="C69" s="213"/>
+      <c r="B69" s="205"/>
+      <c r="C69" s="205"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -12874,13 +12874,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="214" t="s">
+      <c r="B87" s="206" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="215"/>
-      <c r="D87" s="215"/>
-      <c r="E87" s="215"/>
-      <c r="F87" s="216"/>
+      <c r="C87" s="207"/>
+      <c r="D87" s="207"/>
+      <c r="E87" s="207"/>
+      <c r="F87" s="208"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13083,6 +13083,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13090,11 +13095,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -18409,10 +18409,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B44" s="211" t="s">
+      <c r="B44" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="212"/>
+      <c r="C44" s="223"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18477,23 +18477,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="213" t="s">
+      <c r="C47" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="220" t="s">
+      <c r="D47" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="221"/>
-      <c r="F47" s="222"/>
+      <c r="E47" s="213"/>
+      <c r="F47" s="214"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="213" t="s">
+      <c r="J47" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18506,8 +18506,8 @@
       </c>
     </row>
     <row r="48" spans="2:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
+      <c r="B48" s="205"/>
+      <c r="C48" s="205"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18526,7 +18526,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="213"/>
+      <c r="J48" s="205"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -20158,11 +20158,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="205" t="s">
+      <c r="B41" s="216" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="206"/>
-      <c r="D41" s="207"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20280,10 +20280,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="211" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="212"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20306,17 +20306,17 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="208" t="s">
+      <c r="B48" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="209"/>
-      <c r="D48" s="209"/>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="210"/>
+      <c r="C48" s="220"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="220"/>
+      <c r="F48" s="220"/>
+      <c r="G48" s="220"/>
+      <c r="H48" s="220"/>
+      <c r="I48" s="220"/>
+      <c r="J48" s="221"/>
       <c r="K48" s="241"/>
       <c r="L48" s="242"/>
       <c r="M48" s="242"/>
@@ -21173,10 +21173,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="213" t="s">
+      <c r="B68" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="213" t="s">
+      <c r="C68" s="205" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21187,8 +21187,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="213"/>
-      <c r="C69" s="213"/>
+      <c r="B69" s="205"/>
+      <c r="C69" s="205"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -21374,13 +21374,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="208" t="s">
+      <c r="B87" s="219" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="209"/>
-      <c r="D87" s="209"/>
-      <c r="E87" s="209"/>
-      <c r="F87" s="210"/>
+      <c r="C87" s="220"/>
+      <c r="D87" s="220"/>
+      <c r="E87" s="220"/>
+      <c r="F87" s="221"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22399,7 +22399,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>45199577.157971926</v>
+        <v>52732840.017633915</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22428,7 +22428,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>39684809.265477911</v>
+        <v>46298944.143057562</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22457,15 +22457,15 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>7840893.9099794794</v>
+        <v>9147709.5616427269</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="211" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="212"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>92725280.333429322</v>
+        <v>108179493.72233421</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22494,40 +22494,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="208" t="s">
+      <c r="B48" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="209"/>
-      <c r="D48" s="209"/>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="210"/>
-      <c r="K48" s="217"/>
-      <c r="L48" s="218"/>
-      <c r="M48" s="218"/>
-      <c r="N48" s="219"/>
+      <c r="C48" s="220"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="220"/>
+      <c r="F48" s="220"/>
+      <c r="G48" s="220"/>
+      <c r="H48" s="220"/>
+      <c r="I48" s="220"/>
+      <c r="J48" s="221"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="210"/>
+      <c r="M48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="213" t="s">
+      <c r="B49" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="213" t="s">
+      <c r="C49" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="213"/>
+      <c r="F49" s="214"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="213" t="s">
+      <c r="J49" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22535,13 +22535,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="223" t="s">
+      <c r="N49" s="215" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="213"/>
-      <c r="C50" s="213"/>
+      <c r="B50" s="205"/>
+      <c r="C50" s="205"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22560,7 +22560,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="213"/>
+      <c r="J50" s="205"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22570,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="223"/>
+      <c r="N50" s="215"/>
     </row>
     <row r="51" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="201" t="s">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>10853151.666183094</v>
+        <v>12662010.277213609</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>9710688.2133764289</v>
+        <v>11329136.248939166</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22725,7 +22725,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>3136101.5857142848</v>
+        <v>3658785.1833333322</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-2882050.5347162229</v>
+        <v>-3362392.29050226</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>9342455.5436804388</v>
+        <v>10899531.467627177</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>5763393.1753531182</v>
+        <v>6723958.7045786381</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22933,7 +22933,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-1794081.1191956827</v>
+        <v>-2093094.6390616298</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>7915316.3025207175</v>
+        <v>9234535.6862741709</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23037,7 +23037,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>7400867.1550017847</v>
+        <v>8634345.0141687486</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23089,7 +23089,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>5400853.404091456</v>
+        <v>6300995.6381066991</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>12659725.528991302</v>
+        <v>14769679.783823187</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23193,7 +23193,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>8455309.1544409189</v>
+        <v>9864527.3468477372</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>2471834.4973568148</v>
+        <v>2883806.9135829508</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>6450821.850651456</v>
+        <v>7525958.8257600321</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23347,7 +23347,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>84884386.423449904</v>
+        <v>99031784.160691559</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.2">
@@ -23363,10 +23363,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="213" t="s">
+      <c r="B68" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="213" t="s">
+      <c r="C68" s="205" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23374,8 +23374,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="213"/>
-      <c r="C69" s="213"/>
+      <c r="B69" s="205"/>
+      <c r="C69" s="205"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -23569,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="214" t="s">
+      <c r="B87" s="206" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="215"/>
-      <c r="D87" s="215"/>
-      <c r="E87" s="215"/>
-      <c r="F87" s="216"/>
+      <c r="C87" s="207"/>
+      <c r="D87" s="207"/>
+      <c r="E87" s="207"/>
+      <c r="F87" s="208"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23629,7 +23629,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-954498.42259089008</v>
+        <v>-1113581.4930227052</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23658,7 +23658,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-1323534.4812773168</v>
+        <v>-1544123.561490203</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>10118926.813847695</v>
+        <v>11805414.616155645</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23772,12 +23772,17 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>7840893.9099794878</v>
+        <v>9147709.5616427362</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23785,11 +23790,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23940,11 +23940,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>206184756.18072101</v>
+        <v>212167427.80072099</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>35096691.328971997</v>
+        <v>35421015.648971997</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
@@ -23962,11 +23962,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>296101307.21049404</v>
+        <v>309246532.670479</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>83156823.687862009</v>
+        <v>92871246.237861991</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
@@ -23974,27 +23974,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="15">
-        <v>161262313.81243399</v>
+        <v>196309422.20397699</v>
       </c>
       <c r="D10" s="15">
-        <v>24943450.952498998</v>
+        <v>25863250.952498998</v>
       </c>
       <c r="E10" s="15">
-        <v>89609403.25</v>
+        <v>100774808.19</v>
       </c>
       <c r="F10" s="15">
-        <v>275815168.01493299</v>
+        <v>322947481.34647602</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>549726610.54037702</v>
+        <v>582201107.59037697</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>16028568.075153001</v>
+        <v>18129072.575142998</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
@@ -24002,23 +24002,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="15">
-        <v>215869166.06197</v>
+        <v>225020394.74196199</v>
       </c>
       <c r="D11" s="15">
-        <v>50582296.000247002</v>
+        <v>54803361.760242999</v>
       </c>
       <c r="E11" s="15">
         <v>2360360.36</v>
       </c>
       <c r="F11" s="15">
-        <v>268811822.42221701</v>
+        <v>282184116.86220503</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>173290539.23971999</v>
+        <v>197164413.23962</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24030,27 +24030,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="15">
-        <v>149549442.19250301</v>
+        <v>155862235.142488</v>
       </c>
       <c r="D12" s="15">
-        <v>50239797.278047003</v>
+        <v>51775981.068047002</v>
       </c>
       <c r="E12" s="15">
-        <v>29807864.199999999</v>
+        <v>29921364.199999999</v>
       </c>
       <c r="F12" s="15">
-        <v>229597103.67054999</v>
+        <v>237559580.41053501</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>281124971.126176</v>
+        <v>288223079.27416199</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>52560447.290808998</v>
+        <v>54912122.962808996</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.2">
@@ -24058,27 +24058,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="15">
-        <v>146551865.01799101</v>
+        <v>153384297.527991</v>
       </c>
       <c r="D13" s="15">
-        <v>32917026.409814999</v>
+        <v>41095265.169814996</v>
       </c>
       <c r="E13" s="15">
-        <v>16832589.800000001</v>
+        <v>20057814.960000001</v>
       </c>
       <c r="F13" s="15">
-        <v>196301481.227806</v>
+        <v>214537377.65780601</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>543082651.28237295</v>
+        <v>552907346.45246303</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>42792947.329939</v>
+        <v>45672098.689937003</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
@@ -24086,27 +24086,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="15">
-        <v>549726610.54037702</v>
+        <v>582201107.59037697</v>
       </c>
       <c r="D14" s="15">
-        <v>16028568.075153001</v>
+        <v>18129072.575142998</v>
       </c>
       <c r="E14" s="15">
-        <v>138225495.77000001</v>
+        <v>146583333.69</v>
       </c>
       <c r="F14" s="15">
-        <v>703980674.38552999</v>
+        <v>746913513.85552001</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>261878175.58879301</v>
+        <v>284518972.08385497</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>33892692.939971998</v>
+        <v>37425665.979971997</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
@@ -24122,11 +24122,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>215869166.06197</v>
+        <v>225020394.74196199</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>50582296.000247002</v>
+        <v>54803361.760242999</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
@@ -24134,27 +24134,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="15">
-        <v>281124971.126176</v>
+        <v>288223079.27416199</v>
       </c>
       <c r="D16" s="15">
-        <v>52560447.290808998</v>
+        <v>54912122.962808996</v>
       </c>
       <c r="E16" s="15">
         <v>22882161.899999999</v>
       </c>
       <c r="F16" s="15">
-        <v>356567580.31698501</v>
+        <v>366017364.136971</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>314184897.22241002</v>
+        <v>319529239.042409</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>27153940.735466</v>
+        <v>29243601.095465999</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -24162,7 +24162,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="15">
-        <v>173290539.23971999</v>
+        <v>197164413.23962</v>
       </c>
       <c r="D17" s="15">
         <v>46234425.210000001</v>
@@ -24171,18 +24171,18 @@
         <v>168</v>
       </c>
       <c r="F17" s="15">
-        <v>219524964.44972</v>
+        <v>243398838.44962001</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>161262313.81243399</v>
+        <v>196309422.20397699</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>24943450.952498998</v>
+        <v>25863250.952498998</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -24190,27 +24190,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="15">
-        <v>272962870.33803397</v>
+        <v>300585035.238033</v>
       </c>
       <c r="D18" s="15">
         <v>2025072.1099950001</v>
       </c>
       <c r="E18" s="15">
-        <v>5689189.1200000001</v>
+        <v>6986486.4000000004</v>
       </c>
       <c r="F18" s="15">
-        <v>280677131.56802899</v>
+        <v>309596593.74802798</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>401593886.82781702</v>
+        <v>418494886.80674899</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>50952055.171508998</v>
+        <v>68276379.211264998</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
@@ -24218,27 +24218,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="15">
-        <v>543082651.28237295</v>
+        <v>552907346.45246303</v>
       </c>
       <c r="D19" s="15">
-        <v>42792947.329939</v>
+        <v>45672098.689937003</v>
       </c>
       <c r="E19" s="15">
         <v>914346866.62996995</v>
       </c>
       <c r="F19" s="15">
-        <v>1500222465.2422819</v>
+        <v>1512926311.7723701</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>95787896.860800996</v>
+        <v>111310416.547754</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>93353510.079093993</v>
+        <v>106422498.50697801</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
@@ -24246,16 +24246,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="15">
-        <v>70303906.860800996</v>
+        <v>78812636.547754005</v>
       </c>
       <c r="D20" s="15">
-        <v>19557070.13978</v>
+        <v>20773286.339760002</v>
       </c>
       <c r="E20" s="15">
-        <v>3048648.72</v>
+        <v>3913513.6</v>
       </c>
       <c r="F20" s="15">
-        <v>92909625.720580995</v>
+        <v>103499436.487514</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24273,23 +24273,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="15">
-        <v>25483990</v>
+        <v>32497780</v>
       </c>
       <c r="D21" s="15">
-        <v>73796439.939313993</v>
+        <v>85649212.167218</v>
       </c>
       <c r="E21" s="15">
-        <v>16529730.039999999</v>
+        <v>18583784.140000001</v>
       </c>
       <c r="F21" s="15">
-        <v>115810159.979314</v>
+        <v>136730776.30721799</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>548626523.25693297</v>
+        <v>556226172.03801799</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24300,7 +24300,7 @@
         <v>172</v>
       </c>
       <c r="C22" s="15">
-        <v>97592395.5</v>
+        <v>147569605.5</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>168</v>
@@ -24309,7 +24309,7 @@
         <v>4684684.5599999996</v>
       </c>
       <c r="F22" s="15">
-        <v>102277080.06</v>
+        <v>152254290.06</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24340,16 +24340,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="15">
-        <v>206184756.18072101</v>
+        <v>212167427.80072099</v>
       </c>
       <c r="D24" s="15">
-        <v>35096691.328971997</v>
+        <v>35421015.648971997</v>
       </c>
       <c r="E24" s="15">
-        <v>271080095.09987003</v>
+        <v>274761734.67987001</v>
       </c>
       <c r="F24" s="15">
-        <v>512361542.60956299</v>
+        <v>522350178.12956297</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24360,16 +24360,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="15">
-        <v>261878175.58879301</v>
+        <v>284518972.08385497</v>
       </c>
       <c r="D25" s="15">
-        <v>33892692.939971998</v>
+        <v>37425665.979971997</v>
       </c>
       <c r="E25" s="15">
-        <v>143623831.21963</v>
+        <v>151966173.43963</v>
       </c>
       <c r="F25" s="15">
-        <v>439394699.74839503</v>
+        <v>473910811.50345701</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24380,16 +24380,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="15">
-        <v>314184897.22241002</v>
+        <v>319529239.042409</v>
       </c>
       <c r="D26" s="15">
-        <v>27153940.735466</v>
+        <v>29243601.095465999</v>
       </c>
       <c r="E26" s="15">
-        <v>343007483.14965802</v>
+        <v>361548924.39965802</v>
       </c>
       <c r="F26" s="15">
-        <v>684346321.10753405</v>
+        <v>710321764.53753304</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24400,16 +24400,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="15">
-        <v>401593886.82781702</v>
+        <v>418494886.80674899</v>
       </c>
       <c r="D27" s="15">
-        <v>50952055.171508998</v>
+        <v>68276379.211264998</v>
       </c>
       <c r="E27" s="15">
-        <v>5677297.4550000001</v>
+        <v>7244865.0549999997</v>
       </c>
       <c r="F27" s="15">
-        <v>458223239.45432597</v>
+        <v>494016131.07301402</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24456,7 +24456,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="15">
-        <v>98391165.859366</v>
+        <v>117232787.74518099</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24467,7 +24467,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="15">
-        <v>167506691.180985</v>
+        <v>168936934.47497499</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24478,7 +24478,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="15">
-        <v>95460954.966034994</v>
+        <v>103060603.74711999</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24531,17 +24531,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="205" t="s">
+      <c r="B41" s="216" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="206"/>
-      <c r="D41" s="207"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.5</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24584,19 +24584,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>3839634246.0940862</v>
+        <v>4086617522.5945277</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.52892774482012261</v>
+        <v>0.56295085719874427</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>3419645085.9059138</v>
+        <v>3172661809.4054723</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>244260363.27899384</v>
+        <v>264388484.11712268</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24613,19 +24613,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>556747848.80152202</v>
+        <v>615274738.831146</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.3076932343963531</v>
+        <v>0.34003880722818375</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1252677210.198478</v>
+        <v>1194150320.168854</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>89476943.585605577</v>
+        <v>99512526.680737838</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24642,46 +24642,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>814524380.29728401</v>
+        <v>842395894.25817394</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.44488838896470939</v>
+        <v>0.46011164470021249</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1016326683.702716</v>
+        <v>988455169.74182606</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>72594763.121622577</v>
+        <v>82371264.145152166</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="211" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="212"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10899555455</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>5210906475.1928921</v>
+        <v>5544288155.6838474</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.47808431240216043</v>
+        <v>0.50867103512377587</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>5688648979.8071079</v>
+        <v>5355267299.3161526</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>406332069.98622197</v>
+        <v>446272274.94301271</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24691,40 +24691,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="208" t="s">
+      <c r="B48" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="209"/>
-      <c r="D48" s="209"/>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="210"/>
-      <c r="K48" s="217"/>
-      <c r="L48" s="218"/>
-      <c r="M48" s="218"/>
-      <c r="N48" s="219"/>
+      <c r="C48" s="220"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="220"/>
+      <c r="F48" s="220"/>
+      <c r="G48" s="220"/>
+      <c r="H48" s="220"/>
+      <c r="I48" s="220"/>
+      <c r="J48" s="221"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="210"/>
+      <c r="M48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="213" t="s">
+      <c r="B49" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="213" t="s">
+      <c r="C49" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="213"/>
+      <c r="F49" s="214"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="213" t="s">
+      <c r="J49" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24732,13 +24732,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="223" t="s">
+      <c r="N49" s="215" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="213"/>
-      <c r="C50" s="213"/>
+      <c r="B50" s="205"/>
+      <c r="C50" s="205"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24757,7 +24757,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="213"/>
+      <c r="J50" s="205"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24767,7 +24767,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="223"/>
+      <c r="N50" s="215"/>
     </row>
     <row r="51" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -24790,35 +24790,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>206184756.18072101</v>
+        <v>212167427.80072099</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>35096691.328971997</v>
+        <v>35421015.648971997</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>241281447.50969303</v>
+        <v>247588443.44969299</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.43590855997253991</v>
+        <v>0.44730302708277059</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>245498721.81927899</v>
+        <v>239516050.19927901</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>66733731.671028003</v>
+        <v>66409407.351028003</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>312232453.49030697</v>
+        <v>305925457.55030704</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>22302318.106450498</v>
+        <v>25493788.129192252</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -24842,35 +24842,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>296101307.21049404</v>
+        <v>309246532.670479</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>83156823.687862009</v>
+        <v>92871246.237861991</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>379258130.89835608</v>
+        <v>402117778.90834099</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.46518234461777491</v>
+        <v>0.49322104383625465</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>294081063.78950596</v>
+        <v>280935838.329521</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>141949982.31213799</v>
+        <v>132235559.76213801</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>436031046.10164392</v>
+        <v>413171398.09165901</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>31145074.721545994</v>
+        <v>34430949.840971582</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>97592395.5</v>
+        <v>147569605.5</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -24902,15 +24902,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>97592395.5</v>
+        <v>147569605.5</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.40415403455756438</v>
+        <v>0.61112191308894692</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>143880872.5</v>
+        <v>93903662.5</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -24918,11 +24918,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>143880872.5</v>
+        <v>93903662.5</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>10277205.178571429</v>
+        <v>7825305.208333333</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -24946,35 +24946,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>549726610.54037702</v>
+        <v>582201107.59037697</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>16028568.075153001</v>
+        <v>18129072.575142998</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>565755178.61553001</v>
+        <v>600330180.16551995</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.77911149604608843</v>
+        <v>0.82672534422919908</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>95985861.459622979</v>
+        <v>63511364.409623027</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>64413279.924846999</v>
+        <v>62312775.424857005</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>160399141.38446999</v>
+        <v>125824139.83448005</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>11457081.527462142</v>
+        <v>10485344.986206671</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -24998,7 +24998,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>173290539.23971999</v>
+        <v>197164413.23962</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25006,15 +25006,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>219524964.44972</v>
+        <v>243398838.44962001</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.37243081809460354</v>
+        <v>0.4129335757065139</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>335628292.76028001</v>
+        <v>311754418.76038003</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25022,11 +25022,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>369913271.55027997</v>
+        <v>346039397.55037999</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>26422376.539305713</v>
+        <v>28836616.462531667</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25050,35 +25050,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>281124971.126176</v>
+        <v>288223079.27416199</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>52560447.290808998</v>
+        <v>54912122.962808996</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>333685418.41698498</v>
+        <v>343135202.23697102</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.63898384042462864</v>
+        <v>0.65707950425412076</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>158938312.873824</v>
+        <v>151840204.72583801</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>29588877.709191002</v>
+        <v>27237202.037191004</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>188527190.58301502</v>
+        <v>179077406.76302898</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>13466227.898786787</v>
+        <v>14923117.230252415</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25102,35 +25102,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>543082651.28237295</v>
+        <v>552907346.45246303</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>42792947.329939</v>
+        <v>45672098.689937003</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>585875598.61231196</v>
+        <v>598579445.14240003</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.52205586503639245</v>
+        <v>0.53337587495874339</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>453675693.71762705</v>
+        <v>443850998.54753697</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>82695650.670060992</v>
+        <v>79816499.310063004</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>536371344.38768804</v>
+        <v>523667497.85759997</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>38312238.884834863</v>
+        <v>43638958.154799998</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25154,35 +25154,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>261878175.58879301</v>
+        <v>284518972.08385497</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>33892692.939971998</v>
+        <v>37425665.979971997</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>295770868.52876502</v>
+        <v>321944638.06382698</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.46386081470115786</v>
+        <v>0.5049094349412997</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>278408883.41120696</v>
+        <v>255768086.91614503</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>63448733.060028002</v>
+        <v>59915760.020028003</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>341857616.47123498</v>
+        <v>315683846.93617302</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>24418401.176516782</v>
+        <v>26306987.244681086</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>11584213.24</v>
+        <v>13514915.446666667</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25258,35 +25258,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>215869166.06197</v>
+        <v>225020394.74196199</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>50582296.000247002</v>
+        <v>54803361.760242999</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>266451462.062217</v>
+        <v>279823756.50220501</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.43606099699077178</v>
+        <v>0.45794541826744595</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>223148142.93803</v>
+        <v>213996914.25803801</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>121442115.999753</v>
+        <v>117221050.239757</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>344590258.937783</v>
+        <v>331217964.49779499</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>24613589.924127359</v>
+        <v>27601497.041482914</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25310,35 +25310,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>314184897.22241002</v>
+        <v>319529239.042409</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>27153940.735466</v>
+        <v>29243601.095465999</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>341338837.95787603</v>
+        <v>348772840.13787502</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.44976254746431582</v>
+        <v>0.45955790441324951</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>352444698.77758998</v>
+        <v>347100356.957591</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>65147681.264533997</v>
+        <v>63058020.904533997</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>417592380.04212397</v>
+        <v>410158377.86212498</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>29828027.145865999</v>
+        <v>34179864.821843751</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25362,35 +25362,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>161262313.81243399</v>
+        <v>196309422.20397699</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>24943450.952498998</v>
+        <v>25863250.952498998</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>186205764.76493299</v>
+        <v>222172673.15647599</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.35886979389678664</v>
+        <v>0.42818793245104708</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>260280709.18756601</v>
+        <v>225233600.79602301</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>72380725.047500998</v>
+        <v>71460925.047500998</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>332661434.23506701</v>
+        <v>296694525.84352398</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>23761531.016790502</v>
+        <v>24724543.820293665</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25414,35 +25414,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>401593886.82781702</v>
+        <v>418494886.80674899</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>50952055.171508998</v>
+        <v>68276379.211264998</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>452545941.99932599</v>
+        <v>486771266.01801395</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.46097350197193915</v>
+        <v>0.49583618883930347</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>216757055.17218298</v>
+        <v>199856055.19325101</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>312414910.82849097</v>
+        <v>295090586.78873503</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>529171966.00067401</v>
+        <v>494946641.98198605</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>37797997.571476713</v>
+        <v>41245553.498498835</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25466,35 +25466,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>95787896.860800996</v>
+        <v>111310416.547754</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>93353510.079093993</v>
+        <v>106422498.50697801</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>189141406.93989497</v>
+        <v>217732915.05473202</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.32273620644756856</v>
+        <v>0.37152253523135353</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>198737792.13919902</v>
+        <v>183215272.45224601</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>198176542.92090601</v>
+        <v>185107554.49302199</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>396914335.06010503</v>
+        <v>368322826.94526798</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>28351023.932864644</v>
+        <v>30693568.912105665</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25516,35 +25516,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>3839634246.0940862</v>
+        <v>4086617522.5945277</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>556747848.80152202</v>
+        <v>615274738.831146</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>4396382094.8956079</v>
+        <v>4701892261.4256735</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.48478612879461402</v>
+        <v>0.51847453160916179</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>3419645085.9059134</v>
+        <v>3172661809.4054723</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1252677210.198478</v>
+        <v>1194150320.168854</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>4672322296.1043921</v>
+        <v>4366812129.5743265</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>333737306.86459941</v>
+        <v>363901010.79786056</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.2">
@@ -25560,10 +25560,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="213" t="s">
+      <c r="B68" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="213" t="s">
+      <c r="C68" s="205" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25571,8 +25571,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="213"/>
-      <c r="C69" s="213"/>
+      <c r="B69" s="205"/>
+      <c r="C69" s="205"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>271080095.09987003</v>
+        <v>274761734.67987001</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25598,7 +25598,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>46640454</v>
+        <v>49979179.159999996</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25622,7 +25622,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>138225495.77000001</v>
+        <v>146583333.69</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>143623831.21963</v>
+        <v>151966173.43963</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>343007483.14965802</v>
+        <v>361548924.39965802</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25718,7 +25718,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>89609403.25</v>
+        <v>100774808.19</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="D82" s="192">
         <f>IF(E27="",0,E27)</f>
-        <v>5677297.4550000001</v>
+        <v>7244865.0549999997</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>19578378.759999998</v>
+        <v>22497297.740000002</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25752,7 +25752,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>2009818584.0141275</v>
+        <v>2067732461.6641278</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
@@ -25766,13 +25766,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="214" t="s">
+      <c r="B87" s="206" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="215"/>
-      <c r="D87" s="215"/>
-      <c r="E87" s="215"/>
-      <c r="F87" s="216"/>
+      <c r="C87" s="207"/>
+      <c r="D87" s="207"/>
+      <c r="E87" s="207"/>
+      <c r="F87" s="208"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25814,19 +25814,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>98391165.859366</v>
+        <v>117232787.74518099</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.34459067453760717</v>
+        <v>0.41057878574970225</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>187139387.140634</v>
+        <v>168297765.25481901</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>13367099.081473857</v>
+        <v>14024813.771234917</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25843,19 +25843,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>167506691.180985</v>
+        <v>168936934.47497499</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.3906119443749792</v>
+        <v>0.39394715510629907</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>261324770.819015</v>
+        <v>259894527.52502501</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>18666055.058501072</v>
+        <v>21657877.293752085</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25872,19 +25872,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>548626523.25693297</v>
+        <v>556226172.03801799</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.49138549433003259</v>
+        <v>0.49819223263874396</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>567862525.74306703</v>
+        <v>560262876.96198201</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>40561608.981647648</v>
+        <v>46688573.08016517</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25957,24 +25957,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>814524380.29728401</v>
+        <v>842395894.25817394</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.44488838896470939</v>
+        <v>0.46011164470021249</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1016326683.702716</v>
+        <v>988455169.74182606</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>72594763.121622577</v>
+        <v>82371264.145152166</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25982,11 +25987,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26588,11 +26588,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="205" t="s">
+      <c r="B41" s="216" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="206"/>
-      <c r="D41" s="207"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26716,10 +26716,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="211" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="212"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26748,40 +26748,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="208" t="s">
+      <c r="B48" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="209"/>
-      <c r="D48" s="209"/>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="210"/>
-      <c r="K48" s="217"/>
-      <c r="L48" s="218"/>
-      <c r="M48" s="218"/>
-      <c r="N48" s="219"/>
+      <c r="C48" s="220"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="220"/>
+      <c r="F48" s="220"/>
+      <c r="G48" s="220"/>
+      <c r="H48" s="220"/>
+      <c r="I48" s="220"/>
+      <c r="J48" s="221"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="210"/>
+      <c r="M48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="213" t="s">
+      <c r="B49" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="213" t="s">
+      <c r="C49" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="213"/>
+      <c r="F49" s="214"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="213" t="s">
+      <c r="J49" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26789,13 +26789,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="223" t="s">
+      <c r="N49" s="215" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="213"/>
-      <c r="C50" s="213"/>
+      <c r="B50" s="205"/>
+      <c r="C50" s="205"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26814,7 +26814,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="213"/>
+      <c r="J50" s="205"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26824,7 +26824,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="223"/>
+      <c r="N50" s="215"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -27617,10 +27617,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="213" t="s">
+      <c r="B68" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="213" t="s">
+      <c r="C68" s="205" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27628,8 +27628,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="213"/>
-      <c r="C69" s="213"/>
+      <c r="B69" s="205"/>
+      <c r="C69" s="205"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -27823,13 +27823,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="214" t="s">
+      <c r="B87" s="206" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="215"/>
-      <c r="D87" s="215"/>
-      <c r="E87" s="215"/>
-      <c r="F87" s="216"/>
+      <c r="C87" s="207"/>
+      <c r="D87" s="207"/>
+      <c r="E87" s="207"/>
+      <c r="F87" s="208"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28032,6 +28032,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28039,11 +28044,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/randy/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B69C843-D7BA-5B40-815C-4B05E0CAD9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F09FE4-6991-9B4C-A5FD-F09E014F2396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="600" windowWidth="18360" windowHeight="16340" tabRatio="500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1829,6 +1829,30 @@
     <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1860,30 +1884,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3426,11 +3426,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3554,10 +3554,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3586,40 +3586,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3627,13 +3627,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3652,7 +3652,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3662,7 +3662,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -4455,10 +4455,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4466,8 +4466,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -4661,13 +4661,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4870,11 +4870,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4882,6 +4877,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5483,11 +5483,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5611,10 +5611,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5643,40 +5643,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5684,13 +5684,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5709,7 +5709,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5719,7 +5719,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -6512,10 +6512,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6523,8 +6523,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -6718,13 +6718,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6927,11 +6927,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6939,6 +6934,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7540,11 +7540,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7668,10 +7668,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7700,40 +7700,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7741,13 +7741,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7766,7 +7766,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7776,7 +7776,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -8569,10 +8569,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8580,8 +8580,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -8775,13 +8775,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8984,11 +8984,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8996,6 +8991,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9597,11 +9597,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9725,10 +9725,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9757,40 +9757,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9798,13 +9798,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9823,7 +9823,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9833,7 +9833,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -10626,10 +10626,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10637,8 +10637,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -10832,13 +10832,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11041,11 +11041,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11053,6 +11048,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11654,11 +11654,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11781,10 +11781,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11813,40 +11813,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11854,13 +11854,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11879,7 +11879,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11889,7 +11889,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -12668,10 +12668,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12679,8 +12679,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -12874,13 +12874,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13083,11 +13083,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13095,6 +13090,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -18409,10 +18409,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B44" s="222" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="223"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18477,23 +18477,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="205" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="205" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="212" t="s">
+      <c r="D47" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="213"/>
-      <c r="F47" s="214"/>
+      <c r="E47" s="221"/>
+      <c r="F47" s="222"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="205" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18506,8 +18506,8 @@
       </c>
     </row>
     <row r="48" spans="2:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="B48" s="205"/>
-      <c r="C48" s="205"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18526,7 +18526,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="205"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -20158,11 +20158,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20280,10 +20280,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20306,17 +20306,17 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
       <c r="K48" s="241"/>
       <c r="L48" s="242"/>
       <c r="M48" s="242"/>
@@ -21173,10 +21173,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21187,8 +21187,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -21374,13 +21374,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="219" t="s">
+      <c r="B87" s="208" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="220"/>
-      <c r="D87" s="220"/>
-      <c r="E87" s="220"/>
-      <c r="F87" s="221"/>
+      <c r="C87" s="209"/>
+      <c r="D87" s="209"/>
+      <c r="E87" s="209"/>
+      <c r="F87" s="210"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22399,7 +22399,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>52732840.017633915</v>
+        <v>57526734.564691544</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22428,7 +22428,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>46298944.143057562</v>
+        <v>50507939.065153711</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22457,15 +22457,15 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>9147709.5616427269</v>
+        <v>9979319.5217920654</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>108179493.72233421</v>
+        <v>118013993.15163732</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22494,40 +22494,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22535,13 +22535,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22560,7 +22560,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22570,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="201" t="s">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>12662010.277213609</v>
+        <v>13813102.120596664</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>11329136.248939166</v>
+        <v>12359057.726115454</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22725,7 +22725,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>3658785.1833333322</v>
+        <v>3991402.0181818171</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-3362392.29050226</v>
+        <v>-3668064.3169115563</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>10899531.467627177</v>
+        <v>11890397.964684194</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>6723958.7045786381</v>
+        <v>7335227.6777221505</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22933,7 +22933,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-2093094.6390616298</v>
+        <v>-2283375.9698854145</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>9234535.6862741709</v>
+        <v>10074038.930480914</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23037,7 +23037,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>8634345.0141687486</v>
+        <v>9419285.4700022712</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23089,7 +23089,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>6300995.6381066991</v>
+        <v>6873813.4233891256</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>14769679.783823187</v>
+        <v>16112377.945988931</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23193,7 +23193,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>9864527.3468477372</v>
+        <v>10761302.560197532</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>2883806.9135829508</v>
+        <v>3145971.1784541281</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>7525958.8257600321</v>
+        <v>8210136.9008291252</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -23347,7 +23347,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>99031784.160691559</v>
+        <v>108034673.62984534</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.2">
@@ -23363,10 +23363,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23374,8 +23374,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -23569,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23629,7 +23629,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-1113581.4930227052</v>
+        <v>-1214816.1742065875</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23658,7 +23658,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-1544123.561490203</v>
+        <v>-1684498.4307165851</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>11805414.616155645</v>
+        <v>12878634.126715248</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23772,17 +23772,12 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>9147709.5616427362</v>
+        <v>9979319.5217920765</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23790,6 +23785,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23940,11 +23940,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>212167427.80072099</v>
+        <v>221777392.60062101</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>35421015.648971997</v>
+        <v>39074871.528972</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
@@ -23962,11 +23962,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>309246532.670479</v>
+        <v>312770208.47445101</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>92871246.237861991</v>
+        <v>98426809.237782001</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
@@ -23974,27 +23974,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="15">
-        <v>196309422.20397699</v>
+        <v>197869782.723941</v>
       </c>
       <c r="D10" s="15">
-        <v>25863250.952498998</v>
+        <v>26160548.252498999</v>
       </c>
       <c r="E10" s="15">
-        <v>100774808.19</v>
+        <v>101874808.19</v>
       </c>
       <c r="F10" s="15">
-        <v>322947481.34647602</v>
+        <v>325905139.16644001</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>582201107.59037697</v>
+        <v>618235965.53037703</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>18129072.575142998</v>
+        <v>19273613.165139999</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
@@ -24002,16 +24002,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="15">
-        <v>225020394.74196199</v>
+        <v>225520394.74196199</v>
       </c>
       <c r="D11" s="15">
-        <v>54803361.760242999</v>
+        <v>55210361.760242999</v>
       </c>
       <c r="E11" s="15">
         <v>2360360.36</v>
       </c>
       <c r="F11" s="15">
-        <v>282184116.86220503</v>
+        <v>283091116.86220503</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -24030,27 +24030,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="15">
-        <v>155862235.142488</v>
+        <v>156375748.66248801</v>
       </c>
       <c r="D12" s="15">
-        <v>51775981.068047002</v>
+        <v>57331544.067966998</v>
       </c>
       <c r="E12" s="15">
         <v>29921364.199999999</v>
       </c>
       <c r="F12" s="15">
-        <v>237559580.41053501</v>
+        <v>243628656.930455</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>288223079.27416199</v>
+        <v>290723529.70514101</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>54912122.962808996</v>
+        <v>64555906.642809004</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.2">
@@ -24058,27 +24058,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="15">
-        <v>153384297.527991</v>
+        <v>156394459.81196299</v>
       </c>
       <c r="D13" s="15">
         <v>41095265.169814996</v>
       </c>
       <c r="E13" s="15">
-        <v>20057814.960000001</v>
+        <v>23441598.800000001</v>
       </c>
       <c r="F13" s="15">
-        <v>214537377.65780601</v>
+        <v>220931323.78177801</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>552907346.45246303</v>
+        <v>560949217.63143897</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>45672098.689937003</v>
+        <v>46176098.689937003</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
@@ -24086,27 +24086,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="15">
-        <v>582201107.59037697</v>
+        <v>618235965.53037703</v>
       </c>
       <c r="D14" s="15">
-        <v>18129072.575142998</v>
+        <v>19273613.165139999</v>
       </c>
       <c r="E14" s="15">
-        <v>146583333.69</v>
+        <v>157983153.52000001</v>
       </c>
       <c r="F14" s="15">
-        <v>746913513.85552001</v>
+        <v>795492732.21551704</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>284518972.08385497</v>
+        <v>294094242.39383</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>37425665.979971997</v>
+        <v>40127914.659966998</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
@@ -24122,11 +24122,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>225020394.74196199</v>
+        <v>225520394.74196199</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>54803361.760242999</v>
+        <v>55210361.760242999</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
@@ -24134,27 +24134,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="15">
-        <v>288223079.27416199</v>
+        <v>290723529.70514101</v>
       </c>
       <c r="D16" s="15">
-        <v>54912122.962808996</v>
+        <v>64555906.642809004</v>
       </c>
       <c r="E16" s="15">
-        <v>22882161.899999999</v>
+        <v>23882161.899999999</v>
       </c>
       <c r="F16" s="15">
-        <v>366017364.136971</v>
+        <v>379161598.24795002</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>319529239.042409</v>
+        <v>324357383.21240902</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>29243601.095465999</v>
+        <v>29579601.095465999</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -24178,11 +24178,11 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>196309422.20397699</v>
+        <v>197869782.723941</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>25863250.952498998</v>
+        <v>26160548.252498999</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -24190,7 +24190,7 @@
         <v>119</v>
       </c>
       <c r="C18" s="15">
-        <v>300585035.238033</v>
+        <v>300614764.95803303</v>
       </c>
       <c r="D18" s="15">
         <v>2025072.1099950001</v>
@@ -24199,14 +24199,14 @@
         <v>6986486.4000000004</v>
       </c>
       <c r="F18" s="15">
-        <v>309596593.74802798</v>
+        <v>309626323.46802801</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>418494886.80674899</v>
+        <v>418988886.80674899</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
@@ -24218,16 +24218,16 @@
         <v>121</v>
       </c>
       <c r="C19" s="15">
-        <v>552907346.45246303</v>
+        <v>560949217.63143897</v>
       </c>
       <c r="D19" s="15">
-        <v>45672098.689937003</v>
+        <v>46176098.689937003</v>
       </c>
       <c r="E19" s="15">
-        <v>914346866.62996995</v>
+        <v>926144163.82997</v>
       </c>
       <c r="F19" s="15">
-        <v>1512926311.7723701</v>
+        <v>1533269480.151346</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
@@ -24252,10 +24252,10 @@
         <v>20773286.339760002</v>
       </c>
       <c r="E20" s="15">
-        <v>3913513.6</v>
+        <v>8237838</v>
       </c>
       <c r="F20" s="15">
-        <v>103499436.487514</v>
+        <v>107823760.887514</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24279,10 +24279,10 @@
         <v>85649212.167218</v>
       </c>
       <c r="E21" s="15">
-        <v>18583784.140000001</v>
+        <v>33718919.539999999</v>
       </c>
       <c r="F21" s="15">
-        <v>136730776.30721799</v>
+        <v>151865911.70721799</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
@@ -24340,16 +24340,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="15">
-        <v>212167427.80072099</v>
+        <v>221777392.60062101</v>
       </c>
       <c r="D24" s="15">
-        <v>35421015.648971997</v>
+        <v>39074871.528972</v>
       </c>
       <c r="E24" s="15">
-        <v>274761734.67987001</v>
+        <v>277756329.31987</v>
       </c>
       <c r="F24" s="15">
-        <v>522350178.12956297</v>
+        <v>538608593.44946301</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24360,16 +24360,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="15">
-        <v>284518972.08385497</v>
+        <v>294094242.39383</v>
       </c>
       <c r="D25" s="15">
-        <v>37425665.979971997</v>
+        <v>40127914.659966998</v>
       </c>
       <c r="E25" s="15">
-        <v>151966173.43963</v>
+        <v>180866804.28957501</v>
       </c>
       <c r="F25" s="15">
-        <v>473910811.50345701</v>
+        <v>515088961.34337199</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24380,16 +24380,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="15">
-        <v>319529239.042409</v>
+        <v>324357383.21240902</v>
       </c>
       <c r="D26" s="15">
-        <v>29243601.095465999</v>
+        <v>29579601.095465999</v>
       </c>
       <c r="E26" s="15">
-        <v>361548924.39965802</v>
+        <v>368551627.40962303</v>
       </c>
       <c r="F26" s="15">
-        <v>710321764.53753304</v>
+        <v>722488611.71749794</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24400,7 +24400,7 @@
         <v>128</v>
       </c>
       <c r="C27" s="15">
-        <v>418494886.80674899</v>
+        <v>418988886.80674899</v>
       </c>
       <c r="D27" s="15">
         <v>68276379.211264998</v>
@@ -24409,7 +24409,7 @@
         <v>7244865.0549999997</v>
       </c>
       <c r="F27" s="15">
-        <v>494016131.07301402</v>
+        <v>494510131.07301402</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24456,7 +24456,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="15">
-        <v>117232787.74518099</v>
+        <v>118647202.165177</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24467,7 +24467,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="15">
-        <v>168936934.47497499</v>
+        <v>168979862.39857501</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24531,17 +24531,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.56666666666666665</v>
+        <v>0.6</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24584,19 +24584,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>4086617522.5945277</v>
+        <v>4163286117.7482934</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.56295085719874427</v>
+        <v>0.57351231814374459</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>3172661809.4054723</v>
+        <v>3095993214.2517066</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>264388484.11712268</v>
+        <v>281453928.56833696</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24613,19 +24613,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>615274738.831146</v>
+        <v>639519027.96105802</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.34003880722818375</v>
+        <v>0.353437698223598</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1194150320.168854</v>
+        <v>1169906031.0389419</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>99512526.680737838</v>
+        <v>106355093.73081289</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24642,46 +24642,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>842395894.25817394</v>
+        <v>843853236.60176992</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.46011164470021249</v>
+        <v>0.46090763645085331</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>988455169.74182606</v>
+        <v>986997827.39823008</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>82371264.145152166</v>
+        <v>89727075.218020916</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10899555455</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>5544288155.6838474</v>
+        <v>5646658382.311121</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.50867103512377587</v>
+        <v>0.51806318208333946</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>5355267299.3161526</v>
+        <v>5252897072.688879</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>446272274.94301271</v>
+        <v>477536097.51717085</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24691,40 +24691,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24732,13 +24732,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24757,7 +24757,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24767,7 +24767,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -24790,35 +24790,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>212167427.80072099</v>
+        <v>221777392.60062101</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>35421015.648971997</v>
+        <v>39074871.528972</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>247588443.44969299</v>
+        <v>260852264.12959301</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.44730302708277059</v>
+        <v>0.47126596759056466</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>239516050.19927901</v>
+        <v>229906085.39937899</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>66409407.351028003</v>
+        <v>62755551.471028</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>305925457.55030704</v>
+        <v>292661636.87040699</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>25493788.129192252</v>
+        <v>26605603.351855181</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -24842,35 +24842,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>309246532.670479</v>
+        <v>312770208.47445101</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>92871246.237861991</v>
+        <v>98426809.237782001</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>402117778.90834099</v>
+        <v>411197017.71223301</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.49322104383625465</v>
+        <v>0.50435726281232485</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>280935838.329521</v>
+        <v>277412162.52554899</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>132235559.76213801</v>
+        <v>126679996.762218</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>413171398.09165901</v>
+        <v>404092159.28776699</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>34430949.840971582</v>
+        <v>36735650.844342455</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -24922,7 +24922,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>7825305.208333333</v>
+        <v>8536696.5909090918</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -24946,35 +24946,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>582201107.59037697</v>
+        <v>618235965.53037703</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>18129072.575142998</v>
+        <v>19273613.165139999</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>600330180.16551995</v>
+        <v>637509578.69551706</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.82672534422919908</v>
+        <v>0.8779257537096482</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>63511364.409623027</v>
+        <v>27476506.46962297</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>62312775.424857005</v>
+        <v>61168234.834859997</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>125824139.83448005</v>
+        <v>88644741.304482937</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>10485344.986206671</v>
+        <v>8058612.845862085</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>28836616.462531667</v>
+        <v>31458127.050034545</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25050,35 +25050,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>288223079.27416199</v>
+        <v>290723529.70514101</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>54912122.962808996</v>
+        <v>64555906.642809004</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>343135202.23697102</v>
+        <v>355279436.34794998</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.65707950425412076</v>
+        <v>0.68033484872815464</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>151840204.72583801</v>
+        <v>149339754.29485899</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>27237202.037191004</v>
+        <v>17593418.357190996</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>179077406.76302898</v>
+        <v>166933172.65205002</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>14923117.230252415</v>
+        <v>15175742.968368184</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25102,35 +25102,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>552907346.45246303</v>
+        <v>560949217.63143897</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>45672098.689937003</v>
+        <v>46176098.689937003</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>598579445.14240003</v>
+        <v>607125316.32137597</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.53337587495874339</v>
+        <v>0.54099083994686892</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>443850998.54753697</v>
+        <v>435809127.36856103</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>79816499.310063004</v>
+        <v>79312499.310063004</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>523667497.85759997</v>
+        <v>515121626.67862403</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>43638958.154799998</v>
+        <v>46829238.788965821</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25154,35 +25154,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>284518972.08385497</v>
+        <v>294094242.39383</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>37425665.979971997</v>
+        <v>40127914.659966998</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>321944638.06382698</v>
+        <v>334222157.05379701</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.5049094349412997</v>
+        <v>0.52416440751356486</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>255768086.91614503</v>
+        <v>246192816.60617</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>59915760.020028003</v>
+        <v>57213511.340033002</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>315683846.93617302</v>
+        <v>303406327.94620299</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>26306987.244681086</v>
+        <v>27582393.449654818</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>13514915.446666667</v>
+        <v>14743544.123636365</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25258,35 +25258,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>225020394.74196199</v>
+        <v>225520394.74196199</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>54803361.760242999</v>
+        <v>55210361.760242999</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>279823756.50220501</v>
+        <v>280730756.50220501</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.45794541826744595</v>
+        <v>0.45942976862983309</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>213996914.25803801</v>
+        <v>213496914.25803801</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>117221050.239757</v>
+        <v>116814050.239757</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>331217964.49779499</v>
+        <v>330310964.49779499</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>27601497.041482914</v>
+        <v>30028269.499799546</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25310,35 +25310,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>319529239.042409</v>
+        <v>324357383.21240902</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>29243601.095465999</v>
+        <v>29579601.095465999</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>348772840.13787502</v>
+        <v>353936984.30787504</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.45955790441324951</v>
+        <v>0.46636240006123325</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>347100356.957591</v>
+        <v>342272212.78759098</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>63058020.904533997</v>
+        <v>62722020.904533997</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>410158377.86212498</v>
+        <v>404994233.69212496</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>34179864.821843751</v>
+        <v>36817657.608374998</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25362,35 +25362,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>196309422.20397699</v>
+        <v>197869782.723941</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>25863250.952498998</v>
+        <v>26160548.252498999</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>222172673.15647599</v>
+        <v>224030330.97644001</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.42818793245104708</v>
+        <v>0.43176815071025526</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>225233600.79602301</v>
+        <v>223673240.276059</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>71460925.047500998</v>
+        <v>71163627.747501001</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>296694525.84352398</v>
+        <v>294836868.02355999</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>24724543.820293665</v>
+        <v>26803351.638505455</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>418494886.80674899</v>
+        <v>418988886.80674899</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
@@ -25422,15 +25422,15 @@
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>486771266.01801395</v>
+        <v>487265266.01801395</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.49583618883930347</v>
+        <v>0.4963393883795934</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>199856055.19325101</v>
+        <v>199362055.19325101</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
@@ -25438,11 +25438,11 @@
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>494946641.98198605</v>
+        <v>494452641.98198605</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>41245553.498498835</v>
+        <v>44950240.18018055</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>30693568.912105665</v>
+        <v>33483893.358660724</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25516,35 +25516,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>4086617522.5945277</v>
+        <v>4163286117.7482934</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>615274738.831146</v>
+        <v>639519027.96105802</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>4701892261.4256735</v>
+        <v>4802805145.7093515</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.51847453160916179</v>
+        <v>0.52960212822415631</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>3172661809.4054723</v>
+        <v>3095993214.2517066</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1194150320.168854</v>
+        <v>1169906031.0389421</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>4366812129.5743265</v>
+        <v>4265899245.2906485</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>363901010.79786056</v>
+        <v>387809022.29914987</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.2">
@@ -25560,10 +25560,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25571,8 +25571,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>274761734.67987001</v>
+        <v>277756329.31987</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25598,7 +25598,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>49979179.159999996</v>
+        <v>53362963</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25622,7 +25622,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>146583333.69</v>
+        <v>157983153.52000001</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="D75" s="192">
         <f>IF(E16="",0,E16)</f>
-        <v>22882161.899999999</v>
+        <v>23882161.899999999</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25658,7 +25658,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>914346866.62996995</v>
+        <v>926144163.82997</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>151966173.43963</v>
+        <v>180866804.28957501</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>361548924.39965802</v>
+        <v>368551627.40962303</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25718,7 +25718,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>100774808.19</v>
+        <v>101874808.19</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>22497297.740000002</v>
+        <v>41956757.539999999</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -25752,7 +25752,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>2067732461.6641278</v>
+        <v>2154770750.8340383</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
@@ -25766,13 +25766,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25814,19 +25814,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>117232787.74518099</v>
+        <v>118647202.165177</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.41057878574970225</v>
+        <v>0.41553242172713123</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>168297765.25481901</v>
+        <v>166883350.83482301</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>14024813.771234917</v>
+        <v>15171213.712256638</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25843,19 +25843,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>168936934.47497499</v>
+        <v>168979862.39857501</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.39394715510629907</v>
+        <v>0.39404725952354447</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>259894527.52502501</v>
+        <v>259851599.60142499</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>21657877.293752085</v>
+        <v>23622872.691038635</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>46688573.08016517</v>
+        <v>50932988.814725637</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25957,29 +25957,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>842395894.25817394</v>
+        <v>843853236.60176992</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.46011164470021249</v>
+        <v>0.46090763645085331</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>988455169.74182606</v>
+        <v>986997827.39823008</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>82371264.145152166</v>
+        <v>89727075.218020916</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25987,6 +25982,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26588,11 +26588,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26716,10 +26716,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26748,40 +26748,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26789,13 +26789,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26814,7 +26814,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26824,7 +26824,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -27617,10 +27617,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27628,8 +27628,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -27823,13 +27823,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28032,11 +28032,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28044,6 +28039,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 19 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 20 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1928,15 +1928,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1956,6 +1947,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3600,10 +3600,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4664,13 +4664,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4873,6 +4873,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4880,11 +4885,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5657,10 +5657,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6721,13 +6721,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6930,6 +6930,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6937,11 +6942,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7714,10 +7714,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8778,13 +8778,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8987,6 +8987,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8994,11 +8999,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9771,10 +9771,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10835,13 +10835,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11044,6 +11044,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11051,11 +11056,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11827,10 +11827,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12877,13 +12877,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13086,6 +13086,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13093,11 +13098,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22338,11 +22338,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="239" t="s">
+      <c r="B41" s="246" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="240"/>
-      <c r="D41" s="241"/>
+      <c r="C41" s="247"/>
+      <c r="D41" s="248"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>63279408.021160699</v>
+        <v>70310453.356845215</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22431,7 +22431,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>55558732.971669078</v>
+        <v>61731925.524076752</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22460,7 +22460,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>10977251.473971272</v>
+        <v>12196946.082190301</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22487,7 +22487,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>129815392.46680105</v>
+        <v>144239324.96311226</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22508,10 +22508,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22573,7 +22573,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>15194412.332656329</v>
+        <v>16882680.369618144</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>13594963.498726999</v>
+        <v>15105514.998585556</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>4390542.2199999988</v>
+        <v>4878380.2444444429</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22780,7 +22780,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-4034870.7486027121</v>
+        <v>-4483189.7206696803</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>13079437.761152614</v>
+        <v>14532708.623502903</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>8068750.4454943659</v>
+        <v>8965278.2727715168</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-2511713.5668739555</v>
+        <v>-2790792.8520821729</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22988,7 +22988,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>11081442.823529005</v>
+        <v>12312714.248365561</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>10361214.017002499</v>
+        <v>11512460.018891666</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>7561194.7657280387</v>
+        <v>8401327.5174755976</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23144,7 +23144,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>17723615.740587823</v>
+        <v>19692906.378430918</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>11837432.816217285</v>
+        <v>13152703.129130317</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>3460568.2962995409</v>
+        <v>3845075.8847772679</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>9031150.5909120385</v>
+        <v>10034611.767680041</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>118838140.99282987</v>
+        <v>132042378.88092208</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23572,13 +23572,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-1336297.7916272462</v>
+        <v>-1484775.3240302736</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-1852948.2737882435</v>
+        <v>-2058831.4153202707</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23690,7 +23690,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>14166497.539386773</v>
+        <v>15740552.821540859</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23775,12 +23775,17 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>10977251.473971283</v>
+        <v>12196946.082190314</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23788,11 +23793,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23861,7 +23861,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23943,11 +23943,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>227909329.520614</v>
+        <v>240105662.73459801</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>39074871.528972</v>
+        <v>40597582.328971997</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23965,11 +23965,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>346415608.93839598</v>
+        <v>363837739.03838599</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>100278354.28778201</v>
+        <v>105136840.68278199</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23977,27 +23977,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>213306764.673924</v>
+        <v>227764693.44332999</v>
       </c>
       <c r="D10" s="205">
-        <v>26160548.252498999</v>
+        <v>28954987.892499</v>
       </c>
       <c r="E10" s="205">
-        <v>107116249.56999999</v>
+        <v>111327060.09</v>
       </c>
       <c r="F10" s="205">
-        <v>346583562.49642301</v>
+        <v>368046741.42582899</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>662518718.73037696</v>
+        <v>705007069.41037703</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>21435775.325116001</v>
+        <v>21729775.325116001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24005,23 +24005,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>244616959.31193799</v>
+        <v>253946188.583938</v>
       </c>
       <c r="D11" s="205">
-        <v>57732578.010231003</v>
+        <v>58307578.010231003</v>
       </c>
       <c r="E11" s="205">
-        <v>2660360.36</v>
+        <v>2984684.68</v>
       </c>
       <c r="F11" s="205">
-        <v>305009897.68216902</v>
+        <v>315238451.27416903</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>197164413.23962</v>
+        <v>221038287.23952001</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24033,27 +24033,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>179213806.56648299</v>
+        <v>192439032.166473</v>
       </c>
       <c r="D12" s="205">
-        <v>57937440.467967004</v>
+        <v>61990485.422967002</v>
       </c>
       <c r="E12" s="205">
-        <v>29921364.199999999</v>
+        <v>44660102.520000003</v>
       </c>
       <c r="F12" s="205">
-        <v>267072611.23445001</v>
+        <v>299089620.10944003</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>309996006.31993097</v>
+        <v>349386455.89393097</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>66721502.592804</v>
+        <v>73162448.542796999</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24061,23 +24061,23 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>167201802.37191299</v>
+        <v>171398706.87191299</v>
       </c>
       <c r="D13" s="205">
-        <v>42340913.819815002</v>
+        <v>43146355.259815</v>
       </c>
       <c r="E13" s="205">
-        <v>23441598.800000001</v>
+        <v>24432409.600000001</v>
       </c>
       <c r="F13" s="205">
-        <v>232984314.99172801</v>
+        <v>238977471.73172799</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>617478269.668329</v>
+        <v>643442193.42425799</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
@@ -24089,27 +24089,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>662518718.73037696</v>
+        <v>705007069.41037703</v>
       </c>
       <c r="D14" s="205">
-        <v>21435775.325116001</v>
+        <v>21729775.325116001</v>
       </c>
       <c r="E14" s="205">
-        <v>167353423.75</v>
+        <v>183868738.94999999</v>
       </c>
       <c r="F14" s="205">
-        <v>851307917.805493</v>
+        <v>910605583.68549299</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>311030411.29380202</v>
+        <v>315785433.81379801</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>40365214.659966998</v>
+        <v>45357400.229927003</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24125,11 +24125,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>244616959.31193799</v>
+        <v>253946188.583938</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>57732578.010231003</v>
+        <v>58307578.010231003</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24137,27 +24137,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>309996006.31993097</v>
+        <v>349386455.89393097</v>
       </c>
       <c r="D16" s="205">
-        <v>66721502.592804</v>
+        <v>73162448.542796999</v>
       </c>
       <c r="E16" s="205">
-        <v>26026603.300000001</v>
+        <v>29615792.469999999</v>
       </c>
       <c r="F16" s="205">
-        <v>402744112.212735</v>
+        <v>452164696.90672803</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>348878867.74540699</v>
+        <v>363150830.91528499</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>32116601.095465999</v>
+        <v>33421898.395466</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24165,7 +24165,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>197164413.23962</v>
+        <v>221038287.23952001</v>
       </c>
       <c r="D17" s="205">
         <v>46234425.210000001</v>
@@ -24174,18 +24174,18 @@
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>243398838.44962001</v>
+        <v>267272712.44951999</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>213306764.673924</v>
+        <v>227764693.44332999</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>26160548.252498999</v>
+        <v>28954987.892499</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24193,27 +24193,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>300614764.95803303</v>
+        <v>366037115.42803103</v>
       </c>
       <c r="D18" s="205">
-        <v>2025072.1099950001</v>
+        <v>3110178.4299920001</v>
       </c>
       <c r="E18" s="205">
-        <v>6986486.4000000004</v>
+        <v>7148648.5599999996</v>
       </c>
       <c r="F18" s="205">
-        <v>309626323.46802801</v>
+        <v>376295942.41802299</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>460344503.14619899</v>
+        <v>535720541.19608903</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>68959622.491264999</v>
+        <v>83676379.051064998</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24221,27 +24221,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>617478269.668329</v>
+        <v>643442193.42425799</v>
       </c>
       <c r="D19" s="205">
         <v>53069774.369935997</v>
       </c>
       <c r="E19" s="205">
-        <v>1036310110.97997</v>
+        <v>1041553354.17997</v>
       </c>
       <c r="F19" s="205">
-        <v>1706858155.018235</v>
+        <v>1738065321.974164</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>113174610.647754</v>
+        <v>119550881.147754</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>107342298.50697801</v>
+        <v>112207163.30689801</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24249,7 +24249,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>79741690.647753999</v>
+        <v>82751411.147753999</v>
       </c>
       <c r="D20" s="205">
         <v>20773286.339760002</v>
@@ -24258,7 +24258,7 @@
         <v>8237838</v>
       </c>
       <c r="F20" s="205">
-        <v>108752814.987514</v>
+        <v>111762535.487514</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24276,23 +24276,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>33432920</v>
+        <v>36799470</v>
       </c>
       <c r="D21" s="205">
-        <v>86569012.167218</v>
+        <v>91433876.967138007</v>
       </c>
       <c r="E21" s="205">
         <v>42151352.140000001</v>
       </c>
       <c r="F21" s="205">
-        <v>162153284.30721799</v>
+        <v>170384699.10713801</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>561014901.67797804</v>
+        <v>584648207.72793794</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24303,16 +24303,16 @@
         <v>172</v>
       </c>
       <c r="C22" s="205">
-        <v>147569605.5</v>
+        <v>148159605.5</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>168</v>
       </c>
       <c r="E22" s="205">
-        <v>4684684.5599999996</v>
+        <v>7027026.8399999999</v>
       </c>
       <c r="F22" s="205">
-        <v>152254290.06</v>
+        <v>155186632.34</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24343,16 +24343,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>227909329.520614</v>
+        <v>240105662.73459801</v>
       </c>
       <c r="D24" s="205">
-        <v>39074871.528972</v>
+        <v>40597582.328971997</v>
       </c>
       <c r="E24" s="205">
-        <v>283236802.15987003</v>
+        <v>282012477.75986999</v>
       </c>
       <c r="F24" s="205">
-        <v>550221003.20945597</v>
+        <v>562715722.82343996</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24363,16 +24363,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>311030411.29380202</v>
+        <v>315785433.81379801</v>
       </c>
       <c r="D25" s="205">
-        <v>40365214.659966998</v>
+        <v>45357400.229927003</v>
       </c>
       <c r="E25" s="205">
-        <v>188358696.12956899</v>
+        <v>194304641.98956901</v>
       </c>
       <c r="F25" s="205">
-        <v>539754322.08333802</v>
+        <v>555447476.03329396</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24383,16 +24383,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>348878867.74540699</v>
+        <v>363150830.91528499</v>
       </c>
       <c r="D26" s="205">
-        <v>32116601.095465999</v>
+        <v>33421898.395466</v>
       </c>
       <c r="E26" s="205">
-        <v>395037573.40962303</v>
+        <v>423372709.03955197</v>
       </c>
       <c r="F26" s="205">
-        <v>776033042.25049603</v>
+        <v>819945438.35030305</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24403,16 +24403,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>460344503.14619899</v>
+        <v>535720541.19608903</v>
       </c>
       <c r="D27" s="205">
-        <v>68959622.491264999</v>
+        <v>83676379.051064998</v>
       </c>
       <c r="E27" s="205">
-        <v>7244865.0549999997</v>
+        <v>10017838.105</v>
       </c>
       <c r="F27" s="205">
-        <v>536548990.69246399</v>
+        <v>629414758.35215402</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24455,7 +24455,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>123410301.225152</v>
+        <v>141618940.424932</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24466,7 +24466,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>170230619.19855502</v>
+        <v>191802511.778543</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24477,7 +24477,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>106323873.867108</v>
+        <v>115492351.307092</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24488,7 +24488,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>454280027.81086999</v>
+        <v>468744856.42084599</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24540,7 +24540,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.6333333333333333</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24583,19 +24583,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>4487847546.0162907</v>
+        <v>4774339059.6212635</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.61822218718505306</v>
+        <v>0.65768774574843203</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>2771431785.9837093</v>
+        <v>2484940272.3787365</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>277143178.59837091</v>
+        <v>276104474.70874852</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24612,19 +24612,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>659491566.33101606</v>
+        <v>701856253.34568894</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.36447575601472648</v>
+        <v>0.38788909761953777</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1149933492.6689839</v>
+        <v>1107568805.6543112</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>114993349.26689839</v>
+        <v>123063200.6282568</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24641,19 +24641,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>854655822.10168505</v>
+        <v>918069659.93141294</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.46680794462573777</v>
+        <v>0.50144420700482106</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>976195241.89831495</v>
+        <v>912781404.06858706</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>97619524.189831495</v>
+        <v>101420156.00762078</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24668,19 +24668,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>6001994934.4489918</v>
+        <v>6394264972.898365</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.55066419536364397</v>
+        <v>0.58665374008121551</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>4897560520.5510082</v>
+        <v>4505290482.101635</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>489756052.0551008</v>
+        <v>500587831.34462613</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24701,10 +24701,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24789,35 +24789,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>227909329.520614</v>
+        <v>240105662.73459801</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>39074871.528972</v>
+        <v>40597582.328971997</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>266984201.049586</v>
+        <v>280703245.06357002</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.48234416618488141</v>
+        <v>0.50712953108574232</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>223774148.479386</v>
+        <v>211577815.26540199</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>62755551.471028</v>
+        <v>61232840.671028003</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>286529699.950414</v>
+        <v>272810655.93642998</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>28652969.9950414</v>
+        <v>30312295.104047775</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24841,35 +24841,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>346415608.93839598</v>
+        <v>363837739.03838599</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>100278354.28778201</v>
+        <v>105136840.68278199</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>446693963.22617799</v>
+        <v>468974579.72116798</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.54789634871625181</v>
+        <v>0.57522483181592388</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>243766762.06160402</v>
+        <v>226344631.96161401</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>124828451.71221799</v>
+        <v>119969965.31721801</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>368595213.77382201</v>
+        <v>346314597.27883202</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>36859521.377382204</v>
+        <v>38479399.697648004</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>147569605.5</v>
+        <v>148159605.5</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -24901,15 +24901,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>147569605.5</v>
+        <v>148159605.5</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.61112191308894692</v>
+        <v>0.61356524772754562</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>93903662.5</v>
+        <v>93313662.5</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -24917,11 +24917,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>93903662.5</v>
+        <v>93313662.5</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>9390366.25</v>
+        <v>10368184.722222222</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24945,35 +24945,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>662518718.73037696</v>
+        <v>705007069.41037703</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>21435775.325116001</v>
+        <v>21729775.325116001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>683954494.055493</v>
+        <v>726736844.73549306</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.94188587083733522</v>
+        <v>1.0008022051504053</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>-16806246.730376959</v>
+        <v>-59294597.410377026</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>59006072.674883999</v>
+        <v>58712072.674883999</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>42199825.944507003</v>
+        <v>-582524.73549306393</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>4219982.5944507001</v>
+        <v>-64724.970610340439</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>197164413.23962</v>
+        <v>221038287.23952001</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25005,15 +25005,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>243398838.44962001</v>
+        <v>267272712.44952002</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.4129335757065139</v>
+        <v>0.45343633331842426</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>311754418.76038003</v>
+        <v>287880544.76047999</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25021,11 +25021,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>346039397.55037999</v>
+        <v>322165523.55048001</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>34603939.755038001</v>
+        <v>35796169.28338667</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25049,35 +25049,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>309996006.31993097</v>
+        <v>349386455.89393097</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>66721502.592804</v>
+        <v>73162448.542796999</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>376717508.91273499</v>
+        <v>422548904.436728</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.72138723274821381</v>
+        <v>0.80915109507960581</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>130067277.68006903</v>
+        <v>90676828.106069028</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>15427822.407196</v>
+        <v>8986876.4572030008</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>145495100.08726501</v>
+        <v>99663704.563271999</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>14549510.008726502</v>
+        <v>11073744.951474667</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25101,7 +25101,7 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>617478269.668329</v>
+        <v>643442193.42425799</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
@@ -25109,15 +25109,15 @@
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>670548044.03826499</v>
+        <v>696511967.79419398</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.59750489695766096</v>
+        <v>0.62064055699922183</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>379280075.331671</v>
+        <v>353316151.57574201</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
@@ -25125,11 +25125,11 @@
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>451698898.96173501</v>
+        <v>425734975.20580602</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>45169889.8961735</v>
+        <v>47303886.133978449</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25153,35 +25153,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>311030411.29380202</v>
+        <v>315785433.81379801</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>40365214.659966998</v>
+        <v>45357400.229927003</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>351395625.95376903</v>
+        <v>361142834.04372501</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.55109775397466598</v>
+        <v>0.56638441120415917</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>229256647.70619798</v>
+        <v>224501625.18620199</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>56976211.340033002</v>
+        <v>51984025.770072997</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>286232859.04623097</v>
+        <v>276485650.95627499</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>28623285.904623099</v>
+        <v>30720627.884030554</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>11669018.672000002</v>
+        <v>12965576.302222226</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25257,35 +25257,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>244616959.31193799</v>
+        <v>253946188.583938</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>57732578.010231003</v>
+        <v>58307578.010231003</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>302349537.32216901</v>
+        <v>312253766.59416902</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.49480997275825789</v>
+        <v>0.51101873384873009</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>194400349.68806201</v>
+        <v>185071120.416062</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>114291833.989769</v>
+        <v>113716833.989769</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>308692183.67783099</v>
+        <v>298787954.40583098</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>30869218.367783099</v>
+        <v>33198661.600647885</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25309,35 +25309,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>348878867.74540699</v>
+        <v>363150830.91528499</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>32116601.095465999</v>
+        <v>33421898.395466</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>380995468.840873</v>
+        <v>396572729.31075096</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.50201580829011705</v>
+        <v>0.52254106815612766</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>317750728.25459301</v>
+        <v>303478765.08471501</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>60185020.904533997</v>
+        <v>58879723.604534</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>377935749.159127</v>
+        <v>362358488.68924904</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>37793574.915912703</v>
+        <v>40262054.298805445</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25361,35 +25361,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>213306764.673924</v>
+        <v>227764693.44332999</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>26160548.252498999</v>
+        <v>28954987.892499</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>239467312.92642301</v>
+        <v>256719681.33582899</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.46151946661485344</v>
+        <v>0.4947695322244276</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>208236258.326076</v>
+        <v>193778329.55667001</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>71163627.747501001</v>
+        <v>68369188.107501</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>279399886.07357699</v>
+        <v>262147517.66417101</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>27939988.607357699</v>
+        <v>29127501.962685667</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25413,35 +25413,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>460344503.14619899</v>
+        <v>535720541.19608903</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>68959622.491264999</v>
+        <v>83676379.051064998</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>529304125.63746399</v>
+        <v>619396920.247154</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.53916111881445272</v>
+        <v>0.63093167110399095</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>158006438.85380101</v>
+        <v>82630400.803910971</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>294407343.508735</v>
+        <v>279690586.94893503</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>452413782.36253601</v>
+        <v>362320987.752846</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>45241378.236253604</v>
+        <v>40257887.528094001</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25465,35 +25465,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>113174610.647754</v>
+        <v>119550881.147754</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>107342298.50697801</v>
+        <v>112207163.30689801</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>220516909.15473199</v>
+        <v>231758044.45465201</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.37627292653457528</v>
+        <v>0.3954539267267379</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>181351078.35224599</v>
+        <v>174974807.85224599</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>184187754.49302199</v>
+        <v>179322889.693102</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>365538832.84526801</v>
+        <v>354297697.54534799</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>36553883.284526803</v>
+        <v>39366410.838372</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25515,35 +25515,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>4487847546.0162907</v>
+        <v>4774339059.6212635</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>659491566.33101606</v>
+        <v>701856253.34568894</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>5147339112.3473072</v>
+        <v>5476195312.9669523</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.56759365951498542</v>
+        <v>0.60385641397702416</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>2771431785.9837089</v>
+        <v>2484940272.378736</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1149933492.6689839</v>
+        <v>1107568805.6543112</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>3921365278.6526928</v>
+        <v>3592509078.0330477</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>392136527.8652693</v>
+        <v>399167675.33700532</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25584,8 +25584,7 @@
         <v>68</v>
       </c>
       <c r="D70" s="191">
-        <f>IF(E24="",0,E24)</f>
-        <v>283236802.15987003</v>
+        <v>282012477.75986999</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25596,7 +25595,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="192">
-        <v>53362963</v>
+        <v>69092512.120000005</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25607,7 +25606,7 @@
         <v>176</v>
       </c>
       <c r="D72" s="192">
-        <v>4684684.5599999996</v>
+        <v>7027026.8399999999</v>
       </c>
     </row>
     <row r="73" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25618,7 +25617,7 @@
         <v>72</v>
       </c>
       <c r="D73" s="191">
-        <v>167353423.75</v>
+        <v>183868738.94999999</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25641,7 +25640,7 @@
         <v>74</v>
       </c>
       <c r="D75" s="192">
-        <v>26026603.300000001</v>
+        <v>29615792.469999999</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25652,7 +25651,7 @@
         <v>77</v>
       </c>
       <c r="D76" s="192">
-        <v>1036310110.97997</v>
+        <v>1041553354.17997</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25663,7 +25662,7 @@
         <v>79</v>
       </c>
       <c r="D77" s="191">
-        <v>188358696.12956899</v>
+        <v>194304641.98956901</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25685,8 +25684,7 @@
         <v>81</v>
       </c>
       <c r="D79" s="192">
-        <f>IF(E11="",0,E11)</f>
-        <v>2660360.36</v>
+        <v>2984684.68</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25697,7 +25695,7 @@
         <v>83</v>
       </c>
       <c r="D80" s="191">
-        <v>395037573.40962303</v>
+        <v>423372709.03955197</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25708,7 +25706,7 @@
         <v>85</v>
       </c>
       <c r="D81" s="192">
-        <v>107116249.56999999</v>
+        <v>111327060.09</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25719,7 +25717,7 @@
         <v>87</v>
       </c>
       <c r="D82" s="192">
-        <v>7244865.0549999997</v>
+        <v>10017838.105</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25730,7 +25728,6 @@
         <v>89</v>
       </c>
       <c r="D83" s="192">
-        <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
         <v>50389190.140000001</v>
       </c>
     </row>
@@ -25741,7 +25738,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>2331937648.2740316</v>
+        <v>2415722152.2239609</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25755,13 +25752,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25803,19 +25800,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>123410301.225152</v>
+        <v>141618940.424932</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.43221399576511171</v>
+        <v>0.49598524198890898</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>162120251.77484798</v>
+        <v>143911612.575068</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>16212025.177484799</v>
+        <v>15990179.175007556</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25832,19 +25829,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>170230619.19855502</v>
+        <v>191802511.778543</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.39696392238719419</v>
+        <v>0.4472678167875262</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>258600842.80144498</v>
+        <v>237028950.221457</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>25860084.280144498</v>
+        <v>26336550.024606332</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25861,19 +25858,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>561014901.67797804</v>
+        <v>584648207.72793794</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.50248132946799551</v>
+        <v>0.5236488510582229</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>555474147.32202196</v>
+        <v>531840841.27206206</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>55547414.732202195</v>
+        <v>59093426.808006898</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25946,24 +25943,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>854655822.10168505</v>
+        <v>918069659.93141294</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.46680794462573777</v>
+        <v>0.50144420700482106</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>976195241.89831495</v>
+        <v>912781404.06858706</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>97619524.189831495</v>
+        <v>101420156.00762078</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25971,11 +25973,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26748,10 +26745,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -26778,7 +26775,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26813,7 +26810,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27812,13 +27809,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28021,6 +28018,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28028,11 +28030,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 20 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 22 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1928,6 +1928,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1947,15 +1956,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3600,10 +3600,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4664,13 +4664,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4873,11 +4873,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4885,6 +4880,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5657,10 +5657,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6721,13 +6721,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6930,11 +6930,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6942,6 +6937,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7714,10 +7714,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8778,13 +8778,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8987,11 +8987,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8999,6 +8994,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9771,10 +9771,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10835,13 +10835,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11044,11 +11044,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11056,6 +11051,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11827,10 +11827,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12877,13 +12877,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13086,11 +13086,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13098,6 +13093,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22338,11 +22338,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="246" t="s">
+      <c r="B41" s="239" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="247"/>
-      <c r="D41" s="248"/>
+      <c r="C41" s="240"/>
+      <c r="D41" s="241"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>70310453.356845215</v>
+        <v>79099260.026450872</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22431,7 +22431,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>61731925.524076752</v>
+        <v>69448416.214586347</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22460,7 +22460,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>12196946.082190301</v>
+        <v>13721564.342464089</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22487,7 +22487,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>144239324.96311226</v>
+        <v>162269240.58350131</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22508,10 +22508,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22573,7 +22573,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>16882680.369618144</v>
+        <v>18993015.415820412</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>15105514.998585556</v>
+        <v>16993704.37340875</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>4878380.2444444429</v>
+        <v>5488177.7749999985</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22780,7 +22780,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-4483189.7206696803</v>
+        <v>-5043588.4357533902</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>14532708.623502903</v>
+        <v>16349297.201440766</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>8965278.2727715168</v>
+        <v>10085938.056867957</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-2790792.8520821729</v>
+        <v>-3139641.9585924447</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22988,7 +22988,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>12312714.248365561</v>
+        <v>13851803.529411256</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>11512460.018891666</v>
+        <v>12951517.521253124</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>8401327.5174755976</v>
+        <v>9451493.4571600482</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23144,7 +23144,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>19692906.378430918</v>
+        <v>22154519.675734781</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>13152703.129130317</v>
+        <v>14796791.020271607</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>3845075.8847772679</v>
+        <v>4325710.3703744262</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>10034611.767680041</v>
+        <v>11288938.238640048</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>132042378.88092208</v>
+        <v>148547676.24103734</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23572,13 +23572,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-1484775.3240302736</v>
+        <v>-1670372.2395340577</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-2058831.4153202707</v>
+        <v>-2316185.3422353044</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23690,7 +23690,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>15740552.821540859</v>
+        <v>17708121.924233466</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23775,17 +23775,12 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>12196946.082190314</v>
+        <v>13721564.342464104</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23793,6 +23788,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23861,7 +23861,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23943,11 +23943,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>240105662.73459801</v>
+        <v>254247035.77657601</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>40597582.328971997</v>
+        <v>42097257.998971999</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23965,11 +23965,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>363837739.03838599</v>
+        <v>379189288.75834596</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>105136840.68278199</v>
+        <v>112509187.672746</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23977,27 +23977,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>227764693.44332999</v>
+        <v>239547739.734368</v>
       </c>
       <c r="D10" s="205">
-        <v>28954987.892499</v>
+        <v>29458987.892499</v>
       </c>
       <c r="E10" s="205">
-        <v>111327060.09</v>
+        <v>116563996.94</v>
       </c>
       <c r="F10" s="205">
-        <v>368046741.42582899</v>
+        <v>385570724.56686699</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>705007069.41037703</v>
+        <v>734162511.56037199</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>21729775.325116001</v>
+        <v>22337883.425106</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24005,23 +24005,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>253946188.583938</v>
+        <v>261706349.523938</v>
       </c>
       <c r="D11" s="205">
-        <v>58307578.010231003</v>
+        <v>61268244.690229997</v>
       </c>
       <c r="E11" s="205">
         <v>2984684.68</v>
       </c>
       <c r="F11" s="205">
-        <v>315238451.27416903</v>
+        <v>325959278.89416802</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>221038287.23952001</v>
+        <v>252074323.43939</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24033,27 +24033,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>192439032.166473</v>
+        <v>195191978.09645799</v>
       </c>
       <c r="D12" s="205">
-        <v>61990485.422967002</v>
+        <v>68117183.762931004</v>
       </c>
       <c r="E12" s="205">
         <v>44660102.520000003</v>
       </c>
       <c r="F12" s="205">
-        <v>299089620.10944003</v>
+        <v>307969264.37938899</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>349386455.89393097</v>
+        <v>378215569.01279998</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>73162448.542796999</v>
+        <v>79275448.542796999</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24061,27 +24061,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>171398706.87191299</v>
+        <v>183997310.661888</v>
       </c>
       <c r="D13" s="205">
-        <v>43146355.259815</v>
+        <v>44392003.909814999</v>
       </c>
       <c r="E13" s="205">
-        <v>24432409.600000001</v>
+        <v>25873851</v>
       </c>
       <c r="F13" s="205">
-        <v>238977471.73172799</v>
+        <v>254263165.57170299</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>643442193.42425799</v>
+        <v>683565535.57919395</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>53069774.369935997</v>
+        <v>54203774.369935997</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24089,27 +24089,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>705007069.41037703</v>
+        <v>734162511.56037199</v>
       </c>
       <c r="D14" s="205">
-        <v>21729775.325116001</v>
+        <v>22337883.425106</v>
       </c>
       <c r="E14" s="205">
-        <v>183868738.94999999</v>
+        <v>192728793.15000001</v>
       </c>
       <c r="F14" s="205">
-        <v>910605583.68549299</v>
+        <v>949229188.13547802</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>315785433.81379801</v>
+        <v>331299755.438191</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>45357400.229927003</v>
+        <v>48709000.229927003</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24125,11 +24125,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>253946188.583938</v>
+        <v>261706349.523938</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>58307578.010231003</v>
+        <v>61268244.690229997</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24137,27 +24137,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>349386455.89393097</v>
+        <v>378215569.01279998</v>
       </c>
       <c r="D16" s="205">
-        <v>73162448.542796999</v>
+        <v>79275448.542796999</v>
       </c>
       <c r="E16" s="205">
-        <v>29615792.469999999</v>
+        <v>29545792.469999999</v>
       </c>
       <c r="F16" s="205">
-        <v>452164696.90672803</v>
+        <v>487036810.02559698</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>363150830.91528499</v>
+        <v>387876799.67017603</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>33421898.395466</v>
+        <v>33922249.765463002</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24165,7 +24165,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>221038287.23952001</v>
+        <v>252074323.43939</v>
       </c>
       <c r="D17" s="205">
         <v>46234425.210000001</v>
@@ -24174,18 +24174,18 @@
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>267272712.44951999</v>
+        <v>298308748.64938998</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>227764693.44332999</v>
+        <v>239547739.734368</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>28954987.892499</v>
+        <v>29458987.892499</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24193,7 +24193,7 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>366037115.42803103</v>
+        <v>368789358.66303098</v>
       </c>
       <c r="D18" s="205">
         <v>3110178.4299920001</v>
@@ -24202,18 +24202,18 @@
         <v>7148648.5599999996</v>
       </c>
       <c r="F18" s="205">
-        <v>376295942.41802299</v>
+        <v>379048185.653023</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>535720541.19608903</v>
+        <v>573076262.17522895</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>83676379.051064998</v>
+        <v>93927199.401954994</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24221,27 +24221,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>643442193.42425799</v>
+        <v>683565535.57919395</v>
       </c>
       <c r="D19" s="205">
-        <v>53069774.369935997</v>
+        <v>54203774.369935997</v>
       </c>
       <c r="E19" s="205">
-        <v>1041553354.17997</v>
+        <v>1083282108.97997</v>
       </c>
       <c r="F19" s="205">
-        <v>1738065321.974164</v>
+        <v>1821051418.9291</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>119550881.147754</v>
+        <v>126517503.207634</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>112207163.30689801</v>
+        <v>113941217.366872</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24249,16 +24249,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>82751411.147753999</v>
+        <v>89718033.207634002</v>
       </c>
       <c r="D20" s="205">
-        <v>20773286.339760002</v>
+        <v>21291124.199754</v>
       </c>
       <c r="E20" s="205">
         <v>8237838</v>
       </c>
       <c r="F20" s="205">
-        <v>111762535.487514</v>
+        <v>119246995.407388</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24279,20 +24279,20 @@
         <v>36799470</v>
       </c>
       <c r="D21" s="205">
-        <v>91433876.967138007</v>
+        <v>92650093.167117998</v>
       </c>
       <c r="E21" s="205">
         <v>42151352.140000001</v>
       </c>
       <c r="F21" s="205">
-        <v>170384699.10713801</v>
+        <v>171600915.307118</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>584648207.72793794</v>
+        <v>647335150.44178498</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24323,7 +24323,7 @@
         <v>173</v>
       </c>
       <c r="C23" s="205">
-        <v>287443477.27999997</v>
+        <v>304039806.38</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>168</v>
@@ -24332,7 +24332,7 @@
         <v>10156125.859999999</v>
       </c>
       <c r="F23" s="205">
-        <v>297599603.13999999</v>
+        <v>314195932.24000001</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24343,16 +24343,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>240105662.73459801</v>
+        <v>254247035.77657601</v>
       </c>
       <c r="D24" s="205">
-        <v>40597582.328971997</v>
+        <v>42097257.998971999</v>
       </c>
       <c r="E24" s="205">
-        <v>282012477.75986999</v>
+        <v>287387072.25986999</v>
       </c>
       <c r="F24" s="205">
-        <v>562715722.82343996</v>
+        <v>583731366.03541803</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24363,16 +24363,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>315785433.81379801</v>
+        <v>331299755.438191</v>
       </c>
       <c r="D25" s="205">
-        <v>45357400.229927003</v>
+        <v>48709000.229927003</v>
       </c>
       <c r="E25" s="205">
-        <v>194304641.98956901</v>
+        <v>214528065.81951401</v>
       </c>
       <c r="F25" s="205">
-        <v>555447476.03329396</v>
+        <v>594536821.48763204</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24383,16 +24383,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>363150830.91528499</v>
+        <v>387876799.67017603</v>
       </c>
       <c r="D26" s="205">
-        <v>33421898.395466</v>
+        <v>33922249.765463002</v>
       </c>
       <c r="E26" s="205">
-        <v>423372709.03955197</v>
+        <v>443193790.22955197</v>
       </c>
       <c r="F26" s="205">
-        <v>819945438.35030305</v>
+        <v>864992839.66519105</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24403,16 +24403,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>535720541.19608903</v>
+        <v>573076262.17522895</v>
       </c>
       <c r="D27" s="205">
-        <v>83676379.051064998</v>
+        <v>93927199.401954994</v>
       </c>
       <c r="E27" s="205">
-        <v>10017838.105</v>
+        <v>10504324.605</v>
       </c>
       <c r="F27" s="205">
-        <v>629414758.35215402</v>
+        <v>677507786.18218398</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24455,7 +24455,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>141618940.424932</v>
+        <v>145181643.14490199</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24466,7 +24466,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>191802511.778543</v>
+        <v>218811764.803516</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24477,7 +24477,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>115492351.307092</v>
+        <v>119458756.82158899</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24488,7 +24488,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>468744856.42084599</v>
+        <v>527465393.62019598</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24540,7 +24540,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.66666666666666663</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24583,19 +24583,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>4774339059.6212635</v>
+        <v>5053678085.7562141</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.65768774574843203</v>
+        <v>0.69616801539497697</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>2484940272.3787365</v>
+        <v>2205601246.2437859</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>276104474.70874852</v>
+        <v>275700155.78047323</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24612,19 +24612,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>701856253.34568894</v>
+        <v>737884876.56650293</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.38788909761953777</v>
+        <v>0.40780073918855952</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1107568805.6543112</v>
+        <v>1071540182.4334971</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>123063200.6282568</v>
+        <v>133942522.80418713</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24641,19 +24641,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>918069659.93141294</v>
+        <v>1011328558.390203</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.50144420700482106</v>
+        <v>0.55238166461267268</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>912781404.06858706</v>
+        <v>819522505.609797</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>101420156.00762078</v>
+        <v>102440313.20122463</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24668,19 +24668,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>6394264972.898365</v>
+        <v>6802891520.7129192</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.58665374008121551</v>
+        <v>0.62414394319102251</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>4505290482.101635</v>
+        <v>4096663934.2870798</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>500587831.34462613</v>
+        <v>512082991.78588498</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24701,10 +24701,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24789,35 +24789,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>240105662.73459801</v>
+        <v>254247035.77657601</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>40597582.328971997</v>
+        <v>42097257.998971999</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>280703245.06357002</v>
+        <v>296344293.77554798</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.50712953108574232</v>
+        <v>0.53538726532461189</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>211577815.26540199</v>
+        <v>197436442.22342399</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>61232840.671028003</v>
+        <v>59733165.001028001</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>272810655.93642998</v>
+        <v>257169607.22445202</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>30312295.104047775</v>
+        <v>32146200.903056502</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24841,35 +24841,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>363837739.03838599</v>
+        <v>379189288.75834596</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>105136840.68278199</v>
+        <v>112509187.672746</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>468974579.72116798</v>
+        <v>491698476.43109196</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.57522483181592388</v>
+        <v>0.60309702410178312</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>226344631.96161401</v>
+        <v>210993082.24165404</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>119969965.31721801</v>
+        <v>112597618.327254</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>346314597.27883202</v>
+        <v>323590700.56890804</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>38479399.697648004</v>
+        <v>40448837.571113504</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24921,7 +24921,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>10368184.722222222</v>
+        <v>11664207.8125</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24945,35 +24945,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>705007069.41037703</v>
+        <v>734162511.56037199</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>21729775.325116001</v>
+        <v>22337883.425106</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>726736844.73549306</v>
+        <v>756500394.98547804</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>1.0008022051504053</v>
+        <v>1.0417901183669582</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>-59294597.410377026</v>
+        <v>-88450039.560371995</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>58712072.674883999</v>
+        <v>58103964.574893996</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>-582524.73549306393</v>
+        <v>-30346074.985478044</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-64724.970610340439</v>
+        <v>-3793259.3731847554</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>221038287.23952001</v>
+        <v>252074323.43939</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25005,15 +25005,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>267272712.44952002</v>
+        <v>298308748.64938998</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.45343633331842426</v>
+        <v>0.50608991821390759</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>287880544.76047999</v>
+        <v>256844508.56061</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25021,11 +25021,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>322165523.55048001</v>
+        <v>291129487.35061002</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>35796169.28338667</v>
+        <v>36391185.918826252</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25049,35 +25049,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>349386455.89393097</v>
+        <v>378215569.01279998</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>73162448.542796999</v>
+        <v>79275448.542796999</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>422548904.436728</v>
+        <v>457491017.55559695</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.80915109507960581</v>
+        <v>0.87606275618595209</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>90676828.106069028</v>
+        <v>61847714.987200022</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>8986876.4572030008</v>
+        <v>2873876.4572030008</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>99663704.563271999</v>
+        <v>64721591.444403052</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>11073744.951474667</v>
+        <v>8090198.9305503815</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25101,35 +25101,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>643442193.42425799</v>
+        <v>683565535.57919395</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>53069774.369935997</v>
+        <v>54203774.369935997</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>696511967.79419398</v>
+        <v>737769309.94912994</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.62064055699922183</v>
+        <v>0.65740371542195408</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>353316151.57574201</v>
+        <v>313192809.42080605</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>72418823.630064011</v>
+        <v>71284823.630064011</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>425734975.20580602</v>
+        <v>384477633.05087006</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>47303886.133978449</v>
+        <v>48059704.131358758</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25153,35 +25153,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>315785433.81379801</v>
+        <v>331299755.438191</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>45357400.229927003</v>
+        <v>48709000.229927003</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>361142834.04372501</v>
+        <v>380008755.668118</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.56638441120415917</v>
+        <v>0.59597205050856217</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>224501625.18620199</v>
+        <v>208987303.561809</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>51984025.770072997</v>
+        <v>48632425.770072997</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>276485650.95627499</v>
+        <v>257619729.331882</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>30720627.884030554</v>
+        <v>32202466.16648525</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>287443477.27999997</v>
+        <v>304039806.38</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25213,15 +25213,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>287443477.27999997</v>
+        <v>304039806.38</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.7112584347341081</v>
+        <v>0.75232487036764151</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>116690186.72000003</v>
+        <v>100093857.62</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25229,11 +25229,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>116690186.72000003</v>
+        <v>100093857.62</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>12965576.302222226</v>
+        <v>12511732.202500001</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25257,35 +25257,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>253946188.583938</v>
+        <v>261706349.523938</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>58307578.010231003</v>
+        <v>61268244.690229997</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>312253766.59416902</v>
+        <v>322974594.21416801</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.51101873384873009</v>
+        <v>0.52856389852660812</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>185071120.416062</v>
+        <v>177310959.476062</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>113716833.989769</v>
+        <v>110756167.30977</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>298787954.40583098</v>
+        <v>288067126.78583199</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>33198661.600647885</v>
+        <v>36008390.848228998</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25309,35 +25309,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>363150830.91528499</v>
+        <v>387876799.67017603</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>33421898.395466</v>
+        <v>33922249.765463002</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>396572729.31075096</v>
+        <v>421799049.43563902</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.52254106815612766</v>
+        <v>0.5557803387600786</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>303478765.08471501</v>
+        <v>278752796.32982397</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>58879723.604534</v>
+        <v>58379372.234536998</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>362358488.68924904</v>
+        <v>337132168.56436098</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>40262054.298805445</v>
+        <v>42141521.070545122</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25361,35 +25361,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>227764693.44332999</v>
+        <v>239547739.734368</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>28954987.892499</v>
+        <v>29458987.892499</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>256719681.33582899</v>
+        <v>269006727.626867</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.4947695322244276</v>
+        <v>0.51845005455214177</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>193778329.55667001</v>
+        <v>181995283.265632</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>68369188.107501</v>
+        <v>67865188.107501</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>262147517.66417101</v>
+        <v>249860471.373133</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>29127501.962685667</v>
+        <v>31232558.921641625</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25413,35 +25413,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>535720541.19608903</v>
+        <v>573076262.17522895</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>83676379.051064998</v>
+        <v>93927199.401954994</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>619396920.247154</v>
+        <v>667003461.57718396</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.63093167110399095</v>
+        <v>0.67942476768711846</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>82630400.803910971</v>
+        <v>45274679.824771047</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>279690586.94893503</v>
+        <v>269439766.59804499</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>362320987.752846</v>
+        <v>314714446.42281604</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>40257887.528094001</v>
+        <v>39339305.802852005</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25465,35 +25465,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>119550881.147754</v>
+        <v>126517503.207634</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>112207163.30689801</v>
+        <v>113941217.366872</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>231758044.45465201</v>
+        <v>240458720.57450598</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.3954539267267379</v>
+        <v>0.41030008468802953</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>174974807.85224599</v>
+        <v>168008185.792366</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>179322889.693102</v>
+        <v>177588835.63312799</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>354297697.54534799</v>
+        <v>345597021.42549402</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>39366410.838372</v>
+        <v>43199627.678186752</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25515,35 +25515,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>4774339059.6212635</v>
+        <v>5053678085.7562141</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>701856253.34568894</v>
+        <v>737884876.56650293</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>5476195312.9669523</v>
+        <v>5791562962.3227177</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.60385641397702416</v>
+        <v>0.63863179486481048</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>2484940272.378736</v>
+        <v>2205601246.2437859</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1107568805.6543112</v>
+        <v>1071540182.433497</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>3592509078.0330477</v>
+        <v>3277141428.6772833</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>399167675.33700532</v>
+        <v>409642678.58466041</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25584,7 +25584,7 @@
         <v>68</v>
       </c>
       <c r="D70" s="191">
-        <v>282012477.75986999</v>
+        <v>287387072.25986999</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25595,7 +25595,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="192">
-        <v>69092512.120000005</v>
+        <v>70533953.520000011</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25617,7 +25617,7 @@
         <v>72</v>
       </c>
       <c r="D73" s="191">
-        <v>183868738.94999999</v>
+        <v>192728793.15000001</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25640,7 +25640,7 @@
         <v>74</v>
       </c>
       <c r="D75" s="192">
-        <v>29615792.469999999</v>
+        <v>29545792.469999999</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25651,7 +25651,7 @@
         <v>77</v>
       </c>
       <c r="D76" s="192">
-        <v>1041553354.17997</v>
+        <v>1083282108.97997</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25662,7 +25662,7 @@
         <v>79</v>
       </c>
       <c r="D77" s="191">
-        <v>194304641.98956901</v>
+        <v>214528065.81951401</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25695,7 +25695,7 @@
         <v>83</v>
       </c>
       <c r="D80" s="191">
-        <v>423372709.03955197</v>
+        <v>443193790.22955197</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25706,7 +25706,7 @@
         <v>85</v>
       </c>
       <c r="D81" s="192">
-        <v>111327060.09</v>
+        <v>116563996.94</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25717,7 +25717,7 @@
         <v>87</v>
       </c>
       <c r="D82" s="192">
-        <v>10017838.105</v>
+        <v>10504324.605</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25738,7 +25738,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>2415722152.2239609</v>
+        <v>2518824925.493906</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25752,13 +25752,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25800,19 +25800,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>141618940.424932</v>
+        <v>145181643.14490199</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.49598524198890898</v>
+        <v>0.50846272533539338</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>143911612.575068</v>
+        <v>140348909.85509801</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>15990179.175007556</v>
+        <v>17543613.731887251</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25829,19 +25829,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>191802511.778543</v>
+        <v>218811764.803516</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.4472678167875262</v>
+        <v>0.51025119235191752</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>237028950.221457</v>
+        <v>210019697.196484</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>26336550.024606332</v>
+        <v>26252462.1495605</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25858,19 +25858,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>584648207.72793794</v>
+        <v>647335150.44178498</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.5236488510582229</v>
+        <v>0.57979534239192076</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>531840841.27206206</v>
+        <v>469153898.55821502</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>59093426.808006898</v>
+        <v>58644237.319776878</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25943,29 +25943,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>918069659.93141294</v>
+        <v>1011328558.390203</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.50144420700482106</v>
+        <v>0.55238166461267268</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>912781404.06858706</v>
+        <v>819522505.609797</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>101420156.00762078</v>
+        <v>102440313.20122463</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25973,6 +25968,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26745,10 +26745,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -26775,7 +26775,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26810,7 +26810,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27809,13 +27809,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28018,11 +28018,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28030,6 +28025,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 22 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 23 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1928,15 +1928,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1957,6 +1948,18 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3600,10 +3603,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -3630,7 +3633,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3665,7 +3668,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4664,13 +4667,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4873,6 +4876,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4880,11 +4888,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5657,10 +5660,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -5687,7 +5690,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5722,7 +5725,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6721,13 +6724,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6930,6 +6933,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6937,11 +6945,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7714,10 +7717,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -7744,7 +7747,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7779,7 +7782,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8778,13 +8781,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8987,6 +8990,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8994,11 +9002,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9771,10 +9774,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -9801,7 +9804,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9836,7 +9839,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10835,13 +10838,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11044,6 +11047,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11051,11 +11059,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11827,10 +11830,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -11857,7 +11860,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11892,7 +11895,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12877,13 +12880,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13086,6 +13089,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13093,11 +13101,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21665,7 +21668,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22338,11 +22341,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="239" t="s">
+      <c r="B41" s="246" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="240"/>
-      <c r="D41" s="241"/>
+      <c r="C41" s="247"/>
+      <c r="D41" s="248"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22402,7 +22405,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>79099260.026450872</v>
+        <v>90399154.315943852</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22431,7 +22434,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>69448416.214586347</v>
+        <v>79369618.530955821</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22460,7 +22463,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>13721564.342464089</v>
+        <v>15681787.819958959</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22487,7 +22490,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>162269240.58350131</v>
+        <v>185450560.66685864</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22508,10 +22511,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -22538,7 +22541,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22573,7 +22576,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22624,7 +22627,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>18993015.415820412</v>
+        <v>21706303.332366187</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22676,7 +22679,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>16993704.37340875</v>
+        <v>19421376.426752858</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22728,7 +22731,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>5488177.7749999985</v>
+        <v>6272203.1714285696</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22780,7 +22783,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-5043588.4357533902</v>
+        <v>-5764101.0694324458</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22832,7 +22835,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>16349297.201440766</v>
+        <v>18684911.087360878</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22884,7 +22887,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>10085938.056867957</v>
+        <v>11526786.350706236</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22936,7 +22939,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-3139641.9585924447</v>
+        <v>-3588162.2383913654</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22988,7 +22991,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>13851803.529411256</v>
+        <v>15830632.605041435</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23040,7 +23043,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>12951517.521253124</v>
+        <v>14801734.310003569</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23092,7 +23095,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>9451493.4571600482</v>
+        <v>10801706.808182912</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23144,7 +23147,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>22154519.675734781</v>
+        <v>25319451.057982605</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23196,7 +23199,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>14796791.020271607</v>
+        <v>16910618.308881838</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23248,7 +23251,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>4325710.3703744262</v>
+        <v>4943668.9947136296</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23300,7 +23303,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>11288938.238640048</v>
+        <v>12901643.701302912</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23350,7 +23353,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>148547676.24103734</v>
+        <v>169768772.84689981</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23572,13 +23575,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23632,7 +23635,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-1670372.2395340577</v>
+        <v>-1908996.8451817802</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23661,7 +23664,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-2316185.3422353044</v>
+        <v>-2647068.9625546336</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23690,7 +23693,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>17708121.924233466</v>
+        <v>20237853.627695389</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23775,12 +23778,17 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>13721564.342464104</v>
+        <v>15681787.819958976</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23788,11 +23796,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23861,7 +23864,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23943,11 +23946,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>254247035.77657601</v>
+        <v>269228327.14556301</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>42097257.998971999</v>
+        <v>45580726.018472001</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23965,11 +23968,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>379189288.75834596</v>
+        <v>413715743.12521899</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>112509187.672746</v>
+        <v>116164090.418745</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23977,27 +23980,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>239547739.734368</v>
+        <v>248297316.40555099</v>
       </c>
       <c r="D10" s="205">
         <v>29458987.892499</v>
       </c>
       <c r="E10" s="205">
-        <v>116563996.94</v>
+        <v>124077510.04000001</v>
       </c>
       <c r="F10" s="205">
-        <v>385570724.56686699</v>
+        <v>401833814.33805001</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>734162511.56037199</v>
+        <v>779465004.640347</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>22337883.425106</v>
+        <v>23195396.925105002</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24005,16 +24008,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>261706349.523938</v>
+        <v>270823037.35390502</v>
       </c>
       <c r="D11" s="205">
-        <v>61268244.690229997</v>
+        <v>75385183.480155006</v>
       </c>
       <c r="E11" s="205">
         <v>2984684.68</v>
       </c>
       <c r="F11" s="205">
-        <v>325959278.89416802</v>
+        <v>349192905.51406002</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -24025,7 +24028,7 @@
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>46234425.210000001</v>
+        <v>49801992.810000002</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -24033,27 +24036,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>195191978.09645799</v>
+        <v>213662463.846358</v>
       </c>
       <c r="D12" s="205">
-        <v>68117183.762931004</v>
+        <v>71573888.308929995</v>
       </c>
       <c r="E12" s="205">
         <v>44660102.520000003</v>
       </c>
       <c r="F12" s="205">
-        <v>307969264.37938899</v>
+        <v>329896454.67528802</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>378215569.01279998</v>
+        <v>388335116.82376301</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>79275448.542796999</v>
+        <v>80188962.052796006</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24061,27 +24064,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>183997310.661888</v>
+        <v>200053279.27886099</v>
       </c>
       <c r="D13" s="205">
-        <v>44392003.909814999</v>
+        <v>44590202.109815001</v>
       </c>
       <c r="E13" s="205">
-        <v>25873851</v>
+        <v>29747724.800000001</v>
       </c>
       <c r="F13" s="205">
-        <v>254263165.57170299</v>
+        <v>274391206.188676</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>683565535.57919395</v>
+        <v>723607416.51107204</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>54203774.369935997</v>
+        <v>55233572.569936</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24089,27 +24092,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>734162511.56037199</v>
+        <v>779465004.640347</v>
       </c>
       <c r="D14" s="205">
-        <v>22337883.425106</v>
+        <v>23195396.925105002</v>
       </c>
       <c r="E14" s="205">
-        <v>192728793.15000001</v>
+        <v>207802666.91</v>
       </c>
       <c r="F14" s="205">
-        <v>949229188.13547802</v>
+        <v>1010463068.4754519</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>331299755.438191</v>
+        <v>346950683.470164</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>48709000.229927003</v>
+        <v>49437708.359926999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24125,11 +24128,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>261706349.523938</v>
+        <v>270823037.35390502</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>61268244.690229997</v>
+        <v>75385183.480155006</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24137,27 +24140,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>378215569.01279998</v>
+        <v>388335116.82376301</v>
       </c>
       <c r="D16" s="205">
-        <v>79275448.542796999</v>
+        <v>80188962.052796006</v>
       </c>
       <c r="E16" s="205">
-        <v>29545792.469999999</v>
+        <v>30956603.27</v>
       </c>
       <c r="F16" s="205">
-        <v>487036810.02559698</v>
+        <v>499480682.146559</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>387876799.67017603</v>
+        <v>412833801.89116597</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>33922249.765463002</v>
+        <v>36896596.625460997</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24168,20 +24171,20 @@
         <v>252074323.43939</v>
       </c>
       <c r="D17" s="205">
-        <v>46234425.210000001</v>
+        <v>49801992.810000002</v>
       </c>
       <c r="E17" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>298308748.64938998</v>
+        <v>301876316.24939001</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>239547739.734368</v>
+        <v>248297316.40555099</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
@@ -24193,27 +24196,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>368789358.66303098</v>
+        <v>398631172.90298897</v>
       </c>
       <c r="D18" s="205">
-        <v>3110178.4299920001</v>
+        <v>3209277.5299920002</v>
       </c>
       <c r="E18" s="205">
-        <v>7148648.5599999996</v>
+        <v>8770270.1600000001</v>
       </c>
       <c r="F18" s="205">
-        <v>379048185.653023</v>
+        <v>410610720.59298098</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>573076262.17522895</v>
+        <v>618235789.38517201</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>93927199.401954994</v>
+        <v>99871780.521954998</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24221,27 +24224,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>683565535.57919395</v>
+        <v>723607416.51107204</v>
       </c>
       <c r="D19" s="205">
-        <v>54203774.369935997</v>
+        <v>55233572.569936</v>
       </c>
       <c r="E19" s="205">
-        <v>1083282108.97997</v>
+        <v>1130760398.3099501</v>
       </c>
       <c r="F19" s="205">
-        <v>1821051418.9291</v>
+        <v>1909601387.3909581</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>126517503.207634</v>
+        <v>139756959.957582</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>113941217.366872</v>
+        <v>115552929.046872</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24249,7 +24252,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>89718033.207634002</v>
+        <v>96439159.457581997</v>
       </c>
       <c r="D20" s="205">
         <v>21291124.199754</v>
@@ -24258,7 +24261,7 @@
         <v>8237838</v>
       </c>
       <c r="F20" s="205">
-        <v>119246995.407388</v>
+        <v>125968121.657336</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24276,23 +24279,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>36799470</v>
+        <v>43317800.5</v>
       </c>
       <c r="D21" s="205">
-        <v>92650093.167117998</v>
+        <v>94261804.847118005</v>
       </c>
       <c r="E21" s="205">
         <v>42151352.140000001</v>
       </c>
       <c r="F21" s="205">
-        <v>171600915.307118</v>
+        <v>179730957.48711801</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>647335150.44178498</v>
+        <v>693872984.94133496</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24303,7 +24306,7 @@
         <v>172</v>
       </c>
       <c r="C22" s="205">
-        <v>148159605.5</v>
+        <v>174731592.19999999</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>168</v>
@@ -24312,7 +24315,7 @@
         <v>7027026.8399999999</v>
       </c>
       <c r="F22" s="205">
-        <v>155186632.34</v>
+        <v>181758619.03999999</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24323,16 +24326,16 @@
         <v>173</v>
       </c>
       <c r="C23" s="205">
-        <v>304039806.38</v>
+        <v>326729714.68000001</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>168</v>
       </c>
       <c r="E23" s="205">
-        <v>10156125.859999999</v>
+        <v>12750720.380000001</v>
       </c>
       <c r="F23" s="205">
-        <v>314195932.24000001</v>
+        <v>339480435.06</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24343,16 +24346,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>254247035.77657601</v>
+        <v>269228327.14556301</v>
       </c>
       <c r="D24" s="205">
-        <v>42097257.998971999</v>
+        <v>45580726.018472001</v>
       </c>
       <c r="E24" s="205">
-        <v>287387072.25986999</v>
+        <v>288489774.95986998</v>
       </c>
       <c r="F24" s="205">
-        <v>583731366.03541803</v>
+        <v>603298828.12390494</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24363,16 +24366,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>331299755.438191</v>
+        <v>346950683.470164</v>
       </c>
       <c r="D25" s="205">
-        <v>48709000.229927003</v>
+        <v>49437708.359926999</v>
       </c>
       <c r="E25" s="205">
-        <v>214528065.81951401</v>
+        <v>226582120.10947901</v>
       </c>
       <c r="F25" s="205">
-        <v>594536821.48763204</v>
+        <v>622970511.93956995</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24383,16 +24386,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>387876799.67017603</v>
+        <v>412833801.89116597</v>
       </c>
       <c r="D26" s="205">
-        <v>33922249.765463002</v>
+        <v>36896596.625460997</v>
       </c>
       <c r="E26" s="205">
-        <v>443193790.22955197</v>
+        <v>482561357.99949998</v>
       </c>
       <c r="F26" s="205">
-        <v>864992839.66519105</v>
+        <v>932291756.51612699</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24403,16 +24406,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>573076262.17522895</v>
+        <v>618235789.38517201</v>
       </c>
       <c r="D27" s="205">
-        <v>93927199.401954994</v>
+        <v>99871780.521954998</v>
       </c>
       <c r="E27" s="205">
-        <v>10504324.605</v>
+        <v>15485405.749</v>
       </c>
       <c r="F27" s="205">
-        <v>677507786.18218398</v>
+        <v>733592975.65612698</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24455,7 +24458,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>145181643.14490199</v>
+        <v>164073143.30486599</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24466,7 +24469,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>218811764.803516</v>
+        <v>232240413.76351598</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24477,7 +24480,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>119458756.82158899</v>
+        <v>125450648.721535</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24488,7 +24491,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>527465393.62019598</v>
+        <v>568011336.2198</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24540,7 +24543,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.73333333333333328</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24583,19 +24586,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>5053678085.7562141</v>
+        <v>5364784827.0288944</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.69616801539497697</v>
+        <v>0.73902443778132532</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>2205601246.2437859</v>
+        <v>1894494504.9711056</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>275700155.78047323</v>
+        <v>270642072.13872939</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24612,19 +24615,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>737884876.56650293</v>
+        <v>776767926.72192299</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.40780073918855952</v>
+        <v>0.42928991331158689</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1071540182.4334971</v>
+        <v>1032657132.278077</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>133942522.80418713</v>
+        <v>147522447.46829671</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24641,19 +24644,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1011328558.390203</v>
+        <v>1090186542.009717</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.55238166461267268</v>
+        <v>0.59545342788719435</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>819522505.609797</v>
+        <v>740664521.99028301</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>102440313.20122463</v>
+        <v>105809217.42718329</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24668,19 +24671,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>6802891520.7129192</v>
+        <v>7231739295.7605343</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.62414394319102251</v>
+        <v>0.66348938042634453</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>4096663934.2870798</v>
+        <v>3667816159.2394657</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>512082991.78588498</v>
+        <v>523973737.03420937</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24701,10 +24704,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -24731,7 +24734,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24766,7 +24769,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24789,35 +24792,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>254247035.77657601</v>
+        <v>269228327.14556301</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>42097257.998971999</v>
+        <v>45580726.018472001</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>296344293.77554798</v>
+        <v>314809053.16403502</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.53538726532461189</v>
+        <v>0.56874642641366113</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>197436442.22342399</v>
+        <v>182455150.85443699</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>59733165.001028001</v>
+        <v>56249696.981527999</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>257169607.22445202</v>
+        <v>238704847.83596498</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>32146200.903056502</v>
+        <v>34100692.547994994</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24841,35 +24844,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>379189288.75834596</v>
+        <v>413715743.12521899</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>112509187.672746</v>
+        <v>116164090.418745</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>491698476.43109196</v>
+        <v>529879833.54396397</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.60309702410178312</v>
+        <v>0.64992869829788502</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>210993082.24165404</v>
+        <v>176466627.87478101</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>112597618.327254</v>
+        <v>108942715.581255</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>323590700.56890804</v>
+        <v>285409343.45603603</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>40448837.571113504</v>
+        <v>40772763.350862287</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24893,7 +24896,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>148159605.5</v>
+        <v>174731592.19999999</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -24901,15 +24904,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>148159605.5</v>
+        <v>174731592.19999999</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.61356524772754562</v>
+        <v>0.72360635877922519</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>93313662.5</v>
+        <v>66741675.800000012</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -24917,11 +24920,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>93313662.5</v>
+        <v>66741675.800000012</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>11664207.8125</v>
+        <v>9534525.1142857168</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24945,35 +24948,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>734162511.56037199</v>
+        <v>779465004.640347</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>22337883.425106</v>
+        <v>23195396.925105002</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>756500394.98547804</v>
+        <v>802660401.56545198</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>1.0417901183669582</v>
+        <v>1.1053578825578727</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>-88450039.560371995</v>
+        <v>-133752532.640347</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>58103964.574893996</v>
+        <v>57246451.074894994</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>-30346074.985478044</v>
+        <v>-76506081.56545198</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-3793259.3731847554</v>
+        <v>-10929440.223635998</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25001,15 +25004,15 @@
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>46234425.210000001</v>
+        <v>49801992.810000002</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>298308748.64938998</v>
+        <v>301876316.24939001</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.50608991821390759</v>
+        <v>0.5121424057895525</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
@@ -25017,15 +25020,15 @@
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>34284978.789999999</v>
+        <v>30717411.189999998</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>291129487.35061002</v>
+        <v>287561919.75060999</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>36391185.918826252</v>
+        <v>41080274.250087142</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25049,35 +25052,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>378215569.01279998</v>
+        <v>388335116.82376301</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>79275448.542796999</v>
+        <v>80188962.052796006</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>457491017.55559695</v>
+        <v>468524078.87655902</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.87606275618595209</v>
+        <v>0.89719028380748844</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>61847714.987200022</v>
+        <v>51728167.176236987</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>2873876.4572030008</v>
+        <v>1960362.9472039938</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>64721591.444403052</v>
+        <v>53688530.123440981</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>8090198.9305503815</v>
+        <v>7669790.0176344262</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25101,35 +25104,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>683565535.57919395</v>
+        <v>723607416.51107204</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>54203774.369935997</v>
+        <v>55233572.569936</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>737769309.94912994</v>
+        <v>778840989.08100808</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.65740371542195408</v>
+        <v>0.69400143519126345</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>313192809.42080605</v>
+        <v>273150928.48892796</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>71284823.630064011</v>
+        <v>70255025.430063993</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>384477633.05087006</v>
+        <v>343405953.91899192</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>48059704.131358758</v>
+        <v>49057993.416998848</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25153,35 +25156,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>331299755.438191</v>
+        <v>346950683.470164</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>48709000.229927003</v>
+        <v>49437708.359926999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>380008755.668118</v>
+        <v>396388391.830091</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.59597205050856217</v>
+        <v>0.62166042006434363</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>208987303.561809</v>
+        <v>193336375.529836</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>48632425.770072997</v>
+        <v>47903717.640073001</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>257619729.331882</v>
+        <v>241240093.169909</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>32202466.16648525</v>
+        <v>34462870.452844143</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25205,7 +25208,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>304039806.38</v>
+        <v>326729714.68000001</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25213,15 +25216,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>304039806.38</v>
+        <v>326729714.68000001</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.75232487036764151</v>
+        <v>0.80846943421174633</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>100093857.62</v>
+        <v>77403949.319999993</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25229,11 +25232,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>100093857.62</v>
+        <v>77403949.319999993</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>12511732.202500001</v>
+        <v>11057707.045714285</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25257,35 +25260,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>261706349.523938</v>
+        <v>270823037.35390502</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>61268244.690229997</v>
+        <v>75385183.480155006</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>322974594.21416801</v>
+        <v>346208220.83406001</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.52856389852660812</v>
+        <v>0.56658687768074678</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>177310959.476062</v>
+        <v>168194271.64609498</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>110756167.30977</v>
+        <v>96639228.519844994</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>288067126.78583199</v>
+        <v>264833500.16593999</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>36008390.848228998</v>
+        <v>37833357.166562855</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25309,35 +25312,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>387876799.67017603</v>
+        <v>412833801.89116597</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>33922249.765463002</v>
+        <v>36896596.625460997</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>421799049.43563902</v>
+        <v>449730398.51662695</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.5557803387600786</v>
+        <v>0.59258387038260818</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>278752796.32982397</v>
+        <v>253795794.10883403</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>58379372.234536998</v>
+        <v>55405025.374539003</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>337132168.56436098</v>
+        <v>309200819.48337305</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>42141521.070545122</v>
+        <v>44171545.640481867</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25361,7 +25364,7 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>239547739.734368</v>
+        <v>248297316.40555099</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
@@ -25369,15 +25372,15 @@
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>269006727.626867</v>
+        <v>277756304.29804999</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.51845005455214177</v>
+        <v>0.53531289862485598</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>181995283.265632</v>
+        <v>173245706.59444901</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
@@ -25385,11 +25388,11 @@
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>249860471.373133</v>
+        <v>241110894.70195001</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>31232558.921641625</v>
+        <v>34444413.528850004</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25413,35 +25416,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>573076262.17522895</v>
+        <v>618235789.38517201</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>93927199.401954994</v>
+        <v>99871780.521954998</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>667003461.57718396</v>
+        <v>718107569.90712702</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.67942476768711846</v>
+        <v>0.73148056489067026</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>45274679.824771047</v>
+        <v>115152.61482799053</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>269439766.59804499</v>
+        <v>263495185.47804499</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>314714446.42281604</v>
+        <v>263610338.09287298</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>39339305.802852005</v>
+        <v>37658619.727553286</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25465,35 +25468,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>126517503.207634</v>
+        <v>139756959.957582</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>113941217.366872</v>
+        <v>115552929.046872</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>240458720.57450598</v>
+        <v>255309889.00445402</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.41030008468802953</v>
+        <v>0.43564096502693084</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>168008185.792366</v>
+        <v>154768729.042418</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>177588835.63312799</v>
+        <v>175977123.95312798</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>345597021.42549402</v>
+        <v>330745852.99554598</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>43199627.678186752</v>
+        <v>47249407.57079228</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25515,35 +25518,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>5053678085.7562141</v>
+        <v>5364784827.0288944</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>737884876.56650293</v>
+        <v>776767926.72192299</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>5791562962.3227177</v>
+        <v>6141552753.7508173</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.63863179486481048</v>
+        <v>0.67722493632561687</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>2205601246.2437859</v>
+        <v>1894494504.9711061</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1071540182.433497</v>
+        <v>1032657132.278077</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>3277141428.6772833</v>
+        <v>2927151637.2491832</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>409642678.58466041</v>
+        <v>418164519.60702616</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25583,8 +25586,8 @@
       <c r="C70" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="191">
-        <v>287387072.25986999</v>
+      <c r="D70" s="249">
+        <v>288489774.95986998</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25595,7 +25598,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="192">
-        <v>70533953.520000011</v>
+        <v>74407827.320000008</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25605,7 +25608,7 @@
       <c r="C72" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="D72" s="192">
+      <c r="D72" s="249">
         <v>7027026.8399999999</v>
       </c>
     </row>
@@ -25616,8 +25619,8 @@
       <c r="C73" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="D73" s="191">
-        <v>192728793.15000001</v>
+      <c r="D73" s="249">
+        <v>207802666.91</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25639,8 +25642,8 @@
       <c r="C75" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="192">
-        <v>29545792.469999999</v>
+      <c r="D75" s="249">
+        <v>30956603.27</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25650,8 +25653,8 @@
       <c r="C76" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="D76" s="192">
-        <v>1083282108.97997</v>
+      <c r="D76" s="249">
+        <v>1130760398.3099501</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25661,8 +25664,8 @@
       <c r="C77" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="D77" s="191">
-        <v>214528065.81951401</v>
+      <c r="D77" s="249">
+        <v>226582120.10947901</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25672,8 +25675,8 @@
       <c r="C78" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="D78" s="192">
-        <v>10156125.859999999</v>
+      <c r="D78" s="249">
+        <v>12750720.380000001</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25683,7 +25686,7 @@
       <c r="C79" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="D79" s="192">
+      <c r="D79" s="249">
         <v>2984684.68</v>
       </c>
     </row>
@@ -25694,8 +25697,8 @@
       <c r="C80" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="D80" s="191">
-        <v>443193790.22955197</v>
+      <c r="D80" s="249">
+        <v>482561357.99949998</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25705,8 +25708,8 @@
       <c r="C81" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="D81" s="192">
-        <v>116563996.94</v>
+      <c r="D81" s="249">
+        <v>124077510.04000001</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25716,8 +25719,8 @@
       <c r="C82" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="192">
-        <v>10504324.605</v>
+      <c r="D82" s="249">
+        <v>15485405.749</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25738,7 +25741,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>2518824925.493906</v>
+        <v>2654275286.707799</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25752,13 +25755,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25800,19 +25803,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>145181643.14490199</v>
+        <v>164073143.30486599</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.50846272533539338</v>
+        <v>0.57462552284156432</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>140348909.85509801</v>
+        <v>121457409.69513401</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>17543613.731887251</v>
+        <v>17351058.527876288</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25829,19 +25832,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>218811764.803516</v>
+        <v>232240413.76351598</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.51025119235191752</v>
+        <v>0.54156570667736126</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>210019697.196484</v>
+        <v>196591048.23648402</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>26252462.1495605</v>
+        <v>28084435.462354861</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25858,19 +25861,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>647335150.44178498</v>
+        <v>693872984.94133496</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.57979534239192076</v>
+        <v>0.621477645090037</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>469153898.55821502</v>
+        <v>422616064.05866504</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>58644237.319776878</v>
+        <v>60373723.436952151</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25943,24 +25946,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>1011328558.390203</v>
+        <v>1090186542.009717</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.55238166461267268</v>
+        <v>0.59545342788719435</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>819522505.609797</v>
+        <v>740664521.99028301</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>102440313.20122463</v>
+        <v>105809217.42718329</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25968,11 +25976,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26745,10 +26748,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -26775,7 +26778,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26810,7 +26813,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27809,13 +27812,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28018,6 +28021,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28025,11 +28033,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 23 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 24 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1832,6 +1832,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1928,6 +1931,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1948,18 +1960,6 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2716,16 +2716,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="207" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="207"/>
+      <c r="B1" s="208" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="208"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="209" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="208"/>
+      <c r="C3" s="209"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2776,10 +2776,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="209" t="s">
+      <c r="B11" s="210" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="209"/>
+      <c r="C11" s="210"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -3432,11 +3432,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="226" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="227"/>
+      <c r="D41" s="228"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3560,10 +3560,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="224"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3592,40 +3592,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="230" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="225" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3633,13 +3633,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="225"/>
+      <c r="C50" s="225"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3658,7 +3658,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="225"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3668,7 +3668,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4461,10 +4461,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="225" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4472,8 +4472,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="225"/>
+      <c r="C69" s="225"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -4667,13 +4667,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4876,11 +4876,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4888,6 +4883,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5489,11 +5489,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="226" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="227"/>
+      <c r="D41" s="228"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5617,10 +5617,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="224"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5649,40 +5649,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="230" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="225" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5690,13 +5690,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="225"/>
+      <c r="C50" s="225"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5715,7 +5715,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="225"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5725,7 +5725,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6518,10 +6518,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="225" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6529,8 +6529,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="225"/>
+      <c r="C69" s="225"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -6724,13 +6724,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6933,11 +6933,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6945,6 +6940,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7546,11 +7546,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="226" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="227"/>
+      <c r="D41" s="228"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7674,10 +7674,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="224"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7706,40 +7706,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="230" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="225" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7747,13 +7747,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="225"/>
+      <c r="C50" s="225"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7772,7 +7772,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="225"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7782,7 +7782,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8575,10 +8575,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="225" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8586,8 +8586,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="225"/>
+      <c r="C69" s="225"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -8781,13 +8781,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8990,11 +8990,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -9002,6 +8997,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9603,11 +9603,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="226" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="227"/>
+      <c r="D41" s="228"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9731,10 +9731,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="224"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9763,40 +9763,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="230" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="225" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9804,13 +9804,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="225"/>
+      <c r="C50" s="225"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9829,7 +9829,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="225"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9839,7 +9839,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10632,10 +10632,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="225" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10643,8 +10643,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="225"/>
+      <c r="C69" s="225"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -10838,13 +10838,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11047,11 +11047,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11059,6 +11054,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11660,11 +11660,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="226" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="227"/>
+      <c r="D41" s="228"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11787,10 +11787,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="224"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11819,40 +11819,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="230" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="225" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11860,13 +11860,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="225"/>
+      <c r="C50" s="225"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11885,7 +11885,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="225"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11895,7 +11895,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12674,10 +12674,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="225" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12685,8 +12685,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="225"/>
+      <c r="C69" s="225"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -12880,13 +12880,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13089,11 +13089,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13101,6 +13096,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -13175,10 +13175,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="208"/>
+      <c r="C3" s="209"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14655,13 +14655,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="210" t="s">
+      <c r="B29" s="211" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="210"/>
-      <c r="D29" s="210"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="210"/>
+      <c r="C29" s="211"/>
+      <c r="D29" s="211"/>
+      <c r="E29" s="211"/>
+      <c r="F29" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15193,10 +15193,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="212" t="s">
+      <c r="B44" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="213"/>
+      <c r="C44" s="214"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15236,23 +15236,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="214" t="s">
+      <c r="B47" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="214" t="s">
+      <c r="C47" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="215" t="s">
+      <c r="D47" s="216" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="216"/>
-      <c r="F47" s="217"/>
+      <c r="E47" s="217"/>
+      <c r="F47" s="218"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="214" t="s">
+      <c r="J47" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15260,13 +15260,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="211" t="s">
+      <c r="N47" s="212" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="214"/>
-      <c r="C48" s="214"/>
+      <c r="B48" s="215"/>
+      <c r="C48" s="215"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15285,7 +15285,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="214"/>
+      <c r="J48" s="215"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15295,7 +15295,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="211"/>
+      <c r="N48" s="212"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16728,10 +16728,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="212" t="s">
+      <c r="B44" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="213"/>
+      <c r="C44" s="214"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16771,23 +16771,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="214" t="s">
+      <c r="B47" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="214" t="s">
+      <c r="C47" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="215" t="s">
+      <c r="D47" s="216" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="216"/>
-      <c r="F47" s="217"/>
+      <c r="E47" s="217"/>
+      <c r="F47" s="218"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="214" t="s">
+      <c r="J47" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16795,13 +16795,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="211" t="s">
+      <c r="N47" s="212" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="214"/>
-      <c r="C48" s="214"/>
+      <c r="B48" s="215"/>
+      <c r="C48" s="215"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16820,7 +16820,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="214"/>
+      <c r="J48" s="215"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16830,7 +16830,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="211"/>
+      <c r="N48" s="212"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -18415,10 +18415,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="222" t="s">
+      <c r="B44" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="223"/>
+      <c r="C44" s="224"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18483,23 +18483,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="224" t="s">
+      <c r="B47" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="224" t="s">
+      <c r="C47" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="219" t="s">
+      <c r="D47" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="220"/>
-      <c r="F47" s="221"/>
+      <c r="E47" s="221"/>
+      <c r="F47" s="222"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="224" t="s">
+      <c r="J47" s="225" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18507,13 +18507,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="218" t="s">
+      <c r="N47" s="219" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="224"/>
-      <c r="C48" s="224"/>
+      <c r="B48" s="225"/>
+      <c r="C48" s="225"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18532,7 +18532,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="224"/>
+      <c r="J48" s="225"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18542,7 +18542,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -20164,11 +20164,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="226" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="227"/>
+      <c r="D41" s="228"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20286,10 +20286,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="224"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20312,40 +20312,40 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="230" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="236"/>
-      <c r="L48" s="237"/>
-      <c r="M48" s="237"/>
-      <c r="N48" s="238"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="237"/>
+      <c r="L48" s="238"/>
+      <c r="M48" s="238"/>
+      <c r="N48" s="239"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="235" t="s">
+      <c r="B49" s="236" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="235" t="s">
+      <c r="C49" s="236" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="232" t="s">
+      <c r="D49" s="233" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="233"/>
-      <c r="F49" s="234"/>
+      <c r="E49" s="234"/>
+      <c r="F49" s="235"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="235" t="s">
+      <c r="J49" s="236" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20353,13 +20353,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="228" t="s">
+      <c r="N49" s="229" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="235"/>
-      <c r="C50" s="235"/>
+      <c r="B50" s="236"/>
+      <c r="C50" s="236"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20378,7 +20378,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="235"/>
+      <c r="J50" s="236"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20388,7 +20388,7 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="228"/>
+      <c r="N50" s="229"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="183" t="s">
@@ -21179,10 +21179,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="225" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21193,8 +21193,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="225"/>
+      <c r="C69" s="225"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -21380,13 +21380,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="229" t="s">
+      <c r="B87" s="230" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="230"/>
-      <c r="D87" s="230"/>
-      <c r="E87" s="230"/>
-      <c r="F87" s="231"/>
+      <c r="C87" s="231"/>
+      <c r="D87" s="231"/>
+      <c r="E87" s="231"/>
+      <c r="F87" s="232"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21668,7 +21668,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22341,11 +22341,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="246" t="s">
+      <c r="B41" s="240" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="247"/>
-      <c r="D41" s="248"/>
+      <c r="C41" s="241"/>
+      <c r="D41" s="242"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>90399154.315943852</v>
+        <v>105465680.03526783</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>79369618.530955821</v>
+        <v>92597888.286115125</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22463,15 +22463,15 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>15681787.819958959</v>
+        <v>18295419.123285454</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="224"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
@@ -22490,7 +22490,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>185450560.66685864</v>
+        <v>216358987.44466841</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22500,40 +22500,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="230" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="225" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22541,13 +22541,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="225"/>
+      <c r="C50" s="225"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22566,7 +22566,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="225"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22576,7 +22576,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22627,7 +22627,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>21706303.332366187</v>
+        <v>25324020.554427218</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22679,7 +22679,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>19421376.426752858</v>
+        <v>22658272.497878332</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>6272203.1714285696</v>
+        <v>7317570.3666666644</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-5764101.0694324458</v>
+        <v>-6724784.5810045199</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>18684911.087360878</v>
+        <v>21799062.935254354</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22887,7 +22887,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>11526786.350706236</v>
+        <v>13447917.409157276</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-3588162.2383913654</v>
+        <v>-4186189.2781232595</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>15830632.605041435</v>
+        <v>18469071.372548342</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>14801734.310003569</v>
+        <v>17268690.028337497</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>10801706.808182912</v>
+        <v>12601991.276213398</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23147,7 +23147,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>25319451.057982605</v>
+        <v>29539359.567646373</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>16910618.308881838</v>
+        <v>19729054.693695474</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>4943668.9947136296</v>
+        <v>5767613.8271659017</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23303,7 +23303,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>12901643.701302912</v>
+        <v>15051917.651520064</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>169768772.84689981</v>
+        <v>198063568.32138312</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23369,10 +23369,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="225" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23380,8 +23380,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="225"/>
+      <c r="C69" s="225"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -23575,13 +23575,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-1908996.8451817802</v>
+        <v>-2227162.9860454104</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-2647068.9625546336</v>
+        <v>-3088247.122980406</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23693,7 +23693,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>20237853.627695389</v>
+        <v>23610829.23231129</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23778,17 +23778,12 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>15681787.819958976</v>
+        <v>18295419.123285472</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23796,6 +23791,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23864,7 +23864,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23946,11 +23946,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>269228327.14556301</v>
+        <v>283224685.04754502</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>45580726.018472001</v>
+        <v>51991479.633472003</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23968,11 +23968,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>413715743.12521899</v>
+        <v>470556595.661156</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>116164090.418745</v>
+        <v>118996257.09874301</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23980,27 +23980,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>248297316.40555099</v>
+        <v>263441983.37547901</v>
       </c>
       <c r="D10" s="205">
-        <v>29458987.892499</v>
+        <v>31184046.448995002</v>
       </c>
       <c r="E10" s="205">
-        <v>124077510.04000001</v>
+        <v>130512645.09999999</v>
       </c>
       <c r="F10" s="205">
-        <v>401833814.33805001</v>
+        <v>425138674.924474</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>779465004.640347</v>
+        <v>807067617.14033198</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>23195396.925105002</v>
+        <v>23489396.925105002</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24008,23 +24008,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>270823037.35390502</v>
+        <v>296521225.34049201</v>
       </c>
       <c r="D11" s="205">
-        <v>75385183.480155006</v>
+        <v>77219728.510130003</v>
       </c>
       <c r="E11" s="205">
-        <v>2984684.68</v>
+        <v>3184684.68</v>
       </c>
       <c r="F11" s="205">
-        <v>349192905.51406002</v>
+        <v>376925638.53062201</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>252074323.43939</v>
+        <v>275948197.43928999</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24036,27 +24036,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>213662463.846358</v>
+        <v>259578586.62232</v>
       </c>
       <c r="D12" s="205">
-        <v>71573888.308929995</v>
+        <v>72327685.608930007</v>
       </c>
       <c r="E12" s="205">
         <v>44660102.520000003</v>
       </c>
       <c r="F12" s="205">
-        <v>329896454.67528802</v>
+        <v>376566374.75125003</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>388335116.82376301</v>
+        <v>461929828.20271999</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>80188962.052796006</v>
+        <v>83071133.272792995</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24064,27 +24064,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>200053279.27886099</v>
+        <v>210978009.038836</v>
       </c>
       <c r="D13" s="205">
-        <v>44590202.109815001</v>
+        <v>46668571.489813</v>
       </c>
       <c r="E13" s="205">
-        <v>29747724.800000001</v>
+        <v>29847724.800000001</v>
       </c>
       <c r="F13" s="205">
-        <v>274391206.188676</v>
+        <v>287494305.32864898</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>723607416.51107204</v>
+        <v>773550501.95899105</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>55233572.569936</v>
+        <v>67497946.929836005</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24092,27 +24092,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>779465004.640347</v>
+        <v>807067617.14033198</v>
       </c>
       <c r="D14" s="205">
-        <v>23195396.925105002</v>
+        <v>23489396.925105002</v>
       </c>
       <c r="E14" s="205">
-        <v>207802666.91</v>
+        <v>219837802.21000001</v>
       </c>
       <c r="F14" s="205">
-        <v>1010463068.4754519</v>
+        <v>1050394816.275437</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>346950683.470164</v>
+        <v>380980784.24472702</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>49437708.359926999</v>
+        <v>50659108.379927002</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24128,11 +24128,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>270823037.35390502</v>
+        <v>296521225.34049201</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>75385183.480155006</v>
+        <v>77219728.510130003</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24140,27 +24140,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>388335116.82376301</v>
+        <v>461929828.20271999</v>
       </c>
       <c r="D16" s="205">
-        <v>80188962.052796006</v>
+        <v>83071133.272792995</v>
       </c>
       <c r="E16" s="205">
         <v>30956603.27</v>
       </c>
       <c r="F16" s="205">
-        <v>499480682.146559</v>
+        <v>575957564.74551296</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>412833801.89116597</v>
+        <v>436199054.44500101</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>36896596.625460997</v>
+        <v>39706137.095458999</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24168,7 +24168,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>252074323.43939</v>
+        <v>275948197.43928999</v>
       </c>
       <c r="D17" s="205">
         <v>49801992.810000002</v>
@@ -24177,18 +24177,18 @@
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>301876316.24939001</v>
+        <v>325750190.24928999</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>248297316.40555099</v>
+        <v>263441983.37547901</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>29458987.892499</v>
+        <v>31184046.448995002</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24196,7 +24196,7 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>398631172.90298897</v>
+        <v>401343449.60298699</v>
       </c>
       <c r="D18" s="205">
         <v>3209277.5299920002</v>
@@ -24205,18 +24205,18 @@
         <v>8770270.1600000001</v>
       </c>
       <c r="F18" s="205">
-        <v>410610720.59298098</v>
+        <v>413322997.292979</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>618235789.38517201</v>
+        <v>637597986.04513395</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>99871780.521954998</v>
+        <v>104214483.32795499</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24224,27 +24224,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>723607416.51107204</v>
+        <v>773550501.95899105</v>
       </c>
       <c r="D19" s="205">
-        <v>55233572.569936</v>
+        <v>67497946.929836005</v>
       </c>
       <c r="E19" s="205">
-        <v>1130760398.3099501</v>
+        <v>1135702830.3099501</v>
       </c>
       <c r="F19" s="205">
-        <v>1909601387.3909581</v>
+        <v>1976751279.198777</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>139756959.957582</v>
+        <v>150424022.40743202</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>115552929.046872</v>
+        <v>121203268.486872</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24252,7 +24252,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>96439159.457581997</v>
+        <v>101502221.907432</v>
       </c>
       <c r="D20" s="205">
         <v>21291124.199754</v>
@@ -24261,7 +24261,7 @@
         <v>8237838</v>
       </c>
       <c r="F20" s="205">
-        <v>125968121.657336</v>
+        <v>131031184.107186</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24279,23 +24279,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>43317800.5</v>
+        <v>48921800.5</v>
       </c>
       <c r="D21" s="205">
-        <v>94261804.847118005</v>
+        <v>99912144.287118003</v>
       </c>
       <c r="E21" s="205">
-        <v>42151352.140000001</v>
+        <v>73005406.799999997</v>
       </c>
       <c r="F21" s="205">
-        <v>179730957.48711801</v>
+        <v>221839351.587118</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>693872984.94133496</v>
+        <v>718529893.468243</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24306,7 +24306,7 @@
         <v>172</v>
       </c>
       <c r="C22" s="205">
-        <v>174731592.19999999</v>
+        <v>184864971.30000001</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>168</v>
@@ -24315,7 +24315,7 @@
         <v>7027026.8399999999</v>
       </c>
       <c r="F22" s="205">
-        <v>181758619.03999999</v>
+        <v>191891998.13999999</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24326,7 +24326,7 @@
         <v>173</v>
       </c>
       <c r="C23" s="205">
-        <v>326729714.68000001</v>
+        <v>326478829.38</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>168</v>
@@ -24335,7 +24335,7 @@
         <v>12750720.380000001</v>
       </c>
       <c r="F23" s="205">
-        <v>339480435.06</v>
+        <v>339229549.75999999</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24346,16 +24346,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>269228327.14556301</v>
+        <v>283224685.04754502</v>
       </c>
       <c r="D24" s="205">
-        <v>45580726.018472001</v>
+        <v>51991479.633472003</v>
       </c>
       <c r="E24" s="205">
-        <v>288489774.95986998</v>
+        <v>294606837.87987</v>
       </c>
       <c r="F24" s="205">
-        <v>603298828.12390494</v>
+        <v>629823002.56088698</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24366,16 +24366,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>346950683.470164</v>
+        <v>380980784.24472702</v>
       </c>
       <c r="D25" s="205">
-        <v>49437708.359926999</v>
+        <v>50659108.379927002</v>
       </c>
       <c r="E25" s="205">
-        <v>226582120.10947901</v>
+        <v>237765903.78947899</v>
       </c>
       <c r="F25" s="205">
-        <v>622970511.93956995</v>
+        <v>669405796.41413295</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24386,16 +24386,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>412833801.89116597</v>
+        <v>436199054.44500101</v>
       </c>
       <c r="D26" s="205">
-        <v>36896596.625460997</v>
+        <v>39706137.095458999</v>
       </c>
       <c r="E26" s="205">
-        <v>482561357.99949998</v>
+        <v>487518294.9795</v>
       </c>
       <c r="F26" s="205">
-        <v>932291756.51612699</v>
+        <v>963423486.51996005</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24406,16 +24406,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>618235789.38517201</v>
+        <v>637597986.04513395</v>
       </c>
       <c r="D27" s="205">
-        <v>99871780.521954998</v>
+        <v>104214483.32795499</v>
       </c>
       <c r="E27" s="205">
-        <v>15485405.749</v>
+        <v>15391027.368000001</v>
       </c>
       <c r="F27" s="205">
-        <v>733592975.65612698</v>
+        <v>757203496.74108899</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24458,7 +24458,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>164073143.30486599</v>
+        <v>170190736.42485401</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24469,7 +24469,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>232240413.76351598</v>
+        <v>236702305.72351599</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24480,7 +24480,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>125450648.721535</v>
+        <v>141724449.52852201</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24491,7 +24491,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>568011336.2198</v>
+        <v>576394443.93972099</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24533,17 +24533,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="226" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="227"/>
+      <c r="D41" s="228"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.76666666666666672</v>
+        <v>0.8</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24586,19 +24586,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>5364784827.0288944</v>
+        <v>5748786281.9882984</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.73902443778132532</v>
+        <v>0.79192245112359572</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>1894494504.9711056</v>
+        <v>1510493050.0117016</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>270642072.13872939</v>
+        <v>251748841.66861692</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24615,19 +24615,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>776767926.72192299</v>
+        <v>819034978.91928697</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.42928991331158689</v>
+        <v>0.45264929588846098</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1032657132.278077</v>
+        <v>990390080.08071303</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>147522447.46829671</v>
+        <v>165065013.34678552</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24644,46 +24644,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1090186542.009717</v>
+        <v>1125422935.6166129</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.59545342788719435</v>
+        <v>0.61469933723490078</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>740664521.99028301</v>
+        <v>705428128.38338709</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>105809217.42718329</v>
+        <v>117571354.73056452</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="224"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10899555455</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>7231739295.7605343</v>
+        <v>7693244196.5241985</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.66348938042634453</v>
+        <v>0.70583100643751884</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>3667816159.2394657</v>
+        <v>3206311258.4758019</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>523973737.03420937</v>
+        <v>534385209.74596697</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24693,40 +24693,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="230" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="225" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24734,13 +24734,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="225"/>
+      <c r="C50" s="225"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24759,7 +24759,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="225"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24769,7 +24769,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24792,35 +24792,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>269228327.14556301</v>
+        <v>283224685.04754502</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>45580726.018472001</v>
+        <v>51991479.633472003</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>314809053.16403502</v>
+        <v>335216164.68101704</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.56874642641366113</v>
+        <v>0.60561471730954242</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>182455150.85443699</v>
+        <v>168458792.95245498</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>56249696.981527999</v>
+        <v>49838943.366527997</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>238704847.83596498</v>
+        <v>218297736.31898296</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>34100692.547994994</v>
+        <v>36382956.053163826</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24844,35 +24844,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>413715743.12521899</v>
+        <v>470556595.661156</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>116164090.418745</v>
+        <v>118996257.09874301</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>529879833.54396397</v>
+        <v>589552852.75989902</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.64992869829788502</v>
+        <v>0.72312115675233479</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>176466627.87478101</v>
+        <v>119625775.338844</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>108942715.581255</v>
+        <v>106110548.90125699</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>285409343.45603603</v>
+        <v>225736324.24010098</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>40772763.350862287</v>
+        <v>37622720.706683494</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>174731592.19999999</v>
+        <v>184864971.30000001</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -24904,15 +24904,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>174731592.19999999</v>
+        <v>184864971.30000001</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.72360635877922519</v>
+        <v>0.76557116583190488</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>66741675.800000012</v>
+        <v>56608296.699999988</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -24920,11 +24920,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>66741675.800000012</v>
+        <v>56608296.699999988</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>9534525.1142857168</v>
+        <v>9434716.1166666653</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24948,35 +24948,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>779465004.640347</v>
+        <v>807067617.14033198</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>23195396.925105002</v>
+        <v>23489396.925105002</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>802660401.56545198</v>
+        <v>830557014.06543696</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>1.1053578825578727</v>
+        <v>1.1437748026692687</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>-133752532.640347</v>
+        <v>-161355145.14033198</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>57246451.074894994</v>
+        <v>56952451.074894994</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>-76506081.56545198</v>
+        <v>-104402694.06543696</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-10929440.223635998</v>
+        <v>-17400449.01090616</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25000,7 +25000,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>252074323.43939</v>
+        <v>275948197.43928999</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25008,15 +25008,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>301876316.24939001</v>
+        <v>325750190.24928999</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.5121424057895525</v>
+        <v>0.55264516340146275</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>256844508.56061</v>
+        <v>232970634.56071001</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25024,11 +25024,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>287561919.75060999</v>
+        <v>263688045.75071001</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>41080274.250087142</v>
+        <v>43948007.625118338</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25052,35 +25052,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>388335116.82376301</v>
+        <v>461929828.20271999</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>80188962.052796006</v>
+        <v>83071133.272792995</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>468524078.87655902</v>
+        <v>545000961.47551298</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.89719028380748844</v>
+        <v>1.0436380740004556</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>51728167.176236987</v>
+        <v>-21866544.202719986</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>1960362.9472039938</v>
+        <v>-921808.27279299498</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>53688530.123440981</v>
+        <v>-22788352.475512981</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>7669790.0176344262</v>
+        <v>-3798058.7459188304</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25104,35 +25104,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>723607416.51107204</v>
+        <v>773550501.95899105</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>55233572.569936</v>
+        <v>67497946.929836005</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>778840989.08100808</v>
+        <v>841048448.88882709</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.69400143519126345</v>
+        <v>0.74943260405818457</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>273150928.48892796</v>
+        <v>223207843.04100895</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>70255025.430063993</v>
+        <v>57990651.070163995</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>343405953.91899192</v>
+        <v>281198494.11117291</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>49057993.416998848</v>
+        <v>46866415.685195483</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25156,35 +25156,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>346950683.470164</v>
+        <v>380980784.24472702</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>49437708.359926999</v>
+        <v>50659108.379927002</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>396388391.830091</v>
+        <v>431639892.624654</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.62166042006434363</v>
+        <v>0.67694574941182872</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>193336375.529836</v>
+        <v>159306274.75527298</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>47903717.640073001</v>
+        <v>46682317.620072998</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>241240093.169909</v>
+        <v>205988592.375346</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>34462870.452844143</v>
+        <v>34331432.062557667</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25208,7 +25208,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>326729714.68000001</v>
+        <v>326478829.38</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25216,15 +25216,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>326729714.68000001</v>
+        <v>326478829.38</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.80846943421174633</v>
+        <v>0.80784863638580728</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>77403949.319999993</v>
+        <v>77654834.620000005</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25232,11 +25232,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>77403949.319999993</v>
+        <v>77654834.620000005</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>11057707.045714285</v>
+        <v>12942472.436666667</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25260,35 +25260,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>270823037.35390502</v>
+        <v>296521225.34049201</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>75385183.480155006</v>
+        <v>77219728.510130003</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>346208220.83406001</v>
+        <v>373740953.850622</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.56658687768074678</v>
+        <v>0.61164555709711022</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>168194271.64609498</v>
+        <v>142496083.65950799</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>96639228.519844994</v>
+        <v>94804683.489869997</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>264833500.16593999</v>
+        <v>237300767.149378</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>37833357.166562855</v>
+        <v>39550127.858229667</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25312,35 +25312,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>412833801.89116597</v>
+        <v>436199054.44500101</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>36896596.625460997</v>
+        <v>39706137.095458999</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>449730398.51662695</v>
+        <v>475905191.54045999</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.59258387038260818</v>
+        <v>0.62707288915404713</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>253795794.10883403</v>
+        <v>230430541.55499899</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>55405025.374539003</v>
+        <v>52595484.904541001</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>309200819.48337305</v>
+        <v>283026026.45954001</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>44171545.640481867</v>
+        <v>47171004.409923337</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25364,35 +25364,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>248297316.40555099</v>
+        <v>263441983.37547901</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>29458987.892499</v>
+        <v>31184046.448995002</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>277756304.29804999</v>
+        <v>294626029.82447404</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.53531289862485598</v>
+        <v>0.56782550601059301</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>173245706.59444901</v>
+        <v>158101039.62452099</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>67865188.107501</v>
+        <v>66140129.551004998</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>241110894.70195001</v>
+        <v>224241169.17552596</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>34444413.528850004</v>
+        <v>37373528.195920996</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25416,35 +25416,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>618235789.38517201</v>
+        <v>637597986.04513395</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>99871780.521954998</v>
+        <v>104214483.32795499</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>718107569.90712702</v>
+        <v>741812469.37308896</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.73148056489067026</v>
+        <v>0.75562691006049054</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>115152.61482799053</v>
+        <v>-19247044.045133948</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>263495185.47804499</v>
+        <v>259152482.67204499</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>263610338.09287298</v>
+        <v>239905438.62691104</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>37658619.727553286</v>
+        <v>39984239.771151841</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25468,35 +25468,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>139756959.957582</v>
+        <v>150424022.40743202</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>115552929.046872</v>
+        <v>121203268.486872</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>255309889.00445402</v>
+        <v>271627290.89430404</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.43564096502693084</v>
+        <v>0.46348371226145929</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>154768729.042418</v>
+        <v>144101666.59256798</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>175977123.95312798</v>
+        <v>170326784.51312798</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>330745852.99554598</v>
+        <v>314428451.10569596</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>47249407.57079228</v>
+        <v>52404741.850949325</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25518,35 +25518,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>5364784827.0288944</v>
+        <v>5748786281.9882984</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>776767926.72192299</v>
+        <v>819034978.91928697</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>6141552753.7508173</v>
+        <v>6567821260.9075861</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.67722493632561687</v>
+        <v>0.72422928102338957</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>1894494504.9711061</v>
+        <v>1510493050.0117011</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1032657132.278077</v>
+        <v>990390080.08071303</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>2927151637.2491832</v>
+        <v>2500883130.0924139</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>418164519.60702616</v>
+        <v>416813855.01540232</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25562,10 +25562,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="225" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25573,8 +25573,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="225"/>
+      <c r="C69" s="225"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -25586,8 +25586,8 @@
       <c r="C70" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="249">
-        <v>288489774.95986998</v>
+      <c r="D70" s="207">
+        <v>294606837.87987</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25598,7 +25598,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="192">
-        <v>74407827.320000008</v>
+        <v>74507827.320000008</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25608,7 +25608,7 @@
       <c r="C72" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="D72" s="249">
+      <c r="D72" s="207">
         <v>7027026.8399999999</v>
       </c>
     </row>
@@ -25619,8 +25619,8 @@
       <c r="C73" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="D73" s="249">
-        <v>207802666.91</v>
+      <c r="D73" s="207">
+        <v>219837802.21000001</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25642,7 +25642,7 @@
       <c r="C75" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="249">
+      <c r="D75" s="207">
         <v>30956603.27</v>
       </c>
     </row>
@@ -25653,8 +25653,8 @@
       <c r="C76" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="D76" s="249">
-        <v>1130760398.3099501</v>
+      <c r="D76" s="207">
+        <v>1135702830.3099501</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25664,8 +25664,8 @@
       <c r="C77" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="D77" s="249">
-        <v>226582120.10947901</v>
+      <c r="D77" s="207">
+        <v>237765903.78947899</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25675,7 +25675,7 @@
       <c r="C78" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="D78" s="249">
+      <c r="D78" s="207">
         <v>12750720.380000001</v>
       </c>
     </row>
@@ -25686,8 +25686,8 @@
       <c r="C79" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="D79" s="249">
-        <v>2984684.68</v>
+      <c r="D79" s="207">
+        <v>3184684.68</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25697,8 +25697,8 @@
       <c r="C80" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="D80" s="249">
-        <v>482561357.99949998</v>
+      <c r="D80" s="207">
+        <v>487518294.9795</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25708,8 +25708,8 @@
       <c r="C81" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="D81" s="249">
-        <v>124077510.04000001</v>
+      <c r="D81" s="207">
+        <v>130512645.09999999</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25719,8 +25719,8 @@
       <c r="C82" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="249">
-        <v>15485405.749</v>
+      <c r="D82" s="207">
+        <v>15391027.368000001</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25731,7 +25731,7 @@
         <v>89</v>
       </c>
       <c r="D83" s="192">
-        <v>50389190.140000001</v>
+        <v>81243244.799999997</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25741,7 +25741,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>2654275286.707799</v>
+        <v>2731005448.9267993</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25755,13 +25755,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25803,19 +25803,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>164073143.30486599</v>
+        <v>170190736.42485401</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.57462552284156432</v>
+        <v>0.59605087664595391</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>121457409.69513401</v>
+        <v>115339816.57514599</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>17351058.527876288</v>
+        <v>19223302.762524333</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25832,19 +25832,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>232240413.76351598</v>
+        <v>236702305.72351599</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.54156570667736126</v>
+        <v>0.5519704748797466</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>196591048.23648402</v>
+        <v>192129156.27648401</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>28084435.462354861</v>
+        <v>32021526.046080668</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25861,19 +25861,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>693872984.94133496</v>
+        <v>718529893.468243</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.621477645090037</v>
+        <v>0.64356197144235761</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>422616064.05866504</v>
+        <v>397959155.531757</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>60373723.436952151</v>
+        <v>66326525.921959497</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25946,29 +25946,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>1090186542.009717</v>
+        <v>1125422935.6166129</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.59545342788719435</v>
+        <v>0.61469933723490078</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>740664521.99028301</v>
+        <v>705428128.38338697</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>105809217.42718329</v>
+        <v>117571354.73056449</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25976,6 +25971,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26577,11 +26577,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="227"/>
+      <c r="D41" s="228"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26705,10 +26705,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="224"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26737,40 +26737,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="230" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="225" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26778,13 +26778,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="225"/>
+      <c r="C50" s="225"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26803,7 +26803,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="225"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26813,7 +26813,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27606,10 +27606,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="225" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27617,8 +27617,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="225"/>
+      <c r="C69" s="225"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -27812,13 +27812,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28021,11 +28021,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28033,6 +28028,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 24 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 25 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1931,15 +1931,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1959,6 +1950,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3603,10 +3603,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4667,13 +4667,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4876,6 +4876,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4883,11 +4888,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5660,10 +5660,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6724,13 +6724,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6933,6 +6933,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6940,11 +6945,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7717,10 +7717,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8781,13 +8781,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8990,6 +8990,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8997,11 +9002,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9774,10 +9774,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10838,13 +10838,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11047,6 +11047,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11054,11 +11059,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11830,10 +11830,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12880,13 +12880,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13089,6 +13089,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13096,11 +13101,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22341,11 +22341,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="240" t="s">
+      <c r="B41" s="247" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="241"/>
-      <c r="D41" s="242"/>
+      <c r="C41" s="248"/>
+      <c r="D41" s="249"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>105465680.03526783</v>
+        <v>126558816.0423214</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>92597888.286115125</v>
+        <v>111117465.94333816</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22463,7 +22463,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>18295419.123285454</v>
+        <v>21954502.947942544</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22490,7 +22490,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>216358987.44466841</v>
+        <v>259630784.93360209</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22511,10 +22511,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22576,7 +22576,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22627,7 +22627,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>25324020.554427218</v>
+        <v>30388824.665312659</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22679,7 +22679,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>22658272.497878332</v>
+        <v>27189926.997453999</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>7317570.3666666644</v>
+        <v>8781084.4399999976</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-6724784.5810045199</v>
+        <v>-8069741.4972054241</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>21799062.935254354</v>
+        <v>26158875.522305228</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22887,7 +22887,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>13447917.409157276</v>
+        <v>16137500.890988732</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-4186189.2781232595</v>
+        <v>-5023427.1337479111</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>18469071.372548342</v>
+        <v>22162885.64705801</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>17268690.028337497</v>
+        <v>20722428.034004997</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>12601991.276213398</v>
+        <v>15122389.531456077</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23147,7 +23147,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>29539359.567646373</v>
+        <v>35447231.481175646</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>19729054.693695474</v>
+        <v>23674865.632434569</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>5767613.8271659017</v>
+        <v>6921136.5925990818</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23303,7 +23303,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>15051917.651520064</v>
+        <v>18062301.181824077</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>198063568.32138312</v>
+        <v>237676281.98565975</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23575,13 +23575,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-2227162.9860454104</v>
+        <v>-2672595.5832544924</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-3088247.122980406</v>
+        <v>-3705896.5475764871</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23693,7 +23693,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>23610829.23231129</v>
+        <v>28332995.078773547</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23778,12 +23778,17 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>18295419.123285472</v>
+        <v>21954502.947942566</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23791,11 +23796,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23864,7 +23864,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23946,11 +23946,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>283224685.04754502</v>
+        <v>296324484.52852398</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>51991479.633472003</v>
+        <v>53198556.223471999</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23968,11 +23968,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>470556595.661156</v>
+        <v>496431704.69514</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>118996257.09874301</v>
+        <v>120019480.528742</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23980,27 +23980,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>263441983.37547901</v>
+        <v>281014362.03701502</v>
       </c>
       <c r="D10" s="205">
-        <v>31184046.448995002</v>
+        <v>31377289.693994999</v>
       </c>
       <c r="E10" s="205">
-        <v>130512645.09999999</v>
+        <v>134723140.53999999</v>
       </c>
       <c r="F10" s="205">
-        <v>425138674.924474</v>
+        <v>447114792.27100998</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>807067617.14033198</v>
+        <v>839454924.55033195</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>23489396.925105002</v>
+        <v>25301590.525097001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24008,27 +24008,27 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>296521225.34049201</v>
+        <v>312361408.84544998</v>
       </c>
       <c r="D11" s="205">
-        <v>77219728.510130003</v>
+        <v>78376728.510130003</v>
       </c>
       <c r="E11" s="205">
         <v>3184684.68</v>
       </c>
       <c r="F11" s="205">
-        <v>376925638.53062201</v>
+        <v>393922822.03557998</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>275948197.43928999</v>
+        <v>312830431.85913801</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>49801992.810000002</v>
+        <v>50693884.710000001</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -24036,27 +24036,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>259578586.62232</v>
+        <v>280223965.94231999</v>
       </c>
       <c r="D12" s="205">
-        <v>72327685.608930007</v>
+        <v>73350909.038929</v>
       </c>
       <c r="E12" s="205">
-        <v>44660102.520000003</v>
+        <v>49116048.439999998</v>
       </c>
       <c r="F12" s="205">
-        <v>376566374.75125003</v>
+        <v>402690923.42124897</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>461929828.20271999</v>
+        <v>475630323.88770801</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>83071133.272792995</v>
+        <v>85076007.132786006</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24064,7 +24064,7 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>210978009.038836</v>
+        <v>216207738.75281999</v>
       </c>
       <c r="D13" s="205">
         <v>46668571.489813</v>
@@ -24073,18 +24073,18 @@
         <v>29847724.800000001</v>
       </c>
       <c r="F13" s="205">
-        <v>287494305.32864898</v>
+        <v>292724035.042633</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>773550501.95899105</v>
+        <v>893006078.16387904</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>67497946.929836005</v>
+        <v>71857298.289833993</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24092,27 +24092,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>807067617.14033198</v>
+        <v>839454924.55033195</v>
       </c>
       <c r="D14" s="205">
-        <v>23489396.925105002</v>
+        <v>25301590.525097001</v>
       </c>
       <c r="E14" s="205">
-        <v>219837802.21000001</v>
+        <v>235041405.61000001</v>
       </c>
       <c r="F14" s="205">
-        <v>1050394816.275437</v>
+        <v>1099797920.6854291</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>380980784.24472702</v>
+        <v>395976957.20361203</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>50659108.379927002</v>
+        <v>56424982.309926003</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24128,11 +24128,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>296521225.34049201</v>
+        <v>312361408.84544998</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>77219728.510130003</v>
+        <v>78376728.510130003</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24140,27 +24140,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>461929828.20271999</v>
+        <v>475630323.88770801</v>
       </c>
       <c r="D16" s="205">
-        <v>83071133.272792995</v>
+        <v>85076007.132786006</v>
       </c>
       <c r="E16" s="205">
-        <v>30956603.27</v>
+        <v>31767414.07</v>
       </c>
       <c r="F16" s="205">
-        <v>575957564.74551296</v>
+        <v>592473745.09049404</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>436199054.44500101</v>
+        <v>465859381.86678499</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>39706137.095458999</v>
+        <v>40714137.095458999</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24168,27 +24168,27 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>275948197.43928999</v>
+        <v>312830431.85913801</v>
       </c>
       <c r="D17" s="205">
-        <v>49801992.810000002</v>
+        <v>50693884.710000001</v>
       </c>
       <c r="E17" s="205" t="s">
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>325750190.24928999</v>
+        <v>363524316.56913799</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>263441983.37547901</v>
+        <v>281014362.03701502</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>31184046.448995002</v>
+        <v>31377289.693994999</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24196,27 +24196,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>401343449.60298699</v>
+        <v>414904276.00798702</v>
       </c>
       <c r="D18" s="205">
-        <v>3209277.5299920002</v>
+        <v>3400376.6299919998</v>
       </c>
       <c r="E18" s="205">
-        <v>8770270.1600000001</v>
+        <v>8932432.3200000003</v>
       </c>
       <c r="F18" s="205">
-        <v>413322997.292979</v>
+        <v>427237084.95797902</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>637597986.04513395</v>
+        <v>670411415.19487202</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>104214483.32795499</v>
+        <v>166809077.126995</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24224,27 +24224,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>773550501.95899105</v>
+        <v>893006078.16387904</v>
       </c>
       <c r="D19" s="205">
-        <v>67497946.929836005</v>
+        <v>71857298.289833993</v>
       </c>
       <c r="E19" s="205">
-        <v>1135702830.3099501</v>
+        <v>1144280579.6099501</v>
       </c>
       <c r="F19" s="205">
-        <v>1976751279.198777</v>
+        <v>2109143956.063663</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>150424022.40743202</v>
+        <v>162167475.51242</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>121203268.486872</v>
+        <v>132022524.166824</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24252,16 +24252,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>101502221.907432</v>
+        <v>110428375.01242</v>
       </c>
       <c r="D20" s="205">
-        <v>21291124.199754</v>
+        <v>21539772.839754</v>
       </c>
       <c r="E20" s="205">
         <v>8237838</v>
       </c>
       <c r="F20" s="205">
-        <v>131031184.107186</v>
+        <v>140205985.85217401</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24279,23 +24279,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>48921800.5</v>
+        <v>51739100.5</v>
       </c>
       <c r="D21" s="205">
-        <v>99912144.287118003</v>
+        <v>110482751.32707</v>
       </c>
       <c r="E21" s="205">
-        <v>73005406.799999997</v>
+        <v>76810812.239999995</v>
       </c>
       <c r="F21" s="205">
-        <v>221839351.587118</v>
+        <v>239032664.06707001</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>718529893.468243</v>
+        <v>724412838.92821896</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24312,10 +24312,10 @@
         <v>168</v>
       </c>
       <c r="E22" s="205">
-        <v>7027026.8399999999</v>
+        <v>9369369.1199999992</v>
       </c>
       <c r="F22" s="205">
-        <v>191891998.13999999</v>
+        <v>194234340.41999999</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24326,16 +24326,16 @@
         <v>173</v>
       </c>
       <c r="C23" s="205">
-        <v>326478829.38</v>
+        <v>358352859.48000002</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>168</v>
       </c>
       <c r="E23" s="205">
-        <v>12750720.380000001</v>
+        <v>12870720.380000001</v>
       </c>
       <c r="F23" s="205">
-        <v>339229549.75999999</v>
+        <v>371223579.86000001</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24346,16 +24346,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>283224685.04754502</v>
+        <v>296324484.52852398</v>
       </c>
       <c r="D24" s="205">
-        <v>51991479.633472003</v>
+        <v>53198556.223471999</v>
       </c>
       <c r="E24" s="205">
-        <v>294606837.87987</v>
+        <v>354712671.39986998</v>
       </c>
       <c r="F24" s="205">
-        <v>629823002.56088698</v>
+        <v>704235712.15186596</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24366,16 +24366,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>380980784.24472702</v>
+        <v>395976957.20361203</v>
       </c>
       <c r="D25" s="205">
-        <v>50659108.379927002</v>
+        <v>56424982.309926003</v>
       </c>
       <c r="E25" s="205">
-        <v>237765903.78947899</v>
+        <v>248244358.60947901</v>
       </c>
       <c r="F25" s="205">
-        <v>669405796.41413295</v>
+        <v>700646298.12301695</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24386,16 +24386,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>436199054.44500101</v>
+        <v>465859381.86678499</v>
       </c>
       <c r="D26" s="205">
-        <v>39706137.095458999</v>
+        <v>40714137.095458999</v>
       </c>
       <c r="E26" s="205">
-        <v>487518294.9795</v>
+        <v>523397034.06948</v>
       </c>
       <c r="F26" s="205">
-        <v>963423486.51996005</v>
+        <v>1029970553.031724</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24406,16 +24406,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>637597986.04513395</v>
+        <v>670411415.19487202</v>
       </c>
       <c r="D27" s="205">
-        <v>104214483.32795499</v>
+        <v>166809077.126995</v>
       </c>
       <c r="E27" s="205">
         <v>15391027.368000001</v>
       </c>
       <c r="F27" s="205">
-        <v>757203496.74108899</v>
+        <v>852611519.68986702</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24458,7 +24458,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>170190736.42485401</v>
+        <v>172359227.41485301</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24469,7 +24469,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>236702305.72351599</v>
+        <v>279969644.74289101</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24480,7 +24480,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>141724449.52852201</v>
+        <v>146443071.10850999</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24491,7 +24491,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>576394443.93972099</v>
+        <v>577558767.81970894</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24543,7 +24543,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24586,19 +24586,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>5748786281.9882984</v>
+        <v>6144686779.1248751</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.79192245112359572</v>
+        <v>0.84645961370272216</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>1510493050.0117016</v>
+        <v>1114592552.8751249</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>251748841.66861692</v>
+        <v>222918510.57502499</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24615,19 +24615,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>819034978.91928697</v>
+        <v>911871556.31326008</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.45264929588846098</v>
+        <v>0.50395652020936232</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>990390080.08071303</v>
+        <v>897553502.68673992</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>165065013.34678552</v>
+        <v>179510700.53734797</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24644,19 +24644,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1125422935.6166129</v>
+        <v>1176741711.085963</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.61469933723490078</v>
+        <v>0.64272934823821526</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>705428128.38338709</v>
+        <v>654109352.91403699</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>117571354.73056452</v>
+        <v>130821870.58280739</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24671,19 +24671,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>7693244196.5241985</v>
+        <v>8233300046.5240984</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.70583100643751884</v>
+        <v>0.7553794354747928</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>3206311258.4758019</v>
+        <v>2666255408.4759016</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>534385209.74596697</v>
+        <v>533251081.6951803</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24704,10 +24704,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -24734,7 +24734,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24769,7 +24769,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24792,35 +24792,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>283224685.04754502</v>
+        <v>296324484.52852398</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>51991479.633472003</v>
+        <v>53198556.223471999</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>335216164.68101704</v>
+        <v>349523040.75199598</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.60561471730954242</v>
+        <v>0.63146208274179549</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>168458792.95245498</v>
+        <v>155358993.47147602</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>49838943.366527997</v>
+        <v>48631866.776528001</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>218297736.31898296</v>
+        <v>203990860.24800402</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>36382956.053163826</v>
+        <v>40798172.049600802</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24844,35 +24844,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>470556595.661156</v>
+        <v>496431704.69514</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>118996257.09874301</v>
+        <v>120019480.528742</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>589552852.75989902</v>
+        <v>616451185.22388196</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.72312115675233479</v>
+        <v>0.75611353936062609</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>119625775.338844</v>
+        <v>93750666.304859996</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>106110548.90125699</v>
+        <v>105087325.471258</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>225736324.24010098</v>
+        <v>198837991.77611804</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>37622720.706683494</v>
+        <v>39767598.355223611</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>9434716.1166666653</v>
+        <v>11321659.339999998</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24948,35 +24948,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>807067617.14033198</v>
+        <v>839454924.55033195</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>23489396.925105002</v>
+        <v>25301590.525097001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>830557014.06543696</v>
+        <v>864756515.07542896</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>1.1437748026692687</v>
+        <v>1.1908715423953258</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>-161355145.14033198</v>
+        <v>-193742452.55033195</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>56952451.074894994</v>
+        <v>55140257.474903002</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>-104402694.06543696</v>
+        <v>-138602195.07542896</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-17400449.01090616</v>
+        <v>-27720439.015085794</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25000,35 +25000,35 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>275948197.43928999</v>
+        <v>312830431.85913801</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>49801992.810000002</v>
+        <v>50693884.710000001</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>325750190.24928999</v>
+        <v>363524316.56913799</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.55264516340146275</v>
+        <v>0.6167301243232175</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>232970634.56071001</v>
+        <v>196088400.14086199</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>30717411.189999998</v>
+        <v>29825519.289999999</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>263688045.75071001</v>
+        <v>225913919.43086201</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>43948007.625118338</v>
+        <v>45182783.886172399</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25052,35 +25052,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>461929828.20271999</v>
+        <v>475630323.88770801</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>83071133.272792995</v>
+        <v>85076007.132786006</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>545000961.47551298</v>
+        <v>560706331.02049398</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>1.0436380740004556</v>
+        <v>1.0737127395185013</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>-21866544.202719986</v>
+        <v>-35567039.887708008</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>-921808.27279299498</v>
+        <v>-2926682.1327860057</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>-22788352.475512981</v>
+        <v>-38493722.020493984</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>-3798058.7459188304</v>
+        <v>-7698744.4040987967</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25104,35 +25104,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>773550501.95899105</v>
+        <v>893006078.16387904</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>67497946.929836005</v>
+        <v>71857298.289833993</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>841048448.88882709</v>
+        <v>964863376.45371306</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.74943260405818457</v>
+        <v>0.85976030718732199</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>223207843.04100895</v>
+        <v>103752266.83612096</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>57990651.070163995</v>
+        <v>53631299.710166007</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>281198494.11117291</v>
+        <v>157383566.54628694</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>46866415.685195483</v>
+        <v>31476713.309257388</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25156,35 +25156,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>380980784.24472702</v>
+        <v>395976957.20361203</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>50659108.379927002</v>
+        <v>56424982.309926003</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>431639892.624654</v>
+        <v>452401939.513538</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.67694574941182872</v>
+        <v>0.7095071035189684</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>159306274.75527298</v>
+        <v>144310101.79638797</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>46682317.620072998</v>
+        <v>40916443.690073997</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>205988592.375346</v>
+        <v>185226545.486462</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>34331432.062557667</v>
+        <v>37045309.097292401</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25208,7 +25208,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>326478829.38</v>
+        <v>358352859.48000002</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25216,15 +25216,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>326478829.38</v>
+        <v>358352859.48000002</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.80784863638580728</v>
+        <v>0.88671865623151858</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>77654834.620000005</v>
+        <v>45780804.519999981</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25232,11 +25232,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>77654834.620000005</v>
+        <v>45780804.519999981</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>12942472.436666667</v>
+        <v>9156160.9039999954</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25260,35 +25260,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>296521225.34049201</v>
+        <v>312361408.84544998</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>77219728.510130003</v>
+        <v>78376728.510130003</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>373740953.850622</v>
+        <v>390738137.35557997</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.61164555709711022</v>
+        <v>0.639462288624282</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>142496083.65950799</v>
+        <v>126655900.15455002</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>94804683.489869997</v>
+        <v>93647683.489869997</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>237300767.149378</v>
+        <v>220303583.64442003</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>39550127.858229667</v>
+        <v>44060716.728884004</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25312,35 +25312,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>436199054.44500101</v>
+        <v>465859381.86678499</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>39706137.095458999</v>
+        <v>40714137.095458999</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>475905191.54045999</v>
+        <v>506573518.96224397</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.62707288915404713</v>
+        <v>0.66748277966112601</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>230430541.55499899</v>
+        <v>200770214.13321501</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>52595484.904541001</v>
+        <v>51587484.904541001</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>283026026.45954001</v>
+        <v>252357699.03775603</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>47171004.409923337</v>
+        <v>50471539.807551205</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25364,35 +25364,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>263441983.37547901</v>
+        <v>281014362.03701502</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>31184046.448995002</v>
+        <v>31377289.693994999</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>294626029.82447404</v>
+        <v>312391651.73101002</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.56782550601059301</v>
+        <v>0.60206475247052571</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>158101039.62452099</v>
+        <v>140528660.96298498</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>66140129.551004998</v>
+        <v>65946886.306005001</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>224241169.17552596</v>
+        <v>206475547.26898998</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>37373528.195920996</v>
+        <v>41295109.453797996</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25416,35 +25416,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>637597986.04513395</v>
+        <v>670411415.19487202</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>104214483.32795499</v>
+        <v>166809077.126995</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>741812469.37308896</v>
+        <v>837220492.32186699</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.75562691006049054</v>
+        <v>0.85281167380097034</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>-19247044.045133948</v>
+        <v>-52060473.194872022</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>259152482.67204499</v>
+        <v>196557888.873005</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>239905438.62691104</v>
+        <v>144497415.67813301</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>39984239.771151841</v>
+        <v>28899483.135626603</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25468,35 +25468,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>150424022.40743202</v>
+        <v>162167475.51242</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>121203268.486872</v>
+        <v>132022524.166824</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>271627290.89430404</v>
+        <v>294189999.67924398</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.46348371226145929</v>
+        <v>0.50198296611731519</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>144101666.59256798</v>
+        <v>132358213.48758</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>170326784.51312798</v>
+        <v>159507528.83317602</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>314428451.10569596</v>
+        <v>291865742.32075602</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>52404741.850949325</v>
+        <v>58373148.464151204</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25518,35 +25518,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>5748786281.9882984</v>
+        <v>6144686779.1248751</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>819034978.91928697</v>
+        <v>911871556.31326008</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>6567821260.9075861</v>
+        <v>7056558335.4381351</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.72422928102338957</v>
+        <v>0.77812199308660157</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>1510493050.0117011</v>
+        <v>1114592552.8751249</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>990390080.08071303</v>
+        <v>897553502.68673992</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>2500883130.0924139</v>
+        <v>2012146055.5618649</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>416813855.01540232</v>
+        <v>402429211.11237299</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25587,7 +25587,7 @@
         <v>68</v>
       </c>
       <c r="D70" s="207">
-        <v>294606837.87987</v>
+        <v>354712671.39986998</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25598,7 +25598,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="192">
-        <v>74507827.320000008</v>
+        <v>78963773.239999995</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25609,7 +25609,7 @@
         <v>176</v>
       </c>
       <c r="D72" s="207">
-        <v>7027026.8399999999</v>
+        <v>9369369.1199999992</v>
       </c>
     </row>
     <row r="73" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25620,7 +25620,7 @@
         <v>72</v>
       </c>
       <c r="D73" s="207">
-        <v>219837802.21000001</v>
+        <v>235041405.61000001</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25643,7 +25643,7 @@
         <v>74</v>
       </c>
       <c r="D75" s="207">
-        <v>30956603.27</v>
+        <v>31767414.07</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25654,7 +25654,7 @@
         <v>77</v>
       </c>
       <c r="D76" s="207">
-        <v>1135702830.3099501</v>
+        <v>1144280579.6099501</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25665,7 +25665,7 @@
         <v>79</v>
       </c>
       <c r="D77" s="207">
-        <v>237765903.78947899</v>
+        <v>248244358.60947901</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25676,7 +25676,7 @@
         <v>177</v>
       </c>
       <c r="D78" s="207">
-        <v>12750720.380000001</v>
+        <v>12870720.380000001</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25698,7 +25698,7 @@
         <v>83</v>
       </c>
       <c r="D80" s="207">
-        <v>487518294.9795</v>
+        <v>523397034.06948</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25709,7 +25709,7 @@
         <v>85</v>
       </c>
       <c r="D81" s="207">
-        <v>130512645.09999999</v>
+        <v>134723140.53999999</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25731,7 +25731,7 @@
         <v>89</v>
       </c>
       <c r="D83" s="192">
-        <v>81243244.799999997</v>
+        <v>85048650.239999995</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25741,7 +25741,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>2731005448.9267993</v>
+        <v>2876994828.936779</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25755,13 +25755,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25803,19 +25803,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>170190736.42485401</v>
+        <v>172359227.41485301</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.59605087664595391</v>
+        <v>0.60364547893007092</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>115339816.57514599</v>
+        <v>113171325.58514699</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>19223302.762524333</v>
+        <v>22634265.117029399</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25832,19 +25832,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>236702305.72351599</v>
+        <v>279969644.74289101</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.5519704748797466</v>
+        <v>0.65286638120523677</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>192129156.27648401</v>
+        <v>148861817.25710899</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>32021526.046080668</v>
+        <v>29772363.451421797</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25861,19 +25861,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>718529893.468243</v>
+        <v>724412838.92821896</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.64356197144235761</v>
+        <v>0.6488311189232443</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>397959155.531757</v>
+        <v>392076210.07178104</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>66326525.921959497</v>
+        <v>78415242.014356211</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25946,24 +25946,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>1125422935.6166129</v>
+        <v>1176741711.085963</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.61469933723490078</v>
+        <v>0.64272934823821526</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>705428128.38338697</v>
+        <v>654109352.91403699</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>117571354.73056449</v>
+        <v>130821870.58280739</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25971,11 +25976,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26748,10 +26748,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -26778,7 +26778,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26813,7 +26813,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27812,13 +27812,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28021,6 +28021,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28028,11 +28033,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 25 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 26 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1931,6 +1931,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1950,15 +1959,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3603,10 +3603,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4667,13 +4667,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4876,11 +4876,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4888,6 +4883,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5660,10 +5660,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6724,13 +6724,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6933,11 +6933,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6945,6 +6940,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7717,10 +7717,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8781,13 +8781,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8990,11 +8990,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -9002,6 +8997,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9774,10 +9774,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10838,13 +10838,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11047,11 +11047,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11059,6 +11054,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11830,10 +11830,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12880,13 +12880,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13089,11 +13089,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13101,6 +13096,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22341,11 +22341,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="247" t="s">
+      <c r="B41" s="240" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="248"/>
-      <c r="D41" s="249"/>
+      <c r="C41" s="241"/>
+      <c r="D41" s="242"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>126558816.0423214</v>
+        <v>158198520.05290174</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>111117465.94333816</v>
+        <v>138896832.42917269</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22463,7 +22463,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>21954502.947942544</v>
+        <v>27443128.684928179</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22490,7 +22490,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>259630784.93360209</v>
+        <v>324538481.16700262</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22511,10 +22511,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22576,7 +22576,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22627,7 +22627,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>30388824.665312659</v>
+        <v>37986030.831640825</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22679,7 +22679,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>27189926.997453999</v>
+        <v>33987408.746817499</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>8781084.4399999976</v>
+        <v>10976355.549999997</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-8069741.4972054241</v>
+        <v>-10087176.87150678</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>26158875.522305228</v>
+        <v>32698594.402881533</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22887,7 +22887,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>16137500.890988732</v>
+        <v>20171876.113735914</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-5023427.1337479111</v>
+        <v>-6279283.9171848893</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>22162885.64705801</v>
+        <v>27703607.058822513</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>20722428.034004997</v>
+        <v>25903035.042506248</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>15122389.531456077</v>
+        <v>18902986.914320096</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23147,7 +23147,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>35447231.481175646</v>
+        <v>44309039.351469561</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>23674865.632434569</v>
+        <v>29593582.040543213</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>6921136.5925990818</v>
+        <v>8651420.7407488525</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23303,7 +23303,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>18062301.181824077</v>
+        <v>22577876.477280095</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>237676281.98565975</v>
+        <v>297095352.48207468</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23575,13 +23575,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-2672595.5832544924</v>
+        <v>-3340744.4790681154</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-3705896.5475764871</v>
+        <v>-4632370.6844706088</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23693,7 +23693,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>28332995.078773547</v>
+        <v>35416243.848466933</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23778,17 +23778,12 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>21954502.947942566</v>
+        <v>27443128.684928209</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23796,6 +23791,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23864,7 +23864,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23946,11 +23946,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>296324484.52852398</v>
+        <v>307512216.84291101</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>53198556.223471999</v>
+        <v>54527952.623471998</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23968,11 +23968,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>496431704.69514</v>
+        <v>517515831.07107496</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>120019480.528742</v>
+        <v>123132098.54624</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23980,27 +23980,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>281014362.03701502</v>
+        <v>292931454.361534</v>
       </c>
       <c r="D10" s="205">
-        <v>31377289.693994999</v>
+        <v>31937541.943994999</v>
       </c>
       <c r="E10" s="205">
-        <v>134723140.53999999</v>
+        <v>142800797.69999999</v>
       </c>
       <c r="F10" s="205">
-        <v>447114792.27100998</v>
+        <v>467669794.00552899</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>839454924.55033195</v>
+        <v>898160533.31131804</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>25301590.525097001</v>
+        <v>24163356.285101</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24008,23 +24008,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>312361408.84544998</v>
+        <v>317318391.50946999</v>
       </c>
       <c r="D11" s="205">
-        <v>78376728.510130003</v>
+        <v>81843497.900104001</v>
       </c>
       <c r="E11" s="205">
         <v>3184684.68</v>
       </c>
       <c r="F11" s="205">
-        <v>393922822.03557998</v>
+        <v>402346574.08957398</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>312830431.85913801</v>
+        <v>332352954.479056</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24036,27 +24036,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>280223965.94231999</v>
+        <v>286739281.25230497</v>
       </c>
       <c r="D12" s="205">
-        <v>73350909.038929</v>
+        <v>74036337.866427004</v>
       </c>
       <c r="E12" s="205">
-        <v>49116048.439999998</v>
+        <v>49640372.759999998</v>
       </c>
       <c r="F12" s="205">
-        <v>402690923.42124897</v>
+        <v>410415991.87873203</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>475630323.88770801</v>
+        <v>493878313.774674</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>85076007.132786006</v>
+        <v>87112399.032780007</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24064,27 +24064,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>216207738.75281999</v>
+        <v>230776549.81876999</v>
       </c>
       <c r="D13" s="205">
-        <v>46668571.489813</v>
+        <v>49095760.679812998</v>
       </c>
       <c r="E13" s="205">
-        <v>29847724.800000001</v>
+        <v>31661508.559999999</v>
       </c>
       <c r="F13" s="205">
-        <v>292724035.042633</v>
+        <v>311533819.05858302</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>893006078.16387904</v>
+        <v>921564482.62177896</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>71857298.289833993</v>
+        <v>72361298.289833993</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -24092,27 +24092,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>839454924.55033195</v>
+        <v>898160533.31131804</v>
       </c>
       <c r="D14" s="205">
-        <v>25301590.525097001</v>
+        <v>24163356.285101</v>
       </c>
       <c r="E14" s="205">
-        <v>235041405.61000001</v>
+        <v>246201946.16999999</v>
       </c>
       <c r="F14" s="205">
-        <v>1099797920.6854291</v>
+        <v>1168525835.7664189</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>395976957.20361203</v>
+        <v>416317893.77359599</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>56424982.309926003</v>
+        <v>66958412.969920002</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24128,11 +24128,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>312361408.84544998</v>
+        <v>317318391.50946999</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>78376728.510130003</v>
+        <v>81843497.900104001</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24140,27 +24140,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>475630323.88770801</v>
+        <v>493878313.774674</v>
       </c>
       <c r="D16" s="205">
-        <v>85076007.132786006</v>
+        <v>87112399.032780007</v>
       </c>
       <c r="E16" s="205">
         <v>31767414.07</v>
       </c>
       <c r="F16" s="205">
-        <v>592473745.09049404</v>
+        <v>612758126.87745404</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>465859381.86678499</v>
+        <v>478693393.16178501</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>40714137.095458999</v>
+        <v>45733404.635435</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24168,7 +24168,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>312830431.85913801</v>
+        <v>332352954.479056</v>
       </c>
       <c r="D17" s="205">
         <v>50693884.710000001</v>
@@ -24177,18 +24177,18 @@
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>363524316.56913799</v>
+        <v>383046839.18905598</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>281014362.03701502</v>
+        <v>292931454.361534</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>31377289.693994999</v>
+        <v>31937541.943994999</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24196,27 +24196,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>414904276.00798702</v>
+        <v>464434814.49798697</v>
       </c>
       <c r="D18" s="205">
         <v>3400376.6299919998</v>
       </c>
       <c r="E18" s="205">
-        <v>8932432.3200000003</v>
+        <v>9424918.8200000003</v>
       </c>
       <c r="F18" s="205">
-        <v>427237084.95797902</v>
+        <v>477260109.94797897</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>670411415.19487202</v>
+        <v>738384008.49471402</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>166809077.126995</v>
+        <v>218672139.56615499</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24224,27 +24224,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>893006078.16387904</v>
+        <v>921564482.62177896</v>
       </c>
       <c r="D19" s="205">
-        <v>71857298.289833993</v>
+        <v>72361298.289833993</v>
       </c>
       <c r="E19" s="205">
-        <v>1144280579.6099501</v>
+        <v>1179744362.44995</v>
       </c>
       <c r="F19" s="205">
-        <v>2109143956.063663</v>
+        <v>2173670143.3615632</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>162167475.51242</v>
+        <v>168164451.38244</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>132022524.166824</v>
+        <v>133030524.166824</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24252,16 +24252,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>110428375.01242</v>
+        <v>114780140.88244</v>
       </c>
       <c r="D20" s="205">
-        <v>21539772.839754</v>
+        <v>22547772.839754</v>
       </c>
       <c r="E20" s="205">
-        <v>8237838</v>
+        <v>9189189.3599999994</v>
       </c>
       <c r="F20" s="205">
-        <v>140205985.85217401</v>
+        <v>146517103.082194</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24279,23 +24279,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>51739100.5</v>
+        <v>53384310.5</v>
       </c>
       <c r="D21" s="205">
         <v>110482751.32707</v>
       </c>
       <c r="E21" s="205">
-        <v>76810812.239999995</v>
+        <v>78172974.439999998</v>
       </c>
       <c r="F21" s="205">
-        <v>239032664.06707001</v>
+        <v>242040036.26707</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>724412838.92821896</v>
+        <v>733293762.39116895</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24306,7 +24306,7 @@
         <v>172</v>
       </c>
       <c r="C22" s="205">
-        <v>184864971.30000001</v>
+        <v>167671841.09999999</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>168</v>
@@ -24315,7 +24315,7 @@
         <v>9369369.1199999992</v>
       </c>
       <c r="F22" s="205">
-        <v>194234340.41999999</v>
+        <v>177041210.22</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24326,7 +24326,7 @@
         <v>173</v>
       </c>
       <c r="C23" s="205">
-        <v>358352859.48000002</v>
+        <v>388937679.18000001</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>168</v>
@@ -24335,7 +24335,7 @@
         <v>12870720.380000001</v>
       </c>
       <c r="F23" s="205">
-        <v>371223579.86000001</v>
+        <v>401808399.56</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24346,16 +24346,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>296324484.52852398</v>
+        <v>307512216.84291101</v>
       </c>
       <c r="D24" s="205">
-        <v>53198556.223471999</v>
+        <v>54527952.623471998</v>
       </c>
       <c r="E24" s="205">
-        <v>354712671.39986998</v>
+        <v>366957716.21986997</v>
       </c>
       <c r="F24" s="205">
-        <v>704235712.15186596</v>
+        <v>728997885.68625295</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24366,16 +24366,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>395976957.20361203</v>
+        <v>416317893.77359599</v>
       </c>
       <c r="D25" s="205">
-        <v>56424982.309926003</v>
+        <v>66958412.969920002</v>
       </c>
       <c r="E25" s="205">
-        <v>248244358.60947901</v>
+        <v>264582197.19939399</v>
       </c>
       <c r="F25" s="205">
-        <v>700646298.12301695</v>
+        <v>747858503.94290996</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24386,16 +24386,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>465859381.86678499</v>
+        <v>478693393.16178501</v>
       </c>
       <c r="D26" s="205">
-        <v>40714137.095458999</v>
+        <v>45733404.635435</v>
       </c>
       <c r="E26" s="205">
-        <v>523397034.06948</v>
+        <v>542505052.36943495</v>
       </c>
       <c r="F26" s="205">
-        <v>1029970553.031724</v>
+        <v>1066931850.1666549</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24406,16 +24406,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>670411415.19487202</v>
+        <v>738384008.49471402</v>
       </c>
       <c r="D27" s="205">
-        <v>166809077.126995</v>
+        <v>218672139.56615499</v>
       </c>
       <c r="E27" s="205">
         <v>15391027.368000001</v>
       </c>
       <c r="F27" s="205">
-        <v>852611519.68986702</v>
+        <v>972447175.42886901</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24458,7 +24458,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>172359227.41485301</v>
+        <v>166220479.81494001</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24469,7 +24469,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>279969644.74289101</v>
+        <v>325138180.64759201</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24480,7 +24480,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>146443071.10850999</v>
+        <v>153935886.411484</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24491,7 +24491,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>577558767.81970894</v>
+        <v>578946875.97968495</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24543,7 +24543,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.83333333333333337</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24586,19 +24586,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>6144686779.1248751</v>
+        <v>6439403445.0643511</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.84645961370272216</v>
+        <v>0.88705822583221006</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>1114592552.8751249</v>
+        <v>819875886.93564892</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>222918510.57502499</v>
+        <v>204968971.73391223</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24615,19 +24615,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>911871556.31326008</v>
+        <v>990166510.66985989</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.50395652020936232</v>
+        <v>0.5472271458521123</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>897553502.68673992</v>
+        <v>819258548.33014011</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>179510700.53734797</v>
+        <v>204814637.08253503</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24644,19 +24644,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1176741711.085963</v>
+        <v>1224652422.8537011</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.64272934823821526</v>
+        <v>0.66889789504674924</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>654109352.91403699</v>
+        <v>606198641.14629889</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>130821870.58280739</v>
+        <v>151549660.28657472</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24671,19 +24671,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>8233300046.5240984</v>
+        <v>8654222378.5879116</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.7553794354747928</v>
+        <v>0.79399773819380159</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>2666255408.4759016</v>
+        <v>2245333076.4120879</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>533251081.6951803</v>
+        <v>561333269.10302198</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24704,10 +24704,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -24734,7 +24734,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24769,7 +24769,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24792,35 +24792,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>296324484.52852398</v>
+        <v>307512216.84291101</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>53198556.223471999</v>
+        <v>54527952.623471998</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>349523040.75199598</v>
+        <v>362040169.46638298</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.63146208274179549</v>
+        <v>0.65407602015470068</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>155358993.47147602</v>
+        <v>144171261.15708899</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>48631866.776528001</v>
+        <v>47302470.376528002</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>203990860.24800402</v>
+        <v>191473731.53361702</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>40798172.049600802</v>
+        <v>47868432.883404255</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24844,35 +24844,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>496431704.69514</v>
+        <v>517515831.07107496</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>120019480.528742</v>
+        <v>123132098.54624</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>616451185.22388196</v>
+        <v>640647929.61731493</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.75611353936062609</v>
+        <v>0.78579226572673477</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>93750666.304859996</v>
+        <v>72666539.928925037</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>105087325.471258</v>
+        <v>101974707.45376</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>198837991.77611804</v>
+        <v>174641247.38268507</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>39767598.355223611</v>
+        <v>43660311.845671266</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>184864971.30000001</v>
+        <v>167671841.09999999</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -24904,15 +24904,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>184864971.30000001</v>
+        <v>167671841.09999999</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.76557116583190488</v>
+        <v>0.69437019877496331</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>56608296.699999988</v>
+        <v>73801426.900000006</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -24920,11 +24920,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>56608296.699999988</v>
+        <v>73801426.900000006</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>11321659.339999998</v>
+        <v>18450356.725000001</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24948,35 +24948,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>839454924.55033195</v>
+        <v>898160533.31131804</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>25301590.525097001</v>
+        <v>24163356.285101</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>864756515.07542896</v>
+        <v>922323889.5964191</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>1.1908715423953258</v>
+        <v>1.2701485954065785</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>-193742452.55033195</v>
+        <v>-252448061.31131804</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>55140257.474903002</v>
+        <v>56278491.714899004</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>-138602195.07542896</v>
+        <v>-196169569.5964191</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-27720439.015085794</v>
+        <v>-49042392.399104774</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25000,7 +25000,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>312830431.85913801</v>
+        <v>332352954.479056</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25008,15 +25008,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>363524316.56913799</v>
+        <v>383046839.18905598</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.6167301243232175</v>
+        <v>0.64985068119852341</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>196088400.14086199</v>
+        <v>176565877.520944</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25024,11 +25024,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>225913919.43086201</v>
+        <v>206391396.81094402</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>45182783.886172399</v>
+        <v>51597849.202736005</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25052,35 +25052,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>475630323.88770801</v>
+        <v>493878313.774674</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>85076007.132786006</v>
+        <v>87112399.032780007</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>560706331.02049398</v>
+        <v>580990712.80745399</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>1.0737127395185013</v>
+        <v>1.1125558877638169</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>-35567039.887708008</v>
+        <v>-53815029.774673998</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>-2926682.1327860057</v>
+        <v>-4963074.0327800065</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>-38493722.020493984</v>
+        <v>-58778103.80745399</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>-7698744.4040987967</v>
+        <v>-14694525.951863497</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25104,35 +25104,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>893006078.16387904</v>
+        <v>921564482.62177896</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>71857298.289833993</v>
+        <v>72361298.289833993</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>964863376.45371306</v>
+        <v>993925780.91161299</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.85976030718732199</v>
+        <v>0.88565692881696978</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>103752266.83612096</v>
+        <v>75193862.378221035</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>53631299.710166007</v>
+        <v>53127299.710166007</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>157383566.54628694</v>
+        <v>128321162.08838701</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>31476713.309257388</v>
+        <v>32080290.522096753</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25156,35 +25156,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>395976957.20361203</v>
+        <v>416317893.77359599</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>56424982.309926003</v>
+        <v>66958412.969920002</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>452401939.513538</v>
+        <v>483276306.74351597</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.7095071035189684</v>
+        <v>0.75792772454874879</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>144310101.79638797</v>
+        <v>123969165.22640401</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>40916443.690073997</v>
+        <v>30383013.030079998</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>185226545.486462</v>
+        <v>154352178.25648403</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>37045309.097292401</v>
+        <v>38588044.564121008</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25208,7 +25208,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>358352859.48000002</v>
+        <v>388937679.18000001</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -25216,15 +25216,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>358352859.48000002</v>
+        <v>388937679.18000001</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.88671865623151858</v>
+        <v>0.96239861666163995</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>45780804.519999981</v>
+        <v>15195984.819999993</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -25232,11 +25232,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>45780804.519999981</v>
+        <v>15195984.819999993</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>9156160.9039999954</v>
+        <v>3798996.2049999982</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25260,35 +25260,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>312361408.84544998</v>
+        <v>317318391.50946999</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>78376728.510130003</v>
+        <v>81843497.900104001</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>390738137.35557997</v>
+        <v>399161889.40957397</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.639462288624282</v>
+        <v>0.65324817551954684</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>126655900.15455002</v>
+        <v>121698917.49053001</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>93647683.489869997</v>
+        <v>90180914.099895999</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>220303583.64442003</v>
+        <v>211879831.59042603</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>44060716.728884004</v>
+        <v>52969957.897606507</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25312,35 +25312,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>465859381.86678499</v>
+        <v>478693393.16178501</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>40714137.095458999</v>
+        <v>45733404.635435</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>506573518.96224397</v>
+        <v>524426797.79721999</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.66748277966112601</v>
+        <v>0.69100701797355768</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>200770214.13321501</v>
+        <v>187936202.83821499</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>51587484.904541001</v>
+        <v>46568217.364565</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>252357699.03775603</v>
+        <v>234504420.20278001</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>50471539.807551205</v>
+        <v>58626105.050695002</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25364,35 +25364,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>281014362.03701502</v>
+        <v>292931454.361534</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>31377289.693994999</v>
+        <v>31937541.943994999</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>312391651.73101002</v>
+        <v>324868996.305529</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.60206475247052571</v>
+        <v>0.62611203200287291</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>140528660.96298498</v>
+        <v>128611568.638466</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>65946886.306005001</v>
+        <v>65386634.056005001</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>206475547.26898998</v>
+        <v>193998202.694471</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>41295109.453797996</v>
+        <v>48499550.67361775</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25416,35 +25416,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>670411415.19487202</v>
+        <v>738384008.49471402</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>166809077.126995</v>
+        <v>218672139.56615499</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>837220492.32186699</v>
+        <v>957056148.06086898</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.85281167380097034</v>
+        <v>0.97487897517386324</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>-52060473.194872022</v>
+        <v>-120033066.49471402</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>196557888.873005</v>
+        <v>144694826.43384501</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>144497415.67813301</v>
+        <v>24661759.939131021</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>28899483.135626603</v>
+        <v>6165439.9847827554</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25468,35 +25468,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>162167475.51242</v>
+        <v>168164451.38244</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>132022524.166824</v>
+        <v>133030524.166824</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>294189999.67924398</v>
+        <v>301194975.54926401</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.50198296611731519</v>
+        <v>0.51393571287501183</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>132358213.48758</v>
+        <v>126361237.61756</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>159507528.83317602</v>
+        <v>158499528.83317602</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>291865742.32075602</v>
+        <v>284860766.45073599</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>58373148.464151204</v>
+        <v>71215191.612683997</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25518,35 +25518,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>6144686779.1248751</v>
+        <v>6439403445.0643511</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>911871556.31326008</v>
+        <v>990166510.66985989</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>7056558335.4381351</v>
+        <v>7429569955.7342119</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.77812199308660157</v>
+        <v>0.81925373630079901</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>1114592552.8751249</v>
+        <v>819875886.93564796</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>897553502.68673992</v>
+        <v>819258548.33014011</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>2012146055.5618649</v>
+        <v>1639134435.2657878</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>402429211.11237299</v>
+        <v>409783608.81644696</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25587,7 +25587,7 @@
         <v>68</v>
       </c>
       <c r="D70" s="207">
-        <v>354712671.39986998</v>
+        <v>366957716.21986997</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25598,7 +25598,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="192">
-        <v>78963773.239999995</v>
+        <v>81301881.319999993</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25620,7 +25620,7 @@
         <v>72</v>
       </c>
       <c r="D73" s="207">
-        <v>235041405.61000001</v>
+        <v>246201946.16999999</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25654,7 +25654,7 @@
         <v>77</v>
       </c>
       <c r="D76" s="207">
-        <v>1144280579.6099501</v>
+        <v>1179744362.44995</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25665,7 +25665,7 @@
         <v>79</v>
       </c>
       <c r="D77" s="207">
-        <v>248244358.60947901</v>
+        <v>264582197.19939399</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25698,7 +25698,7 @@
         <v>83</v>
       </c>
       <c r="D80" s="207">
-        <v>523397034.06948</v>
+        <v>542505052.36943495</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25709,7 +25709,7 @@
         <v>85</v>
       </c>
       <c r="D81" s="207">
-        <v>134723140.53999999</v>
+        <v>142800797.69999999</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25731,7 +25731,7 @@
         <v>89</v>
       </c>
       <c r="D83" s="192">
-        <v>85048650.239999995</v>
+        <v>87362163.799999997</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25741,7 +25741,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>2876994828.936779</v>
+        <v>2984039332.8466492</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25755,13 +25755,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25803,19 +25803,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>172359227.41485301</v>
+        <v>166220479.81494001</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.60364547893007092</v>
+        <v>0.58214603680237331</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>113171325.58514699</v>
+        <v>119310073.18505999</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>22634265.117029399</v>
+        <v>29827518.296264999</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25832,19 +25832,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>279969644.74289101</v>
+        <v>325138180.64759201</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.65286638120523677</v>
+        <v>0.75819572363277765</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>148861817.25710899</v>
+        <v>103693281.35240799</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>29772363.451421797</v>
+        <v>25923320.338101998</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25861,19 +25861,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>724412838.92821896</v>
+        <v>733293762.39116895</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.6488311189232443</v>
+        <v>0.65678544993159982</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>392076210.07178104</v>
+        <v>383195286.60883105</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>78415242.014356211</v>
+        <v>95798821.652207762</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25946,29 +25946,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>1176741711.085963</v>
+        <v>1224652422.8537011</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.64272934823821526</v>
+        <v>0.66889789504674924</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>654109352.91403699</v>
+        <v>606198641.146299</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>130821870.58280739</v>
+        <v>151549660.28657475</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25976,6 +25971,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26748,10 +26748,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -26778,7 +26778,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26813,7 +26813,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27812,13 +27812,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28021,11 +28021,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28033,6 +28028,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/randy/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380C3F88-9A9B-7140-AE9D-AAEC71ACB62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A8BEE9-F0B4-CD47-9CEF-5151DD8E9A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="15560" windowHeight="16400" tabRatio="500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1829,6 +1829,30 @@
     <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1860,30 +1884,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3426,11 +3426,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3554,10 +3554,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3586,40 +3586,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3627,13 +3627,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3652,7 +3652,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3662,7 +3662,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -4455,10 +4455,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4466,8 +4466,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -4661,13 +4661,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4870,11 +4870,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4882,6 +4877,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5483,11 +5483,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5611,10 +5611,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5643,40 +5643,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5684,13 +5684,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5709,7 +5709,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5719,7 +5719,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -6512,10 +6512,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6523,8 +6523,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -6718,13 +6718,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6927,11 +6927,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6939,6 +6934,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7540,11 +7540,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7668,10 +7668,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7700,40 +7700,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7741,13 +7741,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7766,7 +7766,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7776,7 +7776,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -8569,10 +8569,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8580,8 +8580,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -8775,13 +8775,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8984,11 +8984,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8996,6 +8991,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9597,11 +9597,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9725,10 +9725,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9757,40 +9757,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9798,13 +9798,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9823,7 +9823,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9833,7 +9833,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -10626,10 +10626,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10637,8 +10637,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -10832,13 +10832,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11041,11 +11041,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11053,6 +11048,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11654,11 +11654,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11781,10 +11781,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11813,40 +11813,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11854,13 +11854,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11879,7 +11879,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11889,7 +11889,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -12668,10 +12668,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12679,8 +12679,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -12874,13 +12874,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13083,11 +13083,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13095,6 +13090,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -18409,10 +18409,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B44" s="222" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="223"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18477,23 +18477,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="205" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="205" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="212" t="s">
+      <c r="D47" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="213"/>
-      <c r="F47" s="214"/>
+      <c r="E47" s="221"/>
+      <c r="F47" s="222"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="205" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18506,8 +18506,8 @@
       </c>
     </row>
     <row r="48" spans="2:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="B48" s="205"/>
-      <c r="C48" s="205"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18526,7 +18526,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="205"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -20158,11 +20158,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20280,10 +20280,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20306,17 +20306,17 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
       <c r="K48" s="241"/>
       <c r="L48" s="242"/>
       <c r="M48" s="242"/>
@@ -21173,10 +21173,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21187,8 +21187,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -21374,13 +21374,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="219" t="s">
+      <c r="B87" s="208" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="220"/>
-      <c r="D87" s="220"/>
-      <c r="E87" s="220"/>
-      <c r="F87" s="221"/>
+      <c r="C87" s="209"/>
+      <c r="D87" s="209"/>
+      <c r="E87" s="209"/>
+      <c r="F87" s="210"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -22462,10 +22462,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
@@ -22494,40 +22494,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22535,13 +22535,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22560,7 +22560,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22570,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="201" t="s">
@@ -23363,10 +23363,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23374,8 +23374,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -23569,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23778,11 +23778,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23790,6 +23785,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -24531,11 +24531,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -24659,10 +24659,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10899555455</v>
@@ -24691,40 +24691,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24732,13 +24732,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24757,7 +24757,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24767,7 +24767,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -25560,10 +25560,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25571,8 +25571,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -25766,13 +25766,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25975,11 +25975,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25987,6 +25982,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26588,11 +26588,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="205" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="207"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26716,10 +26716,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="212"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26748,40 +26748,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="211"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="210"/>
+      <c r="K48" s="217"/>
+      <c r="L48" s="218"/>
+      <c r="M48" s="218"/>
+      <c r="N48" s="219"/>
     </row>
     <row r="49" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="212" t="s">
+      <c r="D49" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="213"/>
-      <c r="F49" s="214"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="205" t="s">
+      <c r="J49" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26789,13 +26789,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="215" t="s">
+      <c r="N49" s="223" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="205"/>
-      <c r="C50" s="205"/>
+      <c r="B50" s="213"/>
+      <c r="C50" s="213"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26814,7 +26814,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="205"/>
+      <c r="J50" s="213"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26824,7 +26824,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="215"/>
+      <c r="N50" s="223"/>
     </row>
     <row r="51" spans="2:14" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="50" t="s">
@@ -27617,10 +27617,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="205" t="s">
+      <c r="B68" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="205" t="s">
+      <c r="C68" s="213" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27628,8 +27628,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="205"/>
-      <c r="C69" s="205"/>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -27823,13 +27823,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B87" s="206" t="s">
+      <c r="B87" s="214" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="207"/>
-      <c r="D87" s="207"/>
-      <c r="E87" s="207"/>
-      <c r="F87" s="208"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="216"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28032,11 +28032,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28044,6 +28039,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 29 JUNI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 30 JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1931,6 +1931,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1950,15 +1959,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3603,10 +3603,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4667,13 +4667,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4876,11 +4876,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4888,6 +4883,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5660,10 +5660,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6724,13 +6724,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6933,11 +6933,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6945,6 +6940,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7717,10 +7717,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8781,13 +8781,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8990,11 +8990,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -9002,6 +8997,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9774,10 +9774,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10838,13 +10838,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11047,11 +11047,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11059,6 +11054,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11830,10 +11830,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12880,13 +12880,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13089,11 +13089,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13101,6 +13096,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22341,11 +22341,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="247" t="s">
+      <c r="B41" s="240" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="248"/>
-      <c r="D41" s="249"/>
+      <c r="C41" s="241"/>
+      <c r="D41" s="242"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>316397040.10580349</v>
+        <v>632794080.21160698</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>277793664.85834539</v>
+        <v>555587329.71669078</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22463,7 +22463,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>54886257.369856358</v>
+        <v>109772514.73971272</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22490,7 +22490,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>649076962.33400524</v>
+        <v>1298153924.6680105</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22511,10 +22511,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22576,7 +22576,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22627,7 +22627,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>75972061.663281649</v>
+        <v>151944123.3265633</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22679,7 +22679,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>67974817.493634999</v>
+        <v>135949634.98727</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>21952711.099999994</v>
+        <v>43905422.199999988</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-20174353.743013561</v>
+        <v>-40348707.486027122</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>65397188.805763066</v>
+        <v>130794377.61152613</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22887,7 +22887,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>40343752.227471828</v>
+        <v>80687504.454943657</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-12558567.834369779</v>
+        <v>-25117135.668739557</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>55407214.117645025</v>
+        <v>110814428.23529005</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>51806070.085012496</v>
+        <v>103612140.17002499</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>37805973.828640193</v>
+        <v>75611947.657280385</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23147,7 +23147,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>88618078.702939123</v>
+        <v>177236157.40587825</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>59187164.081086427</v>
+        <v>118374328.16217285</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>17302841.481497705</v>
+        <v>34605682.96299541</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23303,7 +23303,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>45155752.95456019</v>
+        <v>90311505.909120381</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>594190704.96414936</v>
+        <v>1188381409.9282987</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23575,13 +23575,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-6681488.9581362307</v>
+        <v>-13362977.916272461</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-9264741.3689412177</v>
+        <v>-18529482.737882435</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23693,7 +23693,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>70832487.696933866</v>
+        <v>141664975.39386773</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23778,17 +23778,12 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>54886257.369856417</v>
+        <v>109772514.73971283</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23796,6 +23791,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23864,7 +23864,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23946,11 +23946,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>314464563.64290702</v>
+        <v>320575286.94788897</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>54527952.623471998</v>
+        <v>55052087.763467997</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -23968,11 +23968,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>539289858.77096295</v>
+        <v>548772948.85095096</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>129784616.66623899</v>
+        <v>130737490.55623899</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -23980,27 +23980,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>305145633.79370898</v>
+        <v>322280851.83509499</v>
       </c>
       <c r="D10" s="205">
-        <v>34369341.943994999</v>
+        <v>34873341.943994999</v>
       </c>
       <c r="E10" s="205">
-        <v>150004401.21000001</v>
+        <v>158162238.56999999</v>
       </c>
       <c r="F10" s="205">
-        <v>489519376.94770402</v>
+        <v>515316432.34908998</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>952550276.47129405</v>
+        <v>989456477.77127802</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>24359117.545101002</v>
+        <v>37132037.007500999</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -24008,23 +24008,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>334432576.36944002</v>
+        <v>350800236.759597</v>
       </c>
       <c r="D11" s="205">
-        <v>81843497.900104001</v>
+        <v>84864795.200103998</v>
       </c>
       <c r="E11" s="205">
-        <v>3184684.68</v>
+        <v>22719654.219999999</v>
       </c>
       <c r="F11" s="205">
-        <v>419460758.94954401</v>
+        <v>458384686.17970097</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>344289891.47900599</v>
+        <v>368163765.47890598</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -24036,27 +24036,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>301139434.99221802</v>
+        <v>307172074.63220602</v>
       </c>
       <c r="D12" s="205">
-        <v>78169315.436425999</v>
+        <v>78765432.566425994</v>
       </c>
       <c r="E12" s="205">
-        <v>52248480.840000004</v>
+        <v>52572805.159999996</v>
       </c>
       <c r="F12" s="205">
-        <v>431557231.26864398</v>
+        <v>438510312.35863203</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>507865455.227467</v>
+        <v>517028510.48846501</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>87700399.032780007</v>
+        <v>88679408.048779994</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -24064,23 +24064,23 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>238150423.778745</v>
+        <v>241600874.21874499</v>
       </c>
       <c r="D13" s="205">
-        <v>51615301.229813002</v>
+        <v>51972057.989813</v>
       </c>
       <c r="E13" s="205">
-        <v>31661508.559999999</v>
+        <v>36793625.659999996</v>
       </c>
       <c r="F13" s="205">
-        <v>321427233.56855798</v>
+        <v>330366557.86855799</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>950150884.01525795</v>
+        <v>1002756079.983186</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
@@ -24092,27 +24092,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>952550276.47129405</v>
+        <v>989456477.77127802</v>
       </c>
       <c r="D14" s="205">
-        <v>24359117.545101002</v>
+        <v>37132037.007500999</v>
       </c>
       <c r="E14" s="205">
-        <v>255942486.59</v>
+        <v>266587982.37</v>
       </c>
       <c r="F14" s="205">
-        <v>1232851880.606395</v>
+        <v>1293176497.1487789</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>428386511.85815603</v>
+        <v>461849289.23312598</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>70966633.229874</v>
+        <v>75489696.329871997</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -24128,11 +24128,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>334432576.36944002</v>
+        <v>350800236.759597</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>81843497.900104001</v>
+        <v>84864795.200103998</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -24140,27 +24140,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>507865455.227467</v>
+        <v>517028510.48846501</v>
       </c>
       <c r="D16" s="205">
-        <v>87700399.032780007</v>
+        <v>88679408.048779994</v>
       </c>
       <c r="E16" s="205">
-        <v>31767414.07</v>
+        <v>34044891.530000001</v>
       </c>
       <c r="F16" s="205">
-        <v>627333268.33024704</v>
+        <v>639752810.06724501</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>495799375.38565201</v>
+        <v>508735877.73760903</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>48541692.915432997</v>
+        <v>51169801.005402997</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -24168,7 +24168,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>344289891.47900599</v>
+        <v>368163765.47890598</v>
       </c>
       <c r="D17" s="205">
         <v>50693884.710000001</v>
@@ -24177,18 +24177,18 @@
         <v>168</v>
       </c>
       <c r="F17" s="205">
-        <v>394983776.18900597</v>
+        <v>418857650.18890601</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>305145633.79370898</v>
+        <v>322280851.83509499</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>34369341.943994999</v>
+        <v>34873341.943994999</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -24196,27 +24196,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>469756661.567985</v>
+        <v>511987771.98278302</v>
       </c>
       <c r="D18" s="205">
         <v>7135511.989968</v>
       </c>
       <c r="E18" s="205">
-        <v>10397891.779999999</v>
+        <v>11708702.58</v>
       </c>
       <c r="F18" s="205">
-        <v>487290065.33795297</v>
+        <v>530831986.552751</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>758764234.07459402</v>
+        <v>789357999.90691698</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>225366001.69207501</v>
+        <v>235212300.73199099</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -24224,27 +24224,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>950150884.01525795</v>
+        <v>1002756079.983186</v>
       </c>
       <c r="D19" s="205">
         <v>72945098.289833993</v>
       </c>
       <c r="E19" s="205">
-        <v>1206933551.7499499</v>
+        <v>1329858796.62995</v>
       </c>
       <c r="F19" s="205">
-        <v>2230029534.0550418</v>
+        <v>2405559974.9029698</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>174186816.50234002</v>
+        <v>186367654.50230998</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>133030524.166824</v>
+        <v>152552071.034646</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -24252,7 +24252,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>120802506.00234</v>
+        <v>127200704.00230999</v>
       </c>
       <c r="D20" s="205">
         <v>22547772.839754</v>
@@ -24261,7 +24261,7 @@
         <v>10497297.48</v>
       </c>
       <c r="F20" s="205">
-        <v>153847576.32209399</v>
+        <v>160245774.32206401</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -24279,23 +24279,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>53384310.5</v>
+        <v>59166950.5</v>
       </c>
       <c r="D21" s="205">
-        <v>110482751.32707</v>
+        <v>130004298.194892</v>
       </c>
       <c r="E21" s="205">
-        <v>80108109.620000005</v>
+        <v>89578380.079999998</v>
       </c>
       <c r="F21" s="205">
-        <v>243975171.44707</v>
+        <v>278749628.77489197</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>1137168700.515739</v>
+        <v>1208589913.9548378</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -24312,10 +24312,10 @@
         <v>168</v>
       </c>
       <c r="E22" s="205">
-        <v>9369369.1199999992</v>
+        <v>12540540.199999999</v>
       </c>
       <c r="F22" s="205">
-        <v>177041210.22</v>
+        <v>180212381.30000001</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -24332,10 +24332,10 @@
         <v>168</v>
       </c>
       <c r="E23" s="205">
-        <v>12870720.380000001</v>
+        <v>17519368.899999999</v>
       </c>
       <c r="F23" s="205">
-        <v>401808399.56</v>
+        <v>406457048.07999998</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -24346,16 +24346,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>314464563.64290702</v>
+        <v>320575286.94788897</v>
       </c>
       <c r="D24" s="205">
-        <v>54527952.623471998</v>
+        <v>55052087.763467997</v>
       </c>
       <c r="E24" s="205">
-        <v>366957716.21986997</v>
+        <v>379329022.35987002</v>
       </c>
       <c r="F24" s="205">
-        <v>735950232.48624897</v>
+        <v>754956397.07122695</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -24366,16 +24366,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>428386511.85815603</v>
+        <v>461849289.23312598</v>
       </c>
       <c r="D25" s="205">
-        <v>70966633.229874</v>
+        <v>75489696.329871997</v>
       </c>
       <c r="E25" s="205">
-        <v>272870485.819354</v>
+        <v>314812287.69929397</v>
       </c>
       <c r="F25" s="205">
-        <v>772223630.90738404</v>
+        <v>852151273.26229203</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -24386,16 +24386,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>495799375.38565201</v>
+        <v>508735877.73760903</v>
       </c>
       <c r="D26" s="205">
-        <v>48541692.915432997</v>
+        <v>51169801.005402997</v>
       </c>
       <c r="E26" s="205">
-        <v>560811358.64941502</v>
+        <v>581028250.50941503</v>
       </c>
       <c r="F26" s="205">
-        <v>1105152426.9505</v>
+        <v>1140933929.2524271</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -24406,16 +24406,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>758764234.07459402</v>
+        <v>789357999.90691698</v>
       </c>
       <c r="D27" s="205">
-        <v>225366001.69207501</v>
+        <v>235212300.73199099</v>
       </c>
       <c r="E27" s="205">
-        <v>15391027.368000001</v>
+        <v>17184216.607000001</v>
       </c>
       <c r="F27" s="205">
-        <v>999521263.13466895</v>
+        <v>1041754517.245908</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -24458,7 +24458,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>181126497.71479499</v>
+        <v>185272533.73476499</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -24469,7 +24469,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>326116378.85758996</v>
+        <v>334871676.45744997</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -24480,7 +24480,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>161002165.86935601</v>
+        <v>164253111.869317</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -24491,7 +24491,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>666521284.65138304</v>
+        <v>734691552.09052098</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -24543,7 +24543,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=6,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;6,1,0))</f>
-        <v>0.96666666666666667</v>
+        <v>1</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -24586,19 +24586,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>6661935597.8707867</v>
+        <v>6922754499.7753286</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.91771308048499634</v>
+        <v>0.95364211558284873</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>597343734.12921333</v>
+        <v>336524832.22467136</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>298671867.06460667</v>
+        <v>336524832.22467136</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -24615,19 +24615,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>1014128760.7157311</v>
+        <v>1069402012.6218331</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.56047016463682742</v>
+        <v>0.59101757616469108</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>795296298.28426886</v>
+        <v>740023046.37816691</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>397648149.14213443</v>
+        <v>740023046.37816691</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -24644,19 +24644,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1644411577.0881238</v>
+        <v>1728734124.1470528</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.89816785724528148</v>
+        <v>0.9442243326828319</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>186439486.9118762</v>
+        <v>102116939.85294724</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>93219743.455938101</v>
+        <v>102116939.85294724</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -24671,19 +24671,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>9320475935.6746407</v>
+        <v>9720890636.5442142</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.85512441072989065</v>
+        <v>0.89186120265894953</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>1579079519.3253584</v>
+        <v>1178664818.4557855</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>789539759.6626792</v>
+        <v>1178664818.4557855</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -24704,10 +24704,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -24734,7 +24734,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24769,7 +24769,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24792,35 +24792,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>314464563.64290702</v>
+        <v>320575286.94788897</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>54527952.623471998</v>
+        <v>55052087.763467997</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>368992516.266379</v>
+        <v>375627374.711357</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.6666364035297806</v>
+        <v>0.6786231999462593</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>137218914.35709298</v>
+        <v>131108191.05211103</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>47302470.376528002</v>
+        <v>46778335.236532003</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>184521384.733621</v>
+        <v>177886526.288643</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>92260692.366810501</v>
+        <v>177886526.288643</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24844,35 +24844,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>539289858.77096295</v>
+        <v>548772948.85095096</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>129784616.66623899</v>
+        <v>130737490.55623899</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>669074475.43720198</v>
+        <v>679510439.40718997</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.82065909166018769</v>
+        <v>0.83345941363721787</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>50892512.229037046</v>
+        <v>41409422.149049044</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>95322189.333761007</v>
+        <v>94369315.443761006</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>146214701.56279802</v>
+        <v>135778737.59281003</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>73107350.781399012</v>
+        <v>135778737.59281003</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>36900713.450000003</v>
+        <v>73801426.900000006</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24948,35 +24948,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>952550276.47129405</v>
+        <v>989456477.77127802</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>24359117.545101002</v>
+        <v>37132037.007500999</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>976909394.01639509</v>
+        <v>1026588514.778779</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>1.3453192621871273</v>
+        <v>1.4137332609668687</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>-306837804.47129405</v>
+        <v>-343744005.77127802</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>56082730.454898998</v>
+        <v>43309810.992499001</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>-250755074.01639509</v>
+        <v>-300434194.77877903</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-125377537.00819755</v>
+        <v>-300434194.77877903</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25000,7 +25000,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>344289891.47900599</v>
+        <v>368163765.47890598</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -25008,15 +25008,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>394983776.18900597</v>
+        <v>418857650.18890595</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.67010206000447847</v>
+        <v>0.71060481761638883</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>164628940.52099401</v>
+        <v>140755066.52109402</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -25024,11 +25024,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>194454459.81099403</v>
+        <v>170580585.81109405</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>97227229.905497015</v>
+        <v>170580585.81109405</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25052,35 +25052,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>507865455.227467</v>
+        <v>517028510.48846501</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>87700399.032780007</v>
+        <v>88679408.048779994</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>595565854.26024699</v>
+        <v>605707918.53724504</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>1.1404662468811568</v>
+        <v>1.1598875785422582</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>-67802171.227467</v>
+        <v>-76965226.488465011</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>-5551074.0327800065</v>
+        <v>-6530083.0487799942</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>-73353245.260246992</v>
+        <v>-83495309.537245035</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>-36676622.630123496</v>
+        <v>-83495309.537245035</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25104,7 +25104,7 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>950150884.01525795</v>
+        <v>1002756079.983186</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
@@ -25112,15 +25112,15 @@
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>1023095982.305092</v>
+        <v>1075701178.27302</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.91164960500595627</v>
+        <v>0.95852448962564918</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>46607460.984742045</v>
+        <v>-5997734.9831860065</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
@@ -25128,11 +25128,11 @@
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>99150960.694908023</v>
+        <v>46545764.726979971</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>49575480.347454011</v>
+        <v>46545764.726979971</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25156,35 +25156,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>428386511.85815603</v>
+        <v>461849289.23312598</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>70966633.229874</v>
+        <v>75489696.329871997</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>499353145.08803004</v>
+        <v>537338985.56299794</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.78314121284595695</v>
+        <v>0.84271483819139281</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>111900547.14184397</v>
+        <v>78437769.766874015</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>26374792.770126</v>
+        <v>21851729.670128003</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>138275339.91196996</v>
+        <v>100289499.43700206</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>69137669.95598498</v>
+        <v>100289499.43700206</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>7597992.4099999964</v>
+        <v>15195984.819999993</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25260,35 +25260,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>334432576.36944002</v>
+        <v>350800236.759597</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>81843497.900104001</v>
+        <v>84864795.200103998</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>416276074.26954401</v>
+        <v>435665031.959701</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.68125638555136236</v>
+        <v>0.71298737383547828</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>104584732.63055998</v>
+        <v>88217072.240402997</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>90180914.099895999</v>
+        <v>87159616.799896002</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>194765646.73045599</v>
+        <v>175376689.040299</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>97382823.365227997</v>
+        <v>175376689.040299</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25312,35 +25312,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>495799375.38565201</v>
+        <v>508735877.73760903</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>48541692.915432997</v>
+        <v>51169801.005402997</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>544341068.301085</v>
+        <v>559905678.74301207</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.7172469064266177</v>
+        <v>0.73775549807863094</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>170830220.61434799</v>
+        <v>157893718.26239097</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>43759929.084567003</v>
+        <v>41131820.994597003</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>214590149.698915</v>
+        <v>199025539.25698793</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>107295074.8494575</v>
+        <v>199025539.25698793</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25364,35 +25364,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>305145633.79370898</v>
+        <v>322280851.83509499</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>34369341.943994999</v>
+        <v>34873341.943994999</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>339514975.73770398</v>
+        <v>357154193.77908999</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.65433886819602949</v>
+        <v>0.6883344995933921</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>116397389.20629102</v>
+        <v>99262171.164905012</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>62954834.056005001</v>
+        <v>62450834.056005001</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>179352223.26229602</v>
+        <v>161713005.22091001</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>89676111.63114801</v>
+        <v>161713005.22091001</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25416,35 +25416,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>758764234.07459402</v>
+        <v>789357999.90691698</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>225366001.69207501</v>
+        <v>235212300.73199099</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>984130235.76666903</v>
+        <v>1024570300.6389079</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>1.0024572514640011</v>
+        <v>1.0436504135146203</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>-140413292.07459402</v>
+        <v>-171007057.90691698</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>138000964.30792499</v>
+        <v>128154665.26800901</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>-2412327.766669035</v>
+        <v>-42852392.638907909</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>-1206163.8833345175</v>
+        <v>-42852392.638907909</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25468,35 +25468,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>174186816.50234002</v>
+        <v>186367654.50230998</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>133030524.166824</v>
+        <v>152552071.034646</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>307217340.669164</v>
+        <v>338919725.53695595</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.52421180896673814</v>
+        <v>0.57830629622421814</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>120338872.49765998</v>
+        <v>108158034.49769002</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>158499528.83317602</v>
+        <v>138977981.965354</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>278838401.330836</v>
+        <v>247136016.46304405</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>139419200.665418</v>
+        <v>247136016.46304405</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25518,35 +25518,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>6661935597.8707867</v>
+        <v>6922754499.7753286</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>1014128760.7157311</v>
+        <v>1069402012.6218331</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>7676064358.5865164</v>
+        <v>7992156512.3971605</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.84643451011639848</v>
+        <v>0.88128978162842853</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>597343734.12921405</v>
+        <v>336524832.22467113</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>795296298.28426898</v>
+        <v>740023046.37816703</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>1392640032.4134829</v>
+        <v>1076547878.602838</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>696320016.20674145</v>
+        <v>1076547878.602838</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -25587,7 +25587,7 @@
         <v>68</v>
       </c>
       <c r="D70" s="207">
-        <v>366957716.21986997</v>
+        <v>379329022.35987002</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25598,7 +25598,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="192">
-        <v>83909989.400000006</v>
+        <v>89366430.819999993</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25609,7 +25609,7 @@
         <v>176</v>
       </c>
       <c r="D72" s="207">
-        <v>9369369.1199999992</v>
+        <v>12540540.199999999</v>
       </c>
     </row>
     <row r="73" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25620,7 +25620,7 @@
         <v>72</v>
       </c>
       <c r="D73" s="207">
-        <v>255942486.59</v>
+        <v>266587982.37</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25643,7 +25643,7 @@
         <v>74</v>
       </c>
       <c r="D75" s="207">
-        <v>31767414.07</v>
+        <v>34044891.530000001</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25654,7 +25654,7 @@
         <v>77</v>
       </c>
       <c r="D76" s="207">
-        <v>1206933551.7499499</v>
+        <v>1329858796.62995</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25665,7 +25665,7 @@
         <v>79</v>
       </c>
       <c r="D77" s="207">
-        <v>272870485.819354</v>
+        <v>314812287.69929397</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25676,7 +25676,7 @@
         <v>177</v>
       </c>
       <c r="D78" s="207">
-        <v>12870720.380000001</v>
+        <v>17519368.899999999</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25687,7 +25687,7 @@
         <v>81</v>
       </c>
       <c r="D79" s="207">
-        <v>3184684.68</v>
+        <v>22719654.219999999</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25698,7 +25698,7 @@
         <v>83</v>
       </c>
       <c r="D80" s="207">
-        <v>560811358.64941502</v>
+        <v>581028250.50941503</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25709,7 +25709,7 @@
         <v>85</v>
       </c>
       <c r="D81" s="207">
-        <v>150004401.21000001</v>
+        <v>158162238.56999999</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25720,7 +25720,7 @@
         <v>87</v>
       </c>
       <c r="D82" s="207">
-        <v>15391027.368000001</v>
+        <v>17184216.607000001</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25731,7 +25731,7 @@
         <v>89</v>
       </c>
       <c r="D83" s="192">
-        <v>90605407.100000009</v>
+        <v>100075677.56</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25741,7 +25741,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>3060618612.3565888</v>
+        <v>3323229357.9755292</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -25755,13 +25755,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25803,19 +25803,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>181126497.71479499</v>
+        <v>185272533.73476499</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.63435067039846693</v>
+        <v>0.64887113406306818</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>104404055.28520501</v>
+        <v>100258019.26523501</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>52202027.642602503</v>
+        <v>100258019.26523501</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -25832,19 +25832,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>326116378.85758996</v>
+        <v>334871676.45744997</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.76047680209058444</v>
+        <v>0.78089344213613221</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>102715083.14241004</v>
+        <v>93959785.542550027</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>51357541.57120502</v>
+        <v>93959785.542550027</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -25861,19 +25861,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>1137168700.515739</v>
+        <v>1208589913.9548378</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>1.0185220370358858</v>
+        <v>1.08249150767518</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>-20679651.515738964</v>
+        <v>-92100864.954837799</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>-10339825.757869482</v>
+        <v>-92100864.954837799</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -25946,29 +25946,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>1644411577.0881238</v>
+        <v>1728734124.1470528</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.89816785724528148</v>
+        <v>0.9442243326828319</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>186439486.91187608</v>
+        <v>102116939.85294724</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>93219743.455938041</v>
+        <v>102116939.85294724</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25976,6 +25971,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26748,10 +26748,10 @@
       <c r="H48" s="231"/>
       <c r="I48" s="231"/>
       <c r="J48" s="232"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="244"/>
-      <c r="N48" s="245"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="247"/>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="225" t="s">
@@ -26778,7 +26778,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="246" t="s">
+      <c r="N49" s="249" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26813,7 +26813,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="246"/>
+      <c r="N50" s="249"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27812,13 +27812,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="240" t="s">
+      <c r="B87" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="241"/>
-      <c r="D87" s="241"/>
-      <c r="E87" s="241"/>
-      <c r="F87" s="242"/>
+      <c r="C87" s="244"/>
+      <c r="D87" s="244"/>
+      <c r="E87" s="244"/>
+      <c r="F87" s="245"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -28021,11 +28021,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -28033,6 +28028,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9195" windowHeight="7290" tabRatio="500" firstSheet="1" activeTab="7"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" tabRatio="500" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -47,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="186">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -584,9 +583,6 @@
     <t>NN SUJANA</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — JULI 2026</t>
-  </si>
-  <si>
     <t>DATA PENCAPAIAN — GLOBAL — NOVEMBER 2026</t>
   </si>
   <si>
@@ -603,6 +599,12 @@
   </si>
   <si>
     <t>DATA PENCAPAIAN — GLOBAL — 30 JUNI 2026</t>
+  </si>
+  <si>
+    <t>EKA FIB</t>
+  </si>
+  <si>
+    <t>DATA PENCAPAIAN — GLOBAL —  01 JULI 2026</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1232,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1828,13 +1830,7 @@
     <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1931,15 +1927,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1960,6 +1947,18 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2716,16 +2715,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="208" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="208"/>
+      <c r="B1" s="206" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="206"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="209"/>
+      <c r="C3" s="207"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2776,10 +2775,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="210" t="s">
+      <c r="B11" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="210"/>
+      <c r="C11" s="208"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -3432,11 +3431,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="226" t="s">
+      <c r="B41" s="224" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="227"/>
-      <c r="D41" s="228"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3560,10 +3559,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="223" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="224"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3592,40 +3591,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="230" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="231"/>
-      <c r="D48" s="231"/>
-      <c r="E48" s="231"/>
-      <c r="F48" s="231"/>
-      <c r="G48" s="231"/>
-      <c r="H48" s="231"/>
-      <c r="I48" s="231"/>
-      <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="225" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="225" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="225" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3633,13 +3632,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="225"/>
-      <c r="C50" s="225"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3658,7 +3657,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="225"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3668,7 +3667,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4461,10 +4460,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="225" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="225" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4472,8 +4471,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="225"/>
-      <c r="C69" s="225"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -4667,13 +4666,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4876,6 +4875,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4883,11 +4887,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5489,11 +5488,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="226" t="s">
+      <c r="B41" s="224" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="227"/>
-      <c r="D41" s="228"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5617,10 +5616,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="223" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="224"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5649,40 +5648,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="230" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="231"/>
-      <c r="D48" s="231"/>
-      <c r="E48" s="231"/>
-      <c r="F48" s="231"/>
-      <c r="G48" s="231"/>
-      <c r="H48" s="231"/>
-      <c r="I48" s="231"/>
-      <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="225" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="225" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="225" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5690,13 +5689,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="225"/>
-      <c r="C50" s="225"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5715,7 +5714,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="225"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5725,7 +5724,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6518,10 +6517,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="225" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="225" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6529,8 +6528,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="225"/>
-      <c r="C69" s="225"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -6724,13 +6723,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6933,6 +6932,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6940,11 +6944,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7546,11 +7545,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="226" t="s">
+      <c r="B41" s="224" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="227"/>
-      <c r="D41" s="228"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7674,10 +7673,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="223" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="224"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7706,40 +7705,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="230" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="231"/>
-      <c r="D48" s="231"/>
-      <c r="E48" s="231"/>
-      <c r="F48" s="231"/>
-      <c r="G48" s="231"/>
-      <c r="H48" s="231"/>
-      <c r="I48" s="231"/>
-      <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="225" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="225" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="225" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7747,13 +7746,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="225"/>
-      <c r="C50" s="225"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7772,7 +7771,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="225"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7782,7 +7781,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8575,10 +8574,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="225" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="225" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8586,8 +8585,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="225"/>
-      <c r="C69" s="225"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -8781,13 +8780,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8990,6 +8989,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8997,11 +9001,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9603,11 +9602,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="226" t="s">
-        <v>179</v>
-      </c>
-      <c r="C41" s="227"/>
-      <c r="D41" s="228"/>
+      <c r="B41" s="224" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9731,10 +9730,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="223" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="224"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9763,40 +9762,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="230" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="231"/>
-      <c r="D48" s="231"/>
-      <c r="E48" s="231"/>
-      <c r="F48" s="231"/>
-      <c r="G48" s="231"/>
-      <c r="H48" s="231"/>
-      <c r="I48" s="231"/>
-      <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="225" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="225" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="225" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9804,13 +9803,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="225"/>
-      <c r="C50" s="225"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9829,7 +9828,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="225"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9839,7 +9838,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10632,10 +10631,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="225" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="225" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10643,8 +10642,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="225"/>
-      <c r="C69" s="225"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -10838,13 +10837,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11047,6 +11046,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11054,11 +11058,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11101,7 +11100,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -11660,11 +11659,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="226" t="s">
-        <v>181</v>
-      </c>
-      <c r="C41" s="227"/>
-      <c r="D41" s="228"/>
+      <c r="B41" s="224" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11787,10 +11786,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="223" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="224"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11819,40 +11818,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="230" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="231"/>
-      <c r="D48" s="231"/>
-      <c r="E48" s="231"/>
-      <c r="F48" s="231"/>
-      <c r="G48" s="231"/>
-      <c r="H48" s="231"/>
-      <c r="I48" s="231"/>
-      <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="225" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="225" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="225" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11860,13 +11859,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="225"/>
-      <c r="C50" s="225"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11885,7 +11884,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="225"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11895,7 +11894,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12674,10 +12673,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="225" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="225" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12685,8 +12684,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="225"/>
-      <c r="C69" s="225"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -12880,13 +12879,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13089,6 +13088,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13096,11 +13100,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -13126,15 +13125,19 @@
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" customWidth="1"/>
+    <col min="13" max="13" width="8.42578125" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" customWidth="1"/>
+    <col min="15" max="15" width="9.85546875" customWidth="1"/>
+    <col min="16" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10" bestFit="1" customWidth="1"/>
@@ -13175,10 +13178,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="207" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="209"/>
+      <c r="C3" s="207"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -13352,10 +13355,10 @@
         <v>101830423</v>
       </c>
       <c r="P5" s="7">
-        <v>0</v>
+        <v>491237177.12546343</v>
       </c>
       <c r="Q5" s="7">
-        <v>0</v>
+        <v>76328678.073981449</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
@@ -13432,10 +13435,10 @@
         <v>225106806</v>
       </c>
       <c r="P6" s="7">
-        <v>0</v>
+        <v>657457159.85174966</v>
       </c>
       <c r="Q6" s="7">
-        <v>0</v>
+        <v>181265056.8810223</v>
       </c>
       <c r="R6" s="7">
         <v>0</v>
@@ -13507,7 +13510,9 @@
         <v>241473268</v>
       </c>
       <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
+      <c r="P7" s="7">
+        <v>248955573.78787571</v>
+      </c>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
@@ -13564,10 +13569,10 @@
         <v>80441848</v>
       </c>
       <c r="P8" s="7">
-        <v>0</v>
+        <v>728387277.57390273</v>
       </c>
       <c r="Q8" s="7">
-        <v>0</v>
+        <v>51482866.524593353</v>
       </c>
       <c r="R8" s="7">
         <v>0</v>
@@ -13644,10 +13649,10 @@
         <v>80519404</v>
       </c>
       <c r="P9" s="7">
-        <v>0</v>
+        <v>482312178.47736537</v>
       </c>
       <c r="Q9" s="7">
-        <v>0</v>
+        <v>70286112.09958896</v>
       </c>
       <c r="R9" s="7">
         <v>0</v>
@@ -13724,10 +13729,10 @@
         <v>82149325</v>
       </c>
       <c r="P10" s="7">
-        <v>0</v>
+        <v>505192003.00308657</v>
       </c>
       <c r="Q10" s="7">
-        <v>0</v>
+        <v>122952320.80976211</v>
       </c>
       <c r="R10" s="7">
         <v>0</v>
@@ -13804,10 +13809,10 @@
         <v>125488598</v>
       </c>
       <c r="P11" s="7">
-        <v>0</v>
+        <v>1061245403.0487187</v>
       </c>
       <c r="Q11" s="7">
-        <v>0</v>
+        <v>101136997.7886584</v>
       </c>
       <c r="R11" s="7">
         <v>0</v>
@@ -13884,10 +13889,10 @@
         <v>97341426</v>
       </c>
       <c r="P12" s="7">
-        <v>0</v>
+        <v>563114170.73408878</v>
       </c>
       <c r="Q12" s="7">
-        <v>0</v>
+        <v>104665034.75557049</v>
       </c>
       <c r="R12" s="7">
         <v>0</v>
@@ -13959,7 +13964,9 @@
         <v>404133664</v>
       </c>
       <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
+      <c r="P13" s="7">
+        <v>429849184.30128497</v>
+      </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
@@ -14016,10 +14023,10 @@
         <v>172024412</v>
       </c>
       <c r="P14" s="7">
-        <v>0</v>
+        <v>514721111.42684805</v>
       </c>
       <c r="Q14" s="7">
-        <v>0</v>
+        <v>117663432.08216608</v>
       </c>
       <c r="R14" s="7">
         <v>0</v>
@@ -14096,10 +14103,10 @@
         <v>92301622</v>
       </c>
       <c r="P15" s="7">
-        <v>0</v>
+        <v>698845176.23960102</v>
       </c>
       <c r="Q15" s="7">
-        <v>0</v>
+        <v>70945960.626210824</v>
       </c>
       <c r="R15" s="7">
         <v>0</v>
@@ -14176,10 +14183,10 @@
         <v>97324176</v>
       </c>
       <c r="P16" s="7">
-        <v>0</v>
+        <v>481870364.2173661</v>
       </c>
       <c r="Q16" s="7">
-        <v>0</v>
+        <v>48351228.656065792</v>
       </c>
       <c r="R16" s="7">
         <v>0</v>
@@ -14256,10 +14263,10 @@
         <v>363366966</v>
       </c>
       <c r="P17" s="7">
-        <v>0</v>
+        <v>706054928.99280047</v>
       </c>
       <c r="Q17" s="7">
-        <v>0</v>
+        <v>326117403.61363631</v>
       </c>
       <c r="R17" s="7">
         <v>0</v>
@@ -14336,10 +14343,10 @@
         <v>291530053</v>
       </c>
       <c r="P18" s="7">
-        <v>0</v>
+        <v>378602097.56753719</v>
       </c>
       <c r="Q18" s="7">
-        <v>0</v>
+        <v>211510559.17948398</v>
       </c>
       <c r="R18" s="7">
         <v>0</v>
@@ -14460,7 +14467,7 @@
         <v>285530553</v>
       </c>
       <c r="J22" s="7">
-        <v>0</v>
+        <v>293136935.89361715</v>
       </c>
       <c r="K22" s="7">
         <v>0</v>
@@ -14504,7 +14511,7 @@
         <v>428831462</v>
       </c>
       <c r="J23" s="7">
-        <v>0</v>
+        <v>436437844.89361715</v>
       </c>
       <c r="K23" s="7">
         <v>0</v>
@@ -14548,7 +14555,7 @@
         <v>1116489049</v>
       </c>
       <c r="J24" s="7">
-        <v>0</v>
+        <v>1121489049</v>
       </c>
       <c r="K24" s="7">
         <v>0</v>
@@ -14655,13 +14662,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="211" t="s">
+      <c r="B29" s="209" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="211"/>
-      <c r="D29" s="211"/>
-      <c r="E29" s="211"/>
-      <c r="F29" s="211"/>
+      <c r="C29" s="209"/>
+      <c r="D29" s="209"/>
+      <c r="E29" s="209"/>
+      <c r="F29" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15193,10 +15200,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="213" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="214"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15236,23 +15243,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="215" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="215" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="216" t="s">
+      <c r="D47" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="217"/>
-      <c r="F47" s="218"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="216"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="215" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15260,13 +15267,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="212" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="215"/>
-      <c r="C48" s="215"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15285,7 +15292,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="215"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15295,7 +15302,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="212"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16728,10 +16735,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="213" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="214"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16771,23 +16778,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="215" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="215" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="216" t="s">
+      <c r="D47" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="217"/>
-      <c r="F47" s="218"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="216"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="215" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16795,13 +16802,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="212" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="215"/>
-      <c r="C48" s="215"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16820,7 +16827,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="215"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16830,7 +16837,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="212"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -18415,10 +18422,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="223" t="s">
+      <c r="B44" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="224"/>
+      <c r="C44" s="222"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18483,23 +18490,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="225" t="s">
+      <c r="B47" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="225" t="s">
+      <c r="C47" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="220" t="s">
+      <c r="D47" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="221"/>
-      <c r="F47" s="222"/>
+      <c r="E47" s="219"/>
+      <c r="F47" s="220"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="225" t="s">
+      <c r="J47" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18507,13 +18514,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="219" t="s">
+      <c r="N47" s="217" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="225"/>
-      <c r="C48" s="225"/>
+      <c r="B48" s="223"/>
+      <c r="C48" s="223"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18532,7 +18539,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="225"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18542,7 +18549,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="219"/>
+      <c r="N48" s="217"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -20164,11 +20171,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="226" t="s">
-        <v>182</v>
-      </c>
-      <c r="C41" s="227"/>
-      <c r="D41" s="228"/>
+      <c r="B41" s="224" t="s">
+        <v>181</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20286,10 +20293,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="223" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="224"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20312,40 +20319,40 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="230" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="231"/>
-      <c r="D48" s="231"/>
-      <c r="E48" s="231"/>
-      <c r="F48" s="231"/>
-      <c r="G48" s="231"/>
-      <c r="H48" s="231"/>
-      <c r="I48" s="231"/>
-      <c r="J48" s="232"/>
-      <c r="K48" s="237"/>
-      <c r="L48" s="238"/>
-      <c r="M48" s="238"/>
-      <c r="N48" s="239"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="235"/>
+      <c r="L48" s="236"/>
+      <c r="M48" s="236"/>
+      <c r="N48" s="237"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="236" t="s">
+      <c r="B49" s="234" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="236" t="s">
+      <c r="C49" s="234" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="233" t="s">
+      <c r="D49" s="231" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="234"/>
-      <c r="F49" s="235"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="233"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="236" t="s">
+      <c r="J49" s="234" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20353,13 +20360,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="229" t="s">
+      <c r="N49" s="227" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="236"/>
-      <c r="C50" s="236"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="234"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20378,7 +20385,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="236"/>
+      <c r="J50" s="234"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20388,7 +20395,7 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="229"/>
+      <c r="N50" s="227"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="183" t="s">
@@ -21179,10 +21186,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="225" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="225" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21193,8 +21200,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="225"/>
-      <c r="C69" s="225"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -21380,13 +21387,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="230" t="s">
+      <c r="B87" s="228" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="231"/>
-      <c r="D87" s="231"/>
-      <c r="E87" s="231"/>
-      <c r="F87" s="232"/>
+      <c r="C87" s="229"/>
+      <c r="D87" s="229"/>
+      <c r="E87" s="229"/>
+      <c r="F87" s="230"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21668,14 +21675,14 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
         <f ca="1">DAY(EOMONTH(TODAY(),0))</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -21783,16 +21790,16 @@
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="205">
+      <c r="C10" s="15">
         <v>297882183.23181498</v>
       </c>
-      <c r="D10" s="205">
+      <c r="D10" s="15">
         <v>34050666.405826002</v>
       </c>
-      <c r="E10" s="205">
+      <c r="E10" s="15">
         <v>162788612.639999</v>
       </c>
-      <c r="F10" s="205">
+      <c r="F10" s="15">
         <v>494721462.27763999</v>
       </c>
       <c r="H10" s="116"/>
@@ -21811,16 +21818,16 @@
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="205">
+      <c r="C11" s="15">
         <v>374466810.62618703</v>
       </c>
-      <c r="D11" s="205">
+      <c r="D11" s="15">
         <v>92402940.934527993</v>
       </c>
-      <c r="E11" s="205">
+      <c r="E11" s="15">
         <v>40868468.799999997</v>
       </c>
-      <c r="F11" s="205">
+      <c r="F11" s="15">
         <v>507738220.36071497</v>
       </c>
       <c r="H11" s="116"/>
@@ -21839,16 +21846,16 @@
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="205">
+      <c r="C12" s="15">
         <v>278227678.91783297</v>
       </c>
-      <c r="D12" s="205">
+      <c r="D12" s="15">
         <v>62708999.627249002</v>
       </c>
-      <c r="E12" s="205">
+      <c r="E12" s="15">
         <v>52162025.759999998</v>
       </c>
-      <c r="F12" s="205">
+      <c r="F12" s="15">
         <v>393098704.30508202</v>
       </c>
       <c r="H12" s="116"/>
@@ -21867,16 +21874,16 @@
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="205">
+      <c r="C13" s="15">
         <v>236645733.92783001</v>
       </c>
-      <c r="D13" s="205">
+      <c r="D13" s="15">
         <v>33197107.539818</v>
       </c>
-      <c r="E13" s="205">
+      <c r="E13" s="15">
         <v>41510945.439999998</v>
       </c>
-      <c r="F13" s="205">
+      <c r="F13" s="15">
         <v>311353786.90764803</v>
       </c>
       <c r="H13" s="116"/>
@@ -21895,16 +21902,16 @@
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="205">
+      <c r="C14" s="15">
         <v>670664362.43227303</v>
       </c>
-      <c r="D14" s="205">
+      <c r="D14" s="15">
         <v>27278643.871089</v>
       </c>
-      <c r="E14" s="205">
+      <c r="E14" s="15">
         <v>260324322.93000001</v>
       </c>
-      <c r="F14" s="205">
+      <c r="F14" s="15">
         <v>958267329.23336196</v>
       </c>
       <c r="H14" s="116"/>
@@ -21943,16 +21950,16 @@
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="205">
+      <c r="C16" s="15">
         <v>413013469.09840298</v>
       </c>
-      <c r="D16" s="205">
+      <c r="D16" s="15">
         <v>61457252.569306999</v>
       </c>
-      <c r="E16" s="205">
+      <c r="E16" s="15">
         <v>14439639.5</v>
       </c>
-      <c r="F16" s="205">
+      <c r="F16" s="15">
         <v>488910361.16771001</v>
       </c>
       <c r="H16" s="116"/>
@@ -21971,16 +21978,16 @@
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="205">
+      <c r="C17" s="15">
         <v>314350697.279998</v>
       </c>
-      <c r="D17" s="205">
+      <c r="D17" s="15">
         <v>42787524.299999997</v>
       </c>
-      <c r="E17" s="205" t="s">
+      <c r="E17" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="F17" s="205">
+      <c r="F17" s="15">
         <v>357138221.57999802</v>
       </c>
       <c r="H17" s="116"/>
@@ -21999,16 +22006,16 @@
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="205">
+      <c r="C18" s="15">
         <v>976940398.98976696</v>
       </c>
-      <c r="D18" s="205">
+      <c r="D18" s="15">
         <v>11562280.951971</v>
       </c>
-      <c r="E18" s="205">
+      <c r="E18" s="15">
         <v>11405405.380000001</v>
       </c>
-      <c r="F18" s="205">
+      <c r="F18" s="15">
         <v>999908085.321738</v>
       </c>
       <c r="H18" s="116"/>
@@ -22027,16 +22034,16 @@
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="205">
+      <c r="C19" s="15">
         <v>1005613301.6380841</v>
       </c>
-      <c r="D19" s="205">
+      <c r="D19" s="15">
         <v>73190755.369811997</v>
       </c>
-      <c r="E19" s="205">
+      <c r="E19" s="15">
         <v>709237967.049927</v>
       </c>
-      <c r="F19" s="205">
+      <c r="F19" s="15">
         <v>1788042024.0578229</v>
       </c>
       <c r="H19" s="116"/>
@@ -22055,16 +22062,16 @@
       <c r="B20" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="205">
+      <c r="C20" s="15">
         <v>234281528.32828599</v>
       </c>
-      <c r="D20" s="205">
+      <c r="D20" s="15">
         <v>28741885.549775999</v>
       </c>
-      <c r="E20" s="205">
+      <c r="E20" s="15">
         <v>3816216.3</v>
       </c>
-      <c r="F20" s="205">
+      <c r="F20" s="15">
         <v>266839630.17806199</v>
       </c>
       <c r="H20" s="116"/>
@@ -22082,16 +22089,16 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="205">
+      <c r="C21" s="15">
         <v>64055094</v>
       </c>
-      <c r="D21" s="205">
+      <c r="D21" s="15">
         <v>100105707.120704</v>
       </c>
-      <c r="E21" s="205">
+      <c r="E21" s="15">
         <v>79070271.780000001</v>
       </c>
-      <c r="F21" s="205">
+      <c r="F21" s="15">
         <v>243231072.900704</v>
       </c>
       <c r="H21" s="116"/>
@@ -22109,16 +22116,16 @@
       <c r="B22" s="74" t="s">
         <v>172</v>
       </c>
-      <c r="C22" s="205">
+      <c r="C22" s="15">
         <v>197567845.80000001</v>
       </c>
-      <c r="D22" s="205" t="s">
+      <c r="D22" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="E22" s="205">
+      <c r="E22" s="15">
         <v>12832432.08</v>
       </c>
-      <c r="F22" s="205">
+      <c r="F22" s="15">
         <v>210400277.88</v>
       </c>
       <c r="H22" s="116"/>
@@ -22129,16 +22136,16 @@
       <c r="B23" s="74" t="s">
         <v>173</v>
       </c>
-      <c r="C23" s="205">
+      <c r="C23" s="15">
         <v>300521523.82997501</v>
       </c>
-      <c r="D23" s="205" t="s">
+      <c r="D23" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="205">
+      <c r="E23" s="15">
         <v>13813693.32</v>
       </c>
-      <c r="F23" s="205">
+      <c r="F23" s="15">
         <v>314335217.149975</v>
       </c>
       <c r="H23" s="116"/>
@@ -22149,16 +22156,16 @@
       <c r="B24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="205">
+      <c r="C24" s="15">
         <v>288424016.78064901</v>
       </c>
-      <c r="D24" s="205">
+      <c r="D24" s="15">
         <v>44585739.113441996</v>
       </c>
-      <c r="E24" s="205">
+      <c r="E24" s="15">
         <v>126214286.45999999</v>
       </c>
-      <c r="F24" s="205">
+      <c r="F24" s="15">
         <v>459224042.35409099</v>
       </c>
       <c r="H24" s="116"/>
@@ -22169,16 +22176,16 @@
       <c r="B25" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="205">
+      <c r="C25" s="15">
         <v>389875776.90495598</v>
       </c>
-      <c r="D25" s="205">
+      <c r="D25" s="15">
         <v>68378257.859753996</v>
       </c>
-      <c r="E25" s="205">
+      <c r="E25" s="15">
         <v>247976756.949745</v>
       </c>
-      <c r="F25" s="205">
+      <c r="F25" s="15">
         <v>706230791.71445501</v>
       </c>
       <c r="H25" s="116"/>
@@ -22189,16 +22196,16 @@
       <c r="B26" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="205">
+      <c r="C26" s="15">
         <v>454249976.114806</v>
       </c>
-      <c r="D26" s="205">
+      <c r="D26" s="15">
         <v>58885063.089941002</v>
       </c>
-      <c r="E26" s="205">
+      <c r="E26" s="15">
         <v>469103962.04973102</v>
       </c>
-      <c r="F26" s="205">
+      <c r="F26" s="15">
         <v>982239001.25447798</v>
       </c>
       <c r="H26" s="116"/>
@@ -22209,16 +22216,16 @@
       <c r="B27" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="205">
+      <c r="C27" s="15">
         <v>686645252.87729704</v>
       </c>
-      <c r="D27" s="205">
+      <c r="D27" s="15">
         <v>191906951.15242499</v>
       </c>
-      <c r="E27" s="205">
+      <c r="E27" s="15">
         <v>19182702.936000001</v>
       </c>
-      <c r="F27" s="205">
+      <c r="F27" s="15">
         <v>897734906.96572196</v>
       </c>
       <c r="H27" s="116"/>
@@ -22265,7 +22272,7 @@
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="205">
+      <c r="C32" s="15">
         <v>291427595.82048202</v>
       </c>
       <c r="G32" s="116"/>
@@ -22276,7 +22283,7 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="205">
+      <c r="C33" s="15">
         <v>436148035.92440403</v>
       </c>
       <c r="G33" s="116"/>
@@ -22287,7 +22294,7 @@
       <c r="B34" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="205">
+      <c r="C34" s="15">
         <v>135628039.89320499</v>
       </c>
       <c r="G34" s="116"/>
@@ -22298,7 +22305,7 @@
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="205">
+      <c r="C35" s="15">
         <v>513829145.026452</v>
       </c>
       <c r="G35" s="116"/>
@@ -22309,7 +22316,7 @@
       <c r="B36" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="C36" s="205">
+      <c r="C36" s="15">
         <v>296173392</v>
       </c>
       <c r="G36" s="116"/>
@@ -22341,11 +22348,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="240" t="s">
-        <v>183</v>
-      </c>
-      <c r="C41" s="241"/>
-      <c r="D41" s="242"/>
+      <c r="B41" s="245" t="s">
+        <v>182</v>
+      </c>
+      <c r="C41" s="246"/>
+      <c r="D41" s="247"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22405,7 +22412,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>632794080.21160698</v>
+        <v>23436817.785615072</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22434,7 +22441,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>555587329.71669078</v>
+        <v>20577308.508025583</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22463,15 +22470,15 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>109772514.73971272</v>
+        <v>4065648.6940634339</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="223" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="224"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
@@ -22490,7 +22497,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>1298153924.6680105</v>
+        <v>48079774.987704091</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22500,40 +22507,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="230" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="231"/>
-      <c r="D48" s="231"/>
-      <c r="E48" s="231"/>
-      <c r="F48" s="231"/>
-      <c r="G48" s="231"/>
-      <c r="H48" s="231"/>
-      <c r="I48" s="231"/>
-      <c r="J48" s="232"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="247"/>
-      <c r="M48" s="247"/>
-      <c r="N48" s="248"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="225" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="225" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="220" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="221"/>
-      <c r="F49" s="222"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="225" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22541,13 +22548,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="249" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="225"/>
-      <c r="C50" s="225"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22566,7 +22573,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="225"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22576,7 +22583,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="249"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22627,7 +22634,7 @@
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>151944123.3265633</v>
+        <v>5627560.1232060483</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22679,7 +22686,7 @@
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>135949634.98727</v>
+        <v>5035171.6661951849</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22731,7 +22738,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>43905422.199999988</v>
+        <v>1626126.7481481477</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22783,7 +22790,7 @@
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>-40348707.486027122</v>
+        <v>-1494396.5735565601</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22835,7 +22842,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>130794377.61152613</v>
+        <v>4844236.2078343015</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22887,7 +22894,7 @@
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>80687504.454943657</v>
+        <v>2988426.0909238392</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22939,7 +22946,7 @@
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-25117135.668739557</v>
+        <v>-930264.284027391</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22991,7 +22998,7 @@
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>110814428.23529005</v>
+        <v>4104238.0827885205</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23043,7 +23050,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>103612140.17002499</v>
+        <v>3837486.6729638884</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23095,7 +23102,7 @@
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>75611947.657280385</v>
+        <v>2800442.5058251997</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23147,7 +23154,7 @@
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>177236157.40587825</v>
+        <v>6564302.126143639</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23199,7 +23206,7 @@
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>118374328.16217285</v>
+        <v>4384234.3763767723</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23251,7 +23258,7 @@
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>34605682.96299541</v>
+        <v>1281691.9615924226</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23303,7 +23310,7 @@
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>90311505.909120381</v>
+        <v>3344870.5892266808</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23353,7 +23360,7 @@
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>1188381409.9282987</v>
+        <v>44014126.293640696</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23369,10 +23376,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="225" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="225" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23380,8 +23387,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="225"/>
-      <c r="C69" s="225"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>171</v>
       </c>
@@ -23575,13 +23582,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="243" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="244"/>
-      <c r="D87" s="244"/>
-      <c r="E87" s="244"/>
-      <c r="F87" s="245"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23635,7 +23642,7 @@
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>-13362977.916272461</v>
+        <v>-494925.10801009118</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23664,7 +23671,7 @@
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-18529482.737882435</v>
+        <v>-686277.13844009023</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23693,7 +23700,7 @@
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>141664975.39386773</v>
+        <v>5246850.9405136192</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23778,12 +23785,17 @@
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>109772514.73971283</v>
+        <v>4065648.6940634381</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23791,11 +23803,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23864,7 +23871,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23979,16 +23986,16 @@
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="205">
+      <c r="C10" s="15">
         <v>322280851.83509499</v>
       </c>
-      <c r="D10" s="205">
+      <c r="D10" s="15">
         <v>34873341.943994999</v>
       </c>
-      <c r="E10" s="205">
+      <c r="E10" s="15">
         <v>158162238.56999999</v>
       </c>
-      <c r="F10" s="205">
+      <c r="F10" s="15">
         <v>515316432.34908998</v>
       </c>
       <c r="H10" s="116"/>
@@ -24007,16 +24014,16 @@
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="205">
+      <c r="C11" s="15">
         <v>350800236.759597</v>
       </c>
-      <c r="D11" s="205">
+      <c r="D11" s="15">
         <v>84864795.200103998</v>
       </c>
-      <c r="E11" s="205">
+      <c r="E11" s="15">
         <v>22719654.219999999</v>
       </c>
-      <c r="F11" s="205">
+      <c r="F11" s="15">
         <v>458384686.17970097</v>
       </c>
       <c r="H11" s="116"/>
@@ -24035,16 +24042,16 @@
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="205">
+      <c r="C12" s="15">
         <v>307172074.63220602</v>
       </c>
-      <c r="D12" s="205">
+      <c r="D12" s="15">
         <v>78765432.566425994</v>
       </c>
-      <c r="E12" s="205">
+      <c r="E12" s="15">
         <v>52572805.159999996</v>
       </c>
-      <c r="F12" s="205">
+      <c r="F12" s="15">
         <v>438510312.35863203</v>
       </c>
       <c r="H12" s="116"/>
@@ -24063,16 +24070,16 @@
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="205">
+      <c r="C13" s="15">
         <v>241600874.21874499</v>
       </c>
-      <c r="D13" s="205">
+      <c r="D13" s="15">
         <v>51972057.989813</v>
       </c>
-      <c r="E13" s="205">
+      <c r="E13" s="15">
         <v>36793625.659999996</v>
       </c>
-      <c r="F13" s="205">
+      <c r="F13" s="15">
         <v>330366557.86855799</v>
       </c>
       <c r="H13" s="116"/>
@@ -24091,16 +24098,16 @@
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="205">
+      <c r="C14" s="15">
         <v>989456477.77127802</v>
       </c>
-      <c r="D14" s="205">
+      <c r="D14" s="15">
         <v>37132037.007500999</v>
       </c>
-      <c r="E14" s="205">
+      <c r="E14" s="15">
         <v>266587982.37</v>
       </c>
-      <c r="F14" s="205">
+      <c r="F14" s="15">
         <v>1293176497.1487789</v>
       </c>
       <c r="H14" s="116"/>
@@ -24139,16 +24146,16 @@
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="205">
+      <c r="C16" s="15">
         <v>517028510.48846501</v>
       </c>
-      <c r="D16" s="205">
+      <c r="D16" s="15">
         <v>88679408.048779994</v>
       </c>
-      <c r="E16" s="205">
+      <c r="E16" s="15">
         <v>34044891.530000001</v>
       </c>
-      <c r="F16" s="205">
+      <c r="F16" s="15">
         <v>639752810.06724501</v>
       </c>
       <c r="H16" s="116"/>
@@ -24167,16 +24174,16 @@
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="205">
+      <c r="C17" s="15">
         <v>368163765.47890598</v>
       </c>
-      <c r="D17" s="205">
+      <c r="D17" s="15">
         <v>50693884.710000001</v>
       </c>
-      <c r="E17" s="205" t="s">
+      <c r="E17" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="F17" s="205">
+      <c r="F17" s="15">
         <v>418857650.18890601</v>
       </c>
       <c r="H17" s="116"/>
@@ -24195,16 +24202,16 @@
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="205">
+      <c r="C18" s="15">
         <v>511987771.98278302</v>
       </c>
-      <c r="D18" s="205">
+      <c r="D18" s="15">
         <v>7135511.989968</v>
       </c>
-      <c r="E18" s="205">
+      <c r="E18" s="15">
         <v>11708702.58</v>
       </c>
-      <c r="F18" s="205">
+      <c r="F18" s="15">
         <v>530831986.552751</v>
       </c>
       <c r="H18" s="116"/>
@@ -24223,16 +24230,16 @@
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="205">
+      <c r="C19" s="15">
         <v>1002756079.983186</v>
       </c>
-      <c r="D19" s="205">
+      <c r="D19" s="15">
         <v>72945098.289833993</v>
       </c>
-      <c r="E19" s="205">
+      <c r="E19" s="15">
         <v>1329858796.62995</v>
       </c>
-      <c r="F19" s="205">
+      <c r="F19" s="15">
         <v>2405559974.9029698</v>
       </c>
       <c r="H19" s="116"/>
@@ -24251,16 +24258,16 @@
       <c r="B20" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="205">
+      <c r="C20" s="15">
         <v>127200704.00230999</v>
       </c>
-      <c r="D20" s="205">
+      <c r="D20" s="15">
         <v>22547772.839754</v>
       </c>
-      <c r="E20" s="205">
+      <c r="E20" s="15">
         <v>10497297.48</v>
       </c>
-      <c r="F20" s="205">
+      <c r="F20" s="15">
         <v>160245774.32206401</v>
       </c>
       <c r="H20" s="116"/>
@@ -24278,16 +24285,16 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="205">
+      <c r="C21" s="15">
         <v>59166950.5</v>
       </c>
-      <c r="D21" s="205">
+      <c r="D21" s="15">
         <v>13000